--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,111 +425,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>product_link</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>brand_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price_old</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>price_new</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>price_change</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>price_change_percent</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>sold_count_old</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>sold_count_new</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sold_count_increase</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>revenue_increase</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rating_old</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rating_new</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rating_change</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>review_count_old</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>review_count_new</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>review_count_increase</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>date_compared</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -525,73 +537,73 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>279287522</v>
+        <v>274937386</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bộ áo điều hòa KITO NEWPRO KT10 thế hệ mới nhất 2026 quạt 24V siêu bên ,chống chai ,chống phồng</t>
+          <t>Bộ bơi nữ big size cao cấp, mẫu 2 mảnh áo cộc tay có khóa kéo trước, quần boxer trẻ trung, chất thun bơi lạnh Lycra co giãn đa chiều, dày dặn mịn mát, chống thấm nước nhanh khô | KT110</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-ao-dieu-hoa-kito-newpro-kt10-the-he-moi-nhat-2026-quat-24v-sieu-ben-chong-chai-chong-phong-p279287522-p279287522.html</t>
+          <t>https://tiki.vn/bo-boi-nu-big-size-cao-cap-mau-2-manh-ao-coc-tay-co-khoa-keo-truoc-quan-boxer-tre-trung-chat-thun-boi-lanh-lycra-co-gian-da-chieu-day-dan-min-mat-chong-tham-nuoc-nhanh-kho-kt110-p274937386-p274937386.html</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kito</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>963000</v>
+        <v>480000</v>
       </c>
       <c r="G2" t="n">
-        <v>1070000</v>
+        <v>480000</v>
       </c>
       <c r="H2" t="n">
-        <v>107000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1440000</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -602,21 +614,21 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>278498646</v>
+        <v>104791604</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quần short Nam tập Gym thể thao, mặc nhà, đi chơi - T0588</t>
+          <t>Quần lót nữ thái lan 828 – Chất thun lạnh - giao màu ngẫu nhiên</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-short-nam-tap-gym-the-thao-mac-nha-di-choi-t0588-p278498646-p278498646.html</t>
+          <t>https://tiki.vn/quan-lot-nu-thai-lan-828-chat-thun-lanh-giao-mau-ngau-nhien-p104791604-p104791604.html</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -625,53 +637,130 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>110000</v>
+        <v>44000</v>
       </c>
       <c r="G3" t="n">
-        <v>110000</v>
+        <v>36080</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-7920</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="J3" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L3" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-11000000</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>244298960</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quần Mặc Váy Su Thông Hơi Trơn 6530 | Mát Mẻ, Không Lộ, Chống Hớ Hiệu Quả</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-vay-dai-thong-hoi-6530-p244298960-p244298960.html</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34860</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-7140</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-17</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>UPDATED</t>
         </is>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V58"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>55023823</t>
+          <t>35193606</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Set Đồ Bơi 3 Mảnh Rực Rỡ Nắng Hè AT167 MayHomes Bộ Đồ Áo Bơi Nữ, Quần Bơi Nữ Và Váy Bơi Nữ</t>
+          <t>[FREEMAN] Combo 5 quần lót nam 6034</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-do-boi-3-manh-ruc-ro-nang-he-at167-mayhomes-bo-do-ao-boi-nu-quan-boi-nu-va-vay-boi-nu-p55023823.html?spid=55023835</t>
+          <t>https://tiki.vn/freeman-combo-5-quan-lot-nam-6034-p35193606.html?spid=35193613</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MAYHOMES</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>122000</v>
+        <v>195000</v>
       </c>
       <c r="H2" t="n">
-        <v>122000</v>
+        <v>195000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>529</v>
+        <v>179</v>
       </c>
       <c r="L2" t="n">
-        <v>529</v>
+        <v>179</v>
       </c>
       <c r="M2" t="n">
-        <v>64538000</v>
+        <v>34905000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="S2" t="n">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>278529292</t>
+          <t>127379613</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dép quai ngang Bitis xốp nam</t>
+          <t>Giày Sneaker Da Unisex DINCOX D20 White Năng Động Cá Tính</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-ngang-bitis-xop-nam-p278529292.html?spid=278529322</t>
+          <t>https://tiki.vn/giay-sneaker-da-unisex-dincox-d20-nang-dong-ca-tinh-white-p127379613.html?spid=127379716</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -647,101 +647,101 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>DINCOX</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>126000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>126000</v>
+        <v>610000</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>610000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>377</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
-        <v>372</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
-        <v>46872000</v>
+        <v>10370000</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Bán thêm +372 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>167889817</t>
+          <t>100222219</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Giày thể thao trung cấp Bitis nam</t>
+          <t>Quần short thun nam thể thao tập gym - A058</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-trung-cap-bitis-nam-p167889817.html?spid=167889833</t>
+          <t>https://tiki.vn/quan-short-thun-nam-the-thao-tap-gym-a058-p100222219.html?spid=100222248</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>365000</v>
+        <v>160000</v>
       </c>
       <c r="H4" t="n">
-        <v>365000</v>
+        <v>160000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,35 +750,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="L4" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="M4" t="n">
-        <v>21170000</v>
+        <v>3360000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,101 +795,101 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>37975688</t>
+          <t>251773296</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Áo Sơ Mi Nữ Form Dài Che Quần Cá Tính SM013 MayHomes</t>
+          <t>Áo thun Polo Nam Coolmax - Premium nam tính, thanh lịch sang trọng MRM Manlywear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nu-form-dai-che-quan-ca-tinh-sm013-mayhomes-p37975688.html?spid=37975690</t>
+          <t>https://tiki.vn/ao-thun-polo-nam-coolmax-premium-nam-tinh-thanh-lich-sang-trong-mrm-manlywear-p251773296.html?spid=251773298</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MAYHOMES</t>
+          <t>MRM Manlywear</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>249000</v>
       </c>
       <c r="G5" t="n">
-        <v>88000</v>
+        <v>249000</v>
       </c>
       <c r="H5" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="K5" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="L5" t="n">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>10296000</v>
+        <v>2988000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R5" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="S5" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +12 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>126091279</t>
+          <t>277042336</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giày Mọi, Giày Lười Nam Da Bò SUNPOLO SU5059 Hiện đại (Đen)</t>
+          <t>New Arrivals | Giày Da Sneaker Nam DC39 BLACK COFFEE DINCOX Shoes Đế Bằng - Microfiber Leather</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-moi-giay-luoi-nam-da-bo-sunpolo-su5059-hien-dai-den-p126091279.html?spid=126091289</t>
+          <t>https://tiki.vn/new-arrivals-giay-da-sneaker-nam-dc39-black-coffee-dincox-shoes-de-bang-microfiber-leather-p277042336.html?spid=277042342</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SUNPOLO</t>
+          <t>DINCOX</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>660000</v>
       </c>
       <c r="G6" t="n">
-        <v>1100000</v>
+        <v>660000</v>
       </c>
       <c r="H6" t="n">
-        <v>1100000</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -918,166 +918,166 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>8800000</v>
+        <v>2640000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +4 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10063653</t>
+          <t>277544802</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dép Nam Bít Mũi BIGGBEN Da Bò ThậtDN145</t>
+          <t>Áo Chống Nắng Nam ,Chất Vải Thun Lạnh, Chống Tia UV, Thoáng Mát, Thấm Hút Mồ Hôi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-bit-mui-biggben-da-bo-that-cao-cap-dn145-p10063653.html?spid=10063663</t>
+          <t>https://tiki.vn/ao-chong-nang-nam-chat-vai-thun-lanh-chong-tia-uv-thoang-mat-tham-hut-mo-hoi-p277544802.html?spid=277544808</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>399000</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>399000</v>
+        <v>185000</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>4389000</v>
+        <v>1480000</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Bán thêm +11 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>273584264</t>
+          <t>177637940</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quần tây nam không ly Khatoco Q1M478R0-INGI309-2503-0-XÁM TRẮNG</t>
+          <t>Sét 5 Kẹp Tóc Hàn Quốc Cực Xinh Nhiều Mẫu - Hàng Chính Hãng</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-tay-nam-khong-ly-khatoco-q1m478r0-ingi309-2503-0-xam-trang-p273584264.html?spid=273584278</t>
+          <t>https://tiki.vn/set-5-kep-toc-han-quoc-cuc-xinh-nhieu-mau-hang-chinh-hang-p177637940.html?spid=177637944</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">KHATOCO </t>
+          <t>PaKaSa</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>478000</v>
+        <v>39780</v>
       </c>
       <c r="H8" t="n">
-        <v>478000</v>
+        <v>39780</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1086,13 +1086,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="M8" t="n">
-        <v>3824000</v>
+        <v>1193400</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1107,14 +1107,14 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1131,121 +1131,121 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>99968881</t>
+          <t>44014260</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Set 2 quần đùi nam, quần Short Gió nam thể thao Basic trẻ trung năng động, thoáng mát co giãn 4 chiều MRM Manlywear</t>
+          <t>Quần lót lọt khe - Màu mận</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-2-qua-n-du-i-nam-qua-n-short-gio-nam-the-thao-basic-tre-trung-nang-do-ng-thoa-ng-ma-t-co-gia-n-4-chie-u-mrm-manlywear-p99968881.html?spid=99968992</t>
+          <t>https://tiki.vn/quan-lot-lot-khe-mau-man-p44014260.html?spid=44014261</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>Mirato</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>399000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>399000</v>
+        <v>35000</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2505</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2510</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="M9" t="n">
-        <v>1995000</v>
+        <v>1190000</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>633</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>633</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Bán thêm +5 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>273172388</t>
+          <t>110138146</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Giấy Vàng lau giầy thần thánh Sneaker - Hàng Nhập Khẩu</t>
+          <t>Quần lót nữ Cotton Never thoáng mát tôn dáng</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-vang-lau-giay-than-thanh-sneaker-hang-nhap-khau-p273172388.html?spid=273172389</t>
+          <t>https://tiki.vn/quan-lot-nu-cotton-never-thoang-mat-ton-dang-p110138146.html?spid=110138154</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASSTAR</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>35000</v>
+        <v>9000</v>
       </c>
       <c r="H10" t="n">
-        <v>35000</v>
+        <v>9000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1254,22 +1254,22 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="L10" t="n">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="M10" t="n">
-        <v>1890000</v>
+        <v>1125000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1299,121 +1299,121 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>207277686</t>
+          <t>197415480</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Giày thể thao nam phong cách mới – GNA1004C</t>
+          <t>Quần lót lọt khe Sexy kẻ sọc nơ nhỏ bikini T-BACK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-nam-phong-cach-moi-gna1004-p207277686.html?spid=207277690</t>
+          <t>https://tiki.vn/quan-lot-lot-khe-sexy-ke-soc-no-nho-bikini-t-back-p197415480.html?spid=197415482</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bee Gee</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1026000</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>513000</v>
+        <v>35000</v>
       </c>
       <c r="H11" t="n">
-        <v>-513000</v>
+        <v>35000</v>
       </c>
       <c r="I11" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="M11" t="n">
-        <v>1539000</v>
+        <v>805000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Giá giảm 513,000đ (50.0%) | Bán thêm +3 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>276024613</t>
+          <t>276233010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dép Đế Trấu Nam 2 Khóa Charcoal DC01 Dincox</t>
+          <t>Combo 5 đôi Tất nam gân cao cổ khử mùi kháng khuẩn chống hôi chân</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-de-trau-nam-2-khoa-charcoal-dc01-dincox-p276024613.html?spid=276024619</t>
+          <t>https://tiki.vn/combo-5-doi-tat-nam-gan-cao-co-khu-mui-khang-khuan-chong-hoi-chan-p276233010.html?spid=276233011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DINCOX</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>250000</v>
+        <v>59000</v>
       </c>
       <c r="H12" t="n">
-        <v>250000</v>
+        <v>59000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1422,35 +1422,35 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M12" t="n">
-        <v>1000000</v>
+        <v>767000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1467,37 +1467,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>44969160</t>
+          <t>270305243</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01 cặp lót giày thể thao 4D có gờ chống sốc giảm mỏi gang bàn chân - buybox - BBPK36</t>
+          <t>[Sexy] Quần lót nữ lọt khe xuyên thấu thêu hình gợi cảm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/01-cap-lot-giay-the-thao-4d-co-go-chong-soc-giam-moi-gang-ban-chan-buybox-bbpk36-p44969160.html?spid=90220726</t>
+          <t>https://tiki.vn/sexy-quan-lot-nu-lot-khe-xuyen-thau-theu-hinh-goi-cam-p270305243.html?spid=270305251</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>buybox</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>39000</v>
+        <v>35000</v>
       </c>
       <c r="H13" t="n">
-        <v>39000</v>
+        <v>35000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1506,35 +1506,35 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M13" t="n">
-        <v>390000</v>
+        <v>560000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1551,121 +1551,121 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31637590</t>
+          <t>190463811</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Combo 4 quần lót nam tam giác Bamboo Organic mềm mịn thoáng mát thấm hút mồ hôi - MRM Manlywear - Màu Ngẫu Nhiên</t>
+          <t>Sét Đai kẹp tất + Tất Ren kèm kẹp tất quyến rũ gợi cảm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-4-qua-n-lo-t-nam-tam-gia-c-bamboo-organic-me-m-mi-n-thoa-ng-ma-t-tha-m-hu-t-mo-hoi-mrm-manlywear-ma-u-nga-u-nhien-p31637590.html?spid=31637602</t>
+          <t>https://tiki.vn/set-dai-kep-tat-tat-ren-kem-kep-tat-quyen-ru-goi-cam-p190463811.html?spid=190463819</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>249000</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>249000</v>
+        <v>79000</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3768</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>3769</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>474000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>249000</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>910</v>
-      </c>
-      <c r="R14" t="n">
-        <v>910</v>
-      </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>279100044</t>
+          <t>249779733</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chai Xịt Khử Mùi Giày Dép 260ML</t>
+          <t>Quần lót lọt khe nữ dây sexy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-xit-khu-mui-giay-dep-260ml-p279100044.html?spid=279100045</t>
+          <t>https://tiki.vn/quan-lot-lot-khe-nu-day-sexy-p249779733.html?spid=249779741</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>55000</v>
+        <v>39000</v>
       </c>
       <c r="H15" t="n">
-        <v>55000</v>
+        <v>39000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1674,13 +1674,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>55000</v>
+        <v>468000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1719,52 +1719,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>111092835</t>
+          <t>158732070</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bàn chải đánh giày Yuppies nhập khẩu Malaysia; thân gỗ nhẹ, lông mềm; không mọt gỗ, không rụng lông</t>
+          <t>❈✣♚Combo 10 quần lót nữ su đúc cao cấp không đường may, chất mát lạnh, mềm mịn, thoáng</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ban-chai-danh-giay-yuppies-nhap-khau-malaysia-than-go-nhe-long-mem-khong-mot-go-khong-rung-long-p111092835.html?spid=111092841</t>
+          <t>https://tiki.vn/combo-10-quan-lot-nu-su-duc-cao-cap-khong-duong-may-chat-mat-lanh-mem-min-thoang-p158732070.html?spid=242323997</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>YUPPIES</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>39700</v>
+        <v>120000</v>
       </c>
       <c r="G16" t="n">
-        <v>39700</v>
+        <v>140000</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="J16" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>39700</v>
+        <v>420000</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1776,17 +1776,17 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1796,108 +1796,108 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Giá tăng 20,000đ (+16.7%) | Bán thêm +3 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>279071174</t>
+          <t>214919710</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quần tây nam KHATOCO Regular Fit không ly Q1M478R0-INDE311-2707-0</t>
+          <t>Kẹp Tóc Càng Cua Hoa Trà Hàn Quốc Cao Cấp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-tay-nam-khatoco-regular-fit-khong-ly-q1m478r0-inde311-2707-0-p279071174.html?spid=279071194</t>
+          <t>https://tiki.vn/kep-toc-cang-cua-hoa-tra-han-quoc-cao-cap-p214919710.html?spid=264021790</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">KHATOCO </t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>382400</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>478000</v>
+        <v>34900</v>
       </c>
       <c r="H17" t="n">
-        <v>95600</v>
+        <v>34900</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>383900</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá tăng 95,600đ (+25.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>74421501</t>
+          <t>263693472</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
+          <t>Bộ Body Lưới Sexy Gợi Cảm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421539</t>
+          <t>https://tiki.vn/bo-body-luoi-sexy-goi-cam-p263693472.html?spid=263693474</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1911,82 +1911,82 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>118690</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>143000</v>
+        <v>55000</v>
       </c>
       <c r="H18" t="n">
-        <v>24310</v>
+        <v>55000</v>
       </c>
       <c r="I18" t="n">
-        <v>20.48</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>153</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá tăng 24,310đ (+20.5%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>74820156</t>
+          <t>198918912</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG REN 3 MÓC BIG SIZE 395</t>
+          <t>Khăn lau kính Nano chống bám hơi nước, chống mờ sương, sạch bụi bẩn và dấu vân tay, Công nghệ Nhật Bản - Hộp 100 Miếng</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-ren-3-moc-big-size-395-p74820156.html?spid=74820176</t>
+          <t>https://tiki.vn/khan-lau-kinh-nano-chong-bam-hoi-nuoc-chong-mo-suong-sach-bui-ban-va-dau-van-tay-cong-nghe-nhat-ban-hop-100-mieng-p198918912.html?spid=198918913</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1995,50 +1995,50 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>103750</v>
+        <v>70000</v>
       </c>
       <c r="G19" t="n">
-        <v>125000</v>
+        <v>70000</v>
       </c>
       <c r="H19" t="n">
-        <v>21250</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>20.48</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>30</v>
+        <v>462</v>
       </c>
       <c r="K19" t="n">
-        <v>30</v>
+        <v>465</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2048,108 +2048,108 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá tăng 21,250đ (+20.5%)</t>
+          <t>Bán thêm +3 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>59462352</t>
+          <t>161960027</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Áo ngực mỏng thêu hoa cài trước có gọng</t>
+          <t>Quần tất lưới siêu mỏng thoáng khí gợi cảm dành cho nam</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-mong-theu-hoa-cai-truoc-co-gong-p59462352.html?spid=59462384</t>
+          <t>https://tiki.vn/quan-tat-luoi-sieu-mong-thoang-khi-goi-cam-danh-cho-nam-p161960027.html?spid=161960035</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>73800</v>
+        <v>39000</v>
       </c>
       <c r="H20" t="n">
-        <v>-16200</v>
+        <v>39000</v>
       </c>
       <c r="I20" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>204</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>156000</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Giá giảm 16,200đ (18.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>269904929</t>
+          <t>107801368</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quần hai lớp nam tập gym DO GYM SHOP chất thun lỗ kim thoáng khí khi chơi thể thao</t>
+          <t>Combo 2 quần đùi nam May 10 phiên bản có túi 2 bên, màu ngẫu nhiên</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-hai-lop-nam-tap-gym-do-gym-shop-chat-thun-lo-kim-thoang-khi-khi-choi-the-thao-p269904929.html?spid=269904933</t>
+          <t>https://tiki.vn/combo-2-quan-dui-nam-may-10-phien-ban-co-tui-2-ben-mau-ngau-nhien-p107801368.html?spid=107801372</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2159,14 +2159,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>May 10</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>159000</v>
+        <v>145000</v>
       </c>
       <c r="G21" t="n">
-        <v>159000</v>
+        <v>145000</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2175,38 +2175,38 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>1181</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>1182</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>145000</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2216,29 +2216,29 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Rating 0.0→5.0 (+5.00) | Review thêm +1</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13307720</t>
+          <t>108220832</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Combo 10 Quần lót nam, sịp chéo nam xuất Nhật thời trang cao cấp</t>
+          <t>Bra dán ngực bàn tay P29 (kèm dây trong)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nam-sip-cheo-nam-xuat-nhat-thoi-trang-cao-cap-p13307720.html?spid=53788750</t>
+          <t>https://tiki.vn/bra-dan-nguc-ban-tay-p29-kem-day-trong-p108220832.html?spid=242370964</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2247,112 +2247,112 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>385000</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>327250</v>
+        <v>57750</v>
       </c>
       <c r="H22" t="n">
-        <v>-57750</v>
+        <v>57750</v>
       </c>
       <c r="I22" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>115500</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Giá giảm 57,750đ (15.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>275399939</t>
+          <t>66476313</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Set 2 Miếng Mút Đệm Độn Ngực Áo Bra Tập Gym,Yoga,Áo Bơi Tròn Màu Da Nâng Ngực Quyến Rũ</t>
+          <t>Vớ tất dài qua đầu gối ôm sát phối màu quyến rũ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-2-mieng-mut-dem-don-nguc-ao-bra-tap-gym-yoga-ao-boi-tron-mau-da-nang-nguc-quyen-ru-p275399939.html?spid=275399940</t>
+          <t>https://tiki.vn/vo-tat-dai-qua-dau-goi-om-sat-phoi-mau-quyen-ru-p66476313.html?spid=66476314</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>25000</v>
       </c>
       <c r="H23" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="I23" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2374,54 +2374,54 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Giá tăng 10,000đ (+66.7%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>279337471</t>
+          <t>277284408</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Áo sơ mi nam Khatoco</t>
+          <t>Đồ lót ren thêu sang trọng nhẹ nhàng hấp dẫn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nam-khatoco-p279337471.html?spid=279337479</t>
+          <t>https://tiki.vn/do-lot-ren-theu-sang-trong-nhe-nhang-hap-dan-p277284408.html?spid=277284410</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">KHATOCO </t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>350000</v>
+        <v>55000</v>
       </c>
       <c r="H24" t="n">
-        <v>350000</v>
+        <v>55000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2430,13 +2430,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2475,121 +2475,121 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7078807</t>
+          <t>90655833</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
+          <t>Quần lót lọt khe sang trọng nữ tính thêu hoa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858801</t>
+          <t>https://tiki.vn/quan-lot-lot-khe-sang-trong-nu-tinh-theu-hoa-p90655833.html?spid=90655839</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>308000</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>319550</v>
+        <v>25000</v>
       </c>
       <c r="H25" t="n">
-        <v>11550</v>
+        <v>25000</v>
       </c>
       <c r="I25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Giá tăng 11,550đ (+3.8%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>278049759</t>
+          <t>183036428</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Áo sơ mi nam ngắn tay Novelty Casual Hoa văn SMI25001 - 250080N</t>
+          <t>Đồ lót sexy dây nơ quần lót lọt khe nữ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nam-ngan-tay-novelty-casual-hoa-van-smi25001-p278049759.html?spid=278049925</t>
+          <t>https://tiki.vn/do-lot-sexy-day-no-quan-lot-lot-khe-nu-p183036428.html?spid=183036432</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Novelty</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>395000</v>
+        <v>49000</v>
       </c>
       <c r="H26" t="n">
-        <v>395000</v>
+        <v>49000</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,35 +2598,35 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2643,46 +2643,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>35304312</t>
+          <t>244297794</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lót giày thể thao gel silicon cho bóng đá, chạy bộ, cầu lông, tennis, bóng bàn Spenco Gel Comfort</t>
+          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/lot-giay-the-thao-nam-phong-tranh-chan-thuong-spenco-gel-comfort-p35304312.html?spid=275825851</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spenco</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>495000</v>
+        <v>146300</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="H27" t="n">
-        <v>-495000</v>
+        <v>43700</v>
       </c>
       <c r="I27" t="n">
-        <v>-100</v>
+        <v>29.87</v>
       </c>
       <c r="J27" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2691,53 +2691,53 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 43,700đ (+29.9%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>279014298</t>
+          <t>82518572</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Áo sweater thu đông form rộng in hình hài hước "Tự Do Tài Chính" Mr.buffalo - [HN37] Áo Đen</t>
+          <t xml:space="preserve"> combo 4 Quần sịp quần lót nam sịp doremon hoạt hình thun lạnh siêu nhẹ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-sweater-thu-dong-form-rong-in-hinh-hai-huoc-tu-do-tai-chinh-mr-buffalo-p279014298.html?spid=279014313</t>
+          <t>https://tiki.vn/combo-4-quan-sip-quan-lot-nam-sip-doremon-hoat-hinh-thun-lanh-sieu-nhe-p82518572.html?spid=145209317</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2751,22 +2751,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>160000</v>
+        <v>146640</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>188000</v>
       </c>
       <c r="H28" t="n">
-        <v>-160000</v>
+        <v>41360</v>
       </c>
       <c r="I28" t="n">
-        <v>-100</v>
+        <v>28.21</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2775,53 +2775,53 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 41,360đ (+28.2%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>150738986</t>
+          <t>103049077</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Áo Thun Polo Nam Sọc Ngang Thân Màu Xám Xanh Cao Cấp 2021</t>
+          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-polo-nam-soc-ngang-than-mau-xam-xanh-cao-cap-2021-p150738986.html?spid=150739044</t>
+          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2831,26 +2831,26 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OVERCO</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>290000</v>
+        <v>144300</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="H29" t="n">
-        <v>-290000</v>
+        <v>40700</v>
       </c>
       <c r="I29" t="n">
-        <v>-100</v>
+        <v>28.21</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2859,53 +2859,53 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 40,700đ (+28.2%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>37126497</t>
+          <t>174585329</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>( 10 cái ) quần lót nữ Su đúc không đường may, hàng đẹp loại xịn W19_503</t>
+          <t>Áo lót nâng ngực boya mút mỏng, Áo ngực boya nâng ngực cài sau 522BT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-10-quan-lot-su-duc-khong-duong-may-hang-dep-loai-xin-w19_503-p37126497.html?spid=51720423</t>
+          <t>https://tiki.vn/ao-lot-nang-nguc-boya-mut-mong-ao-nguc-boya-nang-nguc-cai-sau-522bt-p174585329.html?spid=203717985</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2919,22 +2919,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>238000</v>
+        <v>84000</v>
       </c>
       <c r="G30" t="n">
-        <v>280000</v>
+        <v>105000</v>
       </c>
       <c r="H30" t="n">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="I30" t="n">
-        <v>17.65</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2943,26 +2943,26 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -2972,24 +2972,24 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Giá tăng 42,000đ (+17.6%)</t>
+          <t>Giá tăng 21,000đ (+25.0%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>73163978</t>
+          <t>214706031</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hộp miếng dán ngực Silicon màu xanh 5 đôi</t>
+          <t>Áo lót áo ngực Thái lan có gọng mút kép nâng ngực tạo khe, áo lót nữ thông hơi hàng CAO CẤP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-mieng-dan-nguc-silicon-mau-xanh-5-doi-p73163978.html?spid=117659470</t>
+          <t>https://tiki.vn/ao-lot-ao-nguc-thai-lan-co-gong-mut-kep-nang-nguc-tao-khe-ao-lot-nu-thong-hoi-hang-cao-cap-p214706031.html?spid=215408042</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2999,26 +2999,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LQ luxury</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>46200</v>
+        <v>96000</v>
       </c>
       <c r="G31" t="n">
-        <v>55000</v>
+        <v>120000</v>
       </c>
       <c r="H31" t="n">
-        <v>8800</v>
+        <v>24000</v>
       </c>
       <c r="I31" t="n">
-        <v>19.05</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3027,26 +3027,26 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3056,53 +3056,53 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Giá tăng 8,800đ (+19.0%)</t>
+          <t>Giá tăng 24,000đ (+25.0%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>193886649</t>
+          <t>150738986</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Áo sơ mi nữ form rộng kiểu tay lỡ cổ tròn NeSa Shop, chất liệu Đũi tơ thấm hút mồ hôi, áo sơ mi nữ nhiều màu, SMH.034</t>
+          <t>Áo Thun Polo Nam Sọc Ngang Thân Màu Xám Xanh Cao Cấp 2021</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nu-form-rong-kieu-tay-lo-co-tron-nesa-shop-chat-lieu-dui-to-tham-hut-mo-hoi-ao-so-mi-nu-nhieu-mau-smh-34-p193886649.html?spid=193886792</t>
+          <t>https://tiki.vn/ao-thun-polo-nam-soc-ngang-than-mau-xam-xanh-cao-cap-2021-p150738986.html?spid=150739044</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>OVERCO</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>114000</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>166000</v>
+        <v>290000</v>
       </c>
       <c r="H32" t="n">
-        <v>52000</v>
+        <v>290000</v>
       </c>
       <c r="I32" t="n">
-        <v>45.61</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3111,53 +3111,53 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Giá tăng 52,000đ (+45.6%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>73862702</t>
+          <t>73163978</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
+          <t>Hộp miếng dán ngực Silicon màu xanh 5 đôi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862742</t>
+          <t>https://tiki.vn/hop-mieng-dan-nguc-silicon-mau-xanh-5-doi-p73163978.html?spid=117659470</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3167,26 +3167,26 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>LQ luxury</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>132000</v>
+        <v>55000</v>
       </c>
       <c r="G33" t="n">
-        <v>136950</v>
+        <v>45650</v>
       </c>
       <c r="H33" t="n">
-        <v>4950</v>
+        <v>-9350</v>
       </c>
       <c r="I33" t="n">
-        <v>3.75</v>
+        <v>-17</v>
       </c>
       <c r="J33" t="n">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3204,17 +3204,17 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3224,24 +3224,24 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Giá tăng 4,950đ (+3.8%)</t>
+          <t>Giá giảm 9,350đ (17.0%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>59205406</t>
+          <t>272629857</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>COMBO 5 ÁO LÁ NGẮN THUN LỤA MẶT TRƯỚC 2 LỚP DÀNH CHO HỌC SINH</t>
+          <t>Quần lót ren chấm bi kim loại chữ V hot girl</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-ao-la-ngan-thun-lua-mat-truoc-2-lop-danh-cho-hoc-sinh-p59205406.html?spid=59205408</t>
+          <t>https://tiki.vn/quan-lot-ren-cham-bi-kim-loai-chu-v-hot-girl-p272629857.html?spid=272629861</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>106600</v>
+        <v>45000</v>
       </c>
       <c r="H34" t="n">
-        <v>-23400</v>
+        <v>45000</v>
       </c>
       <c r="I34" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3279,58 +3279,58 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Giá giảm 23,400đ (18.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>37269401</t>
+          <t>74820156</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nam Thông Hơi Xuất Nhật Mã S02</t>
+          <t>ÁO LÓT NỮ MỎNG REN 3 MÓC BIG SIZE 395</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nam-thong-hoi-xuat-nhat-ma-s02-p37269401.html?spid=198496796</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-ren-3-moc-big-size-395-p74820156.html?spid=74820176</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3339,22 +3339,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="G35" t="n">
-        <v>119000</v>
+        <v>95000</v>
       </c>
       <c r="H35" t="n">
-        <v>119000</v>
+        <v>-30000</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3363,82 +3363,82 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 30,000đ (24.0%)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>275604884</t>
+          <t>74421501</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dép quai ngang Bitis nam (38-43)</t>
+          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-ngang-bitis-nam-38-43-p275604884.html?spid=275604898</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421539</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>143000</v>
       </c>
       <c r="G36" t="n">
-        <v>440000</v>
+        <v>108680</v>
       </c>
       <c r="H36" t="n">
-        <v>440000</v>
+        <v>-34320</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3447,82 +3447,82 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 34,320đ (24.0%)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>134777591</t>
+          <t>277550023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Giày lười da tăng chiều cao nam Bụi Leather G112 - Da bò Nappa cao cấp - Bảo hành 12 tháng</t>
+          <t>Quần vải nam / Quần tây nam dài cotton poly ủi ly trước - RT 10S25PFO004 | ROUTINE CÀ MAU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-luoi-da-tang-chieu-cao-nam-bui-leather-g112-da-bo-nappa-cao-cap-bao-hanh-12-thang-p134777591.html?spid=134777601</t>
+          <t>https://tiki.vn/quan-vai-nam-quan-tay-nam-dai-cotton-poly-ui-ly-truoc-rt-10s25pfo004-routine-ca-mau-p277550023.html?spid=277550045</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bụi Leather</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>840000</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>812000</v>
+        <v>479000</v>
       </c>
       <c r="H37" t="n">
-        <v>-28000</v>
+        <v>479000</v>
       </c>
       <c r="I37" t="n">
-        <v>-3.33</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3531,73 +3531,73 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Giá giảm 28,000đ (3.3%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>278940208</t>
+          <t>279014298</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dép quai ngang Biti's nam (39-44)</t>
+          <t>Áo sweater thu đông form rộng in hình hài hước "Tự Do Tài Chính" Mr.buffalo - [HN37] Áo Đen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-ngang-biti-s-nam-39-44-p278940208.html?spid=278940242</t>
+          <t>https://tiki.vn/ao-sweater-thu-dong-form-rong-in-hinh-hai-huoc-tu-do-tai-chinh-mr-buffalo-p279014298.html?spid=279014313</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>469000</v>
+        <v>160000</v>
       </c>
       <c r="H38" t="n">
-        <v>469000</v>
+        <v>160000</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -3651,46 +3651,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>48312449</t>
+          <t>133160820</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Giày Mọi Nam Da Bò BIGGBEN GM221</t>
+          <t>Quần Lót Su Đúc Nữ (Hàng Loại 1) Không Đường Mai, Thun Lạnh, SIêu Co Dãn, Được Chọn Màu</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-moi-nam-da-bo-biggben-gm221-p48312449.html?spid=48312461</t>
+          <t>https://tiki.vn/quan-lot-su-duc-nu-hang-loai-1-khong-duong-mai-thun-lanh-sieu-co-dan-duoc-chon-mau-p133160820.html?spid=198901960</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>21840</v>
       </c>
       <c r="G39" t="n">
-        <v>700000</v>
+        <v>28000</v>
       </c>
       <c r="H39" t="n">
-        <v>700000</v>
+        <v>6160</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>28.21</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3699,76 +3699,76 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 6,160đ (+28.2%)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>276814071</t>
+          <t>270803997</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New Arrivals | Giày Da Sneaker Nam Nữ DC39 LATTE LOVE DINCOX Shoes Đế Bằng - Microfiber Leather</t>
+          <t>Áo thun Unisex WE.INS Trơn, Áo phông WEINS, Áo thun oversized WEINS, Áo Thun Tay Lỡ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://tiki.vn/new-arrivals-giay-da-sneaker-nam-nu-dc39-latte-love-dincox-shoes-de-bang-microfiber-leather-p276814071.html?spid=276814128</t>
+          <t>https://tiki.vn/ao-thun-unisex-weins-tron-xanh-la-p270803997.html?spid=270804015</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>DINCOX</t>
+          <t>WEINS</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="G40" t="n">
-        <v>660000</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>660000</v>
+        <v>-250000</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3802,34 +3802,34 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>171464598</t>
+          <t>21308472</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Set 10 Khuy Cài Áo Mini Trang Trí</t>
+          <t>Set 3 Cột Tóc Dây Chun Buộc Tóc Đính Ngọc Trai Xinh Xắn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-10-khuy-cai-ao-mini-trang-tri-p171464598.html?spid=270491436</t>
+          <t>https://tiki.vn/set-3-cot-toc-day-chun-buoc-toc-dinh-ngoc-trai-xinh-xan-p21308472.html?spid=84892232</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3843,22 +3843,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>35000</v>
+        <v>21999</v>
       </c>
       <c r="G41" t="n">
-        <v>28000</v>
+        <v>19000</v>
       </c>
       <c r="H41" t="n">
-        <v>-7000</v>
+        <v>-2999</v>
       </c>
       <c r="I41" t="n">
-        <v>-20</v>
+        <v>-13.63</v>
       </c>
       <c r="J41" t="n">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="K41" t="n">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3867,26 +3867,26 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="R41" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -3896,50 +3896,50 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Giá giảm 7,000đ (20.0%)</t>
+          <t>Giá giảm 2,999đ (13.6%)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>22158405</t>
+          <t>275042862</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Áo sơ mi trắng dài tay vải kate</t>
+          <t>GIÀY CHẠY BỘ VÀ ĐI BỘ ĐỊA HÌNH SLM X-ADVENTURE OLIVE NIGHT - L47386000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-trang-dai-tay-vai-kate-p22158405.html?spid=22158419</t>
+          <t>https://tiki.vn/giay-chay-bo-va-di-bo-dia-hinh-slm-x-adventure-olive-night-l47386000-p275042862.html?spid=275042868</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Việt Tiến</t>
+          <t>Salomon</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>480000</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>3800000</v>
       </c>
       <c r="H42" t="n">
-        <v>-480000</v>
+        <v>3800000</v>
       </c>
       <c r="I42" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3951,16 +3951,16 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3970,57 +3970,57 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>278423388</t>
+          <t>279438121</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dép quai ngang Biti's nam (39-44)</t>
+          <t>Áo thun nam hình in Form Regular - ROUTINE 10S26TSS031</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-ngang-biti-s-nam-39-44-p278423388.html?spid=278423390</t>
+          <t>https://tiki.vn/ao-thun-nam-hinh-in-form-regular-routine-10s26tss031-p279438121.html?spid=279438129</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>465000</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>549000</v>
       </c>
       <c r="H43" t="n">
-        <v>-465000</v>
+        <v>549000</v>
       </c>
       <c r="I43" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4035,16 +4035,16 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -4054,63 +4054,63 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5469269</t>
+          <t>277844658</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sandal Nam BIGGBEN Da Bò Thật SD13</t>
+          <t>Đồ bơi nữ dạng váy duyên dáng kín đáo có quần short liền trong váy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://tiki.vn/sandal-nam-biggben-da-bo-that-sd13-p5469269.html?spid=5469289</t>
+          <t>https://tiki.vn/do-boi-nu-dang-vay-duyen-dang-kin-dao-co-quan-short-lien-trong-vay-p277844658.html?spid=277844660</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>379000</v>
+        <v>193000</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>193000</v>
       </c>
       <c r="H44" t="n">
-        <v>-379000</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -4119,142 +4119,142 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P44" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>278820713</t>
+          <t>171464598</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dép nhựa Biti's nam (39-44)</t>
+          <t>Set 10 Khuy Cài Áo Mini Trang Trí</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nhua-biti-s-nam-39-44-p278820713.html?spid=278820723</t>
+          <t>https://tiki.vn/set-10-khuy-cai-ao-mini-trang-tri-p171464598.html?spid=270491436</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>165000</v>
+        <v>28000</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="H45" t="n">
-        <v>-165000</v>
+        <v>7000</v>
       </c>
       <c r="I45" t="n">
-        <v>-100</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
+        <v>37</v>
+      </c>
+      <c r="K45" t="n">
+        <v>37</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
         <v>3</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 7,000đ (+25.0%)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>100222219</t>
+          <t>136019521</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Quần short thun nam thể thao tập gym - A058</t>
+          <t>Khăn Choàng Lụa Hàng Châu Cao Cấp Sang Trọng 180x90 cm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-short-thun-nam-the-thao-tap-gym-a058-p100222219.html?spid=100222248</t>
+          <t>https://tiki.vn/khan-choang-lua-hang-chau-cao-cap-sang-trong-180x90-cm-p136019521.html?spid=278751369</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4263,103 +4263,103 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>160000</v>
+        <v>110880</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="H46" t="n">
-        <v>-160000</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
+        <v>81</v>
+      </c>
+      <c r="K46" t="n">
+        <v>81</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>19</v>
+      </c>
+      <c r="R46" t="n">
         <v>21</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>6</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Review thêm +2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>276422447</t>
+          <t>276580096</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Váy Nữ Trung Niên Chất Liệu Lụa Tuyết Thiết Kế Thời Trang Sành Điệu Phù Hợp Cho Mẹ Đi Chơi Đi Tiệc - Tuấn Tú Store 68</t>
+          <t>Quần nam ống rộng phong cách Hàn Quốc, quần nam cạp cao có dây rút phía trước và lưng chun dễ mặc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://tiki.vn/vay-nu-trung-nien-chat-lieu-lua-tuyet-thiet-ke-thoi-trang-sanh-dieu-phu-hop-cho-me-di-choi-di-tiec-tuan-tu-store-68-p276422447.html?spid=276423219</t>
+          <t>https://tiki.vn/quan-nam-ong-rong-phong-cach-han-quoc-quan-nam-cap-cao-co-day-rut-phia-truoc-va-lung-chun-de-mac-p276580096.html?spid=276580118</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Haint Boutique</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>284000</v>
+        <v>350000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-284000</v>
+        <v>-350000</v>
       </c>
       <c r="I47" t="n">
         <v>-100</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -4407,37 +4407,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>188844705</t>
+          <t>279321285</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Đầm đũi suông, cổ cách điệu, ngắn tay, có dây thắt eo, 2 túi hông tiện lợi Haint Boutique Da164</t>
+          <t>[Chọn LẺ hoặc SET] Quần Lót Nam LT1 Liền Mạch D Danido – Modal Sợi Gỗ Sồi Cao Cấp, Hai Mặt Kháng Khuẩn, Thoáng Khí Cực MátQuần Lót Nam LT1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dam-dui-suong-co-cach-dieu-ngan-tay-co-day-that-eo-2-tui-hong-tien-loi-haint-boutique-da164-p188844705.html?spid=188844717</t>
+          <t>https://tiki.vn/chon-le-hoac-set-quan-lot-nam-lt1-lien-mach-d-danido-modal-soi-go-soi-cao-cap-hai-mat-khang-khuan-thoang-khi-cuc-matquan-lot-nam-lt1-p279321285.html?spid=279321323</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Haint Boutique</t>
+          <t>D Danido</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>350000</v>
+        <v>245000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-350000</v>
+        <v>-245000</v>
       </c>
       <c r="I48" t="n">
         <v>-100</v>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -4491,43 +4491,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>187336557</t>
+          <t>92806576</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Giày Sandal Nam Bít Mũi Da Bò Thật BIGGBEN SD124</t>
+          <t>Áo Khoác Big Size Nam Nữ Có Nón Áo Khoác Dù Nam Nữ Chống Nắng Chống Nước Chống Gió Chống Tia uv Cực Tím Cao Cấp UD54 - ShopN6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-sandal-nam-bit-mui-da-bo-that-biggben-sd124-p187336557.html?spid=187336561</t>
+          <t>https://tiki.vn/ao-khoac-big-size-nam-nu-co-non-ao-khoac-du-nam-nu-chong-nang-chong-nuoc-chong-gio-chong-tia-uv-cuc-tim-cao-cap-ud54-shopn6-p92806576.html?spid=92806599</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>369000</v>
+        <v>189000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-369000</v>
+        <v>-189000</v>
       </c>
       <c r="I49" t="n">
         <v>-100</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -4539,16 +4539,16 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>-5</v>
+        <v>-4.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -4575,43 +4575,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>134739207</t>
+          <t>276664793</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Giày da nam, giày oxford công sở G103 - Da bò Nappa cao cấp</t>
+          <t>Quần gió lót lông QD2 ấm áp thời trang cho nam, Quần nỉ jogger lót lông QD1 sang trọng và dày dặn D Danido</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-da-nam-giay-oxford-cong-so-bui-leather-g103-da-bo-nappa-cao-cap-bao-hanh-12-thang-p134739207.html?spid=134739215</t>
+          <t>https://tiki.vn/quan-gio-lot-long-qd2-am-ap-thoi-trang-cho-nam-quan-ni-jogger-lot-long-qd1-sang-trong-va-day-dan-d-danido-p276664793.html?spid=276664832</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bụi Leather</t>
+          <t>D Danido</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>840000</v>
+        <v>299000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-840000</v>
+        <v>-299000</v>
       </c>
       <c r="I50" t="n">
         <v>-100</v>
       </c>
       <c r="J50" t="n">
-        <v>462</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -4623,16 +4623,16 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>-4.7</v>
+        <v>-5</v>
       </c>
       <c r="Q50" t="n">
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -4659,43 +4659,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>126257972</t>
+          <t>276664685</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Đón gót giày cho mọi tư thế gỗ tự nhiên nguyên khối - Dài 70cm (DGH908) Cho giày Nam &amp; Nữ</t>
+          <t>Quần gió lót lông QD2 ấm áp thời trang cho nam, Quần nỉ jogger lót lông QD1 sang trọng và dày dặn D Danido</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://tiki.vn/don-got-giay-cho-moi-tu-the-go-tu-nhien-nguyen-khoi-dai-70cm-dgh908-cho-giay-nam-nu-p126257972.html?spid=163870749</t>
+          <t>https://tiki.vn/quan-gio-lot-long-qd2-am-ap-thoi-trang-cho-nam-quan-ni-jogger-lot-long-qd1-sang-trong-va-day-dan-d-danido-p276664685.html?spid=276664701</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HAHANCO</t>
+          <t>D Danido</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>90000</v>
+        <v>299000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-90000</v>
+        <v>-299000</v>
       </c>
       <c r="I51" t="n">
         <v>-100</v>
       </c>
       <c r="J51" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>-4.7</v>
+        <v>-5</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -4743,43 +4743,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>276843845</t>
+          <t>200002603</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dép Nam Da Bò HA NAM Đế Siêu Nhẹ Khâu Chỉ Toàn Bộ DNA22039 - Màu Đen</t>
+          <t>Áo Sơ Mi Nam Công Sở Trung Niên Thương Hiệu Anton Somianton Vải Cotton Màu Xanh Trơn Ngắn Tay Có Túi - YSN13</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-da-bo-ha-nam-de-sieu-nhe-khau-chi-toan-bo-dna22039-p276843845.html?spid=276843865</t>
+          <t>https://tiki.vn/ao-so-mi-nam-cong-so-trung-nien-thuong-hie-u-anton-somianton-vai-cotton-mau-xanh-tron-ngan-tay-co-tui-ysn13-p200002603.html?spid=200002609</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HA NAM</t>
+          <t>SOMIANTON</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>360000</v>
+        <v>298000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-360000</v>
+        <v>-298000</v>
       </c>
       <c r="I52" t="n">
         <v>-100</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -4827,43 +4827,43 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>15259840</t>
+          <t>278278634</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Giày Tây Nam BiGGBEN Da Bò Thật GT112</t>
+          <t>Set đồ bơi nữ gồm áo bơi và chân váy phối kèm, thiết kế thời trang, hiện đại, thun co giãn, mềm mịn, nhanh khô mang lại cảm giác thoải mái và tự tin khi đi biển, bơi lội hoặc du lịch.-( Dưới 50 KG )</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-tay-nam-biggben-da-bo-that-gt112-p15259840.html?spid=15259846</t>
+          <t>https://tiki.vn/set-do-boi-nu-gom-ao-boi-va-chan-vay-phoi-kem-thiet-ke-thoi-trang-hien-dai-thun-co-gian-mem-min-nhanh-kho-mang-lai-cam-giac-thoai-mai-va-tu-tin-khi-di-bien-boi-loi-hoac-du-lich-p278278634.html?spid=278278635</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>LYNUSAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>699000</v>
+        <v>129000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-699000</v>
+        <v>-129000</v>
       </c>
       <c r="I53" t="n">
         <v>-100</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4875,16 +4875,16 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -4911,43 +4911,43 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10063962</t>
+          <t>277761408</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dép Nam Bít Mũi BIGGBEN Da Bò ThậtDN146</t>
+          <t>Chân váy maxi dài đính nơ siêu xinh</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-bit-mui-biggben-da-bo-that-cao-cap-dn146-p10063962.html?spid=10063964</t>
+          <t>https://tiki.vn/chan-vay-maxi-dai-dinh-no-sieu-xinh-p277761408.html?spid=277761434</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>399000</v>
+        <v>159000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-399000</v>
+        <v>-159000</v>
       </c>
       <c r="I54" t="n">
         <v>-100</v>
       </c>
       <c r="J54" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -4959,16 +4959,16 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-4.7</v>
+        <v>-0</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -4995,52 +4995,52 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>275276309</t>
+          <t>276955379</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dép tổ ong ĐEN nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Quần Lót Nữ Ren Ôm Nửa Mông Xinh Xắn Nhiều Mẫu Sanny House</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-den-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276309.html?spid=275276315</t>
+          <t>https://tiki.vn/quan-lot-nu-ren-om-nua-mong-xinh-xan-nhieu-mau-sanny-house-p276955379.html?spid=276955534</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>Sanny House</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>63000</v>
+        <v>82500</v>
       </c>
       <c r="G55" t="n">
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-82500</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J55" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-63000</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -5062,123 +5062,123 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Bán thêm -1 sản phẩm</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>116955158</t>
+          <t>274664676</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>QUẦN LÓT REN PHỐI THUN LẠNH WANNABE QL240 NỮ TÍNH</t>
+          <t>Giày Mọi Nam Da Bò Thật BIGGBEN Cao Cấp GM302</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-ren-phoi-thun-lanh-wannabe-ql240-nu-tinh-p116955158.html?spid=116955166</t>
+          <t>https://tiki.vn/giay-moi-nam-da-bo-that-biggben-cao-cap-gm302-p274664676.html?spid=274664688</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wannabe</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>150000</v>
+        <v>749000</v>
       </c>
       <c r="G56" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-749000</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-150000</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Bán thêm -1 sản phẩm</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>54569520</t>
+          <t>197380089</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
+          <t>Đồ bộ nữ lanh lửng mặc nhà tay cánh tiên phối viền chất mềm,mịn,mát BL 153 hoạ tiết dễ thương size 45-65kg</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859809</t>
+          <t>https://tiki.vn/do-bo-lanh-lung-mac-nha-tay-canh-tien-phoi-vien-chat-mem-min-mat-hoa-tiet-de-thuong-size-45-65kg-p197380089.html?spid=197380192</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5187,144 +5187,1236 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>70400</v>
+        <v>110000</v>
       </c>
       <c r="G57" t="n">
-        <v>73040</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2640</v>
+        <v>-110000</v>
       </c>
       <c r="I57" t="n">
-        <v>3.75</v>
+        <v>-100</v>
       </c>
       <c r="J57" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-365200</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>5</v>
       </c>
       <c r="O57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Giá tăng 2,640đ (+3.8%) | Bán thêm -5 sản phẩm</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>67538621</t>
+          <t>195808319</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
+          <t>Váy sơ mi tay ngắn có 2 túi trước, dáng váy dài siêu tôn dáng HB61</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538631</t>
+          <t>https://tiki.vn/dam-so-mi-dai-dang-suong-chat-dui-tre-trung-thoi-trang-haint-boutique-hb61-p195808319.html?spid=195808321</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>May 10</t>
+          <t>Haint Boutique</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>135000</v>
+        <v>350000</v>
       </c>
       <c r="G58" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>-350000</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J58" t="n">
-        <v>16579</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>16576</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>160264804</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Áo sơ mi đũi Haint Boutique, Áo sơ mi nữ cổ V xinh phong cách vitage Sm99</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-so-mi-dui-haint-boutique-ao-so-mi-nu-co-v-xinh-phong-cach-vitage-sm99-p160264804.html?spid=160264810</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Haint Boutique</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-250000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>13</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>4</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>158136035</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Đầm thiết kế dáng suông TFL803 – Váy đầm trung niên bigsize TIFALU</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/dam-thiet-ke-dang-suong-tfl803-vay-dam-trung-nien-bigsize-tifalu-p158136035.html?spid=158136041</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Tifalu</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>780000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-780000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>102738495</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Đầm váy Nữ Haint Boutique Tay Dài Dáng Suông - Váy Nữ thời Trang Phong Cách Hàn Quốc Hb48</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/dam-vay-nu-haint-boutique-tay-dai-dang-suong-vay-nu-thoi-trang-phong-cach-han-quoc-hb48-p102738495.html?spid=102738523</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Haint Boutique</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>249000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-249000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J61" t="n">
+        <v>18</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>6</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>59307366</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>COMBO 5 QUẦN COTTON BOYSHORT (GIAO MÀU NGẪU NHIÊN)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-5-quan-cotton-boyshort-giao-mau-ngau-nhien-p59307366.html?spid=59717773</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>173000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-173000</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J62" t="n">
+        <v>6</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>43842370</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Áo len tăm nữ cổ tim Haint Boutique al72</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-len-tam-nu-co-tim-haint-boutique-al72-p43842370.html?spid=214767996</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Haint Boutique</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>164695322</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mũ Lưỡi Trai Nón Lưỡi Trai Nam Nữ Yes You Can Vải Nhung Tăm Mịn Nón Kết</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/mu-luoi-trai-non-luoi-trai-nam-nu-yes-you-can-vai-nhung-tam-min-non-ket-royal-caps-p164695322.html?spid=181371687</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>49000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-49000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>48312449</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Giày Mọi Nam Da Bò BIGGBEN GM221</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-moi-nam-da-bo-biggben-gm221-p48312449.html?spid=48312461</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>BIGGBEN</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>276313086</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5 đôi tất nam U.ni chống hôi chân cổ ngắn hàng chuẩn</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/5-doi-tat-nam-u-ni-chong-hoi-chan-co-ngan-hang-chuan-p276313086.html?spid=276313087</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DRU</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>95000</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-95000</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
         <v>-3</v>
       </c>
-      <c r="M58" t="n">
-        <v>-405000</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O58" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>4842</v>
-      </c>
-      <c r="R58" t="n">
-        <v>4842</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
+      <c r="Q66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>263021892</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kẹp tóc con bướm - kẹp tóc càng cua 5 răng - kẹp tóc trong suốt - kẹp gấp 5 răng mẫu mới</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/kep-toc-con-buom-kep-toc-cang-cua-5-rang-kep-toc-trong-suot-kep-gap-5-rang-mau-moi-p263021892.html?spid=263021896</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>29900</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-29900</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>114005422</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Thắt Lưng Nam Cao Cấp Vải Dù Bền Bỉ, Mặt Khóa Tự Động U859 US ARMY Phong Cách Lính Mỹ -HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-cao-cap-vai-du-ben-bi-mat-khoa-tu-dong-u859-us-army-phong-cach-linh-my-hang-chinh-hang-p114005422.html?spid=174219358</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>89000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-89000</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J68" t="n">
+        <v>79</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>32</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>140843587</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mũ Lưỡi Trai Lính Mỹ US ARMY U890, Nón Lưỡi Trai Rằn Ri Đi Phượt Phong Cách Lính - HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/mu-luoi-trai-linh-my-us-army-u890-non-luoi-trai-ran-ri-di-phuot-phong-cach-linh-hang-chinh-hang-p140843587.html?spid=174134712</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>89000</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-89000</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J69" t="n">
+        <v>208</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>61</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2004591</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Thắt Lưng Nam Cao Cấp AT Leather P119 - Đen</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-cao-cap-at-leather-p119-den-p2004591.html?spid=2004593</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ANH THO LEATHER</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>450000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-450000</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J70" t="n">
+        <v>96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>25</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>279344691</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Dây Nịt Nam - Thắt Lưng Nam Thời Trang Cao Cấp | Dây Nịch Thắc Lưng (DN-074)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/video-day-nit-nam-that-lung-nam-thoi-trang-cao-cap-day-nich-thac-lung-dn-074-p279344691.html?spid=279344712</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>39999</v>
+      </c>
+      <c r="G71" t="n">
+        <v>39999</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-39999</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
         <is>
           <t>🔄 Đã cập nhật</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Bán thêm -3 sản phẩm</t>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Bán thêm -1 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8407712</t>
+          <t>26666649</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Sandal Nam BIGGBEN Da Bò Thật SD68</t>
+          <t>Dép Nam BIGGBEN Da Bò Thật Cao Cấp DN196</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-sandal-nam-biggben-da-bo-that-sd68-p8407712.html?spid=8407714</t>
+          <t>https://tiki.vn/dep-nam-biggben-da-bo-that-cao-cap-dn196-p26666649.html?spid=26666651</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -570,10 +570,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>419000</v>
+        <v>379000</v>
       </c>
       <c r="H2" t="n">
-        <v>419000</v>
+        <v>379000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="L2" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M2" t="n">
-        <v>43995000</v>
+        <v>41690000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,37 +627,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>38160273</t>
+          <t>66803444</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giày Boot Nam BIGGBEN Da Bò Thật Cao Cấp BT2</t>
+          <t>Áo Cardigan Nữ Họa Tiết Xinh Thời Trang Korea ALN037 MayHomes Mẫu Mới Mùa Xuân</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-boot-nam-biggben-da-bo-that-cao-cap-bt2-p38160273.html?spid=38160275</t>
+          <t>https://tiki.vn/ao-cardigan-nu-hoa-tiet-xinh-thoi-trang-korea-aln037-mayhomes-mau-moi-mua-xuan-p66803444.html?spid=66803452</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>MAYHOMES</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2000000</v>
+        <v>149000</v>
       </c>
       <c r="H3" t="n">
-        <v>2000000</v>
+        <v>149000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="M3" t="n">
-        <v>20000000</v>
+        <v>25628000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,37 +711,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>183685137</t>
+          <t>273388482</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thắt Lưng Dây Nịt Nam Vải Dù US ARMY, Phong Cách Sang Trọng Cổ Điển Mặt Khóa Hợp Kim Thép Chống Ghỉ Cao Cấp -HÀNG CHÍNH HÃNG</t>
+          <t>Combo 7 quần lót cotton nữ nhiều màu du lịch dùng 1 lần</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-day-nit-nam-vai-du-us-army-phong-cach-sang-trong-co-dien-mat-khoa-hop-kim-thep-chong-ghi-cao-cap-hang-chinh-hang-p183685137.html?spid=183685139</t>
+          <t>https://tiki.vn/combo-7-quan-lot-cotton-nu-nhieu-mau-du-lich-dung-1-lan-p273388482.html?spid=273388612</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>79000</v>
+        <v>169000</v>
       </c>
       <c r="H4" t="n">
-        <v>79000</v>
+        <v>169000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,35 +750,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>16511000</v>
+        <v>5577000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,538 +795,538 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20535045</t>
+          <t>190792898</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thắt lưng nam da bò AT Leather - P142</t>
+          <t>Giày sandal nam da bò thật BIGGBEN cao cấp SD123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-nam-da-bo-at-leather-p142-p20535045.html?spid=20535047</t>
+          <t>https://tiki.vn/giay-sandal-nam-da-bo-that-biggben-cao-cap-sd123-p190792898.html?spid=190792908</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANH THO LEATHER</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>295000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>295000</v>
+        <v>399000</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>399000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>181</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>2360000</v>
+        <v>4788000</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Bán thêm +8 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>52189164</t>
+          <t>275431635</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Combo 3 quần lót nam sợi cotton Organic mềm mịn thoáng mát co giãn 4 chiều MRM Manlywear (TẶNG Đôi Tất Nam Cao Cấp màu ngẫu nhiên)</t>
+          <t>Dép quai kẹp Bitis nam (38-43)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-3-qua-n-lo-t-nam-so-i-cotton-organic-me-m-mi-n-thoa-ng-ma-t-co-gia-n-4-chie-u-mrm-manlywear-tang-doi-tat-nam-cao-cap-mau-ngau-nhien-p52189164.html?spid=52189172</t>
+          <t>https://tiki.vn/dep-quai-kep-bitis-nam-38-43-p275431635.html?spid=275431639</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>255000</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>255000</v>
+        <v>75000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3420</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3424</v>
+        <v>22</v>
       </c>
       <c r="L6" t="n">
+        <v>22</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="n">
-        <v>1020000</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>967</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>967</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Bán thêm +4 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>104791604</t>
+          <t>16651795</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quần lót nữ thái lan 828 – Chất thun lạnh - giao màu ngẫu nhiên</t>
+          <t>️[5 Quần] ComBo 5 Quần Lót Nam THUN LẠNH Lưng Bự Hàng Việt Nam Cao Cấp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nu-thai-lan-828-chat-thun-lanh-giao-mau-ngau-nhien-p104791604.html?spid=270215619</t>
+          <t>https://tiki.vn/5-quan-combo-5-quan-lot-nam-thun-lanh-lung-bu-hang-viet-nam-cao-cap-p16651795.html?spid=51148098</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MENLIVE</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>35640</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>44000</v>
+        <v>155800</v>
       </c>
       <c r="H7" t="n">
-        <v>8360</v>
+        <v>155800</v>
       </c>
       <c r="I7" t="n">
-        <v>23.46</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>748000</v>
+        <v>1402200</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Giá tăng 8,360đ (+23.5%) | Bán thêm +17 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>49733157</t>
+          <t>275431720</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quần bơi nam giới dáng vừa, độ dài trên gối, chất thun bơi lạnh dày đẹp, co giãn 4 chiều ôm đùi gọn gàng dễ chịu, thoáng mát nhanh khô | BN005</t>
+          <t>Dép quai kẹp Bitis nam (38-43)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-boi-nam-dang-lung-mau-moi-2020-vai-boi-day-dan-dep-co-gian-4-chieu-bn005-p49733157.html?spid=49733163</t>
+          <t>https://tiki.vn/dep-quai-kep-bitis-nam-38-43-p275431720.html?spid=275431728</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>115000</v>
+        <v>75000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>600000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="n">
-        <v>575000</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +5 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>276303219</t>
+          <t>34159013</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bộ Váy Thể Thao Nữ Gồm Áo Thun Và Váy 2 Lớp Sành Điệu</t>
+          <t>Combo 5 Đôi Tất Cổ Ngắn Cùng Màu Cotton Thương Hiệu MRM Manlywear</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-vay-the-thao-nu-gom-ao-thun-va-vay-2-lop-sanh-dieu-p276303219.html?spid=276306416</t>
+          <t>https://tiki.vn/combo-5-doi-tat-nam-vo-nam-co-ngan-cao-cap-mrm-fashion-cung-mau-p34159013.html?spid=34159015</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MRM Manlywear</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>129000</v>
       </c>
       <c r="G9" t="n">
-        <v>239000</v>
+        <v>129000</v>
       </c>
       <c r="H9" t="n">
-        <v>239000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>5467</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>5470</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>239000</v>
+        <v>387000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1101</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1101</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +3 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>107802069</t>
+          <t>212048690</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
+          <t>NHIỀU MẪU Ghim cài áo đính đá xích cao cấp - ghim cài vest cưới Tien Nguyen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
+          <t>https://tiki.vn/nhieu-mau-ghim-cai-ao-dinh-da-xich-cao-cap-ghim-cai-vest-cuoi-tien-nguyen-p212048690.html?spid=212048699</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>32000</v>
+        <v>159000</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>159000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1022</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1028</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>192000</v>
+        <v>159000</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Bán thêm +6 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>67538621</t>
+          <t>107802069</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
+          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538631</t>
+          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>May 10</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>135000</v>
+        <v>32000</v>
       </c>
       <c r="G11" t="n">
-        <v>135000</v>
+        <v>32000</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1335,38 +1335,38 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>16591</v>
+        <v>1028</v>
       </c>
       <c r="K11" t="n">
-        <v>16592</v>
+        <v>1029</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>135000</v>
+        <v>32000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4842</v>
+        <v>68</v>
       </c>
       <c r="R11" t="n">
-        <v>4842</v>
+        <v>68</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1383,74 +1383,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31649352</t>
+          <t>276945307</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2 cặp miếng lót mũi giày nam cao su non đệm êm ngón chân - buybox - BBPK50</t>
+          <t>Áo lót nữ Angelavic 529 – Bra thun lạnh tăm, mút liền, cài sau, không gọng, nâng đỡ thoải mái</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/2-cap-mieng-lot-mui-giay-nam-cao-su-non-dem-em-ngon-chan-buybox-bbpk50-p31649352.html?spid=85084352</t>
+          <t>https://tiki.vn/ao-lot-nu-ao-bra-thun-lanh-tam-mut-lien-cai-sau-529-p276945307.html?spid=276945325</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>buybox</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>34000</v>
+        <v>84700</v>
       </c>
       <c r="G12" t="n">
-        <v>34000</v>
+        <v>110000</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>25300</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>29.87</v>
       </c>
       <c r="J12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1460,29 +1460,29 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Bán thêm +3 sản phẩm</t>
+          <t>Giá tăng 25,300đ (+29.9%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>272890964</t>
+          <t>277877891</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hộp 40 Viên Pin Nhí AAA (3A) Maxell Super 1.5V - Sử dụng cho remote TV, remote máy lạnh,...</t>
+          <t>Móc Nối Tăng Size Áo Ngực 3 Móc 59S – Phụ Kiện Nới Rộng Bra Linh Hoạt</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-40-vien-pin-nhi-aaa-3a-maxell-super-1-5v-su-dung-cho-remote-tv-remote-may-lanh-p272890964.html?spid=279273132</t>
+          <t>https://tiki.vn/moc-noi-tang-size-ao-nguc-3-moc-59s-phu-kien-noi-rong-bra-linh-hoat-p277877891.html?spid=277877897</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1491,50 +1491,50 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>98000</v>
+        <v>15400</v>
       </c>
       <c r="G13" t="n">
-        <v>98000</v>
+        <v>20000</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>29.87</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K13" t="n">
+        <v>23</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>98000</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,29 +1544,29 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Giá tăng 4,600đ (+29.9%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>207271635</t>
+          <t>193886649</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mũ lưỡi trai nam đẹp chất liệu vải dù thoáng mát dễ thấm hút mồ hôi kiểu dáng đẹp phù hợp cả nam và nữ</t>
+          <t>Áo sơ mi nữ form rộng kiểu tay lỡ cổ tròn NeSa Shop, chất liệu Đũi tơ thấm hút mồ hôi, áo sơ mi nữ nhiều màu, SMH.034</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mu-luoi-trai-nam-dep-chat-lieu-vai-du-thoang-mat-de-tham-hut-mo-hoi-kieu-dang-dep-phu-hop-ca-nam-va-nu-p207271635.html?spid=207271648</t>
+          <t>https://tiki.vn/ao-so-mi-nu-form-rong-kieu-tay-lo-co-tron-nesa-shop-chat-lieu-dui-to-tham-hut-mo-hoi-ao-so-mi-nu-nhieu-mau-smh-34-p193886649.html?spid=193886658</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1575,94 +1575,94 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>189000</v>
       </c>
       <c r="G14" t="n">
-        <v>24900</v>
+        <v>189000</v>
       </c>
       <c r="H14" t="n">
-        <v>24900</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>74700</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q14" t="n">
         <v>5</v>
       </c>
-      <c r="P14" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Rating 4.2→4.3 (+0.10) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>163806087</t>
+          <t>277544802</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da</t>
+          <t>Áo Chống Nắng Nam ,Chất Vải Thun Lạnh, Chống Tia UV, Thoáng Mát, Thấm Hút Mồ Hôi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-p163806087.html?spid=253461440</t>
+          <t>https://tiki.vn/ao-chong-nang-nam-chat-vai-thun-lanh-chong-tia-uv-thoang-mat-tham-hut-mo-hoi-p277544802.html?spid=277544808</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>Kun93</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>59000</v>
+        <v>185000</v>
       </c>
       <c r="G15" t="n">
-        <v>59000</v>
+        <v>185000</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1671,16 +1671,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>59000</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
@@ -1692,17 +1692,17 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1712,29 +1712,29 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>252533129</t>
+          <t>244297794</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Găng Tay Hở 2 Ngón Unisex Chống Nắng, Có Thể Sử Dụng Cảm Ứng Điện Thoại</t>
+          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/gang-tay-ho-2-ngon-unisex-chong-nang-co-the-su-dung-cam-ung-dien-thoai-p252533129.html?spid=252533130</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1743,28 +1743,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>49000</v>
+        <v>150100</v>
       </c>
       <c r="G16" t="n">
-        <v>49000</v>
+        <v>190000</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>39900</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>26.58</v>
       </c>
       <c r="J16" t="n">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>161</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>49000</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1776,17 +1776,17 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1796,81 +1796,81 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Giá tăng 39,900đ (+26.6%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>140429170</t>
+          <t>115852451</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bao tay chơi game găng tay 2 ngón cảm ứng điện thoại gamemobile BT01</t>
+          <t>Chai vệ sinh giày đồ da, túi ví, áo, ghế da giúp làm sạch, dưỡng ẩm chống mốc XIMO XI03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bao-tay-choi-game-gang-tay-2-ngon-cam-ung-dien-thoai-gamemobile-bt01-p140429170.html?spid=198934954</t>
+          <t>https://tiki.vn/chai-ve-sinh-giay-do-da-tui-vi-ao-ghe-da-giup-lam-sach-duong-am-chong-moc-ximo-xi03-p115852451.html?spid=262784198</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>17999</v>
+        <v>70000</v>
       </c>
       <c r="G17" t="n">
-        <v>9999</v>
+        <v>75000</v>
       </c>
       <c r="H17" t="n">
-        <v>-8000</v>
+        <v>5000</v>
       </c>
       <c r="I17" t="n">
-        <v>-44.45</v>
+        <v>7.14</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="K17" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>39996</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1880,47 +1880,47 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá giảm 8,000đ (44.4%) | Bán thêm +4 sản phẩm</t>
+          <t>Giá tăng 5,000đ (+7.1%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>244298960</t>
+          <t>279215984</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quần Mặc Váy Su Thông Hơi Trơn 6530 | Mát Mẻ, Không Lộ, Chống Hớ Hiệu Quả</t>
+          <t>Dép quai Ngang Biti's nam (39-44)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-vay-dai-thong-hoi-6530-p244298960.html?spid=244298972</t>
+          <t>https://tiki.vn/dep-quai-ngang-biti-s-nam-39-44-p279215984.html?spid=279216018</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>33180</v>
+        <v>184000</v>
       </c>
       <c r="G18" t="n">
-        <v>42000</v>
+        <v>184000</v>
       </c>
       <c r="H18" t="n">
-        <v>8820</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>26.58</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1938,23 +1938,23 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1964,24 +1964,24 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá tăng 8,820đ (+26.6%)</t>
+          <t>Rating 0.0→5.0 (+5.00) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>277844658</t>
+          <t>112851354</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Đồ bơi nữ dạng váy duyên dáng kín đáo có quần short liền trong váy</t>
+          <t>Áo ngực học sinh</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/do-boi-nu-dang-vay-duyen-dang-kin-dao-co-quan-short-lien-trong-vay-p277844658.html?spid=278668799</t>
+          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138790</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>219000</v>
+        <v>40000</v>
       </c>
       <c r="G19" t="n">
-        <v>259000</v>
+        <v>32800</v>
       </c>
       <c r="H19" t="n">
-        <v>40000</v>
+        <v>-7200</v>
       </c>
       <c r="I19" t="n">
-        <v>18.26</v>
+        <v>-18</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,26 +2019,26 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2048,29 +2048,29 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá tăng 40,000đ (+18.3%)</t>
+          <t>Giá giảm 7,200đ (18.0%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>277996544</t>
+          <t>277274436</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hộp 5 Quần lót nam cotton lụa – Siêu đẹp, mềm mịn, thoáng mát</t>
+          <t>Set áo cổ tròn sát nách phối quần ống suông thanh lịch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-5-quan-lot-nam-cotton-lua-muji-sieu-dep-mem-min-thoang-mat-p277996544.html?spid=278006738</t>
+          <t>https://tiki.vn/set-ao-co-tron-sat-nach-phoi-quan-ong-suong-thanh-lich-p277274436.html?spid=277274444</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2079,22 +2079,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>172000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>222000</v>
+        <v>199000</v>
       </c>
       <c r="H20" t="n">
-        <v>50000</v>
+        <v>199000</v>
       </c>
       <c r="I20" t="n">
-        <v>29.07</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2103,53 +2103,53 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Giá tăng 50,000đ (+29.1%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>37126497</t>
+          <t>113145806</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>( 10 cái ) quần lót nữ Su đúc không đường may, hàng đẹp loại xịn W19_503</t>
+          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-10-quan-lot-su-duc-khong-duong-may-hang-dep-loai-xin-w19_503-p37126497.html?spid=51720423</t>
+          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2163,22 +2163,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>218400</v>
+        <v>117000</v>
       </c>
       <c r="G21" t="n">
-        <v>280000</v>
+        <v>97110</v>
       </c>
       <c r="H21" t="n">
-        <v>61600</v>
+        <v>-19890</v>
       </c>
       <c r="I21" t="n">
-        <v>28.21</v>
+        <v>-17</v>
       </c>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2187,26 +2187,26 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2216,53 +2216,53 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Giá tăng 61,600đ (+28.2%)</t>
+          <t>Giá giảm 19,890đ (17.0%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>140961698</t>
+          <t>113144956</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Giày Lười Nam Da Bò SUNPOLO SUS510 (Đen, Nâu)</t>
+          <t>siêu phẩm áo lót nhật trơn đệm nâng ngực nhẹ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-luoi-nam-da-bo-sunpolo-sus510-den-nau-p140961698.html?spid=140961714</t>
+          <t>https://tiki.vn/sieu-pham-ao-lot-tron-dem-nang-nguc-nhe-p113144956.html?spid=142116876</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SUNPOLO</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1035000</v>
+        <v>165000</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>136950</v>
       </c>
       <c r="H22" t="n">
-        <v>-1035000</v>
+        <v>-28050</v>
       </c>
       <c r="I22" t="n">
-        <v>-100</v>
+        <v>-17</v>
       </c>
       <c r="J22" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2274,79 +2274,79 @@
         <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 28,050đ (17.0%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>66083356</t>
+          <t>66507793</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Áo phông cổ tròn ALIGRO ALGAPC044</t>
+          <t>Dép Nam Da Bò BIGGBEN Cao Cấp DN260</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-phong-co-tron-aligro-algapc044-p66083356.html?spid=66083362</t>
+          <t>https://tiki.vn/dep-nam-da-bo-biggben-cao-cap-dn260-p66507793.html?spid=66507799</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aligro</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>369000</v>
       </c>
       <c r="G23" t="n">
-        <v>150000</v>
+        <v>400000</v>
       </c>
       <c r="H23" t="n">
-        <v>150000</v>
+        <v>31000</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2355,82 +2355,82 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 31,000đ (+8.4%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>278698318</t>
+          <t>177666546</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Set đồ đùi ba lỗ nữ tập thể thao, mặc nhà hàng Quảng Châu loại 1</t>
+          <t>Dép Nam Quai Ngang Da Bò Thật BIGGBEN Cao Cấp DN308</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-do-dui-ba-lo-nu-tap-the-thao-mac-nha-hang-quang-chau-loai-1-p278698318.html?spid=278698340</t>
+          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-that-biggben-cao-cap-dn308-p177666546.html?spid=177666552</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>319000</v>
+        <v>289000</v>
       </c>
       <c r="G24" t="n">
-        <v>335000</v>
+        <v>380000</v>
       </c>
       <c r="H24" t="n">
-        <v>16000</v>
+        <v>91000</v>
       </c>
       <c r="I24" t="n">
-        <v>5.02</v>
+        <v>31.49</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2439,26 +2439,26 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2468,24 +2468,24 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Giá tăng 16,000đ (+5.0%)</t>
+          <t>Giá tăng 91,000đ (+31.5%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>63174143</t>
+          <t>250056510</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dép Nam Da Bò BIGGBEN Cao Cấp DN258</t>
+          <t>Dép Nam Quai Ngang BIGGBEN Da Bò Thật Cao Cấp DN332</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-da-bo-biggben-cao-cap-dn258-p63174143.html?spid=63174147</t>
+          <t>https://tiki.vn/dep-nam-quai-ngang-biggben-da-bo-that-cao-cap-dn332-p250056510.html?spid=250056524</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2499,22 +2499,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>500000</v>
+        <v>369000</v>
       </c>
       <c r="G25" t="n">
-        <v>419000</v>
+        <v>450000</v>
       </c>
       <c r="H25" t="n">
-        <v>-81000</v>
+        <v>81000</v>
       </c>
       <c r="I25" t="n">
-        <v>-16.2</v>
+        <v>21.95</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2523,26 +2523,26 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2552,53 +2552,53 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Giá giảm 81,000đ (16.2%)</t>
+          <t>Giá tăng 81,000đ (+22.0%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>279068959</t>
+          <t>59206687</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam sọc ngang. Regular - ROUTINE 10F25TSS036</t>
+          <t>GIày Sandal Nam Da Bò BIGGBEN Cao Cấp SD105</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-soc-ngang-regular-routine-10f25tss036-p279068959.html?spid=279068973</t>
+          <t>https://tiki.vn/giay-sandal-nam-da-bo-biggben-cao-cap-sd105-p59206687.html?spid=59206699</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>379000</v>
       </c>
       <c r="G26" t="n">
-        <v>379000</v>
+        <v>439000</v>
       </c>
       <c r="H26" t="n">
-        <v>379000</v>
+        <v>60000</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>15.83</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2607,82 +2607,82 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 60,000đ (+15.8%)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>183895879</t>
+          <t>278872546</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bình xịt lưu hương chống thối chân, khử mùi giày XIMO, kháng khuẩn, công nghệ Bạc ion (VSG08-1)</t>
+          <t>Áo thun tay ngắn nam.Fitted - ROUTINE 10F25TSS039</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/binh-xit-luu-huong-chong-thoi-chan-khu-mui-giay-ximo-khang-khuan-cong-nghe-bac-ion-vsg08-p183895879.html?spid=252869682</t>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-fitted-routine-10f25tss039-p278872546.html?spid=278872558</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>71000</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>66000</v>
+        <v>349000</v>
       </c>
       <c r="H27" t="n">
-        <v>-5000</v>
+        <v>349000</v>
       </c>
       <c r="I27" t="n">
-        <v>-7.04</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2691,82 +2691,82 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Giá giảm 5,000đ (7.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>152632563</t>
+          <t>276094684</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Mút Mỏng Trơn Không Gọng 3281 – Nhẹ Êm, Tự Nhiên, Dễ Mặc Mỗi Ngày</t>
+          <t>Dép Nam Quai Ngang BIGGBEN Da Bò Thật DN356</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-duc-kiem-bra-cao-cap-3281-big-size-p152632563.html?spid=274990712</t>
+          <t>https://tiki.vn/dep-nam-quai-ngang-biggben-da-bo-that-dn356-p276094684.html?spid=276094690</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>80190</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>99000</v>
+        <v>389000</v>
       </c>
       <c r="H28" t="n">
-        <v>18810</v>
+        <v>389000</v>
       </c>
       <c r="I28" t="n">
-        <v>23.46</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2794,63 +2794,63 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Giá tăng 18,810đ (+23.5%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>115852451</t>
+          <t>275233185</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chai vệ sinh giày đồ da, túi ví, áo, ghế da giúp làm sạch, dưỡng ẩm chống mốc XIMO XI03</t>
+          <t>Áo Thun ROUTINE Tay Ngắn Dệt Jacquard Phối Nhãn Form Loose - 10S24TSS014 | LASTORE MENSWEAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-ve-sinh-giay-do-da-tui-vi-ao-ghe-da-giup-lam-sach-duong-am-chong-moc-ximo-xi03-p115852451.html?spid=262784198</t>
+          <t>https://tiki.vn/ao-thun-routine-tay-ngan-det-jacquard-phoi-nhan-form-loose-10s24tss014-lastore-menswear-p275233185.html?spid=275233197</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>70000</v>
+        <v>399000</v>
       </c>
       <c r="H29" t="n">
-        <v>-5000</v>
+        <v>399000</v>
       </c>
       <c r="I29" t="n">
-        <v>-6.67</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2859,36 +2859,36 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Giá giảm 5,000đ (6.7%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
@@ -2919,16 +2919,16 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>460000</v>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
-        <v>-460000</v>
+        <v>460000</v>
       </c>
       <c r="I30" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2962,63 +2962,63 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>191694860</t>
+          <t>274350557</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Giày da nam công sở đế cao Bụi Leather G123 - Da bò Nappa cao cấp - Phong cách trẻ trung năng động - Bảo hành 12 tháng</t>
+          <t>Hộp 100 Khăn Lau Kính Nano, Chống Bám Hơi Nước, Chống Bụi Bẩn - Khăn Lau Kính Nano Hộp 100 Miếng Giấy Lau Kính Chống Bám Hơi Nước, Lau Sạch Vân Tay Bụi Bẩn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-da-nam-cong-so-de-cao-bui-leather-g123-da-bo-nappa-cao-cap-phong-cach-tre-trung-nang-dong-bao-hanh-12-thang-p191694860.html?spid=191694870</t>
+          <t>https://tiki.vn/hop-100-khan-lau-kinh-nano-chong-bam-hoi-nuoc-chong-bui-ban-khan-lau-kinh-nano-hop-100-mieng-giay-lau-kinh-chong-bam-hoi-nuoc-lau-sach-van-tay-bui-ban-p274350557.html?spid=274350558</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bụi Leather</t>
+          <t>fofaHome</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>925000</v>
+        <v>20000</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="H31" t="n">
-        <v>-925000</v>
+        <v>-3000</v>
       </c>
       <c r="I31" t="n">
-        <v>-100</v>
+        <v>-15</v>
       </c>
       <c r="J31" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3030,50 +3030,50 @@
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P31" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 3,000đ (15.0%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>275835289</t>
+          <t>183895879</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dép Nam Quai Ngang BIGGBEN Da Bò Thật DN355</t>
+          <t>Bình xịt lưu hương chống thối chân, khử mùi giày XIMO, kháng khuẩn, công nghệ Bạc ion (VSG08-1)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-biggben-da-bo-that-dn355-p275835289.html?spid=275835315</t>
+          <t>https://tiki.vn/binh-xit-luu-huong-chong-thoi-chan-khu-mui-giay-ximo-khang-khuan-cong-nghe-bac-ion-vsg08-p183895879.html?spid=252869682</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3083,26 +3083,26 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="G32" t="n">
-        <v>399000</v>
+        <v>71000</v>
       </c>
       <c r="H32" t="n">
-        <v>399000</v>
+        <v>5000</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3111,53 +3111,53 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 5,000đ (+7.6%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>262085586</t>
+          <t>192419827</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hộp 100 Miếng Khăn Lau Mắt Kính Nano Chống Mờ Sương, Bám Hơi Nước</t>
+          <t>Khăn Lau Kính Nano Hộp 100 Miếng Giấy Lau Kính Chống Bám Hơi Nước, Lau Sạch Vân Tay Bụi Bẩn</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-100-mieng-khan-lau-mat-kinh-nano-chong-mo-suong-bam-hoi-nuoc-p262085586.html?spid=277964244</t>
+          <t>https://tiki.vn/khan-lau-kinh-nano-hop-100-mieng-giay-lau-kinh-chong-bam-hoi-nuoc-lau-sach-van-tay-bui-ban-p192419827.html?spid=278272152</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3183,10 +3183,10 @@
         <v>17.65</v>
       </c>
       <c r="J33" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3195,26 +3195,26 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3231,17 +3231,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>246853757</t>
+          <t>78513044</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GĂNG TAY CHỐNG NẮNG CHO NỮ</t>
+          <t>Khăn ống cotton tube co giãn 9 kiểu dùng có video hướng dẫn  TUBE01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://tiki.vn/gang-tay-chong-nang-cho-nu-p246853757.html?spid=273131602</t>
+          <t>https://tiki.vn/khan-ong-cotton-tube-co-gian-9-kieu-dung-co-video-huong-dan-tube01-p78513044.html?spid=78518779</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Song An Eco</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>48000</v>
+        <v>15000</v>
       </c>
       <c r="H34" t="n">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="I34" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3279,82 +3279,82 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Giá tăng 6,000đ (+14.3%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>192419827</t>
+          <t>163902369</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Khăn Lau Kính Nano Hộp 100 Miếng Giấy Lau Kính Chống Bám Hơi Nước, Lau Sạch Vân Tay Bụi Bẩn</t>
+          <t>Áo Sơ Mi Nam Xanh Dương Kẻ Caro Ngắn Tay Công Sở Trung Niên Thương Hiệu Anton Vải Sợi Tre - YGD566</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khan-lau-kinh-nano-hop-100-mieng-giay-lau-kinh-chong-bam-hoi-nuoc-lau-sach-van-tay-bui-ban-p192419827.html?spid=278272152</t>
+          <t>https://tiki.vn/ao-so-mi-nam-xanh-duong-ke-caro-ngan-tay-cong-so-trung-nien-thuong-hieu-anton-vai-soi-tre-ygd566-p163902369.html?spid=163902371</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>SOMIANTON</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>20000</v>
+        <v>355000</v>
       </c>
       <c r="G35" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-3000</v>
+        <v>-355000</v>
       </c>
       <c r="I35" t="n">
-        <v>-15</v>
+        <v>-100</v>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3366,76 +3366,76 @@
         <v>5</v>
       </c>
       <c r="O35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Giá giảm 3,000đ (15.0%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>279122825</t>
+          <t>176881225</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thắt lưng nữ phong cách Hàn Quốc, dây nịt quần tây/quần jean da tổng hợp thanh lịch IDIGO FD2-0052</t>
+          <t>Đồ Bơi Nữ Tay Dài Quần Ôm Thân Tôn Dáng AT221 MayHomes Long Sleeves And Long Pants Women Swimwear Set With UPF 50 Sun Protection</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-nu-phong-cach-han-quoc-day-nit-quan-tay-quan-jean-da-tong-hop-thanh-lich-idigo-fd2-0052-p279122825.html?spid=279122831</t>
+          <t>https://tiki.vn/do-boi-nu-tay-dai-quan-om-than-ton-dang-at221-mayhomes-long-sleeves-and-long-pants-women-swimwear-set-with-upf-50-sun-protection-p176881225.html?spid=176881229</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IDIGO</t>
+          <t>MAYHOMES</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>288000</v>
       </c>
       <c r="G36" t="n">
-        <v>117090</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>117090</v>
+        <v>-288000</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3447,16 +3447,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>-4.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3466,34 +3466,34 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>251424864</t>
+          <t>269878543</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Đồ ngủ nữ Wannabe DNS74 đầm ngủ hai dây cổ tim nền hoa xinh xắn trang nhã</t>
+          <t>Cuộn 8M Băng Dán Cổ Áo Sơ Mi Chống Bẩn Vải Không Dệt Thoáng Khí Bám Dính Tốt Thấm Hút Mồ Hôi</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://tiki.vn/do-ngu-nu-wannabe-dns74-dam-ngu-hai-day-co-tim-nen-hoa-xinh-xan-trang-nha-p251424864.html?spid=270903252</t>
+          <t>https://tiki.vn/cuon-8m-bang-dan-co-ao-so-mi-chong-ban-vai-khong-det-thoang-khi-bam-dinh-tot-tham-hut-mo-hoi-p269878543.html?spid=269878549</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3503,23 +3503,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wannabe</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>300000</v>
+        <v>39000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-300000</v>
+        <v>-39000</v>
       </c>
       <c r="I37" t="n">
         <v>-100</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3531,16 +3531,16 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-0</v>
+        <v>-4.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -3567,22 +3567,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>212048690</t>
+          <t>6535821</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NHIỀU MẪU Ghim cài áo đính đá xích cao cấp - ghim cài vest cưới Tien Nguyen</t>
+          <t>Quần Lót Nữ - Quần Đùi Mặc Trong Váy Su Thông Hơi</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://tiki.vn/nhieu-mau-ghim-cai-ao-dinh-da-xich-cao-cap-ghim-cai-vest-cuoi-tien-nguyen-p212048690.html?spid=212048699</t>
+          <t>https://tiki.vn/quan-lot-nu-quan-dui-mac-trong-vay-su-thong-hoi-p6535821.html?spid=51154654</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3591,19 +3591,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>159000</v>
+        <v>42000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-159000</v>
+        <v>-42000</v>
       </c>
       <c r="I38" t="n">
         <v>-100</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3615,16 +3615,16 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-5</v>
+        <v>-4.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -3651,43 +3651,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>278274146</t>
+          <t>273611089</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Củ Cap O.p..p.o 30W_33W_67W Sạc Nhanh Công Nghệ SupperVooc Zin Hãng Cam Kết</t>
+          <t>Xi Đánh Bóng Giày Da Làm Bóng Nhanh Đồ Da, Xi Kem Dưỡng Da Có Đầu Mút Hỗ Trợ - HÀNG CHÍNH HÃNG MINIIN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://tiki.vn/cu-cap-oppo-30w_33w_67w-sac-nhanh-cong-nghe-suppervooc-zin-chinh-hang-cam-ket-p278274146.html?spid=278292995</t>
+          <t>https://tiki.vn/xi-danh-bong-giay-da-lam-bong-nhanh-do-da-xi-kem-duong-da-co-da-u-mu-t-ho-tro-hang-chinh-hang-miniin-p273611089.html?spid=273611093</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MINIIN</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>165000</v>
+        <v>35000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-165000</v>
+        <v>-35000</v>
       </c>
       <c r="I39" t="n">
         <v>-100</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3699,16 +3699,16 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-0</v>
+        <v>-3.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -3735,17 +3735,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6394813</t>
+          <t>107491961</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Giày Tây Nam BIGGBEN Da Bò Thật GT17</t>
+          <t>Dép Nam Quai Ngang Da Bò BIGGBEN Cao Cấp DN283</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-tay-nam-biggben-da-bo-that-gt17-p6394813.html?spid=6394833</t>
+          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-biggben-cao-cap-dn283-p107491961.html?spid=107491965</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3759,19 +3759,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>720000</v>
+        <v>319000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-720000</v>
+        <v>-319000</v>
       </c>
       <c r="I40" t="n">
         <v>-100</v>
       </c>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3783,16 +3783,16 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-4.7</v>
+        <v>-0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -3819,43 +3819,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>275233185</t>
+          <t>275933718</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Áo Thun ROUTINE Tay Ngắn Dệt Jacquard Phối Nhãn Form Loose - 10S24TSS014 | LASTORE MENSWEAR</t>
+          <t>Giày Sneaker Vải Canvas Nam Nữ E18 White Dincox Shoes Sang Trọng</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-routine-tay-ngan-det-jacquard-phoi-nhan-form-loose-10s24tss014-lastore-menswear-p275233185.html?spid=275233197</t>
+          <t>https://tiki.vn/giay-sneaker-vai-canvas-nam-nu-e18-white-dincox-shoes-sang-trong-p275933718.html?spid=275933722</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>DINCOX</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>399000</v>
+        <v>490000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-399000</v>
+        <v>-490000</v>
       </c>
       <c r="I41" t="n">
         <v>-100</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3867,16 +3867,16 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>-0</v>
+        <v>-1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -3903,43 +3903,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>78513044</t>
+          <t>253306906</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Khăn ống cotton tube co giãn 9 kiểu dùng có video hướng dẫn  TUBE01</t>
+          <t>Đón gót giầy gỗ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khan-ong-cotton-tube-co-gian-9-kieu-dung-co-video-huong-dan-tube01-p78513044.html?spid=78518779</t>
+          <t>https://tiki.vn/don-got-giay-p253306906.html?spid=253306912</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Song An Eco</t>
+          <t>DAICAT</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>15000</v>
+        <v>159000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-15000</v>
+        <v>-159000</v>
       </c>
       <c r="I42" t="n">
         <v>-100</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -3987,17 +3987,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>275276260</t>
+          <t>154852782</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dép tổ ong ĐỎ nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Giày Lười, Giày Mọi Nam Da Bò SUNPOLO CS5052 (Đen, Nâu)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-do-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276260.html?spid=275276262</t>
+          <t>https://tiki.vn/giay-luoi-nam-da-bo-sunpolo-su5052-den-nau-p154852782.html?spid=154852796</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4007,81 +4007,81 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>SUNPOLO</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>63000</v>
+        <v>1100000</v>
       </c>
       <c r="G43" t="n">
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-1100000</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
         <v>4</v>
       </c>
-      <c r="L43" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M43" t="n">
-        <v>-126000</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
       <c r="O43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Bán thêm -2 sản phẩm</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>195305781</t>
+          <t>279068959</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Combo 3 quần đùi mặc nhà - Giao màu ngẫu nhiên</t>
+          <t>Áo thun tay ngắn nam sọc ngang. Regular - ROUTINE 10F25TSS036</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-3-quan-dui-mac-nha-giao-mau-ngau-nhien-p195305781.html?spid=195305789</t>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-soc-ngang-regular-routine-10f25tss036-p279068959.html?spid=279068973</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4091,81 +4091,81 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Novelty</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>285000</v>
+        <v>379000</v>
       </c>
       <c r="G44" t="n">
-        <v>285000</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-379000</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-285000</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Bán thêm -1 sản phẩm</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14351068</t>
+          <t>66095198</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Áo thun Nam có cổ thời trang</t>
+          <t>Áo phông cổ tim ALIGRO ALGAPC051</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-co-co-thoi-trang-p14351068.html?spid=14351082</t>
+          <t>https://tiki.vn/ao-phong-co-tim-aligro-algapc051-p66095198.html?spid=66095200</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4175,64 +4175,316 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Aligro</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>160000</v>
+        <v>150000</v>
       </c>
       <c r="G45" t="n">
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-150000</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J45" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-640000</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>66083356</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Áo phông cổ tròn ALIGRO ALGAPC044</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-phong-co-tron-aligro-algapc044-p66083356.html?spid=66083362</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aligro</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-150000</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>277811866</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BỘ Găng Tay Bao Tay Ống Chống Nắng Cao Cấp Unisex MÀU XÁM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/khan-trum-dau-ninja-fullface-chong-nang-mau-den-p277811866.html?spid=277811867</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LuckyJQR</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
         <v>5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>102151424</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kính mát nam EXFASH EF38973 thời trang (62/14/145)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/kinh-mat-nam-exfash-ef38973-thoi-trang-62-14-145-p102151424.html?spid=102151428</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Exfash</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>529000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-529000</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J48" t="n">
         <v>2</v>
       </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Bán thêm -4 sản phẩm | Rating 4.7→4.8 (+0.10) | Review thêm +2</t>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26666649</t>
+          <t>278028606</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dép Nam BIGGBEN Da Bò Thật Cao Cấp DN196</t>
+          <t>KHẨU TRANG UV LOẠI 1 CHỐNG TIA UV</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-biggben-da-bo-that-cao-cap-dn196-p26666649.html?spid=26666651</t>
+          <t>https://tiki.vn/khau-trang-uv-loai-1-chong-tia-uv-p278028606.html?spid=278028610</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>379000</v>
+        <v>60000</v>
       </c>
       <c r="H2" t="n">
-        <v>379000</v>
+        <v>60000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="M2" t="n">
-        <v>41690000</v>
+        <v>1560000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>66803444</t>
+          <t>279104033</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Áo Cardigan Nữ Họa Tiết Xinh Thời Trang Korea ALN037 MayHomes Mẫu Mới Mùa Xuân</t>
+          <t>Áo lót nữ form ba lỗ thông hơi trơn big size 1397 – Size XXL–3XL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-cardigan-nu-hoa-tiet-xinh-thoi-trang-korea-aln037-mayhomes-mau-moi-mua-xuan-p66803444.html?spid=66803452</t>
+          <t>https://tiki.vn/ao-lot-nu-form-ba-lo-thong-hoi-tron-big-size-1397-size-xxl-3xl-p279104033.html?spid=279104035</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MAYHOMES</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>149000</v>
+        <v>99000</v>
       </c>
       <c r="H3" t="n">
-        <v>149000</v>
+        <v>99000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>25628000</v>
+        <v>594000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,22 +711,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>273388482</t>
+          <t>278015269</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Combo 7 quần lót cotton nữ nhiều màu du lịch dùng 1 lần</t>
+          <t>QUẦN SỊP THÔNG HƠI LƯỚI NHỎ TỪ 48-100KG DÀNH CHO NAM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-7-quan-lot-cotton-nu-nhieu-mau-du-lich-dung-1-lan-p273388482.html?spid=273388612</t>
+          <t>https://tiki.vn/quan-sip-thong-hoi-luoi-nho-tu-48-100kg-danh-cho-nam-p278015269.html?spid=278015277</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -738,10 +738,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>169000</v>
+        <v>42000</v>
       </c>
       <c r="H4" t="n">
-        <v>169000</v>
+        <v>42000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,35 +750,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>5577000</v>
+        <v>504000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,37 +795,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>190792898</t>
+          <t>278034638</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày sandal nam da bò thật BIGGBEN cao cấp SD123</t>
+          <t>ÁO LÁ BRA HỌC SINH CHẤT COTTON MÁT KHÔNG MÚT TỪ 8-13 TUỔI DƯỚI 50KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-sandal-nam-da-bo-that-biggben-cao-cap-sd123-p190792898.html?spid=190792908</t>
+          <t>https://tiki.vn/ao-la-bra-hoc-sinh-chat-cotton-mat-khong-mut-duoi-50kg-danh-cho-nu-p278034638.html?spid=278034640</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>399000</v>
+        <v>62000</v>
       </c>
       <c r="H5" t="n">
-        <v>399000</v>
+        <v>62000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -834,35 +834,35 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>4788000</v>
+        <v>372000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -879,17 +879,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>275431635</t>
+          <t>275276220</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dép quai kẹp Bitis nam (38-43)</t>
+          <t>Dép tổ ong CAM nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-kep-bitis-nam-38-43-p275431635.html?spid=275431639</t>
+          <t>https://tiki.vn/dep-to-ong-cam-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276220.html?spid=275276222</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -899,101 +899,101 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="G6" t="n">
-        <v>75000</v>
+        <v>72000</v>
       </c>
       <c r="H6" t="n">
-        <v>75000</v>
+        <v>9000</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>1650000</v>
+        <v>360000</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 9,000đ (+14.3%) | Bán thêm +5 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16651795</t>
+          <t>278008741</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>️[5 Quần] ComBo 5 Quần Lót Nam THUN LẠNH Lưng Bự Hàng Việt Nam Cao Cấp</t>
+          <t>MIẾNG DÁN NGỰC HÌNH HOA SILICON CỰC CHẮC VÀ XINH DÀNH CHO NỮ - HỘP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/5-quan-combo-5-quan-lot-nam-thun-lanh-lung-bu-hang-viet-nam-cao-cap-p16651795.html?spid=51148098</t>
+          <t>https://tiki.vn/mieng-dan-nguc-hinh-hoa-silicon-cuc-chac-va-xinh-danh-cho-nu-p278008741.html?spid=278008743</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MENLIVE</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155800</v>
+        <v>57000</v>
       </c>
       <c r="H7" t="n">
-        <v>155800</v>
+        <v>57000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1002,35 +1002,35 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>1402200</v>
+        <v>342000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,101 +1047,101 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>275431720</t>
+          <t>31637590</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dép quai kẹp Bitis nam (38-43)</t>
+          <t>Combo 4 quần lót nam tam giác Bamboo Organic mềm mịn thoáng mát thấm hút mồ hôi - MRM Manlywear - Màu Ngẫu Nhiên</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-kep-bitis-nam-38-43-p275431720.html?spid=275431728</t>
+          <t>https://tiki.vn/combo-4-qua-n-lo-t-nam-tam-gia-c-bamboo-organic-me-m-mi-n-thoa-ng-ma-t-tha-m-hu-t-mo-hoi-mrm-manlywear-ma-u-nga-u-nhien-p31637590.html?spid=31637602</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>MRM Manlywear</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>249000</v>
       </c>
       <c r="G8" t="n">
-        <v>75000</v>
+        <v>249000</v>
       </c>
       <c r="H8" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3772</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>3773</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>600000</v>
+        <v>249000</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>910</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>34159013</t>
+          <t>277541813</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combo 5 Đôi Tất Cổ Ngắn Cùng Màu Cotton Thương Hiệu MRM Manlywear</t>
+          <t>Găng Tay Chống Nắng Dài Vừa Phải, Chống Trượt Thời Trang Mùa Hè, Đàn Hồi - HÀNG CHÍNH HÃNG MINIIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-doi-tat-nam-vo-nam-co-ngan-cao-cap-mrm-fashion-cung-mau-p34159013.html?spid=34159015</t>
+          <t>https://tiki.vn/gang-tay-chong-nang-dai-vua-phai-chong-truot-thoi-trang-mua-he-dan-hoi-hang-chinh-hang-miniin-p277541813.html?spid=277541823</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1151,14 +1151,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>MINIIN</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>129000</v>
+        <v>49000</v>
       </c>
       <c r="G9" t="n">
-        <v>129000</v>
+        <v>49000</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1167,38 +1167,38 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>5467</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>5470</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>387000</v>
+        <v>196000</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1101</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1101</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1208,24 +1208,24 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Bán thêm +3 sản phẩm</t>
+          <t>Bán thêm +4 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>212048690</t>
+          <t>278945498</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NHIỀU MẪU Ghim cài áo đính đá xích cao cấp - ghim cài vest cưới Tien Nguyen</t>
+          <t>SET 5 ĐÔI TẤT VỚ NỮ CAO CỔ MÃ 17 DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/nhieu-mau-ghim-cai-ao-dinh-da-xich-cao-cap-ghim-cai-vest-cuoi-tien-nguyen-p212048690.html?spid=212048699</t>
+          <t>https://tiki.vn/set-5-doi-tat-vo-nu-cao-co-ma-17-danh-cho-nu-p278945498.html?spid=278945500</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1242,10 +1242,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>159000</v>
+        <v>100000</v>
       </c>
       <c r="H10" t="n">
-        <v>159000</v>
+        <v>100000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1260,29 +1260,29 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>159000</v>
+        <v>100000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1299,158 +1299,158 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>107802069</t>
+          <t>278011349</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
+          <t>QUẦN ĐỘN MÔNG ĐỊNH HÌNH TỪ 40-70KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
+          <t>https://tiki.vn/quan-don-mong-dinh-hinh-tu-40-70kg-danh-cho-nu-p278011349.html?spid=278011357</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>32000</v>
+        <v>85000</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1028</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1029</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>32000</v>
+        <v>85000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>276945307</t>
+          <t>192985737</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Áo lót nữ Angelavic 529 – Bra thun lạnh tăm, mút liền, cài sau, không gọng, nâng đỡ thoải mái</t>
+          <t>Móc Cài Tai Silicon Siêu Dẻo, Giúp Giữ Gọng Kính Không Bị Tuột Khi Chạy, Nhảy, Chơi Thể Thao, Màu Đen, Trong Suốt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ao-bra-thun-lanh-tam-mut-lien-cai-sau-529-p276945307.html?spid=276945325</t>
+          <t>https://tiki.vn/moc-cai-tai-silicon-sieu-deo-giup-giu-gong-kinh-khong-bi-tuot-khi-chay-nhay-choi-the-thao-mau-den-trong-suot-p192985737.html?spid=192985738</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Blue Light</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>84700</v>
+        <v>10000</v>
       </c>
       <c r="G12" t="n">
-        <v>110000</v>
+        <v>10000</v>
       </c>
       <c r="H12" t="n">
-        <v>25300</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>29.87</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1460,29 +1460,29 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Giá tăng 25,300đ (+29.9%)</t>
+          <t>Bán thêm +5 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>277877891</t>
+          <t>252533129</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Móc Nối Tăng Size Áo Ngực 3 Móc 59S – Phụ Kiện Nới Rộng Bra Linh Hoạt</t>
+          <t>Găng Tay Hở 2 Ngón Unisex Chống Nắng, Có Thể Sử Dụng Cảm Ứng Điện Thoại</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/moc-noi-tang-size-ao-nguc-3-moc-59s-phu-kien-noi-rong-bra-linh-hoat-p277877891.html?spid=277877897</t>
+          <t>https://tiki.vn/gang-tay-ho-2-ngon-unisex-chong-nang-co-the-su-dung-cam-ung-dien-thoai-p252533129.html?spid=252533130</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1491,50 +1491,50 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15400</v>
+        <v>49000</v>
       </c>
       <c r="G13" t="n">
-        <v>20000</v>
+        <v>49000</v>
       </c>
       <c r="H13" t="n">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>29.87</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="K13" t="n">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,24 +1544,24 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Giá tăng 4,600đ (+29.9%)</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>193886649</t>
+          <t>167461360</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Áo sơ mi nữ form rộng kiểu tay lỡ cổ tròn NeSa Shop, chất liệu Đũi tơ thấm hút mồ hôi, áo sơ mi nữ nhiều màu, SMH.034</t>
+          <t>Đồ bơi bigsize nữ, áo tắm cộc tay cùng quần boxer cho người béo mập, mẫu thể thao khỏe khoắn, chất đẹp phom đẹp | KT110</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nu-form-rong-kieu-tay-lo-co-tron-nesa-shop-chat-lieu-dui-to-tham-hut-mo-hoi-ao-so-mi-nu-nhieu-mau-smh-34-p193886649.html?spid=193886658</t>
+          <t>https://tiki.vn/do-boi-bigsize-nu-ao-tam-coc-tay-cung-quan-boxer-cho-nguoi-beo-map-mau-the-thao-khoe-khoan-chat-dep-phom-dep-kt110-p167461360.html?spid=195949767</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1575,22 +1575,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>189000</v>
+        <v>460000</v>
       </c>
       <c r="G14" t="n">
-        <v>189000</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-460000</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1599,82 +1599,82 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1</v>
+        <v>-4.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Rating 4.2→4.3 (+0.10) | Review thêm +1</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>277544802</t>
+          <t>278012255</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Áo Chống Nắng Nam ,Chất Vải Thun Lạnh, Chống Tia UV, Thoáng Mát, Thấm Hút Mồ Hôi</t>
+          <t>QUẦN LÓT LỤA SIÊU ĐẸP CAO CẤP PHỐI REN TỪ 40-70KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-chong-nang-nam-chat-vai-thun-lanh-chong-tia-uv-thoang-mat-tham-hut-mo-hoi-p277544802.html?spid=277544808</t>
+          <t>https://tiki.vn/quan-lot-lua-sieu-dep-cao-cap-phoi-ren-tu-40-70kg-danh-cho-nu-p278012255.html?spid=278012271</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kun93</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>185000</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>185000</v>
+        <v>45000</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1683,58 +1683,58 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Review thêm +1</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>244297794</t>
+          <t>278012626</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
+          <t>QUẦN LÓT SU THÔNG HƠI SIÊU ĐẸP SIÊU MỎNG TỪ 40-60KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
+          <t>https://tiki.vn/quan-lot-su-thong-hoi-sieu-dep-sieu-mong-tu-40-60kg-danh-cho-nu-p278012626.html?spid=278012638</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>150100</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>190000</v>
+        <v>38000</v>
       </c>
       <c r="H16" t="n">
-        <v>39900</v>
+        <v>38000</v>
       </c>
       <c r="I16" t="n">
-        <v>26.58</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1767,82 +1767,82 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Giá tăng 39,900đ (+26.6%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>115852451</t>
+          <t>74421501</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chai vệ sinh giày đồ da, túi ví, áo, ghế da giúp làm sạch, dưỡng ẩm chống mốc XIMO XI03</t>
+          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-ve-sinh-giay-do-da-tui-vi-ao-ghe-da-giup-lam-sach-duong-am-chong-moc-ximo-xi03-p115852451.html?spid=262784198</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421539</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>70000</v>
+        <v>118690</v>
       </c>
       <c r="G17" t="n">
-        <v>75000</v>
+        <v>150000</v>
       </c>
       <c r="H17" t="n">
-        <v>5000</v>
+        <v>31310</v>
       </c>
       <c r="I17" t="n">
-        <v>7.14</v>
+        <v>26.38</v>
       </c>
       <c r="J17" t="n">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="K17" t="n">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1860,17 +1860,17 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1880,44 +1880,44 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá tăng 5,000đ (+7.1%)</t>
+          <t>Giá tăng 31,310đ (+26.4%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>279215984</t>
+          <t>278071763</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dép quai Ngang Biti's nam (39-44)</t>
+          <t>Quần sịp nam thông hơi mát lạnh từ 40-100kg dành cho nam</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-ngang-biti-s-nam-39-44-p279215984.html?spid=279216018</t>
+          <t>https://tiki.vn/quan-sip-nam-thong-hoi-mat-lanh-tu-50-100kg-danh-cho-nam-p278071763.html?spid=278071767</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>184000</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>184000</v>
+        <v>94000</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1938,55 +1938,55 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Rating 0.0→5.0 (+5.00) | Review thêm +1</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>112851354</t>
+          <t>278014106</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Áo ngực học sinh</t>
+          <t>QUẦN SỊP CHÉO COTTON CAO CẤP MỀM MỊN TỪ 40-85KG DÀNH CHO NAM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138790</t>
+          <t>https://tiki.vn/quan-sip-cheo-cotton-cao-cap-mem-min-tu-48-85kg-danh-cho-nam-p278014106.html?spid=279145394</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>32800</v>
+        <v>60000</v>
       </c>
       <c r="H19" t="n">
-        <v>-7200</v>
+        <v>60000</v>
       </c>
       <c r="I19" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,53 +2019,53 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá giảm 7,200đ (18.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>277274436</t>
+          <t>278009461</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Set áo cổ tròn sát nách phối quần ống suông thanh lịch</t>
+          <t>ÁO NGỰC BRA ĐẸP QUYẾN RŨ SIZE TỪ 36-40 DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-ao-co-tron-sat-nach-phoi-quan-ong-suong-thanh-lich-p277274436.html?spid=277274444</t>
+          <t>https://tiki.vn/ao-nguc-bra-dep-quyen-ru-size-tu-36-40-danh-cho-nu-p278009461.html?spid=278009479</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2082,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>199000</v>
+        <v>110000</v>
       </c>
       <c r="H20" t="n">
-        <v>199000</v>
+        <v>110000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2139,17 +2139,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>113145806</t>
+          <t>279004066</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
+          <t>QUẦN ĐỘN MÔNG ĐỊNH HÌNH SIÊU ĐẸP TỪ 40-75KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
+          <t>https://tiki.vn/quan-don-mong-dinh-hinh-sieu-dep-tu-40-75kg-danh-cho-nu-p279004066.html?spid=279004070</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2163,22 +2163,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>97110</v>
+        <v>115000</v>
       </c>
       <c r="H21" t="n">
-        <v>-19890</v>
+        <v>115000</v>
       </c>
       <c r="I21" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2187,53 +2187,53 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Giá giảm 19,890đ (17.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>113144956</t>
+          <t>278026067</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>siêu phẩm áo lót nhật trơn đệm nâng ngực nhẹ</t>
+          <t>ÁO CHỐNG NẮNG MỀM MÁT TỪ 40-60KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/sieu-pham-ao-lot-tron-dem-nang-nguc-nhe-p113144956.html?spid=142116876</t>
+          <t>https://tiki.vn/ao-chong-nang-mem-mat-tu-40-60kg-danh-cho-nu-p278026067.html?spid=278026069</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2247,22 +2247,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>136950</v>
+        <v>110000</v>
       </c>
       <c r="H22" t="n">
-        <v>-28050</v>
+        <v>110000</v>
       </c>
       <c r="I22" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2271,82 +2271,82 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Giá giảm 28,050đ (17.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>66507793</t>
+          <t>278013980</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dép Nam Da Bò BIGGBEN Cao Cấp DN260</t>
+          <t>QUẦN ĐÙI CK HOT HIT CÁ TÍNH TỪ 40-70KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-da-bo-biggben-cao-cap-dn260-p66507793.html?spid=66507799</t>
+          <t>https://tiki.vn/quan-dui-ck-hot-hit-ca-tinh-tu-40-70kg-danh-cho-nu-p278013980.html?spid=278021323</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>369000</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>400000</v>
+        <v>75000</v>
       </c>
       <c r="H23" t="n">
-        <v>31000</v>
+        <v>75000</v>
       </c>
       <c r="I23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2355,82 +2355,82 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Giá tăng 31,000đ (+8.4%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>177666546</t>
+          <t>91973812</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dép Nam Quai Ngang Da Bò Thật BIGGBEN Cao Cấp DN308</t>
+          <t>Áo Lót Nữ Su Đúc Hình Lá Không Gọng Đệm Dày Nâng Ngực A01 có ảnh thật</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-that-biggben-cao-cap-dn308-p177666546.html?spid=177666552</t>
+          <t>https://tiki.vn/ao-lot-nu-su-duc-hinh-la-khong-gong-dem-day-nang-nguc-a01-co-anh-that-p91973812.html?spid=279055008</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>289000</v>
+        <v>71400</v>
       </c>
       <c r="G24" t="n">
-        <v>380000</v>
+        <v>85000</v>
       </c>
       <c r="H24" t="n">
-        <v>91000</v>
+        <v>13600</v>
       </c>
       <c r="I24" t="n">
-        <v>31.49</v>
+        <v>19.05</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2439,26 +2439,26 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2468,24 +2468,24 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Giá tăng 91,000đ (+31.5%)</t>
+          <t>Giá tăng 13,600đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>250056510</t>
+          <t>275276422</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dép Nam Quai Ngang BIGGBEN Da Bò Thật Cao Cấp DN332</t>
+          <t>Dép tổ ong XANH NGỌC nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-biggben-da-bo-that-cao-cap-dn332-p250056510.html?spid=250056524</t>
+          <t>https://tiki.vn/dep-to-ong-xanh-ngoc-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276422.html?spid=275276428</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2495,26 +2495,26 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>369000</v>
+        <v>63000</v>
       </c>
       <c r="G25" t="n">
-        <v>450000</v>
+        <v>72000</v>
       </c>
       <c r="H25" t="n">
-        <v>81000</v>
+        <v>9000</v>
       </c>
       <c r="I25" t="n">
-        <v>21.95</v>
+        <v>14.29</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2523,26 +2523,26 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2552,24 +2552,24 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Giá tăng 81,000đ (+22.0%)</t>
+          <t>Giá tăng 9,000đ (+14.3%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>59206687</t>
+          <t>275276374</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GIày Sandal Nam Da Bò BIGGBEN Cao Cấp SD105</t>
+          <t>Dép tổ ong XANH RÊU nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-sandal-nam-da-bo-biggben-cao-cap-sd105-p59206687.html?spid=59206699</t>
+          <t>https://tiki.vn/dep-to-ong-xanh-reu-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276374.html?spid=275276386</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2579,26 +2579,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>379000</v>
+        <v>63000</v>
       </c>
       <c r="G26" t="n">
-        <v>439000</v>
+        <v>72000</v>
       </c>
       <c r="H26" t="n">
-        <v>60000</v>
+        <v>9000</v>
       </c>
       <c r="I26" t="n">
-        <v>15.83</v>
+        <v>14.29</v>
       </c>
       <c r="J26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2616,17 +2616,17 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2636,53 +2636,53 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Giá tăng 60,000đ (+15.8%)</t>
+          <t>Giá tăng 9,000đ (+14.3%)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>278872546</t>
+          <t>275252528</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam.Fitted - ROUTINE 10F25TSS039</t>
+          <t>Dép tổ ong VAC nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-fitted-routine-10f25tss039-p278872546.html?spid=278872558</t>
+          <t>https://tiki.vn/dep-to-ong-size-35-43-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-form-lon-nen-lui-1-2-size-p275252528.html?spid=275252615</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="G27" t="n">
-        <v>349000</v>
+        <v>72000</v>
       </c>
       <c r="H27" t="n">
-        <v>349000</v>
+        <v>9000</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2691,53 +2691,53 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 9,000đ (+14.3%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>276094684</t>
+          <t>275276525</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dép Nam Quai Ngang BIGGBEN Da Bò Thật DN356</t>
+          <t>Dép tổ ong XANH CHUỐI nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-biggben-da-bo-that-dn356-p276094684.html?spid=276094690</t>
+          <t>https://tiki.vn/dep-to-ong-xanh-chuoi-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276525.html?spid=275276527</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2747,26 +2747,26 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="G28" t="n">
-        <v>389000</v>
+        <v>72000</v>
       </c>
       <c r="H28" t="n">
-        <v>389000</v>
+        <v>9000</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2775,82 +2775,82 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 9,000đ (+14.3%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>275233185</t>
+          <t>274795145</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Áo Thun ROUTINE Tay Ngắn Dệt Jacquard Phối Nhãn Form Loose - 10S24TSS014 | LASTORE MENSWEAR</t>
+          <t>Dép tổ ong [Size 39-43] KÈM STICKER NGẪU NHIÊN vật liệu EVA cao cấp siêu bền, siêu nhẹ, chống trơn trượt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-routine-tay-ngan-det-jacquard-phoi-nhan-form-loose-10s24tss014-lastore-menswear-p275233185.html?spid=275233197</t>
+          <t>https://tiki.vn/dep-to-ong-size-39-43-kem-sticker-ngau-nhien-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-p274795145.html?spid=274803713</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="G29" t="n">
-        <v>399000</v>
+        <v>77000</v>
       </c>
       <c r="H29" t="n">
-        <v>399000</v>
+        <v>9000</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>13.24</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2859,82 +2859,82 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 9,000đ (+13.2%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>148081201</t>
+          <t>275276468</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Áo Thun RANVERBAE SUMMER RISE Đen</t>
+          <t>Dép tổ ong XANH NAVY nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-ranverbae-summer-rise-den-p148081201.html?spid=148081222</t>
+          <t>https://tiki.vn/dep-to-ong-xanh-navy-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276468.html?spid=275276480</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RANVERBAE</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="G30" t="n">
-        <v>460000</v>
+        <v>72000</v>
       </c>
       <c r="H30" t="n">
-        <v>460000</v>
+        <v>9000</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2943,82 +2943,82 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 9,000đ (+14.3%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>274350557</t>
+          <t>278026014</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hộp 100 Khăn Lau Kính Nano, Chống Bám Hơi Nước, Chống Bụi Bẩn - Khăn Lau Kính Nano Hộp 100 Miếng Giấy Lau Kính Chống Bám Hơi Nước, Lau Sạch Vân Tay Bụi Bẩn</t>
+          <t>ÁO NGỰC SU CÚP NGANG ĐẸP SIZE 34-38 DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-100-khan-lau-kinh-nano-chong-bam-hoi-nuoc-chong-bui-ban-khan-lau-kinh-nano-hop-100-mieng-giay-lau-kinh-chong-bam-hoi-nuoc-lau-sach-van-tay-bui-ban-p274350557.html?spid=274350558</t>
+          <t>https://tiki.vn/ao-nguc-su-cup-ngang-dep-size-34-38-danh-cho-nu-p278026014.html?spid=278026026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>fofaHome</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>17000</v>
+        <v>110000</v>
       </c>
       <c r="H31" t="n">
-        <v>-3000</v>
+        <v>110000</v>
       </c>
       <c r="I31" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3027,82 +3027,82 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Giá giảm 3,000đ (15.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>183895879</t>
+          <t>278016649</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bình xịt lưu hương chống thối chân, khử mùi giày XIMO, kháng khuẩn, công nghệ Bạc ion (VSG08-1)</t>
+          <t>ÁO LÓT BẦU COTTON SIÊU XINH SIZE 38-42 DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/binh-xit-luu-huong-chong-thoi-chan-khu-mui-giay-ximo-khang-khuan-cong-nghe-bac-ion-vsg08-p183895879.html?spid=252869682</t>
+          <t>https://tiki.vn/ao-lot-bau-cotton-sieu-xinh-size-38-42-danh-cho-nu-p278016649.html?spid=278016655</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>66000</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>71000</v>
+        <v>60000</v>
       </c>
       <c r="H32" t="n">
-        <v>5000</v>
+        <v>60000</v>
       </c>
       <c r="I32" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3111,58 +3111,58 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Giá tăng 5,000đ (+7.6%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>192419827</t>
+          <t>74820156</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Khăn Lau Kính Nano Hộp 100 Miếng Giấy Lau Kính Chống Bám Hơi Nước, Lau Sạch Vân Tay Bụi Bẩn</t>
+          <t>ÁO LÓT NỮ MỎNG REN 3 MÓC BIG SIZE 395</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khan-lau-kinh-nano-hop-100-mieng-giay-lau-kinh-chong-bam-hoi-nuoc-lau-sach-van-tay-bui-ban-p192419827.html?spid=278272152</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-ren-3-moc-big-size-395-p74820156.html?spid=74820176</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3171,22 +3171,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>17000</v>
+        <v>105000</v>
       </c>
       <c r="G33" t="n">
-        <v>20000</v>
+        <v>131000</v>
       </c>
       <c r="H33" t="n">
-        <v>3000</v>
+        <v>26000</v>
       </c>
       <c r="I33" t="n">
-        <v>17.65</v>
+        <v>24.76</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K33" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3204,17 +3204,17 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3224,53 +3224,53 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Giá tăng 3,000đ (+17.6%)</t>
+          <t>Giá tăng 26,000đ (+24.8%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>78513044</t>
+          <t>158732070</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Khăn ống cotton tube co giãn 9 kiểu dùng có video hướng dẫn  TUBE01</t>
+          <t>❈✣♚Combo 10 quần lót nữ su đúc cao cấp không đường may, chất mát lạnh, mềm mịn, thoáng</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khan-ong-cotton-tube-co-gian-9-kieu-dung-co-video-huong-dan-tube01-p78513044.html?spid=78518779</t>
+          <t>https://tiki.vn/combo-10-quan-lot-nu-su-duc-cao-cap-khong-duong-may-chat-mat-lanh-mem-min-thoang-p158732070.html?spid=242324041</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Song An Eco</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G34" t="n">
-        <v>15000</v>
+        <v>320000</v>
       </c>
       <c r="H34" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3279,53 +3279,53 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 20,000đ (+6.7%)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>163902369</t>
+          <t>270469469</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Áo Sơ Mi Nam Xanh Dương Kẻ Caro Ngắn Tay Công Sở Trung Niên Thương Hiệu Anton Vải Sợi Tre - YGD566</t>
+          <t>Áo ba lỗ tanktop thể thao bóng rổ 23 premium, vải siêu nhẹ, thoáng mát, thấm hút mồ hôi tốt, màu xanh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nam-xanh-duong-ke-caro-ngan-tay-cong-so-trung-nien-thuong-hieu-anton-vai-soi-tre-ygd566-p163902369.html?spid=163902371</t>
+          <t>https://tiki.vn/ao-ba-lo-tanktop-the-thao-bong-ro-23-premium-vai-sieu-nhe-thoang-mat-tham-hut-mo-hoi-tot-mau-xanh-p270469469.html?spid=270469473</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3335,23 +3335,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SOMIANTON</t>
+          <t>SIMPLE &amp; BASIC</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>355000</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>359000</v>
       </c>
       <c r="H35" t="n">
-        <v>-355000</v>
+        <v>359000</v>
       </c>
       <c r="I35" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3363,16 +3363,16 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3382,60 +3382,60 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>176881225</t>
+          <t>8716200</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Đồ Bơi Nữ Tay Dài Quần Ôm Thân Tôn Dáng AT221 MayHomes Long Sleeves And Long Pants Women Swimwear Set With UPF 50 Sun Protection</t>
+          <t>Băng Đô Cài Tóc Tai Mèo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://tiki.vn/do-boi-nu-tay-dai-quan-om-than-ton-dang-at221-mayhomes-long-sleeves-and-long-pants-women-swimwear-set-with-upf-50-sun-protection-p176881225.html?spid=176881229</t>
+          <t>https://tiki.vn/bang-do-cai-toc-tai-meo-p8716200.html?spid=13151709</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MAYHOMES</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>288000</v>
+        <v>29000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-288000</v>
+        <v>-29000</v>
       </c>
       <c r="I36" t="n">
         <v>-100</v>
       </c>
       <c r="J36" t="n">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3447,16 +3447,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-4.8</v>
+        <v>-4.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -3483,17 +3483,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>269878543</t>
+          <t>278883514</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cuộn 8M Băng Dán Cổ Áo Sơ Mi Chống Bẩn Vải Không Dệt Thoáng Khí Bám Dính Tốt Thấm Hút Mồ Hôi</t>
+          <t>Áo sơ mi xếp 3 li kết ngọc tay dài</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://tiki.vn/cuon-8m-bang-dan-co-ao-so-mi-chong-ban-vai-khong-det-thoang-khi-bam-dinh-tot-tham-hut-mo-hoi-p269878543.html?spid=269878549</t>
+          <t>https://tiki.vn/ao-so-mi-xep-3-li-ket-ngoc-tay-dai-p278883514.html?spid=278883520</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3507,19 +3507,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>39000</v>
+        <v>125000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-39000</v>
+        <v>-125000</v>
       </c>
       <c r="I37" t="n">
         <v>-100</v>
       </c>
       <c r="J37" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3531,16 +3531,16 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-4.3</v>
+        <v>-0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -3567,46 +3567,46 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6535821</t>
+          <t>275276260</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quần Lót Nữ - Quần Đùi Mặc Trong Váy Su Thông Hơi</t>
+          <t>Dép tổ ong ĐỎ nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nu-quan-dui-mac-trong-vay-su-thong-hoi-p6535821.html?spid=51154654</t>
+          <t>https://tiki.vn/dep-to-ong-do-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276260.html?spid=275276262</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>42000</v>
+        <v>63000</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="H38" t="n">
-        <v>-42000</v>
+        <v>9000</v>
       </c>
       <c r="I38" t="n">
-        <v>-100</v>
+        <v>14.29</v>
       </c>
       <c r="J38" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3615,53 +3615,53 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
-        <v>-4.7</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 9,000đ (+14.3%)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>273611089</t>
+          <t>274804274</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xi Đánh Bóng Giày Da Làm Bóng Nhanh Đồ Da, Xi Kem Dưỡng Da Có Đầu Mút Hỗ Trợ - HÀNG CHÍNH HÃNG MINIIN</t>
+          <t>Dép tổ ong [Size 31-34] KÈM STICKER NGẪU NHIÊN vật liệu EVA cao cấp siêu bền, siêu nhẹ, chống trơn trượt</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://tiki.vn/xi-danh-bong-giay-da-lam-bong-nhanh-do-da-xi-kem-duong-da-co-da-u-mu-t-ho-tro-hang-chinh-hang-miniin-p273611089.html?spid=273611093</t>
+          <t>https://tiki.vn/dep-to-ong-size-31-34-kem-sticker-ngau-nhien-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-p274804274.html?spid=274804515</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3671,26 +3671,26 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MINIIN</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="H39" t="n">
-        <v>-35000</v>
+        <v>5000</v>
       </c>
       <c r="I39" t="n">
-        <v>-100</v>
+        <v>8.33</v>
       </c>
       <c r="J39" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3699,16 +3699,16 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-3.6</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3718,34 +3718,34 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 5,000đ (+8.3%)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>107491961</t>
+          <t>275276334</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dép Nam Quai Ngang Da Bò BIGGBEN Cao Cấp DN283</t>
+          <t>Dép tổ ong XÁM nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-biggben-cao-cap-dn283-p107491961.html?spid=107491965</t>
+          <t>https://tiki.vn/dep-to-ong-xam-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276334.html?spid=275276338</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3755,26 +3755,26 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>319000</v>
+        <v>63000</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="H40" t="n">
-        <v>-319000</v>
+        <v>9000</v>
       </c>
       <c r="I40" t="n">
-        <v>-100</v>
+        <v>14.29</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3783,82 +3783,82 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 9,000đ (+14.3%)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>275933718</t>
+          <t>274350557</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Giày Sneaker Vải Canvas Nam Nữ E18 White Dincox Shoes Sang Trọng</t>
+          <t>Hộp 100 Khăn Lau Kính Nano, Chống Bám Hơi Nước, Chống Bụi Bẩn - Khăn Lau Kính Nano Hộp 100 Miếng Giấy Lau Kính Chống Bám Hơi Nước, Lau Sạch Vân Tay Bụi Bẩn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-sneaker-vai-canvas-nam-nu-e18-white-dincox-shoes-sang-trong-p275933718.html?spid=275933722</t>
+          <t>https://tiki.vn/hop-100-khan-lau-kinh-nano-chong-bam-hoi-nuoc-chong-bui-ban-khan-lau-kinh-nano-hop-100-mieng-giay-lau-kinh-chong-bam-hoi-nuoc-lau-sach-van-tay-bui-ban-p274350557.html?spid=274350558</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DINCOX</t>
+          <t>fofaHome</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>490000</v>
+        <v>17000</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H41" t="n">
-        <v>-490000</v>
+        <v>3000</v>
       </c>
       <c r="I41" t="n">
-        <v>-100</v>
+        <v>17.65</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3867,79 +3867,79 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P41" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 3,000đ (+17.6%)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>253306906</t>
+          <t>279399528</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Đón gót giầy gỗ</t>
+          <t>KHĂN LỤA DÀI KHĂN QUÀNG CỔ KHĂN CHOÀNG LỤA BĂNG ĐÔ TRANG TRÍ NƠ CAO CẤP ĐA NĂNG SANG TRỌNG THANH LỊCH MÃ 18-38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://tiki.vn/don-got-giay-p253306906.html?spid=253306912</t>
+          <t>https://tiki.vn/khan-lua-dai-khan-quang-co-khan-choang-lua-bang-do-trang-tri-no-cao-cap-da-nang-sang-trong-thanh-lich-ma-18-38-p279399528.html?spid=279399560</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DAICAT</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>159000</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="H42" t="n">
-        <v>-159000</v>
+        <v>120000</v>
       </c>
       <c r="I42" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3970,34 +3970,34 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>154852782</t>
+          <t>275276309</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Giày Lười, Giày Mọi Nam Da Bò SUNPOLO CS5052 (Đen, Nâu)</t>
+          <t>Dép tổ ong ĐEN nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-luoi-nam-da-bo-sunpolo-su5052-den-nau-p154852782.html?spid=154852796</t>
+          <t>https://tiki.vn/dep-to-ong-den-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276309.html?spid=275276325</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4007,26 +4007,26 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SUNPOLO</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1100000</v>
+        <v>63000</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="H43" t="n">
-        <v>-1100000</v>
+        <v>9000</v>
       </c>
       <c r="I43" t="n">
-        <v>-100</v>
+        <v>14.29</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -4035,16 +4035,16 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -4054,57 +4054,57 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 9,000đ (+14.3%)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>279068959</t>
+          <t>278064718</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam sọc ngang. Regular - ROUTINE 10F25TSS036</t>
+          <t>KHẨU TRANG COTTON KHÁNG KHUẨN CHÓNG TIA UV DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-soc-ngang-regular-routine-10f25tss036-p279068959.html?spid=279068973</t>
+          <t>https://tiki.vn/khau-trang-cotton-khang-khuan-chong-tia-uv-danh-cho-nu-p278064718.html?spid=278064724</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>379000</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="H44" t="n">
-        <v>-379000</v>
+        <v>34000</v>
       </c>
       <c r="I44" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -4138,57 +4138,57 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>66095198</t>
+          <t>278423322</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Áo phông cổ tim ALIGRO ALGAPC051</t>
+          <t>Dép quai ngang Biti's nam (39-44)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-phong-co-tim-aligro-algapc051-p66095198.html?spid=66095200</t>
+          <t>https://tiki.vn/dep-quai-ngang-biti-s-nam-39-44-p278423322.html?spid=278423326</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aligro</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>465000</v>
       </c>
       <c r="H45" t="n">
-        <v>-150000</v>
+        <v>465000</v>
       </c>
       <c r="I45" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -4222,34 +4222,34 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>66083356</t>
+          <t>275878934</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Áo phông cổ tròn ALIGRO ALGAPC044</t>
+          <t>Áo chống nắng nam thun lạnh thoáng mát chống tia UV cao cấp UPF50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-phong-co-tron-aligro-algapc044-p66083356.html?spid=66083362</t>
+          <t>https://tiki.vn/ao-chong-nang-nam-cao-cap-thong-hoi-chong-nang-chong-tia-uv-chong-bam-bui-fmtht024-p275878934.html?spid=275878936</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4259,23 +4259,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aligro</t>
+          <t>LuckyJQR</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>150000</v>
+        <v>180000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-150000</v>
+        <v>-180000</v>
       </c>
       <c r="I46" t="n">
         <v>-100</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -4323,43 +4323,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>277811866</t>
+          <t>276348729</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BỘ Găng Tay Bao Tay Ống Chống Nắng Cao Cấp Unisex MÀU XÁM</t>
+          <t>Quần Lót Nam Boxer Relax - Quần Sịp Chất Thun Lạnh Thoải Mái Tặng Vớ Khi Mua Combo 2 Quần</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khan-trum-dau-ninja-fullface-chong-nang-mau-den-p277811866.html?spid=277811867</t>
+          <t>https://tiki.vn/quan-lot-nam-boxer-relax-quan-sip-chat-thun-lanh-thoai-mai-tang-vo-khi-mua-combo-2-quan-p276348729.html?spid=276348760</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LuckyJQR</t>
+          <t>Relax</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>100000</v>
+        <v>114000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-100000</v>
+        <v>-114000</v>
       </c>
       <c r="I47" t="n">
         <v>-100</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -4371,16 +4371,16 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -4407,84 +4407,1680 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>102151424</t>
+          <t>59079180</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kính mát nam EXFASH EF38973 thời trang (62/14/145)</t>
+          <t>ÁO KHOÁC LEN NAM CÀI NÚT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://tiki.vn/kinh-mat-nam-exfash-ef38973-thoi-trang-62-14-145-p102151424.html?spid=102151428</t>
+          <t>https://tiki.vn/ao-khoac-len-nam-cai-nut-p59079180.html?spid=113225866</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Exfash</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>529000</v>
+        <v>325750</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-529000</v>
+        <v>-325750</v>
       </c>
       <c r="I48" t="n">
         <v>-100</v>
       </c>
       <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>274894622</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Quần tây nam 1 ly Khatoco Q1M528R1-INDE305-2503-1-ĐEN</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-tay-nam-1-ly-khatoco-q1m528r1-inde305-2503-1-den-p274894622.html?spid=274894626</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KHATOCO </t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>422400</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-422400</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>274948189</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Đồ bơi nữ trung niên cho mẹ cho bà, áo tắm người già trung tuổi, có size lớn tránh lộ bụng, mẫu trẻ trung thanh lịch, dễ mặc, chất bơi mát mịn đẹp | KT009</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-boi-nu-trung-nien-cho-me-cho-ba-ao-tam-nguoi-gia-trung-tuoi-co-size-lon-tranh-lo-bung-mau-tre-trung-thanh-lich-de-mac-chat-boi-mat-min-dep-kt009-p274948189.html?spid=274948209</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-420000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J50" t="n">
         <v>2</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>59205406</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>COMBO 5 ÁO LÁ NGẮN THUN LỤA MẶT TRƯỚC 2 LỚP DÀNH CHO HỌC SINH</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-5-ao-la-ngan-thun-lua-mat-truoc-2-lop-danh-cho-hoc-sinh-p59205406.html?spid=59205408</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>101400</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-101400</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J51" t="n">
+        <v>92</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>29</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>24350235</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cài Tóc Tai Mèo Dễ Thương</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/cai-toc-tai-meo-de-thuong-p24350235.html?spid=55201698</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J52" t="n">
+        <v>86</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>17</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>162562752</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Combo 10 quần lót nữ chất liệu cotton chất đẹp</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-10-quan-lot-nu-chat-lieu-cotton-chat-dep-p162562752.html?spid=162562761</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>134400</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-134400</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>278012594</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Quần Gen Định Hình Bụng Khóa Kéo Phối Ren Quyến Rũ 2055 – Eo Thon, Bụng Phẳng, Tự Tin Mỗi Ngày</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-gen-dinh-hinh-bung-khoa-keo-phoi-ren-quyen-ru-2055-eo-thon-bung-phang-tu-tin-moi-ngay-p278012594.html?spid=278592879</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>277274436</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Set áo cổ tròn sát nách phối quần ống suông thanh lịch</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/set-ao-co-tron-sat-nach-phoi-quan-ong-suong-thanh-lich-p277274436.html?spid=277274444</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>276303219</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bộ Váy Thể Thao Nữ Gồm Áo Thun Và Váy 2 Lớp Sành Điệu</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-vay-the-thao-nu-gom-ao-thun-va-vay-2-lop-sanh-dieu-p276303219.html?spid=276306416</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>239000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-239000</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>276147904</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Quần lót nữ ren sexy</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-lot-nu-ren-sexy-p276147904.html?spid=276147905</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>FTAKY</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>273388482</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Combo 7 quần lót cotton nữ nhiều màu du lịch dùng 1 lần</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-7-quan-lot-cotton-nu-nhieu-mau-du-lich-dung-1-lan-p273388482.html?spid=273388612</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>169000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-169000</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J58" t="n">
+        <v>33</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>182481410</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Áo sơ mi nữ tay lỡ cổ đức, họa tiết thêu hoa tinh tế, chất liệu Đũi mềm mát co giãn nhẹ, form đẹp NeSa Shop SMH.55</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-so-mi-nu-tay-lo-co-duc-hoa-tiet-theu-hoa-tinh-te-chat-lieu-dui-mem-mat-co-gian-nhe-form-dep-nesa-shop-smh-55-p182481410.html?spid=182481432</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>145000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-145000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>17</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>7</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>212048690</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NHIỀU MẪU Ghim cài áo đính đá xích cao cấp - ghim cài vest cưới Tien Nguyen</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/nhieu-mau-ghim-cai-ao-dinh-da-xich-cao-cap-ghim-cai-vest-cuoi-tien-nguyen-p212048690.html?spid=212048699</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>159000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-159000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
         <v>5</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
         <v>-5</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q60" t="n">
         <v>1</v>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
         <is>
           <t>❌ Đã xóa</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>165256024</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mũ phớt cao bồi Fedora Classic nỉ MP021 cao cấp cho nam và nữ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/mu-phot-cao-boi-fedora-classic-ni-mp021-cao-cap-cho-nam-va-nu-p165256024.html?spid=165256026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	OEM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>145000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-145000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J61" t="n">
+        <v>8</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>14815744</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Chân Váy Serena</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/chan-vay-serena-p14815744.html?spid=14815760</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>135000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-135000</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J62" t="n">
+        <v>60</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>15</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>275262532</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Giày Sandal Nam Nữ Chất Liệu Nhựa EVA Mềm, Nhẹ, Êm Chân, Thoải Mái, Chống Trơn Trượt (FORM LỚN ĐẶT LÙI 1 SIZE) Giày đi học - Giày đi làm - Giày đi chơi</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-sandal-nam-chat-lieu-nhua-eva-mem-nhe-em-chan-thoai-mai-chong-tron-truot-p275262532.html?spid=279226521</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VAC </t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>220000</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-220000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J63" t="n">
+        <v>18</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>275276585</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Dép tổ ong KEM nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/dep-to-ong-kem-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276585.html?spid=275276595</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VAC </t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>63000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>72000</v>
+      </c>
+      <c r="H64" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="J64" t="n">
+        <v>87</v>
+      </c>
+      <c r="K64" t="n">
+        <v>86</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>-72000</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O64" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>5</v>
+      </c>
+      <c r="R64" t="n">
+        <v>5</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Giá tăng 9,000đ (+14.3%) | Bán thêm -1 sản phẩm</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>67538621</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538625</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>May 10</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>135000</v>
+      </c>
+      <c r="G65" t="n">
+        <v>135000</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>16592</v>
+      </c>
+      <c r="K65" t="n">
+        <v>16590</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-270000</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>4842</v>
+      </c>
+      <c r="R65" t="n">
+        <v>4842</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Bán thêm -2 sản phẩm</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>262691682</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mũ Lưỡi Trai Chóp Vuông Jeep, Nón Kết Chóp Phẳng Màu Đen, Xanh Than M189</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/mu-luoi-trai-chop-vuong-jeep-non-ket-chop-phang-mau-den-xanh-than-m189-p262691682.html?spid=262691684</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>350000</v>
+      </c>
+      <c r="G66" t="n">
+        <v>350000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>6</v>
+      </c>
+      <c r="K66" t="n">
+        <v>5</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>-350000</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
+      </c>
+      <c r="O66" t="n">
+        <v>5</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Bán thêm -1 sản phẩm</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>275276395</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Dép tổ ong TRẮNG nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/dep-to-ong-trangvat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276395.html?spid=275276403</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VAC </t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>63000</v>
+      </c>
+      <c r="G67" t="n">
+        <v>72000</v>
+      </c>
+      <c r="H67" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I67" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="J67" t="n">
+        <v>36</v>
+      </c>
+      <c r="K67" t="n">
+        <v>30</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-432000</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>5</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>3</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Giá tăng 9,000đ (+14.3%) | Bán thêm -6 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>278028606</t>
+          <t>193978418</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KHẨU TRANG UV LOẠI 1 CHỐNG TIA UV</t>
+          <t>Quần Jean nam Leman xám khói trơn JD13 - Slim Form</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khau-trang-uv-loai-1-chong-tia-uv-p278028606.html?spid=278028610</t>
+          <t>https://tiki.vn/quan-jean-nam-leman-xam-khoi-tron-jd13-slim-form-p193978418.html?spid=193978434</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Leman</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>60000</v>
+        <v>549000</v>
       </c>
       <c r="H2" t="n">
-        <v>60000</v>
+        <v>549000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="L2" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="M2" t="n">
-        <v>1560000</v>
+        <v>34038000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,37 +627,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>279104033</t>
+          <t>2710151</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Áo lót nữ form ba lỗ thông hơi trơn big size 1397 – Size XXL–3XL</t>
+          <t>Lót giày sức khỏe Spenco Total Support Thin 46-696 cho giày thể thao, công sở nâng vòm hỗ trợ giảm mỏi chân khi đi nhiều, đứng lâu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-form-ba-lo-thong-hoi-tron-big-size-1397-size-xxl-3xl-p279104033.html?spid=279104035</t>
+          <t>https://tiki.vn/lot-giay-cong-so-giam-dau-moi-chan-spenco-total-suport-thin-46-696-p2710151.html?spid=2710155</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Spenco</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>99000</v>
+        <v>895000</v>
       </c>
       <c r="H3" t="n">
-        <v>99000</v>
+        <v>895000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,13 +666,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="M3" t="n">
-        <v>594000</v>
+        <v>17005000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -687,14 +687,14 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,37 +711,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>278015269</t>
+          <t>276634531</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QUẦN SỊP THÔNG HƠI LƯỚI NHỎ TỪ 48-100KG DÀNH CHO NAM</t>
+          <t>Keo Dán Giày Thể Thao Sêu Dính Dùng Nhiệt Trong Suốt Không Tổn Thương Da, Keo Dính Giày Đa Năng Siêu Bền Chống Nước Tốt Xanh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-sip-thong-hoi-luoi-nho-tu-48-100kg-danh-cho-nam-p278015269.html?spid=278015277</t>
+          <t>https://tiki.vn/keo-dan-giay-the-thao-seu-dinh-dung-nhiet-trong-suot-khong-ton-thuong-da-keo-dinh-giay-da-nang-sieu-ben-chong-nuoc-tot-p276634531.html?spid=276634532</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>LuckyJQR</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>42000</v>
+        <v>160000</v>
       </c>
       <c r="H4" t="n">
-        <v>42000</v>
+        <v>160000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,35 +750,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>504000</v>
+        <v>5600000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,37 +795,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>278034638</t>
+          <t>275262532</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ÁO LÁ BRA HỌC SINH CHẤT COTTON MÁT KHÔNG MÚT TỪ 8-13 TUỔI DƯỚI 50KG DÀNH CHO NỮ</t>
+          <t>Giày Sandal Nam Nữ Chất Liệu Nhựa EVA Mềm, Nhẹ, Êm Chân, Thoải Mái, Chống Trơn Trượt (FORM LỚN ĐẶT LÙI 1 SIZE) Giày đi học - Giày đi làm - Giày đi chơi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-la-bra-hoc-sinh-chat-cotton-mat-khong-mut-duoi-50kg-danh-cho-nu-p278034638.html?spid=278034640</t>
+          <t>https://tiki.vn/giay-sandal-nam-chat-lieu-nhua-eva-mem-nhe-em-chan-thoai-mai-chong-tron-truot-p275262532.html?spid=279226513</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>62000</v>
+        <v>140000</v>
       </c>
       <c r="H5" t="n">
-        <v>62000</v>
+        <v>140000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -834,13 +834,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M5" t="n">
-        <v>372000</v>
+        <v>2520000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -879,121 +879,121 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>275276220</t>
+          <t>277347854</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dép tổ ong CAM nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Thắt lưng nữ DA BÒ THẬT - BEE GEE N8051</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-cam-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276220.html?spid=275276222</t>
+          <t>https://tiki.vn/that-lung-nu-da-bo-that-bee-gee-n8051-p277347854.html?spid=277347856</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>Bee Gee</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>72000</v>
+        <v>150000</v>
       </c>
       <c r="H6" t="n">
-        <v>9000</v>
+        <v>150000</v>
       </c>
       <c r="I6" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>360000</v>
+        <v>1500000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Giá tăng 9,000đ (+14.3%) | Bán thêm +5 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>278008741</t>
+          <t>140836685</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIẾNG DÁN NGỰC HÌNH HOA SILICON CỰC CHẮC VÀ XINH DÀNH CHO NỮ - HỘP</t>
+          <t>Giày Lười Nam Da Bò SUNPOLO MU2588 (Xanh Navy)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mieng-dan-nguc-hinh-hoa-silicon-cuc-chac-va-xinh-danh-cho-nu-p278008741.html?spid=278008743</t>
+          <t>https://tiki.vn/giay-luoi-nam-da-bo-sunpolo-mu2588-xanh-navy-p140836685.html?spid=140836687</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>SUNPOLO</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>57000</v>
+        <v>1200000</v>
       </c>
       <c r="H7" t="n">
-        <v>57000</v>
+        <v>1200000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1002,13 +1002,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>342000</v>
+        <v>1200000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,17 +1047,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>31637590</t>
+          <t>52184516</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Combo 4 quần lót nam tam giác Bamboo Organic mềm mịn thoáng mát thấm hút mồ hôi - MRM Manlywear - Màu Ngẫu Nhiên</t>
+          <t>Combo 3 quần lót nam Boxer sợi Organic mềm mịn thoáng mát co giãn 4 chiều MRM Manlywear ( TẶNG Đôi Tất Nam Cao Cấp Giao Ngẫu Nhiên)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-4-qua-n-lo-t-nam-tam-gia-c-bamboo-organic-me-m-mi-n-thoa-ng-ma-t-tha-m-hu-t-mo-hoi-mrm-manlywear-ma-u-nga-u-nhien-p31637590.html?spid=31637602</t>
+          <t>https://tiki.vn/combo-3-qua-n-lo-t-nam-boxer-so-i-cotton-organic-me-m-mi-n-thoa-ng-ma-t-co-gia-n-4-chie-u-mrm-manlywear-tang-doi-tat-nam-cao-cap-giao-ngau-nhien-p52184516.html?spid=52184518</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>249000</v>
+        <v>199000</v>
       </c>
       <c r="G8" t="n">
-        <v>249000</v>
+        <v>199000</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1083,38 +1083,38 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3772</v>
+        <v>4333</v>
       </c>
       <c r="K8" t="n">
-        <v>3773</v>
+        <v>4339</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>249000</v>
+        <v>1194000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>910</v>
+        <v>1245</v>
       </c>
       <c r="R8" t="n">
-        <v>910</v>
+        <v>1245</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1124,59 +1124,59 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Bán thêm +6 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>277541813</t>
+          <t>16375016</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Găng Tay Chống Nắng Dài Vừa Phải, Chống Trượt Thời Trang Mùa Hè, Đàn Hồi - HÀNG CHÍNH HÃNG MINIIN</t>
+          <t>COMBO HỘP 5 Quần Lót ĐÙI Nam Xuất Nhật Cao Cấp (MIX NGẪU NHIÊN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/gang-tay-chong-nang-dai-vua-phai-chong-truot-thoi-trang-mua-he-dan-hoi-hang-chinh-hang-miniin-p277541813.html?spid=277541823</t>
+          <t>https://tiki.vn/combo-hop-5-quan-lot-dui-nam-xuat-nhat-cao-cap-mix-ngau-nhien-p16375016.html?spid=277961877</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MINIIN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>49000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>49000</v>
+        <v>251000</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>251000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>196000</v>
+        <v>753000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1198,118 +1198,118 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Bán thêm +4 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>278945498</t>
+          <t>275276468</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SET 5 ĐÔI TẤT VỚ NỮ CAO CỔ MÃ 17 DÀNH CHO NỮ</t>
+          <t>Dép tổ ong XANH NAVY nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-5-doi-tat-vo-nu-cao-co-ma-17-danh-cho-nu-p278945498.html?spid=278945500</t>
+          <t>https://tiki.vn/dep-to-ong-xanh-navy-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276468.html?spid=275276484</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="G10" t="n">
-        <v>100000</v>
+        <v>72000</v>
       </c>
       <c r="H10" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>720000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +10 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>278011349</t>
+          <t>278000485</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>QUẦN ĐỘN MÔNG ĐỊNH HÌNH TỪ 40-70KG DÀNH CHO NỮ</t>
+          <t>Áo lót nữ 718 – Mút mỏng thông hơi, không gọng, cài sau 3 móc, co giãn thoải mái</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-don-mong-dinh-hinh-tu-40-70kg-danh-cho-nu-p278011349.html?spid=278011357</t>
+          <t>https://tiki.vn/ao-lot-nu-718-mut-mong-thong-hoi-khong-gong-cai-sau-3-moc-co-gian-thoai-mai-p278000485.html?spid=278000491</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1323,28 +1323,28 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="G11" t="n">
-        <v>85000</v>
+        <v>100000</v>
       </c>
       <c r="H11" t="n">
-        <v>85000</v>
+        <v>20000</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>85000</v>
+        <v>600000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1366,91 +1366,91 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 20,000đ (+25.0%) | Bán thêm +6 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>192985737</t>
+          <t>278092142</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Móc Cài Tai Silicon Siêu Dẻo, Giúp Giữ Gọng Kính Không Bị Tuột Khi Chạy, Nhảy, Chơi Thể Thao, Màu Đen, Trong Suốt</t>
+          <t>Quần kiểu nữ ống rộng, chất liệu vải Đũi xước, mềm mịn, mặc mát, Quần Short nữ đẹp Nesa Shop</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/moc-cai-tai-silicon-sieu-deo-giup-giu-gong-kinh-khong-bi-tuot-khi-chay-nhay-choi-the-thao-mau-den-trong-suot-p192985737.html?spid=192985738</t>
+          <t>https://tiki.vn/quan-kieu-nu-ong-rong-chat-lieu-vai-dui-xuoc-mem-min-mac-mat-quan-short-nu-dep-nesa-shop-p278092142.html?spid=278092148</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Blue Light</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10000</v>
+        <v>55000</v>
       </c>
       <c r="G12" t="n">
-        <v>10000</v>
+        <v>49000</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-10.91</v>
       </c>
       <c r="J12" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>161</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>392000</v>
+      </c>
+      <c r="N12" t="n">
         <v>5</v>
       </c>
-      <c r="M12" t="n">
-        <v>50000</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.8</v>
-      </c>
       <c r="O12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1460,41 +1460,41 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Bán thêm +5 sản phẩm</t>
+          <t>Giá giảm 6,000đ (10.9%) | Bán thêm +8 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>252533129</t>
+          <t>67538621</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Găng Tay Hở 2 Ngón Unisex Chống Nắng, Có Thể Sử Dụng Cảm Ứng Điện Thoại</t>
+          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/gang-tay-ho-2-ngon-unisex-chong-nang-co-the-su-dung-cam-ung-dien-thoai-p252533129.html?spid=252533130</t>
+          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538631</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>May 10</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49000</v>
+        <v>135000</v>
       </c>
       <c r="G13" t="n">
-        <v>49000</v>
+        <v>135000</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1503,38 +1503,38 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>161</v>
+        <v>16590</v>
       </c>
       <c r="K13" t="n">
-        <v>162</v>
+        <v>16592</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>49000</v>
+        <v>270000</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>4842</v>
       </c>
       <c r="R13" t="n">
-        <v>19</v>
+        <v>4842</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,197 +1544,197 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Bán thêm +2 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>167461360</t>
+          <t>275738156</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Đồ bơi bigsize nữ, áo tắm cộc tay cùng quần boxer cho người béo mập, mẫu thể thao khỏe khoắn, chất đẹp phom đẹp | KT110</t>
+          <t>Mặt Khóa Thắt Lưng Nam Cao Cấp,Mặt Thắt Lưng Nam Khóa Tự Động 203851</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/do-boi-bigsize-nu-ao-tam-coc-tay-cung-quan-boxer-cho-nguoi-beo-map-mau-the-thao-khoe-khoan-chat-dep-phom-dep-kt110-p167461360.html?spid=195949767</t>
+          <t>https://tiki.vn/mat-khoa-that-lung-nam-cao-cap-mat-that-lung-nam-khoa-tu-dong-203851-p275738156.html?spid=275738157</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>TLG Thành Long</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>460000</v>
+        <v>61250</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>61250</v>
       </c>
       <c r="H14" t="n">
-        <v>-460000</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>61250</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.7</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>278012255</t>
+          <t>192985737</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>QUẦN LÓT LỤA SIÊU ĐẸP CAO CẤP PHỐI REN TỪ 40-70KG DÀNH CHO NỮ</t>
+          <t>Móc Cài Tai Silicon Siêu Dẻo, Giúp Giữ Gọng Kính Không Bị Tuột Khi Chạy, Nhảy, Chơi Thể Thao, Màu Đen, Trong Suốt</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-lua-sieu-dep-cao-cap-phoi-ren-tu-40-70kg-danh-cho-nu-p278012255.html?spid=278012271</t>
+          <t>https://tiki.vn/moc-cai-tai-silicon-sieu-deo-giup-giu-gong-kinh-khong-bi-tuot-khi-chay-nhay-choi-the-thao-mau-den-trong-suot-p192985737.html?spid=192985738</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Blue Light</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G15" t="n">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="H15" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +6 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>278012626</t>
+          <t>140429170</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>QUẦN LÓT SU THÔNG HƠI SIÊU ĐẸP SIÊU MỎNG TỪ 40-60KG DÀNH CHO NỮ</t>
+          <t>Bao tay chơi game găng tay 2 ngón cảm ứng điện thoại gamemobile BT01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-su-thong-hoi-sieu-dep-sieu-mong-tu-40-60kg-danh-cho-nu-p278012626.html?spid=278012638</t>
+          <t>https://tiki.vn/bao-tay-choi-game-gang-tay-2-ngon-cam-ung-dien-thoai-gamemobile-bt01-p140429170.html?spid=198934954</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1743,28 +1743,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="G16" t="n">
-        <v>38000</v>
+        <v>9999</v>
       </c>
       <c r="H16" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1786,39 +1786,39 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>74421501</t>
+          <t>278021672</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
+          <t>Quần Lót Nam Đùi Boxer Lụa Băng Menpro MP9 - Mỏng nhem Thoáng Khí</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421539</t>
+          <t>https://tiki.vn/quan-lot-nam-dui-boxer-lua-bang-menpro-mp9-mong-nhem-thoang-khi-p278021672.html?spid=278021702</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>118690</v>
+        <v>63200</v>
       </c>
       <c r="G17" t="n">
-        <v>150000</v>
+        <v>79000</v>
       </c>
       <c r="H17" t="n">
-        <v>31310</v>
+        <v>15800</v>
       </c>
       <c r="I17" t="n">
-        <v>26.38</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1851,26 +1851,26 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1880,24 +1880,24 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá tăng 31,310đ (+26.4%)</t>
+          <t>Giá tăng 15,800đ (+25.0%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>278071763</t>
+          <t>2212215</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quần sịp nam thông hơi mát lạnh từ 40-100kg dành cho nam</t>
+          <t>Combo 04 quần lót nam Pro Ben bảng nhỏ MS914</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-sip-nam-thong-hoi-mat-lanh-tu-50-100kg-danh-cho-nam-p278071763.html?spid=278071767</t>
+          <t>https://tiki.vn/combo-04-quan-lot-nam-pro-ben-bang-nho-ms914-p2212215.html?spid=53788047</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1907,26 +1907,26 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Pro Ben</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>135520</v>
       </c>
       <c r="G18" t="n">
-        <v>94000</v>
+        <v>176000</v>
       </c>
       <c r="H18" t="n">
-        <v>94000</v>
+        <v>40480</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>29.87</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1935,53 +1935,53 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 40,480đ (+29.9%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>278014106</t>
+          <t>244297794</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>QUẦN SỊP CHÉO COTTON CAO CẤP MỀM MỊN TỪ 40-85KG DÀNH CHO NAM</t>
+          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-sip-cheo-cotton-cao-cap-mem-min-tu-48-85kg-danh-cho-nam-p278014106.html?spid=279145394</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="G19" t="n">
-        <v>60000</v>
+        <v>159600</v>
       </c>
       <c r="H19" t="n">
-        <v>60000</v>
+        <v>-30400</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,53 +2019,53 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 30,400đ (16.0%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>278009461</t>
+          <t>277983818</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ÁO NGỰC BRA ĐẸP QUYẾN RŨ SIZE TỪ 36-40 DÀNH CHO NỮ</t>
+          <t>Áo Lót Nữ Ren Dày Cài Trước Có Gọng Nâng Ngực Belle VC02 – Combo Đa Màu, Đệm Mút 3 cm, Quyến Rũ &amp; Đỡ Đỡ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-bra-dep-quyen-ru-size-tu-36-40-danh-cho-nu-p278009461.html?spid=278009479</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-day-cai-truoc-co-gong-nang-nguc-belle-vc02-combo-da-mau-dem-mut-3-cm-quyen-ru-do-do-p277983818.html?spid=277983822</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2079,16 +2079,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>126000</v>
       </c>
       <c r="G20" t="n">
-        <v>110000</v>
+        <v>150000</v>
       </c>
       <c r="H20" t="n">
-        <v>110000</v>
+        <v>24000</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>19.05</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2122,63 +2122,63 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 24,000đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>279004066</t>
+          <t>115852451</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>QUẦN ĐỘN MÔNG ĐỊNH HÌNH SIÊU ĐẸP TỪ 40-75KG DÀNH CHO NỮ</t>
+          <t>Chai vệ sinh giày đồ da, túi ví, áo, ghế da giúp làm sạch, dưỡng ẩm chống mốc XIMO XI03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-don-mong-dinh-hinh-sieu-dep-tu-40-75kg-danh-cho-nu-p279004066.html?spid=279004070</t>
+          <t>https://tiki.vn/chai-ve-sinh-giay-do-da-tui-vi-ao-ghe-da-giup-lam-sach-duong-am-chong-moc-ximo-xi03-p115852451.html?spid=262784198</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="G21" t="n">
-        <v>115000</v>
+        <v>70000</v>
       </c>
       <c r="H21" t="n">
-        <v>115000</v>
+        <v>-5000</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-6.67</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2187,53 +2187,53 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 5,000đ (6.7%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>278026067</t>
+          <t>277610005</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ÁO CHỐNG NẮNG MỀM MÁT TỪ 40-60KG DÀNH CHO NỮ</t>
+          <t>Áo Lót 3281 Không Gọng Mút Mỏng Bản 3 Móc Che Khuyết Điểm Đẹp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-chong-nang-mem-mat-tu-40-60kg-danh-cho-nu-p278026067.html?spid=278026069</t>
+          <t>https://tiki.vn/ao-lot-3281-khong-gong-mut-mong-ban-3-moc-che-khuyet-diem-dep-p277610005.html?spid=277610035</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Sanny House</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>110000</v>
+        <v>96000</v>
       </c>
       <c r="H22" t="n">
-        <v>110000</v>
+        <v>96000</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2307,17 +2307,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>278013980</t>
+          <t>277969210</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>QUẦN ĐÙI CK HOT HIT CÁ TÍNH TỪ 40-70KG DÀNH CHO NỮ</t>
+          <t>Combo 5 quần lót nữ lọt khe lụa trơn Voronin Q8289 – Mềm mịn, ôm dáng</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-dui-ck-hot-hit-ca-tinh-tu-40-70kg-danh-cho-nu-p278013980.html?spid=278021323</t>
+          <t>https://tiki.vn/combo-5-quan-lot-khe-nu-bang-lua-tron-lien-mach-voronin-q8289-p277969210.html?spid=277969212</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2331,22 +2331,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>205800</v>
       </c>
       <c r="G23" t="n">
-        <v>75000</v>
+        <v>245000</v>
       </c>
       <c r="H23" t="n">
-        <v>75000</v>
+        <v>39200</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>19.05</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2374,34 +2374,34 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 39,200đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>91973812</t>
+          <t>277919931</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Su Đúc Hình Lá Không Gọng Đệm Dày Nâng Ngực A01 có ảnh thật</t>
+          <t>Combo 5 quần lót nữ thun lạnh thông hơi Voronin 2067 – Mát mịn, co giãn 4 chiều, không hằn viền</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-su-duc-hinh-la-khong-gong-dem-day-nang-nguc-a01-co-anh-that-p91973812.html?spid=279055008</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nu-thun-lanh-thong-hoi-voronin-2067-mat-min-co-gian-4-chieu-khong-han-vien-p277919931.html?spid=277919932</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2415,22 +2415,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>71400</v>
+        <v>159600</v>
       </c>
       <c r="G24" t="n">
-        <v>85000</v>
+        <v>190000</v>
       </c>
       <c r="H24" t="n">
-        <v>13600</v>
+        <v>30400</v>
       </c>
       <c r="I24" t="n">
         <v>19.05</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2468,53 +2468,53 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Giá tăng 13,600đ (+19.0%)</t>
+          <t>Giá tăng 30,400đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>275276422</t>
+          <t>199996713</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dép tổ ong XANH NGỌC nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Quần Âu Nam Công Sở Thương Hiệu Anton Cao Cấp Xếp ly, Chỉnh Cạp Màu Nâu- QA102</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-xanh-ngoc-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276422.html?spid=275276428</t>
+          <t>https://tiki.vn/quan-au-nam-cong-so-thuong-hieu-anton-cao-cap-xep-ly-chinh-cap-mau-nau-qa102-p199996713.html?spid=199996719</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>SOMIANTON</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>63000</v>
+        <v>368000</v>
       </c>
       <c r="G25" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>9000</v>
+        <v>-368000</v>
       </c>
       <c r="I25" t="n">
-        <v>14.29</v>
+        <v>-100</v>
       </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2526,50 +2526,50 @@
         <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Giá tăng 9,000đ (+14.3%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>275276374</t>
+          <t>72136586</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dép tổ ong XANH RÊU nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Giày Tây Nam Da Bò BIGGBEN Cao Cấp GT200</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-xanh-reu-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276374.html?spid=275276386</t>
+          <t>https://tiki.vn/giay-tay-nam-da-bo-biggben-cao-cap-gt200-p72136586.html?spid=72136606</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2579,26 +2579,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>72000</v>
+        <v>750000</v>
       </c>
       <c r="H26" t="n">
-        <v>9000</v>
+        <v>750000</v>
       </c>
       <c r="I26" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2607,53 +2607,53 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Giá tăng 9,000đ (+14.3%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>275252528</t>
+          <t>270246737</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dép tổ ong VAC nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Giày Tây Nam BIGGBEN Da Bò Thật Cao Cấp GT246</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-size-35-43-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-form-lon-nen-lui-1-2-size-p275252528.html?spid=275252615</t>
+          <t>https://tiki.vn/giay-tay-nam-biggben-da-bo-that-cao-cap-gt246-p270246737.html?spid=270246761</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2663,26 +2663,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>63000</v>
+        <v>749000</v>
       </c>
       <c r="G27" t="n">
-        <v>72000</v>
+        <v>850000</v>
       </c>
       <c r="H27" t="n">
-        <v>9000</v>
+        <v>101000</v>
       </c>
       <c r="I27" t="n">
-        <v>14.29</v>
+        <v>13.48</v>
       </c>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2691,26 +2691,26 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2720,24 +2720,24 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Giá tăng 9,000đ (+14.3%)</t>
+          <t>Giá tăng 101,000đ (+13.5%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>275276525</t>
+          <t>55150033</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dép tổ ong XANH CHUỐI nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Giày Tây Nam Da Bò BIGGBEN Cao Cấp GT187</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-xanh-chuoi-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276525.html?spid=275276527</t>
+          <t>https://tiki.vn/giay-tay-nam-da-bo-biggben-cao-cap-gt187-p55150033.html?spid=55150039</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2747,26 +2747,26 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>63000</v>
+        <v>649000</v>
       </c>
       <c r="G28" t="n">
-        <v>72000</v>
+        <v>750000</v>
       </c>
       <c r="H28" t="n">
-        <v>9000</v>
+        <v>101000</v>
       </c>
       <c r="I28" t="n">
-        <v>14.29</v>
+        <v>15.56</v>
       </c>
       <c r="J28" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2775,26 +2775,26 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2804,53 +2804,53 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Giá tăng 9,000đ (+14.3%)</t>
+          <t>Giá tăng 101,000đ (+15.6%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>274795145</t>
+          <t>152632563</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dép tổ ong [Size 39-43] KÈM STICKER NGẪU NHIÊN vật liệu EVA cao cấp siêu bền, siêu nhẹ, chống trơn trượt</t>
+          <t>Áo Lót Nữ Mút Mỏng Trơn Không Gọng 3281 – Nhẹ Êm, Tự Nhiên, Dễ Mặc Mỗi Ngày</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-size-39-43-kem-sticker-ngau-nhien-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-p274795145.html?spid=274803713</t>
+          <t>https://tiki.vn/ao-lot-duc-kiem-bra-cao-cap-3281-big-size-p152632563.html?spid=274990712</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>68000</v>
+        <v>99000</v>
       </c>
       <c r="G29" t="n">
-        <v>77000</v>
+        <v>82170</v>
       </c>
       <c r="H29" t="n">
-        <v>9000</v>
+        <v>-16830</v>
       </c>
       <c r="I29" t="n">
-        <v>13.24</v>
+        <v>-17</v>
       </c>
       <c r="J29" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2859,26 +2859,26 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -2888,53 +2888,53 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Giá tăng 9,000đ (+13.2%)</t>
+          <t>Giá giảm 16,830đ (17.0%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>275276468</t>
+          <t>276945307</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dép tổ ong XANH NAVY nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Áo lót nữ Angelavic 529 – Bra thun lạnh tăm, mút liền, cài sau, không gọng, nâng đỡ thoải mái</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-xanh-navy-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276468.html?spid=275276480</t>
+          <t>https://tiki.vn/ao-lot-nu-ao-bra-thun-lanh-tam-mut-lien-cai-sau-529-p276945307.html?spid=276945325</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>63000</v>
+        <v>110000</v>
       </c>
       <c r="G30" t="n">
-        <v>72000</v>
+        <v>82500</v>
       </c>
       <c r="H30" t="n">
-        <v>9000</v>
+        <v>-27500</v>
       </c>
       <c r="I30" t="n">
-        <v>14.29</v>
+        <v>-25</v>
       </c>
       <c r="J30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2943,26 +2943,26 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -2972,53 +2972,53 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Giá tăng 9,000đ (+14.3%)</t>
+          <t>Giá giảm 27,500đ (25.0%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>278026014</t>
+          <t>277573177</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ÁO NGỰC SU CÚP NGANG ĐẸP SIZE 34-38 DÀNH CHO NỮ</t>
+          <t>[Set 100 chiếc] Khẩu Trang 9A 5 Lớp Chống Nắng, Che Kín Mặt, Bảo Vệ Tia UV - HÀNG CHÍNH HÃNG MINIIN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-su-cup-ngang-dep-size-34-38-danh-cho-nu-p278026014.html?spid=278026026</t>
+          <t>https://tiki.vn/set-100-chiec-khau-trang-9a-5-lop-chong-nang-che-kin-mat-bao-ve-tia-uv-hang-chinh-hang-miniin-p277573177.html?spid=277573179</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MINIIN</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="G31" t="n">
-        <v>110000</v>
+        <v>65000</v>
       </c>
       <c r="H31" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3030,55 +3030,55 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Rating 0.0→4.0 (+4.00) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>278016649</t>
+          <t>13307720</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ÁO LÓT BẦU COTTON SIÊU XINH SIZE 38-42 DÀNH CHO NỮ</t>
+          <t>Combo 10 Quần lót nam, sịp chéo nam xuất Nhật thời trang cao cấp</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-bau-cotton-sieu-xinh-size-38-42-danh-cho-nu-p278016649.html?spid=278016655</t>
+          <t>https://tiki.vn/combo-10-quan-lot-nam-sip-cheo-nam-xuat-nhat-thoi-trang-cao-cap-p13307720.html?spid=53788749</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3087,19 +3087,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>296450</v>
       </c>
       <c r="G32" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>60000</v>
+        <v>-296450</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3111,16 +3111,16 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3130,63 +3130,63 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>74820156</t>
+          <t>248092080</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG REN 3 MÓC BIG SIZE 395</t>
+          <t>Giày lười nam da bò buộc dây Trường Hải màu nâu đề cao 3cm GM446N</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-ren-3-moc-big-size-395-p74820156.html?spid=74820176</t>
+          <t>https://tiki.vn/giay-luoi-nam-da-bo-buoc-day-truong-hai-mau-nau-de-cao-3cm-gm446n-p248092080.html?spid=248092084</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Trường Hải</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>105000</v>
+        <v>749000</v>
       </c>
       <c r="G33" t="n">
-        <v>131000</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>26000</v>
+        <v>-749000</v>
       </c>
       <c r="I33" t="n">
-        <v>24.76</v>
+        <v>-100</v>
       </c>
       <c r="J33" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3198,50 +3198,50 @@
         <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Giá tăng 26,000đ (+24.8%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>158732070</t>
+          <t>278442851</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>❈✣♚Combo 10 quần lót nữ su đúc cao cấp không đường may, chất mát lạnh, mềm mịn, thoáng</t>
+          <t>Quần Lót Nữ, Combo 6 Quần Lót Su Thạch Mát Lạnh Ngày Hè, Quần Lót Nữ Không Đường Viền - Hàng Nhập Khẩu</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nu-su-duc-cao-cap-khong-duong-may-chat-mat-lanh-mem-min-thoang-p158732070.html?spid=242324041</t>
+          <t>https://tiki.vn/quan-lot-nu-combo-6-quan-lot-su-thach-mat-lanh-ngay-he-quan-lot-nu-khong-duong-vien-hang-nhap-khau-p278442851.html?spid=278442852</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>HT SYS</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>300000</v>
+        <v>122000</v>
       </c>
       <c r="G34" t="n">
-        <v>320000</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>20000</v>
+        <v>-122000</v>
       </c>
       <c r="I34" t="n">
-        <v>6.67</v>
+        <v>-100</v>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3279,79 +3279,79 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Giá tăng 20,000đ (+6.7%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>270469469</t>
+          <t>278529292</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Áo ba lỗ tanktop thể thao bóng rổ 23 premium, vải siêu nhẹ, thoáng mát, thấm hút mồ hôi tốt, màu xanh</t>
+          <t>Dép quai ngang Bitis xốp nam</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-ba-lo-tanktop-the-thao-bong-ro-23-premium-vai-sieu-nhe-thoang-mat-tham-hut-mo-hoi-tot-mau-xanh-p270469469.html?spid=270469473</t>
+          <t>https://tiki.vn/dep-quai-ngang-bitis-xop-nam-p278529292.html?spid=278529322</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SIMPLE &amp; BASIC</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>126000</v>
       </c>
       <c r="G35" t="n">
-        <v>359000</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>359000</v>
+        <v>-126000</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3363,16 +3363,16 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>-4.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3382,60 +3382,60 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8716200</t>
+          <t>270249539</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Băng Đô Cài Tóc Tai Mèo</t>
+          <t>Giày Tây Nam Tăng Chiều Cao BIGGBEN Da Bò Thật Cao Cấp GT252</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bang-do-cai-toc-tai-meo-p8716200.html?spid=13151709</t>
+          <t>https://tiki.vn/giay-tay-nam-tang-chieu-cao-biggben-da-bo-that-cao-cap-gt252-p270249539.html?spid=270249555</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>29000</v>
+        <v>799000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-29000</v>
+        <v>-799000</v>
       </c>
       <c r="I36" t="n">
         <v>-100</v>
       </c>
       <c r="J36" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3447,16 +3447,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-4.7</v>
+        <v>-0</v>
       </c>
       <c r="Q36" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -3483,43 +3483,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>278883514</t>
+          <t>208746104</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Áo sơ mi xếp 3 li kết ngọc tay dài</t>
+          <t>Giày Thể Thao Biti's Nam Hunter X DSMH10500</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-xep-3-li-ket-ngoc-tay-dai-p278883514.html?spid=278883520</t>
+          <t>https://tiki.vn/giay-the-thao-biti-s-nam-hunter-x-dsmh10500-p208746104.html?spid=208746130</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>125000</v>
+        <v>1050000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-125000</v>
+        <v>-1050000</v>
       </c>
       <c r="I37" t="n">
         <v>-100</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3531,16 +3531,16 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-0</v>
+        <v>-4</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -3567,17 +3567,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>275276260</t>
+          <t>276545723</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dép tổ ong ĐỎ nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Dép quai kẹp Bitis nam (38-43)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-do-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276260.html?spid=275276262</t>
+          <t>https://tiki.vn/dep-quai-kep-bitis-nam-38-43-p276545723.html?spid=276545737</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3587,26 +3587,26 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>63000</v>
+        <v>92000</v>
       </c>
       <c r="G38" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>9000</v>
+        <v>-92000</v>
       </c>
       <c r="I38" t="n">
-        <v>14.29</v>
+        <v>-100</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3615,82 +3615,82 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Giá tăng 9,000đ (+14.3%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>274804274</t>
+          <t>52317590</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dép tổ ong [Size 31-34] KÈM STICKER NGẪU NHIÊN vật liệu EVA cao cấp siêu bền, siêu nhẹ, chống trơn trượt</t>
+          <t>Bộ 2 mũ lưỡi trai cho nam ( đen - trắng)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-size-31-34-kem-sticker-ngau-nhien-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-p274804274.html?spid=274804515</t>
+          <t>https://tiki.vn/bo-2-mu-luoi-trai-cho-nam-den-trang-p52317590.html?spid=162171783</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>LQ luxury</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>60000</v>
+        <v>49000</v>
       </c>
       <c r="G39" t="n">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>5000</v>
+        <v>-49000</v>
       </c>
       <c r="I39" t="n">
-        <v>8.33</v>
+        <v>-100</v>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3699,16 +3699,16 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3718,91 +3718,91 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Giá tăng 5,000đ (+8.3%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>275276334</t>
+          <t>278004504</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dép tổ ong XÁM nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Combo 5 Quần Lót Nữ Su Tăm Trơn Không Viền Mỏng Nhẹ 892 – Co Giãn 4 Chiều, Thoáng Mát, Không Lộ Viền (Size L/XL/XXL)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-xam-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276334.html?spid=275276338</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nu-su-tam-tron-khong-vien-mong-nhe-892-co-gian-4-chieu-thoang-mat-khong-lo-vien-size-l-xl-xxl-p278004504.html?spid=278004508</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>63000</v>
+        <v>168000</v>
       </c>
       <c r="G40" t="n">
-        <v>72000</v>
+        <v>230000</v>
       </c>
       <c r="H40" t="n">
-        <v>9000</v>
+        <v>62000</v>
       </c>
       <c r="I40" t="n">
-        <v>14.29</v>
+        <v>36.9</v>
       </c>
       <c r="J40" t="n">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>-230000</v>
       </c>
       <c r="N40" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -3812,2275 +3812,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Giá tăng 9,000đ (+14.3%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>274350557</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Hộp 100 Khăn Lau Kính Nano, Chống Bám Hơi Nước, Chống Bụi Bẩn - Khăn Lau Kính Nano Hộp 100 Miếng Giấy Lau Kính Chống Bám Hơi Nước, Lau Sạch Vân Tay Bụi Bẩn</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/hop-100-khan-lau-kinh-nano-chong-bam-hoi-nuoc-chong-bui-ban-khan-lau-kinh-nano-hop-100-mieng-giay-lau-kinh-chong-bam-hoi-nuoc-lau-sach-van-tay-bui-ban-p274350557.html?spid=274350558</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>fofaHome</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>17000</v>
-      </c>
-      <c r="G41" t="n">
-        <v>20000</v>
-      </c>
-      <c r="H41" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I41" t="n">
-        <v>17.65</v>
-      </c>
-      <c r="J41" t="n">
-        <v>80</v>
-      </c>
-      <c r="K41" t="n">
-        <v>80</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5</v>
-      </c>
-      <c r="O41" t="n">
-        <v>5</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>2</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Giá tăng 3,000đ (+17.6%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>279399528</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>KHĂN LỤA DÀI KHĂN QUÀNG CỔ KHĂN CHOÀNG LỤA BĂNG ĐÔ TRANG TRÍ NƠ CAO CẤP ĐA NĂNG SANG TRỌNG THANH LỊCH MÃ 18-38</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/khan-lua-dai-khan-quang-co-khan-choang-lua-bang-do-trang-tri-no-cao-cap-da-nang-sang-trong-thanh-lich-ma-18-38-p279399528.html?spid=279399560</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>120000</v>
-      </c>
-      <c r="H42" t="n">
-        <v>120000</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>🆕 Sản phẩm mới</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>275276309</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Dép tổ ong ĐEN nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-to-ong-den-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276309.html?spid=275276325</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VAC </t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>63000</v>
-      </c>
-      <c r="G43" t="n">
-        <v>72000</v>
-      </c>
-      <c r="H43" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I43" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="J43" t="n">
-        <v>36</v>
-      </c>
-      <c r="K43" t="n">
-        <v>36</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Giá tăng 9,000đ (+14.3%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>278064718</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>KHẨU TRANG COTTON KHÁNG KHUẨN CHÓNG TIA UV DÀNH CHO NỮ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/khau-trang-cotton-khang-khuan-chong-tia-uv-danh-cho-nu-p278064718.html?spid=278064724</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>34000</v>
-      </c>
-      <c r="H44" t="n">
-        <v>34000</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>🆕 Sản phẩm mới</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>278423322</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Dép quai ngang Biti's nam (39-44)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-quai-ngang-biti-s-nam-39-44-p278423322.html?spid=278423326</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Biti's</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>465000</v>
-      </c>
-      <c r="H45" t="n">
-        <v>465000</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>🆕 Sản phẩm mới</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>275878934</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Áo chống nắng nam thun lạnh thoáng mát chống tia UV cao cấp UPF50</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-chong-nang-nam-cao-cap-thong-hoi-chong-nang-chong-tia-uv-chong-bam-bui-fmtht024-p275878934.html?spid=275878936</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>LuckyJQR</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>180000</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-180000</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J46" t="n">
-        <v>6</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>276348729</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Quần Lót Nam Boxer Relax - Quần Sịp Chất Thun Lạnh Thoải Mái Tặng Vớ Khi Mua Combo 2 Quần</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/quan-lot-nam-boxer-relax-quan-sip-chat-thun-lanh-thoai-mai-tang-vo-khi-mua-combo-2-quan-p276348729.html?spid=276348760</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Relax</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>114000</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-114000</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>59079180</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>ÁO KHOÁC LEN NAM CÀI NÚT</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-khoac-len-nam-cai-nut-p59079180.html?spid=113225866</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>325750</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-325750</v>
-      </c>
-      <c r="I48" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>274894622</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Quần tây nam 1 ly Khatoco Q1M528R1-INDE305-2503-1-ĐEN</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/quan-tay-nam-1-ly-khatoco-q1m528r1-inde305-2503-1-den-p274894622.html?spid=274894626</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KHATOCO </t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>422400</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-422400</v>
-      </c>
-      <c r="I49" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>274948189</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Đồ bơi nữ trung niên cho mẹ cho bà, áo tắm người già trung tuổi, có size lớn tránh lộ bụng, mẫu trẻ trung thanh lịch, dễ mặc, chất bơi mát mịn đẹp | KT009</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/do-boi-nu-trung-nien-cho-me-cho-ba-ao-tam-nguoi-gia-trung-tuoi-co-size-lon-tranh-lo-bung-mau-tre-trung-thanh-lich-de-mac-chat-boi-mat-min-dep-kt009-p274948189.html?spid=274948209</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>420000</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-420000</v>
-      </c>
-      <c r="I50" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>59205406</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>COMBO 5 ÁO LÁ NGẮN THUN LỤA MẶT TRƯỚC 2 LỚP DÀNH CHO HỌC SINH</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/combo-5-ao-la-ngan-thun-lua-mat-truoc-2-lop-danh-cho-hoc-sinh-p59205406.html?spid=59205408</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>101400</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-101400</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J51" t="n">
-        <v>92</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>29</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>24350235</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Cài Tóc Tai Mèo Dễ Thương</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/cai-toc-tai-meo-de-thuong-p24350235.html?spid=55201698</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="I52" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J52" t="n">
-        <v>86</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>17</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>162562752</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Combo 10 quần lót nữ chất liệu cotton chất đẹp</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nu-chat-lieu-cotton-chat-dep-p162562752.html?spid=162562761</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>134400</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-134400</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>278012594</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Quần Gen Định Hình Bụng Khóa Kéo Phối Ren Quyến Rũ 2055 – Eo Thon, Bụng Phẳng, Tự Tin Mỗi Ngày</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/quan-gen-dinh-hinh-bung-khoa-keo-phoi-ren-quyen-ru-2055-eo-thon-bung-phang-tu-tin-moi-ngay-p278012594.html?spid=278592879</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>120000</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-120000</v>
-      </c>
-      <c r="I54" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>277274436</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Set áo cổ tròn sát nách phối quần ống suông thanh lịch</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/set-ao-co-tron-sat-nach-phoi-quan-ong-suong-thanh-lich-p277274436.html?spid=277274444</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>199000</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-199000</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>276303219</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Bộ Váy Thể Thao Nữ Gồm Áo Thun Và Váy 2 Lớp Sành Điệu</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/bo-vay-the-thao-nu-gom-ao-thun-va-vay-2-lop-sanh-dieu-p276303219.html?spid=276306416</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>239000</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-239000</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>276147904</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Quần lót nữ ren sexy</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/quan-lot-nu-ren-sexy-p276147904.html?spid=276147905</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>FTAKY</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>273388482</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Combo 7 quần lót cotton nữ nhiều màu du lịch dùng 1 lần</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/combo-7-quan-lot-cotton-nu-nhieu-mau-du-lich-dung-1-lan-p273388482.html?spid=273388612</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>169000</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-169000</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J58" t="n">
-        <v>33</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>3</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>182481410</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Áo sơ mi nữ tay lỡ cổ đức, họa tiết thêu hoa tinh tế, chất liệu Đũi mềm mát co giãn nhẹ, form đẹp NeSa Shop SMH.55</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-so-mi-nu-tay-lo-co-duc-hoa-tiet-theu-hoa-tinh-te-chat-lieu-dui-mem-mat-co-gian-nhe-form-dep-nesa-shop-smh-55-p182481410.html?spid=182481432</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>145000</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-145000</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J59" t="n">
-        <v>17</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>7</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>212048690</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>NHIỀU MẪU Ghim cài áo đính đá xích cao cấp - ghim cài vest cưới Tien Nguyen</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/nhieu-mau-ghim-cai-ao-dinh-da-xich-cao-cap-ghim-cai-vest-cuoi-tien-nguyen-p212048690.html?spid=212048699</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>159000</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-159000</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>5</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>165256024</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Mũ phớt cao bồi Fedora Classic nỉ MP021 cao cấp cho nam và nữ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/mu-phot-cao-boi-fedora-classic-ni-mp021-cao-cap-cho-nam-va-nu-p165256024.html?spid=165256026</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	OEM</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>145000</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-145000</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J61" t="n">
-        <v>8</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>5</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>14815744</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Chân Váy Serena</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/chan-vay-serena-p14815744.html?spid=14815760</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>135000</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-135000</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J62" t="n">
-        <v>60</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>15</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>275262532</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Giày Sandal Nam Nữ Chất Liệu Nhựa EVA Mềm, Nhẹ, Êm Chân, Thoải Mái, Chống Trơn Trượt (FORM LỚN ĐẶT LÙI 1 SIZE) Giày đi học - Giày đi làm - Giày đi chơi</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/giay-sandal-nam-chat-lieu-nhua-eva-mem-nhe-em-chan-thoai-mai-chong-tron-truot-p275262532.html?spid=279226521</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VAC </t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>220000</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-220000</v>
-      </c>
-      <c r="I63" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J63" t="n">
-        <v>18</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>275276585</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Dép tổ ong KEM nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-to-ong-kem-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276585.html?spid=275276595</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VAC </t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>63000</v>
-      </c>
-      <c r="G64" t="n">
-        <v>72000</v>
-      </c>
-      <c r="H64" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I64" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="J64" t="n">
-        <v>87</v>
-      </c>
-      <c r="K64" t="n">
-        <v>86</v>
-      </c>
-      <c r="L64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M64" t="n">
-        <v>-72000</v>
-      </c>
-      <c r="N64" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O64" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>5</v>
-      </c>
-      <c r="R64" t="n">
-        <v>5</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Giá tăng 9,000đ (+14.3%) | Bán thêm -1 sản phẩm</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>67538621</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538625</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>May 10</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>135000</v>
-      </c>
-      <c r="G65" t="n">
-        <v>135000</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>16592</v>
-      </c>
-      <c r="K65" t="n">
-        <v>16590</v>
-      </c>
-      <c r="L65" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M65" t="n">
-        <v>-270000</v>
-      </c>
-      <c r="N65" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O65" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>4842</v>
-      </c>
-      <c r="R65" t="n">
-        <v>4842</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Bán thêm -2 sản phẩm</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>262691682</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Mũ Lưỡi Trai Chóp Vuông Jeep, Nón Kết Chóp Phẳng Màu Đen, Xanh Than M189</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/mu-luoi-trai-chop-vuong-jeep-non-ket-chop-phang-mau-den-xanh-than-m189-p262691682.html?spid=262691684</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>350000</v>
-      </c>
-      <c r="G66" t="n">
-        <v>350000</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>6</v>
-      </c>
-      <c r="K66" t="n">
-        <v>5</v>
-      </c>
-      <c r="L66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M66" t="n">
-        <v>-350000</v>
-      </c>
-      <c r="N66" t="n">
-        <v>5</v>
-      </c>
-      <c r="O66" t="n">
-        <v>5</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Bán thêm -1 sản phẩm</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>275276395</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Dép tổ ong TRẮNG nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-to-ong-trangvat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276395.html?spid=275276403</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VAC </t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>63000</v>
-      </c>
-      <c r="G67" t="n">
-        <v>72000</v>
-      </c>
-      <c r="H67" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I67" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="J67" t="n">
-        <v>36</v>
-      </c>
-      <c r="K67" t="n">
-        <v>30</v>
-      </c>
-      <c r="L67" t="n">
-        <v>-6</v>
-      </c>
-      <c r="M67" t="n">
-        <v>-432000</v>
-      </c>
-      <c r="N67" t="n">
-        <v>5</v>
-      </c>
-      <c r="O67" t="n">
-        <v>5</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>3</v>
-      </c>
-      <c r="R67" t="n">
-        <v>3</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Giá tăng 9,000đ (+14.3%) | Bán thêm -6 sản phẩm</t>
+          <t>Giá tăng 62,000đ (+36.9%) | Bán thêm -1 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>193978418</t>
+          <t>2302097</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quần Jean nam Leman xám khói trơn JD13 - Slim Form</t>
+          <t>Combo 3 Đôi Vớ Nam Cotton Thể Thao Donakein 195F3D1M02 (Free Size)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-jean-nam-leman-xam-khoi-tron-jd13-slim-form-p193978418.html?spid=193978434</t>
+          <t>https://tiki.vn/combo-3-doi-vo-nam-cotton-the-thao-donakein-195f3d1m02-free-size-p2302097.html?spid=2340107</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Leman</t>
+          <t>Donakein</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>549000</v>
+        <v>135000</v>
       </c>
       <c r="H2" t="n">
-        <v>549000</v>
+        <v>135000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,13 +582,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L2" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M2" t="n">
-        <v>34038000</v>
+        <v>7965000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -603,14 +603,14 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="S2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2710151</t>
+          <t>208746104</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lót giày sức khỏe Spenco Total Support Thin 46-696 cho giày thể thao, công sở nâng vòm hỗ trợ giảm mỏi chân khi đi nhiều, đứng lâu</t>
+          <t>Giày Thể Thao Biti's Nam Hunter X DSMH10500</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/lot-giay-cong-so-giam-dau-moi-chan-spenco-total-suport-thin-46-696-p2710151.html?spid=2710155</t>
+          <t>https://tiki.vn/giay-the-thao-biti-s-nam-hunter-x-dsmh10500-p208746104.html?spid=208746130</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spenco</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>895000</v>
+        <v>1050000</v>
       </c>
       <c r="H3" t="n">
-        <v>895000</v>
+        <v>1050000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>17005000</v>
+        <v>5250000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,17 +711,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276634531</t>
+          <t>278820713</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Keo Dán Giày Thể Thao Sêu Dính Dùng Nhiệt Trong Suốt Không Tổn Thương Da, Keo Dính Giày Đa Năng Siêu Bền Chống Nước Tốt Xanh</t>
+          <t>Dép nhựa Biti's nam (39-44)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/keo-dan-giay-the-thao-seu-dinh-dung-nhiet-trong-suot-khong-ton-thuong-da-keo-dinh-giay-da-nang-sieu-ben-chong-nuoc-tot-p276634531.html?spid=276634532</t>
+          <t>https://tiki.vn/dep-nhua-biti-s-nam-39-44-p278820713.html?spid=278820719</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LuckyJQR</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>160000</v>
+        <v>206000</v>
       </c>
       <c r="H4" t="n">
-        <v>160000</v>
+        <v>206000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,35 +750,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>5600000</v>
+        <v>1030000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,121 +795,121 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>275262532</t>
+          <t>54569520</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày Sandal Nam Nữ Chất Liệu Nhựa EVA Mềm, Nhẹ, Êm Chân, Thoải Mái, Chống Trơn Trượt (FORM LỚN ĐẶT LÙI 1 SIZE) Giày đi học - Giày đi làm - Giày đi chơi</t>
+          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-sandal-nam-chat-lieu-nhua-eva-mem-nhe-em-chan-thoai-mai-chong-tron-truot-p275262532.html?spid=279226513</t>
+          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>68640</v>
       </c>
       <c r="G5" t="n">
-        <v>140000</v>
+        <v>88000</v>
       </c>
       <c r="H5" t="n">
-        <v>140000</v>
+        <v>19360</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>28.21</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>2520000</v>
+        <v>440000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 19,360đ (+28.2%) | Bán thêm +5 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>277347854</t>
+          <t>253306906</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thắt lưng nữ DA BÒ THẬT - BEE GEE N8051</t>
+          <t>Đón gót giầy gỗ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-nu-da-bo-that-bee-gee-n8051-p277347854.html?spid=277347856</t>
+          <t>https://tiki.vn/don-got-giay-p253306906.html?spid=253306912</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bee Gee</t>
+          <t>DAICAT</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>150000</v>
+        <v>159000</v>
       </c>
       <c r="H6" t="n">
-        <v>150000</v>
+        <v>159000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>1500000</v>
+        <v>318000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -963,37 +963,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>140836685</t>
+          <t>37269401</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giày Lười Nam Da Bò SUNPOLO MU2588 (Xanh Navy)</t>
+          <t>Combo 5 Quần Lót Nam Thông Hơi Xuất Nhật Mã S02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-luoi-nam-da-bo-sunpolo-mu2588-xanh-navy-p140836685.html?spid=140836687</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-thong-hoi-xuat-nhat-ma-s02-p37269401.html?spid=198496796</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SUNPOLO</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1200000</v>
+        <v>119000</v>
       </c>
       <c r="H7" t="n">
-        <v>1200000</v>
+        <v>119000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1002,13 +1002,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>1200000</v>
+        <v>238000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,34 +1047,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>52184516</t>
+          <t>52758433</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Combo 3 quần lót nam Boxer sợi Organic mềm mịn thoáng mát co giãn 4 chiều MRM Manlywear ( TẶNG Đôi Tất Nam Cao Cấp Giao Ngẫu Nhiên)</t>
+          <t>Combo 5 Đôi Tất Nam Vớ Nam Cổ Dài Sợi Cotton Mix Màu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-3-qua-n-lo-t-nam-boxer-so-i-cotton-organic-me-m-mi-n-thoa-ng-ma-t-co-gia-n-4-chie-u-mrm-manlywear-tang-doi-tat-nam-cao-cap-giao-ngau-nhien-p52184516.html?spid=52184518</t>
+          <t>https://tiki.vn/combo-5-doi-tat-nam-vo-nam-co-dai-soi-cotton-mix-mau-p52758433.html?spid=67297062</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>JM Jamano</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>199000</v>
+        <v>99000</v>
       </c>
       <c r="G8" t="n">
-        <v>199000</v>
+        <v>99000</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1083,38 +1083,38 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>4333</v>
+        <v>3762</v>
       </c>
       <c r="K8" t="n">
-        <v>4339</v>
+        <v>3763</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1194000</v>
+        <v>99000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1245</v>
+        <v>1001</v>
       </c>
       <c r="R8" t="n">
-        <v>1245</v>
+        <v>1001</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1124,29 +1124,29 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +6 sản phẩm</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16375016</t>
+          <t>274036763</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COMBO HỘP 5 Quần Lót ĐÙI Nam Xuất Nhật Cao Cấp (MIX NGẪU NHIÊN)</t>
+          <t>Tất vớ lười nữ màu trơn Kikiya cao cấp Hàn Quốc W-N-008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-hop-5-quan-lot-dui-nam-xuat-nhat-cao-cap-mix-ngau-nhien-p16375016.html?spid=277961877</t>
+          <t>https://tiki.vn/tat-vo-luoi-nu-mau-tron-kikiya-cao-cap-han-quoc-w-n-008-p274036763.html?spid=274036764</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1158,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>251000</v>
+        <v>44100</v>
       </c>
       <c r="H9" t="n">
-        <v>251000</v>
+        <v>44100</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1170,13 +1170,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>753000</v>
+        <v>88200</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1215,34 +1215,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>275276468</t>
+          <t>19843976</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dép tổ ong XANH NAVY nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Combo 10 Đôi Tất Nam Chống Hôi Chân Thời Trang</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-xanh-navy-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276468.html?spid=275276484</t>
+          <t>https://tiki.vn/combo-10-doi-tat-nam-chong-hoi-chan-thoi-trang-p19843976.html?spid=71526312</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>72000</v>
+        <v>79000</v>
       </c>
       <c r="G10" t="n">
-        <v>72000</v>
+        <v>79000</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1251,38 +1251,38 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>375</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>376</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>720000</v>
+        <v>79000</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1292,81 +1292,81 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Bán thêm +10 sản phẩm</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>278000485</t>
+          <t>183685137</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Áo lót nữ 718 – Mút mỏng thông hơi, không gọng, cài sau 3 móc, co giãn thoải mái</t>
+          <t>Thắt Lưng Dây Nịt Nam Vải Dù US ARMY, Phong Cách Sang Trọng Cổ Điển Mặt Khóa Hợp Kim Thép Chống Ghỉ Cao Cấp -HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-718-mut-mong-thong-hoi-khong-gong-cai-sau-3-moc-co-gian-thoai-mai-p278000485.html?spid=278000491</t>
+          <t>https://tiki.vn/that-lung-day-nit-nam-vai-du-us-army-phong-cach-sang-trong-co-dien-mat-khoa-hop-kim-thep-chong-ghi-cao-cap-hang-chinh-hang-p183685137.html?spid=183685139</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>80000</v>
+        <v>79000</v>
       </c>
       <c r="G11" t="n">
-        <v>100000</v>
+        <v>79000</v>
       </c>
       <c r="H11" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>209</v>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>210</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>600000</v>
+        <v>79000</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1376,81 +1376,81 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Giá tăng 20,000đ (+25.0%) | Bán thêm +6 sản phẩm</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>278092142</t>
+          <t>107802069</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quần kiểu nữ ống rộng, chất liệu vải Đũi xước, mềm mịn, mặc mát, Quần Short nữ đẹp Nesa Shop</t>
+          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-kieu-nu-ong-rong-chat-lieu-vai-dui-xuoc-mem-min-mac-mat-quan-short-nu-dep-nesa-shop-p278092142.html?spid=278092148</t>
+          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55000</v>
+        <v>32000</v>
       </c>
       <c r="G12" t="n">
-        <v>49000</v>
+        <v>32000</v>
       </c>
       <c r="H12" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-10.91</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>1030</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>392000</v>
+        <v>32000</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1460,41 +1460,41 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Giá giảm 6,000đ (10.9%) | Bán thêm +8 sản phẩm</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>67538621</t>
+          <t>83423370</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
+          <t>Bộ dụng cụ tua vít đa năng sửa kính, mắt kính</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538631</t>
+          <t>https://tiki.vn/bo-dung-cu-tua-vit-da-nang-sua-kinh-mat-kinh-p83423370.html?spid=113070838</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>May 10</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>135000</v>
+        <v>9500</v>
       </c>
       <c r="G13" t="n">
-        <v>135000</v>
+        <v>9500</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1503,38 +1503,38 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>16590</v>
+        <v>89</v>
       </c>
       <c r="K13" t="n">
-        <v>16592</v>
+        <v>90</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>270000</v>
+        <v>9500</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4842</v>
+        <v>16</v>
       </c>
       <c r="R13" t="n">
-        <v>4842</v>
+        <v>16</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,24 +1544,24 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Bán thêm +2 sản phẩm</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>275738156</t>
+          <t>198300891</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mặt Khóa Thắt Lưng Nam Cao Cấp,Mặt Thắt Lưng Nam Khóa Tự Động 203851</t>
+          <t>Khẩu Trang Chống Tia Uv, Khẩu Trang Chống Nắng Upf 50+ - Unisex Nam Nữ Đều Thích Hợp- Vải Mềm Mát Thoáng Khí</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mat-khoa-that-lung-nam-cao-cap-mat-that-lung-nam-khoa-tu-dong-203851-p275738156.html?spid=275738157</t>
+          <t>https://tiki.vn/khau-trang-chong-tia-uv-khau-trang-chong-nang-upf-50-unisex-nam-nu-deu-thich-hop-vai-mem-mat-thoang-khi-p198300891.html?spid=279253596</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1571,54 +1571,54 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TLG Thành Long</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>61250</v>
+        <v>23000</v>
       </c>
       <c r="G14" t="n">
-        <v>61250</v>
+        <v>31000</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>34.78</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>61250</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1628,113 +1628,113 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Giá tăng 8,000đ (+34.8%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>192985737</t>
+          <t>66095198</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Móc Cài Tai Silicon Siêu Dẻo, Giúp Giữ Gọng Kính Không Bị Tuột Khi Chạy, Nhảy, Chơi Thể Thao, Màu Đen, Trong Suốt</t>
+          <t>Áo phông cổ tim ALIGRO ALGAPC051</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/moc-cai-tai-silicon-sieu-deo-giup-giu-gong-kinh-khong-bi-tuot-khi-chay-nhay-choi-the-thao-mau-den-trong-suot-p192985737.html?spid=192985738</t>
+          <t>https://tiki.vn/ao-phong-co-tim-aligro-algapc051-p66095198.html?spid=66095200</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Blue Light</t>
+          <t>Aligro</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>10000</v>
+        <v>150000</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Bán thêm +6 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>140429170</t>
+          <t>277600025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bao tay chơi game găng tay 2 ngón cảm ứng điện thoại gamemobile BT01</t>
+          <t>Áo Polo Nam Công Sở Đẹp, Sang Trọng | Hàng Hiệu Cao Cấp PLN05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bao-tay-choi-game-gang-tay-2-ngon-cam-ung-dien-thoai-gamemobile-bt01-p140429170.html?spid=198934954</t>
+          <t>https://tiki.vn/ao-polo-nam-cong-so-dep-sang-trong-hang-hieu-cao-cap-pln05-p277600025.html?spid=277600091</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9999</v>
+        <v>270000</v>
       </c>
       <c r="G16" t="n">
-        <v>9999</v>
+        <v>270000</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1755,38 +1755,38 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>9999</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1796,29 +1796,29 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>278021672</t>
+          <t>244298960</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quần Lót Nam Đùi Boxer Lụa Băng Menpro MP9 - Mỏng nhem Thoáng Khí</t>
+          <t>Quần Mặc Váy Su Thông Hơi Trơn 6530 | Mát Mẻ, Không Lộ, Chống Hớ Hiệu Quả</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-dui-boxer-lua-bang-menpro-mp9-mong-nhem-thoang-khi-p278021672.html?spid=278021702</t>
+          <t>https://tiki.vn/quan-vay-dai-thong-hoi-6530-p244298960.html?spid=244298972</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1827,16 +1827,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>63200</v>
+        <v>42000</v>
       </c>
       <c r="G17" t="n">
-        <v>79000</v>
+        <v>35280</v>
       </c>
       <c r="H17" t="n">
-        <v>15800</v>
+        <v>-6720</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>-16</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1880,53 +1880,53 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá tăng 15,800đ (+25.0%)</t>
+          <t>Giá giảm 6,720đ (16.0%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2212215</t>
+          <t>104791604</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Combo 04 quần lót nam Pro Ben bảng nhỏ MS914</t>
+          <t>Quần lót nữ thái lan 828 – Chất thun lạnh - giao màu ngẫu nhiên</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-04-quan-lot-nam-pro-ben-bang-nho-ms914-p2212215.html?spid=53788047</t>
+          <t>https://tiki.vn/quan-lot-nu-thai-lan-828-chat-thun-lanh-giao-mau-ngau-nhien-p104791604.html?spid=270215619</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pro Ben</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>135520</v>
+        <v>44000</v>
       </c>
       <c r="G18" t="n">
-        <v>176000</v>
+        <v>33880</v>
       </c>
       <c r="H18" t="n">
-        <v>40480</v>
+        <v>-10120</v>
       </c>
       <c r="I18" t="n">
-        <v>29.87</v>
+        <v>-23</v>
       </c>
       <c r="J18" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="K18" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1964,24 +1964,24 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá tăng 40,480đ (+29.9%)</t>
+          <t>Giá giảm 10,120đ (23.0%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>244297794</t>
+          <t>7078807</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
+          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
+          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858801</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>190000</v>
+        <v>300300</v>
       </c>
       <c r="G19" t="n">
-        <v>159600</v>
+        <v>385000</v>
       </c>
       <c r="H19" t="n">
-        <v>-30400</v>
+        <v>84700</v>
       </c>
       <c r="I19" t="n">
-        <v>-16</v>
+        <v>28.21</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,10 +2019,10 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2048,29 +2048,29 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá giảm 30,400đ (16.0%)</t>
+          <t>Giá tăng 84,700đ (+28.2%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>277983818</t>
+          <t>278021672</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Ren Dày Cài Trước Có Gọng Nâng Ngực Belle VC02 – Combo Đa Màu, Đệm Mút 3 cm, Quyến Rũ &amp; Đỡ Đỡ</t>
+          <t>Quần Lót Nam Đùi Boxer Lụa Băng Menpro MP9 - Mỏng nhem Thoáng Khí</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ren-day-cai-truoc-co-gong-nang-nguc-belle-vc02-combo-da-mau-dem-mut-3-cm-quyen-ru-do-do-p277983818.html?spid=277983822</t>
+          <t>https://tiki.vn/quan-lot-nam-dui-boxer-lua-bang-menpro-mp9-mong-nhem-thoang-khi-p278021672.html?spid=278021702</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2079,16 +2079,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>126000</v>
+        <v>79000</v>
       </c>
       <c r="G20" t="n">
-        <v>150000</v>
+        <v>63200</v>
       </c>
       <c r="H20" t="n">
-        <v>24000</v>
+        <v>-15800</v>
       </c>
       <c r="I20" t="n">
-        <v>19.05</v>
+        <v>-20</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2132,53 +2132,53 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Giá tăng 24,000đ (+19.0%)</t>
+          <t>Giá giảm 15,800đ (20.0%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>115852451</t>
+          <t>278872546</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chai vệ sinh giày đồ da, túi ví, áo, ghế da giúp làm sạch, dưỡng ẩm chống mốc XIMO XI03</t>
+          <t>Áo thun tay ngắn nam.Fitted - ROUTINE 10F25TSS039</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-ve-sinh-giay-do-da-tui-vi-ao-ghe-da-giup-lam-sach-duong-am-chong-moc-ximo-xi03-p115852451.html?spid=262784198</t>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-fitted-routine-10f25tss039-p278872546.html?spid=278872562</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>75000</v>
+        <v>349000</v>
       </c>
       <c r="G21" t="n">
-        <v>70000</v>
+        <v>349000</v>
       </c>
       <c r="H21" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.67</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2187,26 +2187,26 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2216,50 +2216,50 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Giá giảm 5,000đ (6.7%)</t>
+          <t>Rating 0.0→5.0 (+5.00) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>277610005</t>
+          <t>195305781</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Áo Lót 3281 Không Gọng Mút Mỏng Bản 3 Móc Che Khuyết Điểm Đẹp</t>
+          <t>Combo 3 quần đùi mặc nhà - Giao màu ngẫu nhiên</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-3281-khong-gong-mut-mong-ban-3-moc-che-khuyet-diem-dep-p277610005.html?spid=277610035</t>
+          <t>https://tiki.vn/combo-3-quan-dui-mac-nha-giao-mau-ngau-nhien-p195305781.html?spid=195305789</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sanny House</t>
+          <t>Novelty</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>285000</v>
       </c>
       <c r="G22" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>96000</v>
+        <v>-285000</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2271,16 +2271,16 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2290,63 +2290,63 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>277969210</t>
+          <t>195304668</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Combo 5 quần lót nữ lọt khe lụa trơn Voronin Q8289 – Mềm mịn, ôm dáng</t>
+          <t>COMBO 2 QUẦN ĐÙI MẶC NHÀ - GIAO MÀU NGẪU NHIÊN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-khe-nu-bang-lua-tron-lien-mach-voronin-q8289-p277969210.html?spid=277969212</t>
+          <t>https://tiki.vn/combo-2-quan-dui-mac-nha-giao-mau-ngau-nhien-p195304668.html?spid=195304672</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Novelty</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>205800</v>
+        <v>190000</v>
       </c>
       <c r="G23" t="n">
-        <v>245000</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>39200</v>
+        <v>-190000</v>
       </c>
       <c r="I23" t="n">
-        <v>19.05</v>
+        <v>-100</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2374,34 +2374,34 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Giá tăng 39,200đ (+19.0%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>277919931</t>
+          <t>73862702</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Combo 5 quần lót nữ thun lạnh thông hơi Voronin 2067 – Mát mịn, co giãn 4 chiều, không hằn viền</t>
+          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nu-thun-lanh-thong-hoi-voronin-2067-mat-min-co-gian-4-chieu-khong-han-vien-p277919931.html?spid=277919932</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862742</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2415,22 +2415,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>159600</v>
+        <v>143590</v>
       </c>
       <c r="G24" t="n">
-        <v>190000</v>
+        <v>173000</v>
       </c>
       <c r="H24" t="n">
-        <v>30400</v>
+        <v>29410</v>
       </c>
       <c r="I24" t="n">
-        <v>19.05</v>
+        <v>20.48</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2439,26 +2439,26 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2468,53 +2468,53 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Giá tăng 30,400đ (+19.0%)</t>
+          <t>Giá tăng 29,410đ (+20.5%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>199996713</t>
+          <t>115852451</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quần Âu Nam Công Sở Thương Hiệu Anton Cao Cấp Xếp ly, Chỉnh Cạp Màu Nâu- QA102</t>
+          <t>Chai vệ sinh giày đồ da, túi ví, áo, ghế da giúp làm sạch, dưỡng ẩm chống mốc XIMO XI03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-au-nam-cong-so-thuong-hieu-anton-cao-cap-xep-ly-chinh-cap-mau-nau-qa102-p199996713.html?spid=199996719</t>
+          <t>https://tiki.vn/chai-ve-sinh-giay-do-da-tui-vi-ao-ghe-da-giup-lam-sach-duong-am-chong-moc-ximo-xi03-p115852451.html?spid=262784198</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SOMIANTON</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>368000</v>
+        <v>70000</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="H25" t="n">
-        <v>-368000</v>
+        <v>5000</v>
       </c>
       <c r="I25" t="n">
-        <v>-100</v>
+        <v>7.14</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2523,82 +2523,82 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P25" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 5,000đ (+7.1%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>72136586</t>
+          <t>278092142</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Giày Tây Nam Da Bò BIGGBEN Cao Cấp GT200</t>
+          <t>Quần kiểu nữ ống rộng, chất liệu vải Đũi xước, mềm mịn, mặc mát, Quần Short nữ đẹp Nesa Shop</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-tay-nam-da-bo-biggben-cao-cap-gt200-p72136586.html?spid=72136606</t>
+          <t>https://tiki.vn/quan-kieu-nu-ong-rong-chat-lieu-vai-dui-xuoc-mem-min-mac-mat-quan-short-nu-dep-nesa-shop-p278092142.html?spid=278092148</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="G26" t="n">
-        <v>750000</v>
+        <v>55000</v>
       </c>
       <c r="H26" t="n">
-        <v>750000</v>
+        <v>6000</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>12.24</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2607,82 +2607,82 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 6,000đ (+12.2%)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>270246737</t>
+          <t>59462352</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Giày Tây Nam BIGGBEN Da Bò Thật Cao Cấp GT246</t>
+          <t>Áo ngực mỏng thêu hoa cài trước có gọng</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-tay-nam-biggben-da-bo-that-cao-cap-gt246-p270246737.html?spid=270246761</t>
+          <t>https://tiki.vn/ao-nguc-mong-theu-hoa-cai-truoc-co-gong-p59462352.html?spid=59462384</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>749000</v>
+        <v>70200</v>
       </c>
       <c r="G27" t="n">
-        <v>850000</v>
+        <v>90000</v>
       </c>
       <c r="H27" t="n">
-        <v>101000</v>
+        <v>19800</v>
       </c>
       <c r="I27" t="n">
-        <v>13.48</v>
+        <v>28.21</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2691,26 +2691,26 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2720,53 +2720,53 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Giá tăng 101,000đ (+13.5%)</t>
+          <t>Giá tăng 19,800đ (+28.2%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>55150033</t>
+          <t>252533129</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Giày Tây Nam Da Bò BIGGBEN Cao Cấp GT187</t>
+          <t>Găng Tay Hở 2 Ngón Unisex Chống Nắng, Có Thể Sử Dụng Cảm Ứng Điện Thoại</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-tay-nam-da-bo-biggben-cao-cap-gt187-p55150033.html?spid=55150039</t>
+          <t>https://tiki.vn/gang-tay-ho-2-ngon-unisex-chong-nang-co-the-su-dung-cam-ung-dien-thoai-p252533129.html?spid=252533130</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>649000</v>
+        <v>49000</v>
       </c>
       <c r="G28" t="n">
-        <v>750000</v>
+        <v>44000</v>
       </c>
       <c r="H28" t="n">
-        <v>101000</v>
+        <v>-5000</v>
       </c>
       <c r="I28" t="n">
-        <v>15.56</v>
+        <v>-10.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2775,26 +2775,26 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2804,53 +2804,53 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Giá tăng 101,000đ (+15.6%)</t>
+          <t>Giá giảm 5,000đ (10.2%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>152632563</t>
+          <t>277347854</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Mút Mỏng Trơn Không Gọng 3281 – Nhẹ Êm, Tự Nhiên, Dễ Mặc Mỗi Ngày</t>
+          <t>Thắt lưng nữ DA BÒ THẬT - BEE GEE N8051</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-duc-kiem-bra-cao-cap-3281-big-size-p152632563.html?spid=274990712</t>
+          <t>https://tiki.vn/that-lung-nu-da-bo-that-bee-gee-n8051-p277347854.html?spid=277347856</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Bee Gee</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>99000</v>
+        <v>150000</v>
       </c>
       <c r="G29" t="n">
-        <v>82170</v>
+        <v>300000</v>
       </c>
       <c r="H29" t="n">
-        <v>-16830</v>
+        <v>150000</v>
       </c>
       <c r="I29" t="n">
-        <v>-17</v>
+        <v>100</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -2888,47 +2888,47 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Giá giảm 16,830đ (17.0%)</t>
+          <t>Giá tăng 150,000đ (+100.0%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>276945307</t>
+          <t>278851165</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Áo lót nữ Angelavic 529 – Bra thun lạnh tăm, mút liền, cài sau, không gọng, nâng đỡ thoải mái</t>
+          <t>Dép quai ngang Biti's nam (38-43)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ao-bra-thun-lanh-tam-mut-lien-cai-sau-529-p276945307.html?spid=276945325</t>
+          <t>https://tiki.vn/dep-quai-ngang-biti-s-nam-38-43-p278851165.html?spid=278851187</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>110000</v>
+        <v>237000</v>
       </c>
       <c r="G30" t="n">
-        <v>82500</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-27500</v>
+        <v>-237000</v>
       </c>
       <c r="I30" t="n">
-        <v>-25</v>
+        <v>-100</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2943,16 +2943,16 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2962,63 +2962,63 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Giá giảm 27,500đ (25.0%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>277573177</t>
+          <t>277327053</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[Set 100 chiếc] Khẩu Trang 9A 5 Lớp Chống Nắng, Che Kín Mặt, Bảo Vệ Tia UV - HÀNG CHÍNH HÃNG MINIIN</t>
+          <t>Áo thun tay ngắn nam. Loose - RT 10S25TSS013 | ROUTINE CÀ MAU</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-100-chiec-khau-trang-9a-5-lop-chong-nang-che-kin-mat-bao-ve-tia-uv-hang-chinh-hang-miniin-p277573177.html?spid=277573179</t>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-loose-rt-10s25tss013-routine-ca-mau-p277327053.html?spid=277327071</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MINIIN</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>65000</v>
+        <v>379000</v>
       </c>
       <c r="G31" t="n">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-379000</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3030,76 +3030,76 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>-0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Rating 0.0→4.0 (+4.00) | Review thêm +1</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13307720</t>
+          <t>66507793</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Combo 10 Quần lót nam, sịp chéo nam xuất Nhật thời trang cao cấp</t>
+          <t>Dép Nam Da Bò BIGGBEN Cao Cấp DN260</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nam-sip-cheo-nam-xuat-nhat-thoi-trang-cao-cap-p13307720.html?spid=53788749</t>
+          <t>https://tiki.vn/dep-nam-da-bo-biggben-cao-cap-dn260-p66507793.html?spid=66507799</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>296450</v>
+        <v>400000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-296450</v>
+        <v>-400000</v>
       </c>
       <c r="I32" t="n">
         <v>-100</v>
       </c>
       <c r="J32" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3111,16 +3111,16 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-5</v>
+        <v>-4.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3147,17 +3147,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>248092080</t>
+          <t>250056510</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Giày lười nam da bò buộc dây Trường Hải màu nâu đề cao 3cm GM446N</t>
+          <t>Dép Nam Quai Ngang BIGGBEN Da Bò Thật Cao Cấp DN332</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-luoi-nam-da-bo-buoc-day-truong-hai-mau-nau-de-cao-3cm-gm446n-p248092080.html?spid=248092084</t>
+          <t>https://tiki.vn/dep-nam-quai-ngang-biggben-da-bo-that-cao-cap-dn332-p250056510.html?spid=250056524</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3167,23 +3167,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trường Hải</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>749000</v>
+        <v>450000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-749000</v>
+        <v>-450000</v>
       </c>
       <c r="I33" t="n">
         <v>-100</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3195,16 +3195,16 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3231,43 +3231,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>278442851</t>
+          <t>260889428</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quần Lót Nữ, Combo 6 Quần Lót Su Thạch Mát Lạnh Ngày Hè, Quần Lót Nữ Không Đường Viền - Hàng Nhập Khẩu</t>
+          <t>Khẩu Trang Chống Tia UV - Khẩu trang chống nắng che mặt UPF 50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nu-combo-6-quan-lot-su-thach-mat-lanh-ngay-he-quan-lot-nu-khong-duong-vien-hang-nhap-khau-p278442851.html?spid=278442852</t>
+          <t>https://tiki.vn/khau-trang-chong-tia-uv-khau-trang-chong-nang-che-mat-upf-50-p260889428.html?spid=279253607</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HT SYS</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>122000</v>
+        <v>19000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-122000</v>
+        <v>-19000</v>
       </c>
       <c r="I34" t="n">
         <v>-100</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3315,43 +3315,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>278529292</t>
+          <t>78513044</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dép quai ngang Bitis xốp nam</t>
+          <t>Khăn ống cotton tube co giãn 9 kiểu dùng có video hướng dẫn  TUBE01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-ngang-bitis-xop-nam-p278529292.html?spid=278529322</t>
+          <t>https://tiki.vn/khan-ong-cotton-tube-co-gian-9-kieu-dung-co-video-huong-dan-tube01-p78513044.html?spid=78518779</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>Song An Eco</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>126000</v>
+        <v>15000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-126000</v>
+        <v>-15000</v>
       </c>
       <c r="I35" t="n">
         <v>-100</v>
       </c>
       <c r="J35" t="n">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3363,16 +3363,16 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-4.6</v>
+        <v>-0</v>
       </c>
       <c r="Q35" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -3399,420 +3399,168 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>270249539</t>
+          <t>193504415</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Giày Tây Nam Tăng Chiều Cao BIGGBEN Da Bò Thật Cao Cấp GT252</t>
+          <t>Combo 2 Áo thun thể thao nam MRM Active Pro thấm hút mồ hôi tốt co dãn thoải mái vận động</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-tay-nam-tang-chieu-cao-biggben-da-bo-that-cao-cap-gt252-p270249539.html?spid=270249555</t>
+          <t>https://tiki.vn/combo-2-ao-thun-the-thao-nam-mrm-active-pro-tham-hut-mo-hoi-tot-co-dan-thoai-mai-van-dong-p193504415.html?spid=193504423</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>MRM Manlywear</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>799000</v>
+        <v>229000</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>229000</v>
       </c>
       <c r="H36" t="n">
-        <v>-799000</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>-916000</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Bán thêm -4 sản phẩm | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>208746104</t>
+          <t>275396535</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Giày Thể Thao Biti's Nam Hunter X DSMH10500</t>
+          <t>Bộ bơi nam quần 2 lớp trẻ trung nam tính thời trang, đồ bơi đồ tập kín đáo chống lộ, chất thoáng khí nhanh khô, áo thun bơi co giãn tốt, có size lớn | BN032</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-biti-s-nam-hunter-x-dsmh10500-p208746104.html?spid=208746130</t>
+          <t>https://tiki.vn/bo-boi-nam-quan-2-lop-tre-trung-nam-tinh-thoi-trang-do-boi-do-tap-kin-dao-chong-lo-chat-thoang-khi-nhanh-kho-ao-thun-boi-co-gian-tot-co-size-lon-bn032-p275396535.html?spid=275396555</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1050000</v>
+        <v>310000</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>310000</v>
       </c>
       <c r="H37" t="n">
-        <v>-1050000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
+        <v>9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-930000</v>
+      </c>
+      <c r="N37" t="n">
         <v>5</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>4</v>
-      </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>276545723</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Dép quai kẹp Bitis nam (38-43)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-quai-kep-bitis-nam-38-43-p276545723.html?spid=276545737</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Biti's</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>92000</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-92000</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J38" t="n">
-        <v>7</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>52317590</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Bộ 2 mũ lưỡi trai cho nam ( đen - trắng)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/bo-2-mu-luoi-trai-cho-nam-den-trang-p52317590.html?spid=162171783</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>LQ luxury</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>49000</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-49000</v>
-      </c>
-      <c r="I39" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J39" t="n">
-        <v>21</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>278004504</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Combo 5 Quần Lót Nữ Su Tăm Trơn Không Viền Mỏng Nhẹ 892 – Co Giãn 4 Chiều, Thoáng Mát, Không Lộ Viền (Size L/XL/XXL)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nu-su-tam-tron-khong-vien-mong-nhe-892-co-gian-4-chieu-thoang-mat-khong-lo-vien-size-l-xl-xxl-p278004504.html?spid=278004508</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>168000</v>
-      </c>
-      <c r="G40" t="n">
-        <v>230000</v>
-      </c>
-      <c r="H40" t="n">
-        <v>62000</v>
-      </c>
-      <c r="I40" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M40" t="n">
-        <v>-230000</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Giá tăng 62,000đ (+36.9%) | Bán thêm -1 sản phẩm</t>
+          <t>Bán thêm -3 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>73214429</t>
+          <t>67538621</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Áo Khoác Nam Áo Khoác Dù Nam Nữ Hai Lớp Chống Nước Chống Nắng Chống Gió Phối Nón Cao Cấp QD54 - ShopN6 (Nhiều Màu)</t>
+          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-nam-ao-khoac-du-nam-nu-hai-lop-chong-nuoc-chong-nang-chong-gio-phoi-non-cao-cap-qd54-shopn6-nhieu-mau-p73214429.html?spid=73214433</t>
+          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538623</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -563,81 +563,81 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N6</t>
+          <t>May 10</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="G2" t="n">
-        <v>189000</v>
+        <v>135000</v>
       </c>
       <c r="H2" t="n">
-        <v>189000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>16583</v>
       </c>
       <c r="K2" t="n">
-        <v>442</v>
+        <v>16599</v>
       </c>
       <c r="L2" t="n">
-        <v>442</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
-        <v>83538000</v>
+        <v>2160000</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4842</v>
       </c>
       <c r="R2" t="n">
-        <v>181</v>
+        <v>4842</v>
       </c>
       <c r="S2" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +16 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>134757898</t>
+          <t>263276725</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giày da nam, giày oxford công sở Bụi Leather G106 - Da bò Nappa cao cấp - Bảo hành 12 tháng</t>
+          <t>Chuck Taylor Classic Black Canvas Low | Giày Thể Thao Đen Cổ Thấp M9166C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-da-nam-giay-oxford-cong-so-bui-leather-g106-da-bo-nappa-cao-cap-bao-hanh-12-thang-p134757898.html?spid=134757930</t>
+          <t>https://tiki.vn/chuck-taylor-classic-black-giay-the-thao-den-co-thap-p263276725.html?spid=263276727</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bụi Leather</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>865000</v>
+        <v>1600000</v>
       </c>
       <c r="H3" t="n">
-        <v>865000</v>
+        <v>1600000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>61415000</v>
+        <v>1600000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,17 +711,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>136093004</t>
+          <t>275396535</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Áo thun may ô ngắn tay (áo đông xuân) nam</t>
+          <t>Bộ bơi nam quần 2 lớp trẻ trung nam tính thời trang, đồ bơi đồ tập kín đáo chống lộ, chất thoáng khí nhanh khô, áo thun bơi co giãn tốt, có size lớn | BN032</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-may-o-ngan-tay-ao-dong-xuan-nam-p136093004.html?spid=136093008</t>
+          <t>https://tiki.vn/bo-boi-nam-quan-2-lop-tre-trung-nam-tinh-thoi-trang-do-boi-do-tap-kin-dao-chong-lo-chat-thoang-khi-nhanh-kho-ao-thun-boi-co-gian-tot-co-size-lon-bn032-p275396535.html?spid=275396553</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -731,14 +731,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">	OEM</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>69000</v>
+        <v>310000</v>
       </c>
       <c r="G4" t="n">
-        <v>69000</v>
+        <v>310000</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -747,16 +747,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>232</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>258</v>
+        <v>17</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>1794000</v>
+        <v>1550000</v>
       </c>
       <c r="N4" t="n">
         <v>5</v>
@@ -768,17 +768,17 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -788,128 +788,128 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Bán thêm +26 sản phẩm</t>
+          <t>Bán thêm +5 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>174437687</t>
+          <t>277468360</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dép nhựa Bitis nam</t>
+          <t>Mũ Trùm Đầu Chống Nắng Kèm Khẩu Trang Nam Nữ - Nón Che Nắng Chống Tia UV Có Dây Rút</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nhua-bitis-nam-p174437687.html?spid=174437691</t>
+          <t>https://tiki.vn/mu-trum-dau-chong-nang-kem-khau-trang-nam-nu-non-che-nang-chong-tia-uv-co-day-rut-p277468360.html?spid=277468368</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>105000</v>
+        <v>153000</v>
       </c>
       <c r="H5" t="n">
-        <v>15000</v>
+        <v>153000</v>
       </c>
       <c r="I5" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>1680000</v>
+        <v>612000</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Giá tăng 15,000đ (+16.7%) | Bán thêm +16 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>147249168</t>
+          <t>162562752</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dép Nam Quai Ngang HÀ NAM Da Bò Thật Cao Cấp DNA2158</t>
+          <t>Combo 10 quần lót nữ chất liệu cotton chất đẹp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-ha-nam-cao-cap-dna2158-p147249168.html?spid=147249212</t>
+          <t>https://tiki.vn/combo-10-quan-lot-nu-chat-lieu-cotton-chat-dep-p162562752.html?spid=162562761</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HA NAM</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>372000</v>
+        <v>150000</v>
       </c>
       <c r="H6" t="n">
-        <v>372000</v>
+        <v>150000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>372000</v>
+        <v>300000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -963,22 +963,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23452446</t>
+          <t>279279665</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Áo Khoác kaki nam</t>
+          <t>Hộp đựng thuốc 20Đ dài slim Foucs YH061</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-kaki-nam-p23452446.html?spid=113226723</t>
+          <t>https://tiki.vn/hop-dung-thuoc-20d-dai-slim-foucs-yh061-p279279665.html?spid=279279667</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -990,10 +990,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>331000</v>
+        <v>99000</v>
       </c>
       <c r="H7" t="n">
-        <v>331000</v>
+        <v>99000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1002,13 +1002,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>331000</v>
+        <v>198000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,34 +1047,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>808362</t>
+          <t>275276422</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bộ 5 Đôi Vớ Nam Modal Công Sở Sọc Đen Donakein 7MM5D5M02</t>
+          <t>Dép tổ ong XANH NGỌC nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-5-doi-vo-nam-modal-cong-so-soc-den-donakein-7mm5d5m02-p808362.html?spid=811320</t>
+          <t>https://tiki.vn/dep-to-ong-xanh-ngoc-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276422.html?spid=275276436</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Donakein</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>199000</v>
+        <v>72000</v>
       </c>
       <c r="G8" t="n">
-        <v>199000</v>
+        <v>72000</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1083,16 +1083,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>199000</v>
+        <v>144000</v>
       </c>
       <c r="N8" t="n">
         <v>5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1124,128 +1124,128 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Bán thêm +2 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>262052731</t>
+          <t>34159085</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Áo thun nam thể thao DO GYM SHOP form ôm body, thun lạnh 4 chiều không xù lông</t>
+          <t>Combo 5 Đôi Tất Cổ Trung Cùng Màu Cotton Thương Hiệu MRM Manlywear</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-the-thao-do-gym-shop-form-om-body-thun-lanh-4-chieu-khong-xu-long-p262052731.html?spid=267343581</t>
+          <t>https://tiki.vn/combo-5-doi-tat-nam-tat-nam-vo-nam-co-dai-cao-cap-mrm-fashion-cung-mau-p34159085.html?spid=34159089</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MRM Manlywear</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="G9" t="n">
-        <v>159000</v>
+        <v>135000</v>
       </c>
       <c r="H9" t="n">
-        <v>159000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>4716</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>4717</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>159000</v>
+        <v>135000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>225209462</t>
+          <t>51299947</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MŨ CHỐNG NẮNG CÓI NỬA ĐẦU RỘNG VÀNH CÁ TÍNH CHO NỮ</t>
+          <t>Áo Sơ Mi Caro TitiShop SM1164 ( Luxury)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mu-chong-nang-coi-nua-dau-rong-vanh-ca-tinh-cho-nu-p225209462.html?spid=247940496</t>
+          <t>https://tiki.vn/ao-so-mi-caro-titishop-sm1164-luxury-p51299947.html?spid=51299949</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Titishop</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>55000</v>
+        <v>79000</v>
       </c>
       <c r="H10" t="n">
-        <v>55000</v>
+        <v>79000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1254,35 +1254,35 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>110000</v>
+        <v>79000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1299,17 +1299,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>252533129</t>
+          <t>271973646</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Găng Tay Hở 2 Ngón Unisex Chống Nắng, Có Thể Sử Dụng Cảm Ứng Điện Thoại</t>
+          <t>Miếng dán hình xăm kinh dị hóa trang Halloween vết sẹo xước máu giả vết khâu chảy máu vết thương Legaxi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/gang-tay-ho-2-ngon-unisex-chong-nang-co-the-su-dung-cam-ung-dien-thoai-p252533129.html?spid=252533130</t>
+          <t>https://tiki.vn/mieng-dan-hinh-xam-kinh-di-hoa-trang-halloween-vet-seo-xuoc-mau-gia-vet-khau-chay-mau-vet-thuong-legaxi-p271973646.html?spid=271973648</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1319,14 +1319,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Legaxi</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>49000</v>
+        <v>25000</v>
       </c>
       <c r="G11" t="n">
-        <v>49000</v>
+        <v>25000</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1335,16 +1335,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>98000</v>
+        <v>25000</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -1356,17 +1356,17 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1376,24 +1376,24 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Bán thêm +2 sản phẩm</t>
+          <t>Bán thêm +1 sản phẩm | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>214504425</t>
+          <t>279296102</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chai Xịt Tạo Bọt Vệ Sinh Giày XIMO Cao Cấp 300ml XVSG02</t>
+          <t>[NEW ARRIVAL] Giày Sneaker Nam Nữ DC48 SHADOW MOVE Dincox Shoes Đế Bằng - Da phối Suede Cao Cấp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-xit-tao-bot-ve-sinh-giay-ximo-cao-cap-300ml-xvsg02-p214504425.html?spid=252869350</t>
+          <t>https://tiki.vn/new-arrival-giay-sneaker-nam-nu-dc48-shadow-move-dincox-shoes-de-bang-da-phoi-suede-cao-cap-p279296102.html?spid=279296104</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1403,81 +1403,81 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>DINCOX</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>72000</v>
+        <v>650000</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>112851354</t>
+          <t>276945307</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Áo ngực học sinh</t>
+          <t>Áo lót nữ Angelavic 529 – Bra thun lạnh tăm, mút liền, cài sau, không gọng, nâng đỡ thoải mái</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138792</t>
+          <t>https://tiki.vn/ao-lot-nu-ao-bra-thun-lanh-tam-mut-lien-cai-sau-529-p276945307.html?spid=276945325</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1491,22 +1491,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40000</v>
+        <v>82500</v>
       </c>
       <c r="G13" t="n">
-        <v>30400</v>
+        <v>110000</v>
       </c>
       <c r="H13" t="n">
-        <v>-9600</v>
+        <v>27500</v>
       </c>
       <c r="I13" t="n">
-        <v>-24</v>
+        <v>33.33</v>
       </c>
       <c r="J13" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1515,26 +1515,26 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,53 +1544,53 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Giá giảm 9,600đ (24.0%)</t>
+          <t>Giá tăng 27,500đ (+33.3%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>277718250</t>
+          <t>244297794</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Giày Sandal nam cao cấp kiểu dáng mới – GSDNA10</t>
+          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-sandal-nam-cao-cap-kieu-dang-moi-gsdna10-p277718250.html?spid=277718278</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bee Gee</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>159600</v>
       </c>
       <c r="G14" t="n">
-        <v>583440</v>
+        <v>190000</v>
       </c>
       <c r="H14" t="n">
-        <v>583440</v>
+        <v>30400</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>19.05</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1599,53 +1599,53 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 30,400đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>279013580</t>
+          <t>72881856</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Áo sweater thu đông form rộng in hình hài hước "Mập rõ chứ không mập mờ" Mr.buffalo - [HN11] Áo Trắng</t>
+          <t>Quần lót nam thun lạnh không đường may, sịp đùi nam cao cấp kiểu dáng boxer nam ôm sát, chất liệu su thoáng mát, mềm mịn và mỏng nhẹ, quần lót cạp nhỏ đơn giản với màu trơn QLW806</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-sweater-thu-dong-form-rong-in-hinh-hai-huoc-map-ro-chu-khong-map-mo-mr-buffalo-p279013580.html?spid=279013592</t>
+          <t>https://tiki.vn/quan-lot-nam-thun-lanh-khong-duong-may-sip-dui-nam-cao-cap-kieu-dang-boxer-nam-om-sat-chat-lieu-su-thoang-mat-mem-min-va-mong-nhe-quan-lot-cap-nho-don-gian-voi-mau-tron-qlw806-p72881856.html?spid=102551187</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1659,22 +1659,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>160000</v>
+        <v>69000</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="H15" t="n">
-        <v>-160000</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1683,82 +1683,82 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>113145806</t>
+          <t>51297510</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
+          <t>Áo Sơ Mi Caro TitiShop SM1161 ( Luxury)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
+          <t>https://tiki.vn/ao-so-mi-caro-titishop-sm1161-luxury-p51297510.html?spid=51297512</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Titishop</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>88920</v>
+        <v>79000</v>
       </c>
       <c r="H16" t="n">
-        <v>-28080</v>
+        <v>79000</v>
       </c>
       <c r="I16" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1767,82 +1767,82 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Giá giảm 28,080đ (24.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>107802069</t>
+          <t>136093004</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
+          <t>Áo thun may ô ngắn tay (áo đông xuân) nam</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
+          <t>https://tiki.vn/ao-thun-may-o-ngan-tay-ao-dong-xuan-nam-p136093004.html?spid=136093008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t xml:space="preserve">	OEM</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>26000</v>
+        <v>69000</v>
       </c>
       <c r="G17" t="n">
-        <v>42000</v>
+        <v>89000</v>
       </c>
       <c r="H17" t="n">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="I17" t="n">
-        <v>61.54</v>
+        <v>28.99</v>
       </c>
       <c r="J17" t="n">
-        <v>1033</v>
+        <v>258</v>
       </c>
       <c r="K17" t="n">
-        <v>1033</v>
+        <v>258</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1851,26 +1851,26 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="R17" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1880,53 +1880,53 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá tăng 16,000đ (+61.5%)</t>
+          <t>Giá tăng 20,000đ (+29.0%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>278004504</t>
+          <t>277420779</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nữ Su Tăm Trơn Không Viền Mỏng Nhẹ 892 – Co Giãn 4 Chiều, Thoáng Mát, Không Lộ Viền (Size L/XL/XXL)</t>
+          <t>Khẩu Trang Chống Nắng Cao Cấp UPF 50+,Khẩu Trang Chống Nám Chống Tia UV, Bảo Vệ Da Hiệu Quả - HÀNG CHÍNH HÃNG MINIIN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nu-su-tam-tron-khong-vien-mong-nhe-892-co-gian-4-chieu-thoang-mat-khong-lo-vien-size-l-xl-xxl-p278004504.html?spid=278004508</t>
+          <t>https://tiki.vn/khau-trang-chong-nang-enaide-cao-cap-upf-50-chong-tia-uv-bao-ve-da-hieu-qua-hang-chinh-hang-miniin-p277420779.html?spid=277420793</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MINIIN</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>230000</v>
+        <v>55000</v>
       </c>
       <c r="G18" t="n">
-        <v>188600</v>
+        <v>27000</v>
       </c>
       <c r="H18" t="n">
-        <v>-41400</v>
+        <v>-28000</v>
       </c>
       <c r="I18" t="n">
-        <v>-18</v>
+        <v>-50.91</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1964,29 +1964,29 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá giảm 41,400đ (18.0%)</t>
+          <t>Giá giảm 28,000đ (50.9%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>113144956</t>
+          <t>279100044</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>siêu phẩm áo lót nhật trơn đệm nâng ngực nhẹ</t>
+          <t>Chai Xịt Khử Mùi Giày Dép 260ML</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/sieu-pham-ao-lot-tron-dem-nang-nguc-nhe-p113144956.html?spid=142116876</t>
+          <t>https://tiki.vn/chai-xit-khu-mui-giay-dep-260ml-p279100044.html?spid=279100045</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>165000</v>
+        <v>48000</v>
       </c>
       <c r="G19" t="n">
-        <v>123750</v>
+        <v>59000</v>
       </c>
       <c r="H19" t="n">
-        <v>-41250</v>
+        <v>11000</v>
       </c>
       <c r="I19" t="n">
-        <v>-25</v>
+        <v>22.92</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,26 +2019,26 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2048,41 +2048,41 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá giảm 41,250đ (25.0%)</t>
+          <t>Giá tăng 11,000đ (+22.9%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31638135</t>
+          <t>112814658</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Combo 4 quần lót nam Boxer sợi cạp 1cm sợi tre tự nhiên mềm mịn thấm hút mồ hôi, co giãn 4 chiều MRM Manlywear - Màu ngẫu nhiên</t>
+          <t>Thắt Lưng Nam Dây Vải Dù Phong Cách Lính U379 US ARMY, Khóa Cài Tự Động Dễ Dàng Điều Chỉnh Theo Vòng Bụng- HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-4-quan-sip-dui-nam-quan-lot-nam-boxer-soi-tre-mem-min-sieu-thoang-mat-co-gian-4-chieu-cao-cap-cap-1cm-mrm-fashion-3-mau-p31638135.html?spid=31638146</t>
+          <t>https://tiki.vn/that-lung-nam-day-vai-du-phong-cach-linh-u379-us-army-khoa-cai-tu-dong-de-dang-dieu-chinh-theo-vong-bung-hang-chinh-hang-p112814658.html?spid=174134932</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>255000</v>
+        <v>99000</v>
       </c>
       <c r="G20" t="n">
-        <v>255000</v>
+        <v>99000</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2091,10 +2091,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>5855</v>
+        <v>75</v>
       </c>
       <c r="K20" t="n">
-        <v>5855</v>
+        <v>75</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2103,26 +2103,26 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1371</v>
+        <v>28</v>
       </c>
       <c r="R20" t="n">
-        <v>1372</v>
+        <v>29</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2139,22 +2139,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>279100044</t>
+          <t>276146188</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chai Xịt Khử Mùi Giày Dép 260ML</t>
+          <t>Combo đồ bơi nam quần 2 lớp kèm kính mũ bơi, túi đựng đồ và bịt tai kẹp mũi, set bơi đầy đủ tiện lợi cho nam giới, quần bơi 2 lớp &amp; kính chống đọng sương | BN032</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-xit-khu-mui-giay-dep-260ml-p279100044.html?spid=279100045</t>
+          <t>https://tiki.vn/combo-do-boi-nam-quan-2-lop-kem-kinh-mu-boi-tui-dung-do-va-bit-tai-kep-mui-set-boi-day-du-tien-loi-cho-nam-gioi-quan-boi-2-lop-kinh-chong-dong-suong-bn032-p276146188.html?spid=276146212</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2163,22 +2163,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>59000</v>
+        <v>350000</v>
       </c>
       <c r="G21" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-11000</v>
+        <v>-350000</v>
       </c>
       <c r="I21" t="n">
-        <v>-18.64</v>
+        <v>-100</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2206,54 +2206,54 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Giá giảm 11,000đ (18.6%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>279295872</t>
+          <t>75728341</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Giày Da Sneaker Nam Nữ DC39 Oreo Dincox Shoes Đế Bằng - Microfiber Leather</t>
+          <t>Áo Sơ Mi Nam Titishop SM1281</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-da-sneaker-nam-nu-dc39-oreo-dincox-shoes-de-bang-microfiber-leather-p279295872.html?spid=279295884</t>
+          <t>https://tiki.vn/ao-so-mi-nam-titishop-sm1281-p75728341.html?spid=75728349</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DINCOX</t>
+          <t>Titishop</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>660000</v>
+        <v>59000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-660000</v>
+        <v>-59000</v>
       </c>
       <c r="I22" t="n">
         <v>-100</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2307,43 +2307,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>276561845</t>
+          <t>152632563</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Giày thể thao Bitis hunter nam (40-45)</t>
+          <t>Áo Lót Nữ Mút Mỏng Trơn Không Gọng 3281 – Nhẹ Êm, Tự Nhiên, Dễ Mặc Mỗi Ngày</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-bitis-hunter-nam-40-45-p276561845.html?spid=276561867</t>
+          <t>https://tiki.vn/ao-lot-duc-kiem-bra-cao-cap-3281-big-size-p152632563.html?spid=274990712</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>869000</v>
+        <v>82170</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-869000</v>
+        <v>-82170</v>
       </c>
       <c r="I23" t="n">
         <v>-100</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2355,16 +2355,16 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2391,43 +2391,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>160418420</t>
+          <t>163806087</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ÁO CHỐNG NẮNG NAM THÔNG HƠI VẢI KIM CƯƠNG</t>
+          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-chong-nang-nam-thong-hoi-vai-kim-cuong-p160418420.html?spid=174620121</t>
+          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-p163806087.html?spid=253461440</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>165000</v>
+        <v>59000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-165000</v>
+        <v>-59000</v>
       </c>
       <c r="I24" t="n">
         <v>-100</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2439,16 +2439,16 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2475,17 +2475,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>279149590</t>
+          <t>273550361</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Keo Dán Sửa Chữa Giày Siêu Chắc Shoe Glue Plr80 60Ml Đa Năng</t>
+          <t>Lót giày sức khỏe cho chân vòm cao Spenco Ground Control High Arch ôm sát vòm chân</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/keo-dan-sua-chua-giay-sieu-chac-shoe-glue-plr80-60ml-da-nang-p279149590.html?spid=279149591</t>
+          <t>https://tiki.vn/lot-giay-y-khoa-spenco-ground-control-high-arch-p273550361.html?spid=273550365</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2495,23 +2495,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Spenco</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>49000</v>
+        <v>895000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-49000</v>
+        <v>-895000</v>
       </c>
       <c r="I25" t="n">
         <v>-100</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2523,16 +2523,16 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2559,43 +2559,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>277342816</t>
+          <t>273097909</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam. Regular - RT 10F24TSS070R1 | ROUTINE CÀ MAU</t>
+          <t>Tròng kính cận/viễn/loạn mỏng 1.60 chemi đổi màu thời trang OURESS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-regular-rt-10f24tss070r1-routine-ca-mau-p277342816.html?spid=277342840</t>
+          <t>https://tiki.vn/trong-kinh-can-vien-loan-mong-1-60-chemi-doi-mau-thoi-trang-ouress-p273097909.html?spid=273097910</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OURESS</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>349000</v>
+        <v>1100000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-349000</v>
+        <v>-1100000</v>
       </c>
       <c r="I26" t="n">
         <v>-100</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2643,17 +2643,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16212451</t>
+          <t>225209462</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Combo 6 Quần tất da nữ siêu dai và mịn</t>
+          <t>MŨ CHỐNG NẮNG CÓI NỬA ĐẦU RỘNG VÀNH CÁ TÍNH CHO NỮ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-6-quan-tat-da-nu-sieu-dai-va-min-p16212451.html?spid=44145983</t>
+          <t>https://tiki.vn/mu-chong-nang-coi-nua-dau-rong-vanh-ca-tinh-cho-nu-p225209462.html?spid=247940496</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2663,23 +2663,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TOMAN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>144000</v>
+        <v>55000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-144000</v>
+        <v>-55000</v>
       </c>
       <c r="I27" t="n">
         <v>-100</v>
       </c>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2691,16 +2691,16 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2721,174 +2721,6 @@
       <c r="V27" t="inlineStr">
         <is>
           <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>275276334</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Dép tổ ong XÁM nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-to-ong-xam-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276334.html?spid=275276350</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VAC </t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>72000</v>
-      </c>
-      <c r="G28" t="n">
-        <v>72000</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>87</v>
-      </c>
-      <c r="K28" t="n">
-        <v>85</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-144000</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Bán thêm -2 sản phẩm</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>274937386</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Bộ bơi nữ big size cao cấp, mẫu 2 mảnh áo cộc tay có khóa kéo trước, quần boxer trẻ trung, chất thun bơi lạnh Lycra co giãn đa chiều, dày dặn mịn mát, chống thấm nước nhanh khô | KT110</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/bo-boi-nu-big-size-cao-cap-mau-2-manh-ao-coc-tay-co-khoa-keo-truoc-quan-boxer-tre-trung-chat-thun-boi-lanh-lycra-co-gian-da-chieu-day-dan-min-mat-chong-tham-nuoc-nhanh-kho-kt110-p274937386.html?spid=274937410</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>480000</v>
-      </c>
-      <c r="G29" t="n">
-        <v>480000</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>12</v>
-      </c>
-      <c r="K29" t="n">
-        <v>9</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>-1440000</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>5</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Bán thêm -3 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -543,185 +543,185 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>67538621</t>
+          <t>24030500</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
+          <t>Bộ 5 quần lót nữ basic Comfort Modal MILEY LINGERIE - Màu ngẫu nhiên</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538623</t>
+          <t>https://tiki.vn/bo-5-quan-lot-nu-basic-comfort-modal-miley-lingerie-mau-ngau-nhien-p24030500.html?spid=24030504</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>May 10</t>
+          <t>Miley Lingerie</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>135000</v>
+        <v>320000</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>320000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>16583</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>16599</v>
+        <v>72</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="M2" t="n">
-        <v>2160000</v>
+        <v>23040000</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>4842</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4842</v>
+        <v>12</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Bán thêm +16 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>263276725</t>
+          <t>277573177</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chuck Taylor Classic Black Canvas Low | Giày Thể Thao Đen Cổ Thấp M9166C</t>
+          <t>[Set 100 chiếc] Khẩu Trang 9A 5 Lớp Chống Nắng, Che Kín Mặt, Bảo Vệ Tia UV - HÀNG CHÍNH HÃNG MINIIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chuck-taylor-classic-black-giay-the-thao-den-co-thap-p263276725.html?spid=263276727</t>
+          <t>https://tiki.vn/set-100-chiec-khau-trang-9a-5-lop-chong-nang-che-kin-mat-bao-ve-tia-uv-hang-chinh-hang-miniin-p277573177.html?spid=277573181</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>MINIIN</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="G3" t="n">
-        <v>1600000</v>
+        <v>59000</v>
       </c>
       <c r="H3" t="n">
-        <v>1600000</v>
+        <v>-6000</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-9.23</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
+        <v>21</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>944000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 6,000đ (9.2%) | Bán thêm +16 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>275396535</t>
+          <t>14351068</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bộ bơi nam quần 2 lớp trẻ trung nam tính thời trang, đồ bơi đồ tập kín đáo chống lộ, chất thoáng khí nhanh khô, áo thun bơi co giãn tốt, có size lớn | BN032</t>
+          <t>Áo thun Nam có cổ thời trang</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-boi-nam-quan-2-lop-tre-trung-nam-tinh-thoi-trang-do-boi-do-tap-kin-dao-chong-lo-chat-thoang-khi-nhanh-kho-ao-thun-boi-co-gian-tot-co-size-lon-bn032-p275396535.html?spid=275396553</t>
+          <t>https://tiki.vn/ao-thun-nam-co-co-thoi-trang-p14351068.html?spid=14351092</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>310000</v>
+        <v>160000</v>
       </c>
       <c r="G4" t="n">
-        <v>310000</v>
+        <v>160000</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -747,38 +747,38 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>640000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" t="n">
-        <v>1550000</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>5</v>
       </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -788,29 +788,29 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Bán thêm +5 sản phẩm</t>
+          <t>Bán thêm +4 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>277468360</t>
+          <t>244297794</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mũ Trùm Đầu Chống Nắng Kèm Khẩu Trang Nam Nữ - Nón Che Nắng Chống Tia UV Có Dây Rút</t>
+          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mu-trum-dau-chong-nang-kem-khau-trang-nam-nu-non-che-nang-chong-tia-uv-co-day-rut-p277468360.html?spid=277468368</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -819,82 +819,82 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="G5" t="n">
-        <v>153000</v>
+        <v>148200</v>
       </c>
       <c r="H5" t="n">
-        <v>153000</v>
+        <v>-41800</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>612000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 41,800đ (22.0%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>162562752</t>
+          <t>16375016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Combo 10 quần lót nữ chất liệu cotton chất đẹp</t>
+          <t>COMBO HỘP 5 Quần Lót ĐÙI Nam Xuất Nhật Cao Cấp (MIX NGẪU NHIÊN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nu-chat-lieu-cotton-chat-dep-p162562752.html?spid=162562761</t>
+          <t>https://tiki.vn/combo-hop-5-quan-lot-dui-nam-xuat-nhat-cao-cap-mix-ngau-nhien-p16375016.html?spid=277961877</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -903,28 +903,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>251000</v>
       </c>
       <c r="G6" t="n">
-        <v>150000</v>
+        <v>198290</v>
       </c>
       <c r="H6" t="n">
-        <v>150000</v>
+        <v>-52710</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -946,39 +946,39 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 52,710đ (21.0%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>279279665</t>
+          <t>277919931</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hộp đựng thuốc 20Đ dài slim Foucs YH061</t>
+          <t>Combo 5 quần lót nữ thun lạnh thông hơi Voronin 2067 – Mát mịn, co giãn 4 chiều, không hằn viền</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-dung-thuoc-20d-dai-slim-foucs-yh061-p279279665.html?spid=279279667</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nu-thun-lanh-thong-hoi-voronin-2067-mat-min-co-gian-4-chieu-khong-han-vien-p277919931.html?spid=277919932</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -987,134 +987,134 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="G7" t="n">
-        <v>99000</v>
+        <v>150100</v>
       </c>
       <c r="H7" t="n">
-        <v>99000</v>
+        <v>-39900</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>198000</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 39,900đ (21.0%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>275276422</t>
+          <t>74421501</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dép tổ ong XANH NGỌC nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-xanh-ngoc-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276422.html?spid=275276436</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>72000</v>
+        <v>118500</v>
       </c>
       <c r="G8" t="n">
-        <v>72000</v>
+        <v>160000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>41500</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>35.02</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>153</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>144000</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1124,81 +1124,81 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +2 sản phẩm</t>
+          <t>Giá tăng 41,500đ (+35.0%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>34159085</t>
+          <t>244298352</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combo 5 Đôi Tất Cổ Trung Cùng Màu Cotton Thương Hiệu MRM Manlywear</t>
+          <t>Quần Gen Ôm Bụng Dạng Đùi Có Thanh Chống Cuộn Voronin 8292 – Siêu Gọn, Siêu Định Hình</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-doi-tat-nam-tat-nam-vo-nam-co-dai-cao-cap-mrm-fashion-cung-mau-p34159085.html?spid=34159089</t>
+          <t>https://tiki.vn/quan-gen-chong-cuon-dui-8292-p244298352.html?spid=244298362</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>135000</v>
+        <v>122000</v>
       </c>
       <c r="G9" t="n">
-        <v>135000</v>
+        <v>97600</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-24400</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="J9" t="n">
-        <v>4716</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4717</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1208,24 +1208,24 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Giá giảm 24,400đ (20.0%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>51299947</t>
+          <t>278021672</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Áo Sơ Mi Caro TitiShop SM1164 ( Luxury)</t>
+          <t>Quần Lót Nam Đùi Boxer Lụa Băng Menpro MP9 - Mỏng nhem Thoáng Khí</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-caro-titishop-sm1164-luxury-p51299947.html?spid=51299949</t>
+          <t>https://tiki.vn/quan-lot-nam-dui-boxer-lua-bang-menpro-mp9-mong-nhem-thoang-khi-p278021672.html?spid=278021690</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1235,32 +1235,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Titishop</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>63200</v>
       </c>
       <c r="G10" t="n">
         <v>79000</v>
       </c>
       <c r="H10" t="n">
-        <v>79000</v>
+        <v>15800</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>79000</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1282,51 +1282,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 15,800đ (+25.0%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>271973646</t>
+          <t>67538621</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Miếng dán hình xăm kinh dị hóa trang Halloween vết sẹo xước máu giả vết khâu chảy máu vết thương Legaxi</t>
+          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mieng-dan-hinh-xam-kinh-di-hoa-trang-halloween-vet-seo-xuoc-mau-gia-vet-khau-chay-mau-vet-thuong-legaxi-p271973646.html?spid=271973648</t>
+          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538623</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Legaxi</t>
+          <t>May 10</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>25000</v>
+        <v>135000</v>
       </c>
       <c r="G11" t="n">
-        <v>25000</v>
+        <v>135000</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1335,38 +1335,38 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>16599</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>16599</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>4842</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>4843</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1376,47 +1376,47 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm | Review thêm +1</t>
+          <t>Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>279296102</t>
+          <t>277983818</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[NEW ARRIVAL] Giày Sneaker Nam Nữ DC48 SHADOW MOVE Dincox Shoes Đế Bằng - Da phối Suede Cao Cấp</t>
+          <t>Áo Lót Nữ Ren Dày Cài Trước Có Gọng Nâng Ngực Belle VC02 – Combo Đa Màu, Đệm Mút 3 cm, Quyến Rũ &amp; Đỡ Đỡ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/new-arrival-giay-sneaker-nam-nu-dc48-shadow-move-dincox-shoes-de-bang-da-phoi-suede-cao-cap-p279296102.html?spid=279296104</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-day-cai-truoc-co-gong-nang-nguc-belle-vc02-combo-da-mau-dem-mut-3-cm-quyen-ru-do-do-p277983818.html?spid=277983822</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DINCOX</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="G12" t="n">
-        <v>650000</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>650000</v>
+        <v>-150000</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1450,34 +1450,34 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>276945307</t>
+          <t>278883514</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Áo lót nữ Angelavic 529 – Bra thun lạnh tăm, mút liền, cài sau, không gọng, nâng đỡ thoải mái</t>
+          <t>Áo sơ mi xếp 3 li kết ngọc tay dài</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ao-bra-thun-lanh-tam-mut-lien-cai-sau-529-p276945307.html?spid=276945325</t>
+          <t>https://tiki.vn/ao-so-mi-xep-3-li-ket-ngoc-tay-dai-p278883514.html?spid=278883520</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1491,16 +1491,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>82500</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>110000</v>
+        <v>125000</v>
       </c>
       <c r="H13" t="n">
-        <v>27500</v>
+        <v>125000</v>
       </c>
       <c r="I13" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1534,63 +1534,63 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Giá tăng 27,500đ (+33.3%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>244297794</t>
+          <t>115852451</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
+          <t>Chai vệ sinh giày đồ da, túi ví, áo, ghế da giúp làm sạch, dưỡng ẩm chống mốc XIMO XI03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
+          <t>https://tiki.vn/chai-ve-sinh-giay-do-da-tui-vi-ao-ghe-da-giup-lam-sach-duong-am-chong-moc-ximo-xi03-p115852451.html?spid=262784198</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>159600</v>
+        <v>75000</v>
       </c>
       <c r="G14" t="n">
-        <v>190000</v>
+        <v>70000</v>
       </c>
       <c r="H14" t="n">
-        <v>30400</v>
+        <v>-5000</v>
       </c>
       <c r="I14" t="n">
-        <v>19.05</v>
+        <v>-6.67</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1599,26 +1599,26 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1628,29 +1628,29 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Giá tăng 30,400đ (+19.0%)</t>
+          <t>Giá giảm 5,000đ (6.7%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>72881856</t>
+          <t>244297862</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quần lót nam thun lạnh không đường may, sịp đùi nam cao cấp kiểu dáng boxer nam ôm sát, chất liệu su thoáng mát, mềm mịn và mỏng nhẹ, quần lót cạp nhỏ đơn giản với màu trơn QLW806</t>
+          <t>Áo Lót Nữ Bra Ống Su Gân Viền Ren Cài Sau 4003 – Seamless, Co Giãn 4 Chiều</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-thun-lanh-khong-duong-may-sip-dui-nam-cao-cap-kieu-dang-boxer-nam-om-sat-chat-lieu-su-thoang-mat-mem-min-va-mong-nhe-quan-lot-cap-nho-don-gian-voi-mau-tron-qlw806-p72881856.html?spid=102551187</t>
+          <t>https://tiki.vn/ao-bra-ong-su-gan-cai-sau-4003-p244297862.html?spid=244297867</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1659,22 +1659,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>69000</v>
+        <v>36800</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>36800</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1683,73 +1683,73 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Review thêm +1</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51297510</t>
+          <t>279295829</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Áo Sơ Mi Caro TitiShop SM1161 ( Luxury)</t>
+          <t>Giày Sneaker Da - GAT Shoes Nam Nữ DC36 White Dune Dincox Shoes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-caro-titishop-sm1161-luxury-p51297510.html?spid=51297512</t>
+          <t>https://tiki.vn/giay-sneaker-da-gat-shoes-nam-nu-dc36-white-dune-dincox-shoes-p279295829.html?spid=279295837</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Titishop</t>
+          <t>DINCOX</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>79000</v>
+        <v>600000</v>
       </c>
       <c r="H16" t="n">
-        <v>79000</v>
+        <v>600000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1803,46 +1803,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>136093004</t>
+          <t>278957623</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Áo thun may ô ngắn tay (áo đông xuân) nam</t>
+          <t>Dép quai kẹp Biti's nam (size 38-43)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-may-o-ngan-tay-ao-dong-xuan-nam-p136093004.html?spid=136093008</t>
+          <t>https://tiki.vn/dep-quai-kep-biti-s-nam-size-38-43-p278957623.html?spid=278957641</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">	OEM</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>89000</v>
+        <v>232000</v>
       </c>
       <c r="H17" t="n">
-        <v>20000</v>
+        <v>232000</v>
       </c>
       <c r="I17" t="n">
-        <v>28.99</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1851,53 +1851,53 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá tăng 20,000đ (+29.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>277420779</t>
+          <t>278863219</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Khẩu Trang Chống Nắng Cao Cấp UPF 50+,Khẩu Trang Chống Nám Chống Tia UV, Bảo Vệ Da Hiệu Quả - HÀNG CHÍNH HÃNG MINIIN</t>
+          <t>Dây Lưng Nam Thắt Lưng Da Chính Hãng GENCE LG52 Chất Liệu Da Bò Cao Cấp Màu Nâu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khau-trang-chong-nang-enaide-cao-cap-upf-50-chong-tia-uv-bao-ve-da-hieu-qua-hang-chinh-hang-miniin-p277420779.html?spid=277420793</t>
+          <t>https://tiki.vn/day-lung-nam-that-lung-da-chinh-hang-gence-lg52-chat-lieu-da-bo-cao-cap-mau-nau-p278863219.html?spid=278863220</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1907,26 +1907,26 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MINIIN</t>
+          <t>Gence</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>27000</v>
+        <v>715000</v>
       </c>
       <c r="H18" t="n">
-        <v>-28000</v>
+        <v>715000</v>
       </c>
       <c r="I18" t="n">
-        <v>-50.91</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1954,39 +1954,39 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá giảm 28,000đ (50.9%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>279100044</t>
+          <t>146589320</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chai Xịt Khử Mùi Giày Dép 260ML</t>
+          <t>Cài tóc pha lê kim cương sang trọng - bờm tóc pha lê - quà tặng cho bạn gái</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-xit-khu-mui-giay-dep-260ml-p279100044.html?spid=279100045</t>
+          <t>https://tiki.vn/cai-toc-pha-le-kim-cuong-sang-trong-bom-toc-pha-le-qua-tang-cho-ban-gai-p146589320.html?spid=146589326</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1995,50 +1995,50 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>48000</v>
+        <v>68000</v>
       </c>
       <c r="G19" t="n">
-        <v>59000</v>
+        <v>68000</v>
       </c>
       <c r="H19" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>22.92</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
+        <v>130</v>
+      </c>
+      <c r="K19" t="n">
+        <v>130</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>18</v>
+      </c>
+      <c r="R19" t="n">
+        <v>19</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2048,53 +2048,53 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá tăng 11,000đ (+22.9%)</t>
+          <t>Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>112814658</t>
+          <t>147249168</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thắt Lưng Nam Dây Vải Dù Phong Cách Lính U379 US ARMY, Khóa Cài Tự Động Dễ Dàng Điều Chỉnh Theo Vòng Bụng- HÀNG CHÍNH HÃNG</t>
+          <t>Dép Nam Quai Ngang HÀ NAM Da Bò Thật Cao Cấp DNA2158</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-nam-day-vai-du-phong-cach-linh-u379-us-army-khoa-cai-tu-dong-de-dang-dieu-chinh-theo-vong-bung-hang-chinh-hang-p112814658.html?spid=174134932</t>
+          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-ha-nam-cao-cap-dna2158-p147249168.html?spid=147249212</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>HA NAM</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>99000</v>
+        <v>372000</v>
       </c>
       <c r="G20" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-372000</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2103,73 +2103,73 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Review thêm +1</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>276146188</t>
+          <t>277718250</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Combo đồ bơi nam quần 2 lớp kèm kính mũ bơi, túi đựng đồ và bịt tai kẹp mũi, set bơi đầy đủ tiện lợi cho nam giới, quần bơi 2 lớp &amp; kính chống đọng sương | BN032</t>
+          <t>Giày Sandal nam cao cấp kiểu dáng mới – GSDNA10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-do-boi-nam-quan-2-lop-kem-kinh-mu-boi-tui-dung-do-va-bit-tai-kep-mui-set-boi-day-du-tien-loi-cho-nam-gioi-quan-boi-2-lop-kinh-chong-dong-suong-bn032-p276146188.html?spid=276146212</t>
+          <t>https://tiki.vn/giay-sandal-nam-cao-cap-kieu-dang-moi-gsdna10-p277718250.html?spid=277718278</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Bee Gee</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>350000</v>
+        <v>583440</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-350000</v>
+        <v>-583440</v>
       </c>
       <c r="I21" t="n">
         <v>-100</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2223,37 +2223,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>75728341</t>
+          <t>244298960</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Áo Sơ Mi Nam Titishop SM1281</t>
+          <t>Quần Mặc Váy Su Thông Hơi Trơn 6530 | Mát Mẻ, Không Lộ, Chống Hớ Hiệu Quả</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nam-titishop-sm1281-p75728341.html?spid=75728349</t>
+          <t>https://tiki.vn/quan-vay-dai-thong-hoi-6530-p244298960.html?spid=244298972</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Titishop</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>59000</v>
+        <v>35280</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-59000</v>
+        <v>-35280</v>
       </c>
       <c r="I22" t="n">
         <v>-100</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2307,17 +2307,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>152632563</t>
+          <t>279292197</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Mút Mỏng Trơn Không Gọng 3281 – Nhẹ Êm, Tự Nhiên, Dễ Mặc Mỗi Ngày</t>
+          <t>Quần Lọt Khe Thêu Nơ Ren Lưới Xuyên Thấu Đính Nơ Sau Xinh Xắn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-duc-kiem-bra-cao-cap-3281-big-size-p152632563.html?spid=274990712</t>
+          <t>https://tiki.vn/quan-lot-khe-theu-no-ren-luoi-xuyen-thau-dinh-no-sau-xinh-xan-p279292197.html?spid=279292199</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2327,23 +2327,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Sanny House</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>82170</v>
+        <v>82500</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-82170</v>
+        <v>-82500</v>
       </c>
       <c r="I23" t="n">
         <v>-100</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2391,43 +2391,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>163806087</t>
+          <t>275632752</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da</t>
+          <t>Thắt lưng nam da bò nguyên chất mặt khóa tự động hợp kim cao cấp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-p163806087.html?spid=253461440</t>
+          <t>https://tiki.vn/that-lung-nam-da-bo-nguyen-chat-mat-khoa-tu-dong-hop-kim-cao-cap-p275632752.html?spid=275632754</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>ANANSHOP688</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>59000</v>
+        <v>190000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-59000</v>
+        <v>-190000</v>
       </c>
       <c r="I24" t="n">
         <v>-100</v>
       </c>
       <c r="J24" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2439,16 +2439,16 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-5</v>
+        <v>-4.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2475,17 +2475,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>273550361</t>
+          <t>275276374</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lót giày sức khỏe cho chân vòm cao Spenco Ground Control High Arch ôm sát vòm chân</t>
+          <t>Dép tổ ong XANH RÊU nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/lot-giay-y-khoa-spenco-ground-control-high-arch-p273550361.html?spid=273550365</t>
+          <t>https://tiki.vn/dep-to-ong-xanh-reu-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276374.html?spid=275276382</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2495,170 +2495,170 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spenco</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>895000</v>
+        <v>72000</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="H25" t="n">
-        <v>-895000</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>-72000</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Bán thêm -1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>273097909</t>
+          <t>174437687</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tròng kính cận/viễn/loạn mỏng 1.60 chemi đổi màu thời trang OURESS</t>
+          <t>Dép nhựa Bitis nam</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/trong-kinh-can-vien-loan-mong-1-60-chemi-doi-mau-thoi-trang-ouress-p273097909.html?spid=273097910</t>
+          <t>https://tiki.vn/dep-nhua-bitis-nam-p174437687.html?spid=174437689</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OURESS</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1100000</v>
+        <v>105000</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>89000</v>
       </c>
       <c r="H26" t="n">
-        <v>-1100000</v>
+        <v>-16000</v>
       </c>
       <c r="I26" t="n">
-        <v>-100</v>
+        <v>-15.24</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>-267000</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 16,000đ (15.2%) | Bán thêm -3 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>225209462</t>
+          <t>104791604</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MŨ CHỐNG NẮNG CÓI NỬA ĐẦU RỘNG VÀNH CÁ TÍNH CHO NỮ</t>
+          <t>Quần lót nữ thái lan 828 – Chất thun lạnh - giao màu ngẫu nhiên</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mu-chong-nang-coi-nua-dau-rong-vanh-ca-tinh-cho-nu-p225209462.html?spid=247940496</t>
+          <t>https://tiki.vn/quan-lot-nu-thai-lan-828-chat-thun-lanh-giao-mau-ngau-nhien-p104791604.html?spid=270215621</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2667,60 +2667,60 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>55000</v>
+        <v>33880</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>36520</v>
       </c>
       <c r="H27" t="n">
-        <v>-55000</v>
+        <v>2640</v>
       </c>
       <c r="I27" t="n">
-        <v>-100</v>
+        <v>7.79</v>
       </c>
       <c r="J27" t="n">
+        <v>41</v>
+      </c>
+      <c r="K27" t="n">
+        <v>24</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-17</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-620840</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="R27" t="n">
         <v>3</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 2,640đ (+7.8%) | Bán thêm -17 sản phẩm | Rating 4.5→4.7 (+0.20) | Review thêm +1</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7997276</t>
+          <t>58362412</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Sneaker Unisex Converse Chuck Taylor All Star 1970s All Hi 2018 - White (Size</t>
+          <t>Áo khoác da cá GOKING 6 túi cho nam nữ, form unisex. Chống lanh, giữ ấm, chống nắng, chống tia UV hiệu quả</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-sneaker-unisex-converse-chuck-taylor-all-star-1970s-all-white-hi-2018-p7997276.html?spid=26499478</t>
+          <t>https://tiki.vn/ao-khoac-nam-goking-chuyen-chong-nang-6-tui-tien-dung-vai-day-cong-nghe-nhat-ban-cao-cap-p58362412.html?spid=58362420</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>GOKING</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2000000</v>
+        <v>339000</v>
       </c>
       <c r="H2" t="n">
-        <v>2000000</v>
+        <v>339000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,13 +582,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="L2" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="M2" t="n">
-        <v>78000000</v>
+        <v>28476000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -603,14 +603,14 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7995403</t>
+          <t>126091279</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giày Converse Chuck Taylor All Star Classic Hi Top - 121184</t>
+          <t>Giày Mọi, Giày Lười Nam Da Bò SUNPOLO SU5059 Hiện đại (Đen)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-classic-hi-top-121184-p7995403.html?spid=20342953</t>
+          <t>https://tiki.vn/giay-moi-giay-luoi-nam-da-bo-sunpolo-su5059-hien-dai-den-p126091279.html?spid=126091289</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>SUNPOLO</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1550000</v>
+        <v>1100000</v>
       </c>
       <c r="H3" t="n">
-        <v>1550000</v>
+        <v>1100000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,13 +666,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>34100000</v>
+        <v>8800000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -687,14 +687,14 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,17 +711,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>112188948</t>
+          <t>132286309</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dép Nam Quai Ngang HA NAM Da Bò Thật Cao Cấp DNA2074</t>
+          <t>Bộ Dụng Cụ Đánh Giày 7 Món Có Kèm Sẵn 2 Hộp Xi Tiện Dụng- Đánh Bóng Mới - Hàng Loại 1- Chính Hãng MINIIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-cao-cap-dna2074-p112188948.html?spid=112188950</t>
+          <t>https://tiki.vn/bo-dung-cu-danh-giay-7-mon-co-kem-san-2-hop-xi-tien-dung-danh-bong-moi-hang-loai-1-chinh-hang-miniin-p132286309.html?spid=132286315</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HA NAM</t>
+          <t>MINIIN</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>380000</v>
+        <v>99000</v>
       </c>
       <c r="H4" t="n">
-        <v>380000</v>
+        <v>99000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,13 +750,13 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>21280000</v>
+        <v>5247000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -771,14 +771,14 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,22 +795,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>181566777</t>
+          <t>26652440</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Áo sơ mi nam sọc tay ngắn dáng ôm body chuẩn form nhiều màu sắc - MON01</t>
+          <t>1 Hộp Khăn Lau Kính Mắt - Màn Hình Điện Tử</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nam-soc-tay-ngan-dang-om-body-chuan-form-nhieu-mau-sac-mon01-p181566777.html?spid=181566813</t>
+          <t>https://tiki.vn/1-hop-khan-lau-kinh-mat-man-hinh-dien-tu-p26652440.html?spid=146386798</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -822,10 +822,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>137500</v>
+        <v>99000</v>
       </c>
       <c r="H5" t="n">
-        <v>137500</v>
+        <v>99000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -834,13 +834,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>3162500</v>
+        <v>2673000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -855,14 +855,14 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -879,17 +879,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>52758100</t>
+          <t>183685137</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Combo 5 Đôi Tất Nam Vớ Nam Cổ Dài Sợi Cotton Cùng Màu</t>
+          <t>Thắt Lưng Dây Nịt Nam Vải Dù US ARMY, Phong Cách Sang Trọng Cổ Điển Mặt Khóa Hợp Kim Thép Chống Ghỉ Cao Cấp -HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-doi-tat-nam-vo-nam-co-dai-soi-cotton-cung-mau-p52758100.html?spid=67294705</t>
+          <t>https://tiki.vn/that-lung-day-nit-nam-vai-du-us-army-phong-cach-sang-trong-co-dien-mat-khoa-hop-kim-thep-chong-ghi-cao-cap-hang-chinh-hang-p183685137.html?spid=183685139</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -899,54 +899,54 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JM Jamano</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>99000</v>
+        <v>79000</v>
       </c>
       <c r="G6" t="n">
-        <v>175000</v>
+        <v>79000</v>
       </c>
       <c r="H6" t="n">
-        <v>76000</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>76.77</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4207</v>
+        <v>210</v>
       </c>
       <c r="K6" t="n">
-        <v>4211</v>
+        <v>222</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>700000</v>
+        <v>948000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>859</v>
+        <v>59</v>
       </c>
       <c r="R6" t="n">
-        <v>859</v>
+        <v>59</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Giá tăng 76,000đ (+76.8%) | Bán thêm +4 sản phẩm</t>
+          <t>Bán thêm +12 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>189528669</t>
+          <t>191422227</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Áo sơ mi nữ rộng dài tay phong cách hàn quốc trẻ trung năng động vải lụa mềm mịn -MURD05</t>
+          <t>Cột tóc scrunchies màu cánh dán ánh kim size trung</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nu-rong-dai-tay-phong-cach-han-quoc-tre-trung-nang-dong-vai-lua-mem-min-murd05-p189528669.html?spid=189528683</t>
+          <t>https://tiki.vn/day-cot-toc-scrunchies-mau-canh-dan-anh-kim-size-trung-p191422227.html?spid=191422228</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -987,28 +987,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>24900</v>
       </c>
       <c r="G7" t="n">
-        <v>115500</v>
+        <v>24900</v>
       </c>
       <c r="H7" t="n">
-        <v>115500</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="M7" t="n">
-        <v>693000</v>
+        <v>821700</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1030,219 +1030,219 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +33 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>107802069</t>
+          <t>201594583</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
+          <t>Áo Thun Nam Dài Tay Aligro Chất Liệu Cotton Cao Cấp, Siêu Mềm Mại, Dày Dặn, Cực Dễ Chịu, Thấm Hút Tốt ALGAPD055</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
+          <t>https://tiki.vn/ao-thun-nam-dai-tay-aligro-chat-lieu-cotton-cao-cap-sieu-mem-mai-day-dan-cuc-de-chiu-tham-hut-tot-algapd055-p201594583.html?spid=201594593</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>Aligro</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>42000</v>
+        <v>335000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>335000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1041</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>336000</v>
+        <v>335000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +8 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>278149879</t>
+          <t>107802069</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combo 5 quần lót nữ du lịch dùng 1 lần Size L 45-55kg</t>
+          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-bao-quan-lot-mien-giat-tien-loi-travel-mate-nu-5-cai-bao-size-m-vong-mong-84-94-cm-p278149879.html?spid=278149880</t>
+          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LuckyJQR</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="G9" t="n">
-        <v>110000</v>
+        <v>42000</v>
       </c>
       <c r="H9" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1047</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>220000</v>
+        <v>252000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +6 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>183498218</t>
+          <t>272408652</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nón Kết Nam Lính Mỹ U558 Thêu AIR FORCE Chóp Tròn , Nón Lưỡi Trai Nam Vải Kaki Cao Cấp Thời Trang US ARMY Phong Cách Lính Mỹ - HÀNG CHÍNH HÃNG</t>
+          <t>Áo Thun T-shirt Nam Cổ Tròn TRẮNG, ĐEN 100% Cotton Cao Cấp, Trẻ Trung, Thanh Lịch - Gold Rhino</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/non-ket-nam-linh-my-u558-theu-air-force-chop-tron-non-luoi-trai-nam-vai-kaki-cao-cap-thoi-trang-us-army-phong-cach-linh-my-hang-chinh-hang-p183498218.html?spid=183498220</t>
+          <t>https://tiki.vn/ao-thun-nam-t-shirt-mau-trang-co-tron-100-cotton-tre-trung-thanh-lich-p272408652.html?spid=272408850</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>Gold Rhino</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>94500</v>
+        <v>209000</v>
       </c>
       <c r="G10" t="n">
-        <v>94500</v>
+        <v>209000</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1251,38 +1251,38 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>259</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>261</v>
+        <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>189000</v>
+        <v>209000</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1292,81 +1292,81 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Bán thêm +2 sản phẩm</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>275276374</t>
+          <t>49210060</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dép tổ ong XANH RÊU nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Vỉ 3 Kẹp Tóc Càng Cua PASTEL 3 Chấu Loại Xịn MP120.3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-xanh-reu-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276374.html?spid=275276390</t>
+          <t>https://tiki.vn/vi-3-kep-toc-cang-cua-pastel-3-chau-loai-xin-mp120-3-p49210060.html?spid=51138209</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>72000</v>
+        <v>34900</v>
       </c>
       <c r="G11" t="n">
-        <v>75000</v>
+        <v>34900</v>
       </c>
       <c r="H11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>38</v>
+        <v>531</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>532</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>150000</v>
+        <v>34900</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1376,24 +1376,24 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Giá tăng 3,000đ (+4.2%) | Bán thêm +2 sản phẩm</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>190142008</t>
+          <t>54569520</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Áo sơ mi nam form rộng cổ tàu cổ trụ tay dài Giấu Nút phong cách hàn quốc trẻ trung lịch lãm-MRDT02</t>
+          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nam-form-rong-co-tau-co-tru-tay-dai-giau-nut-phong-cach-han-quoc-tre-trung-lich-lam-mrdt02-p190142008.html?spid=190142020</t>
+          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1407,50 +1407,50 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>115000</v>
+        <v>88000</v>
       </c>
       <c r="G12" t="n">
-        <v>121000</v>
+        <v>67760</v>
       </c>
       <c r="H12" t="n">
-        <v>6000</v>
+        <v>-20240</v>
       </c>
       <c r="I12" t="n">
-        <v>5.22</v>
+        <v>-23</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1460,81 +1460,81 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Giá tăng 6,000đ (+5.2%) | Bán thêm +1 sản phẩm</t>
+          <t>Giá giảm 20,240đ (23.0%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>126144478</t>
+          <t>103049077</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Đón gót giày bằng sừng bóng đẹp (DGH903) Đón gót giày mọi tư thế Cho giày Nam &amp; Nữ - Tiện lợi</t>
+          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/don-got-giay-bang-sung-bong-dep-dgh903-don-got-giay-moi-tu-the-cho-giay-nam-nu-p126144478.html?spid=163423850</t>
+          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HAHANCO</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>59000</v>
+        <v>185000</v>
       </c>
       <c r="G13" t="n">
-        <v>59000</v>
+        <v>153550</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-31450</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="J13" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>59000</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,24 +1544,24 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Giá giảm 31,450đ (17.0%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>73163978</t>
+          <t>279491793</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hộp miếng dán ngực Silicon màu xanh 5 đôi</t>
+          <t>Đầm xoè linen cao cấp,độ bền cao,mát mịn,thấm hút mồ hôi,may viền tỉ mỉ,sản xuất độc quyền tại Kiều Oanh Designer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-mieng-dan-nguc-silicon-mau-xanh-5-doi-p73163978.html?spid=117659470</t>
+          <t>https://tiki.vn/dam-xoe-linen-cao-cap-do-ben-cao-mat-min-tham-hut-mo-hoi-may-vien-ti-mi-san-xuat-doc-quyen-tai-kieu-oanh-designer-p279491793.html?spid=279491958</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1571,86 +1571,86 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LQ luxury</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>55000</v>
+        <v>860000</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>860000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>190129715</t>
+          <t>73862702</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Áo sơ mi nam cổ tàu cổ trụ form rộng tay dài trẻ trung thanh lịch vải lụa mềm mịn mát ít nhăn- MRDT01</t>
+          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nam-co-tau-co-tru-form-rong-tay-dai-tre-trung-thanh-lich-vai-lua-mem-min-mat-it-nhan-mrdt01-p190129715.html?spid=190129725</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862720</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1659,22 +1659,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>115000</v>
+        <v>173000</v>
       </c>
       <c r="G15" t="n">
-        <v>121000</v>
+        <v>140130</v>
       </c>
       <c r="H15" t="n">
-        <v>6000</v>
+        <v>-32870</v>
       </c>
       <c r="I15" t="n">
-        <v>5.22</v>
+        <v>-19</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1692,17 +1692,17 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1712,29 +1712,29 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Giá tăng 6,000đ (+5.2%)</t>
+          <t>Giá giảm 32,870đ (19.0%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>103049077</t>
+          <t>278004504</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
+          <t>Combo 5 Quần Lót Nữ Su Tăm Trơn Không Viền Mỏng Nhẹ 892 – Co Giãn 4 Chiều, Thoáng Mát, Không Lộ Viền (Size L/XL/XXL)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nu-su-tam-tron-khong-vien-mong-nhe-892-co-gian-4-chieu-thoang-mat-khong-lo-vien-size-l-xl-xxl-p278004504.html?spid=278004508</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>140600</v>
+        <v>188600</v>
       </c>
       <c r="G16" t="n">
-        <v>185000</v>
+        <v>230000</v>
       </c>
       <c r="H16" t="n">
-        <v>44400</v>
+        <v>41400</v>
       </c>
       <c r="I16" t="n">
-        <v>31.58</v>
+        <v>21.95</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1767,26 +1767,26 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1796,53 +1796,53 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Giá tăng 44,400đ (+31.6%)</t>
+          <t>Giá tăng 41,400đ (+22.0%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>279256558</t>
+          <t>74421501</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Áo polo nam tay ngắn phối cố Form Fitted - ROUTINE 10F25POL028</t>
+          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-polo-nam-tay-ngan-phoi-co-form-fitted-routine-10f25pol028-p279256558.html?spid=279256564</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="G17" t="n">
-        <v>579000</v>
+        <v>129600</v>
       </c>
       <c r="H17" t="n">
-        <v>579000</v>
+        <v>-30400</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1851,53 +1851,53 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 30,400đ (19.0%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>91388606</t>
+          <t>7078807</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ÁO THUN NAM CAO CẤP CỔ BẺ PEGA IN</t>
+          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/product-p91388606.html?spid=113227822</t>
+          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858717</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1911,22 +1911,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>385000</v>
       </c>
       <c r="G18" t="n">
-        <v>454900</v>
+        <v>296450</v>
       </c>
       <c r="H18" t="n">
-        <v>454900</v>
+        <v>-88550</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1935,53 +1935,53 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 88,550đ (23.0%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>133160820</t>
+          <t>113144956</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quần Lót Su Đúc Nữ (Hàng Loại 1) Không Đường Mai, Thun Lạnh, SIêu Co Dãn, Được Chọn Màu</t>
+          <t>siêu phẩm áo lót nhật trơn đệm nâng ngực nhẹ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-su-duc-nu-hang-loai-1-khong-duong-mai-thun-lanh-sieu-co-dan-duoc-chon-mau-p133160820.html?spid=198901960</t>
+          <t>https://tiki.vn/sieu-pham-ao-lot-tron-dem-nang-nguc-nhe-p113144956.html?spid=142116876</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>22680</v>
+        <v>123750</v>
       </c>
       <c r="G19" t="n">
-        <v>28000</v>
+        <v>165000</v>
       </c>
       <c r="H19" t="n">
-        <v>5320</v>
+        <v>41250</v>
       </c>
       <c r="I19" t="n">
-        <v>23.46</v>
+        <v>33.33</v>
       </c>
       <c r="J19" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá tăng 5,320đ (+23.5%)</t>
+          <t>Giá tăng 41,250đ (+33.3%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>201934265</t>
+          <t>56041700</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Combo 2 Áo khoác gió nam chống nắng trượt nước cản gió cản bụi hiệu quả MRM Manlywear</t>
+          <t>Quần bơi nam cao cấp, đồ bơi nam boxer đẹp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-2-ao-khoac-gio-nam-giu-nhiet-chong-nuoc-can-gio-can-bui-hieu-qua-mrm-manlywear-p201934265.html?spid=201934281</t>
+          <t>https://tiki.vn/quan-boi-nam-cao-cap-do-boi-nam-boxer-dep-p56041700.html?spid=56041702</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2075,23 +2075,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>899000</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>899000</v>
+        <v>-200000</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2103,16 +2103,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2122,34 +2122,34 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>274505062</t>
+          <t>52054230</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Áo polo thể thao Phiten polo (light) - Đen</t>
+          <t>combo 5 quần sịp chéo cotton nam xuất nhật túi zip bạc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-polo-the-thao-phiten-polo-light-p274505062.html?spid=274505078</t>
+          <t>https://tiki.vn/combo-5-quan-sip-cheo-cotton-nam-xuat-nhat-tui-zip-bac-p52054230.html?spid=73622918</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2159,23 +2159,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phiten</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>189000</v>
       </c>
       <c r="G21" t="n">
-        <v>1780000</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1780000</v>
+        <v>-189000</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2206,63 +2206,63 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>174001966</t>
+          <t>173635485</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quần Jean nam Leman xanh trơn JD03 - Slim Form</t>
+          <t>Giày Lười Nam Tăng Chiều Cao Da Bò Thật BIGGBEN Cao Cấp GM270</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-jean-nam-leman-xanh-tron-jd03-slim-form-p174001966.html?spid=174001978</t>
+          <t>https://tiki.vn/giay-luoi-nam-tang-chieu-cao-da-bo-that-biggben-cao-cap-gm269-p173635485.html?spid=278818066</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leman</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>549000</v>
+        <v>999000</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1700000</v>
       </c>
       <c r="H22" t="n">
-        <v>-549000</v>
+        <v>701000</v>
       </c>
       <c r="I22" t="n">
-        <v>-100</v>
+        <v>70.17</v>
       </c>
       <c r="J22" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2274,70 +2274,70 @@
         <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 701,000đ (+70.2%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>276827848</t>
+          <t>275042862</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quần Jean Ống Rộng Classic Carolina Blue Aaa Jeans</t>
+          <t>GIÀY CHẠY BỘ VÀ ĐI BỘ ĐỊA HÌNH SLM X-ADVENTURE OLIVE NIGHT - L47386000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-jean-o-ng-rong-classic-carolina-blue-aaa-jeans-p276827848.html?spid=276827850</t>
+          <t>https://tiki.vn/giay-chay-bo-va-di-bo-dia-hinh-slm-x-adventure-olive-night-l47386000-p275042862.html?spid=275042868</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TRIPLE A</t>
+          <t>Salomon</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>650000</v>
+        <v>3800000</v>
       </c>
       <c r="H23" t="n">
-        <v>650000</v>
+        <v>3800000</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2391,17 +2391,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>112851354</t>
+          <t>113145806</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Áo ngực học sinh</t>
+          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138792</t>
+          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2415,22 +2415,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>30400</v>
+        <v>88920</v>
       </c>
       <c r="G24" t="n">
-        <v>42000</v>
+        <v>117000</v>
       </c>
       <c r="H24" t="n">
-        <v>11600</v>
+        <v>28080</v>
       </c>
       <c r="I24" t="n">
-        <v>38.16</v>
+        <v>31.58</v>
       </c>
       <c r="J24" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2439,26 +2439,26 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2468,24 +2468,24 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Giá tăng 11,600đ (+38.2%)</t>
+          <t>Giá tăng 28,080đ (+31.6%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>108220832</t>
+          <t>144236336</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bra dán ngực bàn tay P29 (kèm dây trong)</t>
+          <t>COMBO 5 ÁO LÓT VẢI KHÔNG GỌNG KHÔNG MÚT (SIZE 32-42)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bra-dan-nguc-ban-tay-p29-kem-day-trong-p108220832.html?spid=242370964</t>
+          <t>https://tiki.vn/combo-5-ao-lot-vai-khong-gong-khong-mut-size-32-42-p144236336.html?spid=146366320</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2499,22 +2499,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>56250</v>
+        <v>210000</v>
       </c>
       <c r="G25" t="n">
-        <v>75000</v>
+        <v>174300</v>
       </c>
       <c r="H25" t="n">
-        <v>18750</v>
+        <v>-35700</v>
       </c>
       <c r="I25" t="n">
-        <v>33.33</v>
+        <v>-17</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2532,17 +2532,17 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2552,53 +2552,53 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Giá tăng 18,750đ (+33.3%)</t>
+          <t>Giá giảm 35,700đ (17.0%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>214706031</t>
+          <t>276086848</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Áo lót áo ngực Thái lan có gọng mút kép nâng ngực tạo khe, áo lót nữ thông hơi hàng CAO CẤP</t>
+          <t>Cục bông trang trí nhiều màu sắc chọn lựa (tùy chọn màu sắc) (hàng có sẵn giao nhanh) (Hàng Chính Hãng)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-ao-nguc-thai-lan-co-gong-mut-kep-nang-nguc-tao-khe-ao-lot-nu-thong-hoi-hang-cao-cap-p214706031.html?spid=215408041</t>
+          <t>https://tiki.vn/cuc-bong-trang-tri-nhieu-mau-sac-chon-lua-tuy-chon-mau-sac-hang-co-san-giao-nhanh-hang-chinh-hang-p276086848.html?spid=276086851</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Bilaha</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>97200</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>120000</v>
+        <v>70000</v>
       </c>
       <c r="H26" t="n">
-        <v>22800</v>
+        <v>70000</v>
       </c>
       <c r="I26" t="n">
-        <v>23.46</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2626,39 +2626,39 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Giá tăng 22,800đ (+23.5%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>187278904</t>
+          <t>192642640</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Áo sơ mi nữ form rộng tay dài phồng hot trend hàn quốc trẻ trung thanh lịch vải lụa mềm mịn-MUD02</t>
+          <t>Cài tóc bảng nhỏ 1 cm - cài tóc nam nữ - cài tóc đơn giản</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nu-form-rong-tay-dai-phong-hot-trend-han-quoc-tre-trung-thanh-lich-vai-lua-mem-min-mud02-p187278904.html?spid=187278918</t>
+          <t>https://tiki.vn/cai-toc-bang-nho-1-cm-cai-toc-nam-nu-cai-toc-don-gian-p192642640.html?spid=192642674</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2667,22 +2667,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>230000</v>
+        <v>24000</v>
       </c>
       <c r="G27" t="n">
-        <v>135000</v>
+        <v>24000</v>
       </c>
       <c r="H27" t="n">
-        <v>-95000</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-41.3</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K27" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2691,26 +2691,26 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2720,53 +2720,53 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Giá giảm 95,000đ (41.3%)</t>
+          <t>Review thêm +2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>174585329</t>
+          <t>38160273</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Áo lót nâng ngực boya mút mỏng, Áo ngực boya nâng ngực cài sau 522BT</t>
+          <t>Giày Boot Nam BIGGBEN Da Bò Thật Cao Cấp BT2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nang-nguc-boya-mut-mong-ao-nguc-boya-nang-nguc-cai-sau-522bt-p174585329.html?spid=203717976</t>
+          <t>https://tiki.vn/giay-boot-nam-biggben-da-bo-that-cao-cap-bt2-p38160273.html?spid=38160275</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>85050</v>
+        <v>2000000</v>
       </c>
       <c r="G28" t="n">
-        <v>105000</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>19950</v>
+        <v>-2000000</v>
       </c>
       <c r="I28" t="n">
-        <v>23.46</v>
+        <v>-100</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2775,82 +2775,82 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Giá tăng 19,950đ (+23.5%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>158732070</t>
+          <t>278957623</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>❈✣♚Combo 10 quần lót nữ su đúc cao cấp không đường may, chất mát lạnh, mềm mịn, thoáng</t>
+          <t>Dép quai kẹp Biti's nam (size 38-43)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nu-su-duc-cao-cap-khong-duong-may-chat-mat-lanh-mem-min-thoang-p158732070.html?spid=242324041</t>
+          <t>https://tiki.vn/dep-quai-kep-biti-s-nam-size-38-43-p278957623.html?spid=278957641</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Biti's</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>240000</v>
+        <v>232000</v>
       </c>
       <c r="G29" t="n">
-        <v>320000</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>80000</v>
+        <v>-232000</v>
       </c>
       <c r="I29" t="n">
-        <v>33.33</v>
+        <v>-100</v>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2859,82 +2859,82 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Giá tăng 80,000đ (+33.3%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>275276309</t>
+          <t>276827848</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dép tổ ong ĐEN nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Quần Jean Ống Rộng Classic Carolina Blue Aaa Jeans</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-den-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276309.html?spid=275276319</t>
+          <t>https://tiki.vn/quan-jean-o-ng-rong-classic-carolina-blue-aaa-jeans-p276827848.html?spid=276827850</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>TRIPLE A</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>72000</v>
+        <v>650000</v>
       </c>
       <c r="G30" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3000</v>
+        <v>-650000</v>
       </c>
       <c r="I30" t="n">
-        <v>4.17</v>
+        <v>-100</v>
       </c>
       <c r="J30" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2962,34 +2962,34 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Giá tăng 3,000đ (+4.2%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>275276422</t>
+          <t>277744886</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dép tổ ong XANH NGỌC nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Giày Da Nam Italy - 1720BIA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-xanh-ngoc-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276422.html?spid=275276436</t>
+          <t>https://tiki.vn/giay-da-nam-italy-1720bia-p277744886.html?spid=277744894</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2999,26 +2999,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>Gianni Conti</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>72000</v>
+        <v>4000000</v>
       </c>
       <c r="G31" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3000</v>
+        <v>-4000000</v>
       </c>
       <c r="I31" t="n">
-        <v>4.17</v>
+        <v>-100</v>
       </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3027,82 +3027,82 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Giá tăng 3,000đ (+4.2%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>274804274</t>
+          <t>278449303</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dép tổ ong [Size 31-34] KÈM STICKER NGẪU NHIÊN vật liệu EVA cao cấp siêu bền, siêu nhẹ, chống trơn trượt</t>
+          <t xml:space="preserve">Mấy Xajy Bột Khô Siêu Khỏe 3000W – Bột Mịn Siêu Tốc, Nghiêjn Ngjũ Cốc &amp; Hạt Khô Đa Năng, đèn trang trí   đồng hồ treo tường </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-size-31-34-kem-sticker-ngau-nhien-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-p274804274.html?spid=274804515</t>
+          <t>https://tiki.vn/may-xajy-bot-kho-sieu-khoe-3000w-bot-min-sieu-toc-nghiejn-ngju-coc-hat-kho-da-nang-den-trang-tri-dong-ho-treo-tuong-p278449303.html?spid=278449304</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>65000</v>
+        <v>1288000</v>
       </c>
       <c r="G32" t="n">
-        <v>73000</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>8000</v>
+        <v>-1288000</v>
       </c>
       <c r="I32" t="n">
-        <v>12.31</v>
+        <v>-100</v>
       </c>
       <c r="J32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3130,60 +3130,60 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Giá tăng 8,000đ (+12.3%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>276558531</t>
+          <t>68491184</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Giày thể thao Bitis Hunter (39-45) 969k</t>
+          <t>Kính râm Nam thời trang + Tặng Tuavit Kính Xinh Mini đa năng</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-bitis-hunter-39-45-969k-p276558531.html?spid=276558541</t>
+          <t>https://tiki.vn/kinh-ram-nam-thoi-trang-tang-tuavit-kinh-xinh-mini-da-nang-p68491184.html?spid=68491185</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>HOKO</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>169000</v>
       </c>
       <c r="G33" t="n">
-        <v>969000</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>969000</v>
+        <v>-169000</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3214,34 +3214,34 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>275276260</t>
+          <t>272224450</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dép tổ ong ĐỎ nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Dép quai ngang nam, nữ siêu nhẹ DUWA - Hàng chính hãng - TK9056</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-do-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276260.html?spid=275276270</t>
+          <t>https://tiki.vn/dep-quai-ngang-nam-nu-sieu-nhe-duwa-hang-chinh-hang-tk9056-p272224450.html?spid=272224458</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3251,54 +3251,54 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>DUWA</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>72000</v>
+        <v>159000</v>
       </c>
       <c r="G34" t="n">
-        <v>75000</v>
+        <v>159000</v>
       </c>
       <c r="H34" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>-318000</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3308,59 +3308,59 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Giá tăng 3,000đ (+4.2%)</t>
+          <t>Bán thêm -2 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>262796074</t>
+          <t>278000485</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chai vệ sinh đồ da làm sạch, dưỡng ẩm chống mốc, kháng khuẩn giày, túi ví, áo, ghế da 150ml</t>
+          <t>Áo lót nữ 718 – Mút mỏng thông hơi, không gọng, cài sau 3 móc, co giãn thoải mái</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-ve-sinh-do-da-lam-sach-duong-am-chong-moc-khang-khuan-giay-tui-vi-ao-ghe-da-150ml-p262796074.html?spid=262796075</t>
+          <t>https://tiki.vn/ao-lot-nu-718-mut-mong-thong-hoi-khong-gong-cai-sau-3-moc-co-gian-thoai-mai-p278000485.html?spid=278000517</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>70000</v>
+        <v>100000</v>
       </c>
       <c r="G35" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="H35" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>-400000</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -3392,1519 +3392,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Giá tăng 5,000đ (+7.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>275276334</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Dép tổ ong XÁM nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-to-ong-xam-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276334.html?spid=275276350</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VAC </t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>72000</v>
-      </c>
-      <c r="G36" t="n">
-        <v>75000</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I36" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="J36" t="n">
-        <v>85</v>
-      </c>
-      <c r="K36" t="n">
-        <v>85</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
-      <c r="R36" t="n">
-        <v>4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Giá tăng 3,000đ (+4.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>275276468</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Dép tổ ong XANH NAVY nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-to-ong-xanh-navy-vat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276468.html?spid=275276484</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VAC </t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>72000</v>
-      </c>
-      <c r="G37" t="n">
-        <v>75000</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I37" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="J37" t="n">
-        <v>23</v>
-      </c>
-      <c r="K37" t="n">
-        <v>23</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>5</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Giá tăng 3,000đ (+4.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>192642401</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Giày Thể Thao Nam Biti's Hunter X LITEPLEX DSMH09800</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/giay-the-thao-nam-biti-s-hunter-x-liteplex-dsmh09800-p192642401.html?spid=192642413</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Biti's</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1010000</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-1010000</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J38" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>4</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>252533129</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Găng Tay Hở 2 Ngón Unisex Chống Nắng, Có Thể Sử Dụng Cảm Ứng Điện Thoại</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/gang-tay-ho-2-ngon-unisex-chong-nang-co-the-su-dung-cam-ung-dien-thoai-p252533129.html?spid=252533130</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>19600</v>
-      </c>
-      <c r="G39" t="n">
-        <v>49000</v>
-      </c>
-      <c r="H39" t="n">
-        <v>29400</v>
-      </c>
-      <c r="I39" t="n">
-        <v>150</v>
-      </c>
-      <c r="J39" t="n">
-        <v>164</v>
-      </c>
-      <c r="K39" t="n">
-        <v>164</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>5</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>19</v>
-      </c>
-      <c r="R39" t="n">
-        <v>19</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Giá tăng 29,400đ (+150.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>52154918</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trâm Cài Áo Nữ Hình Hoa Mẫu Đơn Trang Nhã Sang Trọng </t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/tram-cai-ao-nu-hinh-hoa-mau-don-trang-nha-sang-trong-p52154918.html?spid=52154919</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>29600</v>
-      </c>
-      <c r="G40" t="n">
-        <v>69000</v>
-      </c>
-      <c r="H40" t="n">
-        <v>39400</v>
-      </c>
-      <c r="I40" t="n">
-        <v>133.11</v>
-      </c>
-      <c r="J40" t="n">
-        <v>26</v>
-      </c>
-      <c r="K40" t="n">
-        <v>26</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>5</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>9</v>
-      </c>
-      <c r="R40" t="n">
-        <v>9</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Giá tăng 39,400đ (+133.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>277420779</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Khẩu Trang Chống Nắng Cao Cấp UPF 50+,Khẩu Trang Chống Nám Chống Tia UV, Bảo Vệ Da Hiệu Quả - HÀNG CHÍNH HÃNG MINIIN</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/khau-trang-chong-nang-enaide-cao-cap-upf-50-chong-tia-uv-bao-ve-da-hieu-qua-hang-chinh-hang-miniin-p277420779.html?spid=277420791</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>MINIIN</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>27000</v>
-      </c>
-      <c r="G41" t="n">
-        <v>27000</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>7</v>
-      </c>
-      <c r="K41" t="n">
-        <v>7</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Rating 0.0→1.0 (+1.00) | Review thêm +1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>35087712</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Quần lót nam thun lạnh không đường may, sịp nam tam giác cao cấp chất liệu thoáng mát, mềm mịn QLW606</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/quan-lot-nam-thun-lanh-su-qlw606-p35087712.html?spid=116563301</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>69000</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-69000</v>
-      </c>
-      <c r="I42" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J42" t="n">
-        <v>434</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>86</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>134757633</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Áo Sơ Mi Form Rộng GIẤU NÚT Tay Dài Hàn Quốc Áo Unisex Nam Nữ Vải Lụa Mềm Mịn Thoáng Mát Ít Nhăn - SMD02</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-so-mi-form-rong-giau-nut-tay-dai-han-quoc-ao-unisex-nam-nu-vai-lua-mem-min-thoang-mat-it-nhan-smd02-p134757633.html?spid=134757665</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>125000</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-125000</v>
-      </c>
-      <c r="I43" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J43" t="n">
-        <v>99</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>34</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>177502414</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Áo sơ mi trơn form rộng tay dài unisex nam nữ kiểu cổ bẻ phong cách hàn quốc trẻ trung - MRD03</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-so-mi-tron-form-rong-tay-dai-unisex-nam-nu-kieu-co-be-phong-cach-han-quoc-tre-trung-mrd03-p177502414.html?spid=177502428</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>115500</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-115500</v>
-      </c>
-      <c r="I44" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J44" t="n">
-        <v>9</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>72881856</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Quần lót nam thun lạnh không đường may, sịp đùi nam cao cấp kiểu dáng boxer nam ôm sát, chất liệu su thoáng mát, mềm mịn và mỏng nhẹ, quần lót cạp nhỏ đơn giản với màu trơn QLW806</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/quan-lot-nam-thun-lanh-khong-duong-may-sip-dui-nam-cao-cap-kieu-dang-boxer-nam-om-sat-chat-lieu-su-thoang-mat-mem-min-va-mong-nhe-quan-lot-cap-nho-don-gian-voi-mau-tron-qlw806-p72881856.html?spid=102551187</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>69000</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-69000</v>
-      </c>
-      <c r="I45" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J45" t="n">
-        <v>143</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>36</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>7997237</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Giày Converse Chuck Taylor All Star 1970s Low Top - 162058V</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-1970s-low-top-162058v-p7997237.html?spid=20296398</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-1900000</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J46" t="n">
-        <v>231</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>5</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>73</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>186271142</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Quần lót chất ren phối đáy cotton cao cấp sexy</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/quan-lot-chat-ren-phoi-day-cotton-cao-cap-sexy-p186271142.html?spid=186271150</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-35000</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J47" t="n">
-        <v>4</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>192947717</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Áo sơ mi nữ form rộng tay ngắn chuẩn form hàn quốc trẻ trung năng động vải lạu mềm mại ít nhăn-MURN02</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-so-mi-nu-form-rong-tay-ngan-chuan-form-han-quoc-tre-trung-nang-dong-vai-lau-mem-mai-it-nhan-murn02-p192947717.html?spid=192947757</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>115000</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-115000</v>
-      </c>
-      <c r="I48" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>5</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>189527267</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Áo sơ mi nữ tay dài form rộng phong cách trẻ trung hàn quốc vải lụa mềm mịn mát -MURD04</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-so-mi-nu-tay-dai-form-rong-phong-cach-tre-trung-han-quoc-vai-lua-mem-min-mat-murd04-p189527267.html?spid=189527319</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>115500</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-115500</v>
-      </c>
-      <c r="I49" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J49" t="n">
-        <v>7</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>5</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>275042862</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>GIÀY CHẠY BỘ VÀ ĐI BỘ ĐỊA HÌNH SLM X-ADVENTURE OLIVE NIGHT - L47386000</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/giay-chay-bo-va-di-bo-dia-hinh-slm-x-adventure-olive-night-l47386000-p275042862.html?spid=275042868</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Salomon</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-3800000</v>
-      </c>
-      <c r="I50" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>279277580</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Giày sandal thể thao, sandal học sinh VN2224 size 35-45 chính hãng VINASAN. Hàng Việt Nam xuất khẩu</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/giay-sandal-the-thao-sandal-hoc-sinh-vn2224-size-35-45-chinh-hang-vinasan-hang-viet-nam-xuat-khau-p279277580.html?spid=279277678</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>VINASAN</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>245000</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-245000</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>274795145</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Dép tổ ong [Size 39-43] KÈM STICKER NGẪU NHIÊN vật liệu EVA cao cấp siêu bền, siêu nhẹ, chống trơn trượt</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-to-ong-size-39-43-kem-sticker-ngau-nhien-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-p274795145.html?spid=274803734</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VAC </t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>77000</v>
-      </c>
-      <c r="G52" t="n">
-        <v>83000</v>
-      </c>
-      <c r="H52" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I52" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="J52" t="n">
-        <v>51</v>
-      </c>
-      <c r="K52" t="n">
-        <v>50</v>
-      </c>
-      <c r="L52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>-83000</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>5</v>
-      </c>
-      <c r="R52" t="n">
-        <v>5</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Giá tăng 6,000đ (+7.8%) | Bán thêm -1 sản phẩm</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>262803154</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Đầm ngủ WANNABE DNS71 váy ngủ 2 dây cúp ngực lót mút mỏng tạo dáng cho người mặc in hoa ngọt ngào nữ tính quyến rũ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/do-ngu-nu-wannabe-dns71-dam-ngu-hai-day-ra-cup-lot-mut-nu-tinh-quyen-ru-p262803154.html?spid=271126198</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Wannabe</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>390000</v>
-      </c>
-      <c r="G53" t="n">
-        <v>390000</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>8</v>
-      </c>
-      <c r="K53" t="n">
-        <v>6</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M53" t="n">
-        <v>-780000</v>
-      </c>
-      <c r="N53" t="n">
-        <v>5</v>
-      </c>
-      <c r="O53" t="n">
-        <v>5</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>2</v>
-      </c>
-      <c r="R53" t="n">
-        <v>2</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Bán thêm -2 sản phẩm</t>
+          <t>Bán thêm -4 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>58362412</t>
+          <t>279287522</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Áo khoác da cá GOKING 6 túi cho nam nữ, form unisex. Chống lanh, giữ ấm, chống nắng, chống tia UV hiệu quả</t>
+          <t>Bộ áo điều hòa KITO NEWPRO KT10 thế hệ mới nhất 2026 quạt 24V siêu bên ,chống chai ,chống phồng</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-nam-goking-chuyen-chong-nang-6-tui-tien-dung-vai-day-cong-nghe-nhat-ban-cao-cap-p58362412.html?spid=58362420</t>
+          <t>https://tiki.vn/bo-ao-dieu-hoa-kito-newpro-kt10-the-he-moi-nhat-2026-quat-24v-sieu-ben-chong-chai-chong-phong-p279287522.html?spid=279287524</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GOKING</t>
+          <t>Kito</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1070000</v>
       </c>
       <c r="G2" t="n">
-        <v>339000</v>
+        <v>1070000</v>
       </c>
       <c r="H2" t="n">
-        <v>339000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,62 +582,62 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>28476000</v>
+        <v>9630000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +9 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>126091279</t>
+          <t>228132185</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giày Mọi, Giày Lười Nam Da Bò SUNPOLO SU5059 Hiện đại (Đen)</t>
+          <t>Dép Nam Quai Ngang HÀ NAM Da Bò Thật Cao Cấp DNA2210</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-moi-giay-luoi-nam-da-bo-sunpolo-su5059-hien-dai-den-p126091279.html?spid=126091289</t>
+          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-that-ha-nam-cao-cap-dna2210-p228132185.html?spid=228132221</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SUNPOLO</t>
+          <t>HA NAM</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1100000</v>
+        <v>450000</v>
       </c>
       <c r="H3" t="n">
-        <v>1100000</v>
+        <v>450000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,13 +666,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>8800000</v>
+        <v>1800000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -687,14 +687,14 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,17 +711,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>132286309</t>
+          <t>276814141</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bộ Dụng Cụ Đánh Giày 7 Món Có Kèm Sẵn 2 Hộp Xi Tiện Dụng- Đánh Bóng Mới - Hàng Loại 1- Chính Hãng MINIIN</t>
+          <t>New Arrivals | Giày Da Sneaker Nam Nữ DC39 COCO MILK DINCOX Shoes Đế Bằng - Microfiber Leather</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-dung-cu-danh-giay-7-mon-co-kem-san-2-hop-xi-tien-dung-danh-bong-moi-hang-loai-1-chinh-hang-miniin-p132286309.html?spid=132286315</t>
+          <t>https://tiki.vn/new-arrivals-giay-da-sneaker-nam-nu-dc39-coco-milk-dincox-shoes-de-bang-microfiber-leather-p276814141.html?spid=276814174</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -731,81 +731,81 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MINIIN</t>
+          <t>DINCOX</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>660000</v>
       </c>
       <c r="G4" t="n">
-        <v>99000</v>
+        <v>660000</v>
       </c>
       <c r="H4" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>5247000</v>
+        <v>660000</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26652440</t>
+          <t>34159085</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1 Hộp Khăn Lau Kính Mắt - Màn Hình Điện Tử</t>
+          <t>Combo 5 Đôi Tất Cổ Trung Cùng Màu Cotton Thương Hiệu MRM Manlywear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/1-hop-khan-lau-kinh-mat-man-hinh-dien-tu-p26652440.html?spid=146386798</t>
+          <t>https://tiki.vn/combo-5-doi-tat-nam-tat-nam-vo-nam-co-dai-cao-cap-mrm-fashion-cung-mau-p34159085.html?spid=34159089</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -815,81 +815,81 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MRM Manlywear</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>149000</v>
       </c>
       <c r="G5" t="n">
-        <v>99000</v>
+        <v>149000</v>
       </c>
       <c r="H5" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>4717</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>4720</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>2673000</v>
+        <v>447000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>901</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +3 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>183685137</t>
+          <t>68491184</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thắt Lưng Dây Nịt Nam Vải Dù US ARMY, Phong Cách Sang Trọng Cổ Điển Mặt Khóa Hợp Kim Thép Chống Ghỉ Cao Cấp -HÀNG CHÍNH HÃNG</t>
+          <t>Kính râm Nam thời trang + Tặng Tuavit Kính Xinh Mini đa năng</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-day-nit-nam-vai-du-us-army-phong-cach-sang-trong-co-dien-mat-khoa-hop-kim-thep-chong-ghi-cao-cap-hang-chinh-hang-p183685137.html?spid=183685139</t>
+          <t>https://tiki.vn/kinh-ram-nam-thoi-trang-tang-tuavit-kinh-xinh-mini-da-nang-p68491184.html?spid=68491185</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -899,138 +899,138 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>HOKO</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>79000</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>79000</v>
+        <v>169000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>169000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>222</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>948000</v>
+        <v>338000</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Bán thêm +12 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>191422227</t>
+          <t>107802069</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cột tóc scrunchies màu cánh dán ánh kim size trung</t>
+          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/day-cot-toc-scrunchies-mau-canh-dan-anh-kim-size-trung-p191422227.html?spid=191422228</t>
+          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>24900</v>
+        <v>42000</v>
       </c>
       <c r="G7" t="n">
-        <v>24900</v>
+        <v>27000</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-35.71</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>1047</v>
       </c>
       <c r="K7" t="n">
-        <v>37</v>
+        <v>1048</v>
       </c>
       <c r="L7" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>821700</v>
+        <v>27000</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1040,44 +1040,44 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Bán thêm +33 sản phẩm</t>
+          <t>Giá giảm 15,000đ (35.7%) | Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>201594583</t>
+          <t>158565446</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Áo Thun Nam Dài Tay Aligro Chất Liệu Cotton Cao Cấp, Siêu Mềm Mại, Dày Dặn, Cực Dễ Chịu, Thấm Hút Tốt ALGAPD055</t>
+          <t>Áo Lót Nữ, Áo Ngực Trơn Mút Dày Hàng Thái Lan Hãng.A2280</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-dai-tay-aligro-chat-lieu-cotton-cao-cap-sieu-mem-mai-day-dan-cuc-de-chiu-tham-hut-tot-algapd055-p201594583.html?spid=201594593</t>
+          <t>https://tiki.vn/ao-lot-nu-ao-nguc-tron-mut-day-hang-thai-lan-hang-a2280-p158565446.html?spid=276838010</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aligro</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>335000</v>
+        <v>87400</v>
       </c>
       <c r="H8" t="n">
-        <v>335000</v>
+        <v>87400</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1086,13 +1086,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>335000</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1131,74 +1131,74 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>107802069</t>
+          <t>276945307</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
+          <t>Áo lót nữ Angelavic 529 – Bra thun lạnh tăm, mút liền, cài sau, không gọng, nâng đỡ thoải mái</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
+          <t>https://tiki.vn/ao-lot-nu-ao-bra-thun-lanh-tam-mut-lien-cai-sau-529-p276945307.html?spid=276945325</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>42000</v>
+        <v>110000</v>
       </c>
       <c r="G9" t="n">
-        <v>42000</v>
+        <v>83600</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-26400</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="J9" t="n">
-        <v>1041</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1047</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>252000</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1208,41 +1208,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Bán thêm +6 sản phẩm</t>
+          <t>Giá giảm 26,400đ (24.0%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>272408652</t>
+          <t>277610005</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Áo Thun T-shirt Nam Cổ Tròn TRẮNG, ĐEN 100% Cotton Cao Cấp, Trẻ Trung, Thanh Lịch - Gold Rhino</t>
+          <t>Áo Lót 3281 Không Gọng Mút Mỏng Bản 3 Móc Che Khuyết Điểm Đẹp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-t-shirt-mau-trang-co-tron-100-cotton-tre-trung-thanh-lich-p272408652.html?spid=272408850</t>
+          <t>https://tiki.vn/ao-lot-3281-khong-gong-mut-mong-ban-3-moc-che-khuyet-diem-dep-p277610005.html?spid=277610045</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gold Rhino</t>
+          <t>Sanny House</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>209000</v>
+        <v>96000</v>
       </c>
       <c r="G10" t="n">
-        <v>209000</v>
+        <v>96000</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1251,38 +1251,38 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>209000</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1292,29 +1292,29 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Rating 0.0→5.0 (+5.00) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>49210060</t>
+          <t>16375016</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vỉ 3 Kẹp Tóc Càng Cua PASTEL 3 Chấu Loại Xịn MP120.3</t>
+          <t>COMBO HỘP 5 Quần Lót ĐÙI Nam Xuất Nhật Cao Cấp (MIX NGẪU NHIÊN)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/vi-3-kep-toc-cang-cua-pastel-3-chau-loai-xin-mp120-3-p49210060.html?spid=51138209</t>
+          <t>https://tiki.vn/combo-hop-5-quan-lot-dui-nam-xuat-nhat-cao-cap-mix-ngau-nhien-p16375016.html?spid=277961877</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1323,50 +1323,50 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>34900</v>
+        <v>198290</v>
       </c>
       <c r="G11" t="n">
-        <v>34900</v>
+        <v>274000</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>75710</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>38.18</v>
       </c>
       <c r="J11" t="n">
-        <v>531</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>532</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>34900</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1376,24 +1376,24 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Giá tăng 75,710đ (+38.2%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>54569520</t>
+          <t>277996544</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
+          <t>Hộp 5 Quần lót nam cotton lụa – Siêu đẹp, mềm mịn, thoáng mát</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
+          <t>https://tiki.vn/hop-5-quan-lot-nam-cotton-lua-muji-sieu-dep-mem-min-thoang-mat-p277996544.html?spid=278006734</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1407,22 +1407,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>88000</v>
+        <v>172200</v>
       </c>
       <c r="G12" t="n">
-        <v>67760</v>
+        <v>220000</v>
       </c>
       <c r="H12" t="n">
-        <v>-20240</v>
+        <v>47800</v>
       </c>
       <c r="I12" t="n">
-        <v>-23</v>
+        <v>27.76</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1440,17 +1440,17 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1460,24 +1460,24 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Giá giảm 20,240đ (23.0%)</t>
+          <t>Giá tăng 47,800đ (+27.8%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>103049077</t>
+          <t>16546849</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
+          <t>Combo 5 Quần Lót Nam Tam Giác Nhật</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-tam-giac-nhat-p16546849.html?spid=53006035</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1491,22 +1491,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>185000</v>
+        <v>161700</v>
       </c>
       <c r="G13" t="n">
-        <v>153550</v>
+        <v>210000</v>
       </c>
       <c r="H13" t="n">
-        <v>-31450</v>
+        <v>48300</v>
       </c>
       <c r="I13" t="n">
-        <v>-17</v>
+        <v>29.87</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1515,26 +1515,26 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,29 +1544,29 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Giá giảm 31,450đ (17.0%)</t>
+          <t>Giá tăng 48,300đ (+29.9%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>279491793</t>
+          <t>7078807</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Đầm xoè linen cao cấp,độ bền cao,mát mịn,thấm hút mồ hôi,may viền tỉ mỉ,sản xuất độc quyền tại Kiều Oanh Designer</t>
+          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dam-xoe-linen-cao-cap-do-ben-cao-mat-min-tham-hut-mo-hoi-may-vien-ti-mi-san-xuat-doc-quyen-tai-kieu-oanh-designer-p279491793.html?spid=279491958</t>
+          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858717</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1575,22 +1575,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>296450</v>
       </c>
       <c r="G14" t="n">
-        <v>860000</v>
+        <v>420000</v>
       </c>
       <c r="H14" t="n">
-        <v>860000</v>
+        <v>123550</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>41.68</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1599,53 +1599,53 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 123,550đ (+41.7%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>73862702</t>
+          <t>143940811</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
+          <t>Đồ bộ Tole lửng</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862720</t>
+          <t>https://tiki.vn/do-bo-tole-lung-p143940811.html?spid=278943919</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1659,22 +1659,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>173000</v>
+        <v>100000</v>
       </c>
       <c r="G15" t="n">
-        <v>140130</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-32870</v>
+        <v>-100000</v>
       </c>
       <c r="I15" t="n">
-        <v>-19</v>
+        <v>-100</v>
       </c>
       <c r="J15" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1683,53 +1683,53 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Giá giảm 32,870đ (19.0%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>278004504</t>
+          <t>279491793</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nữ Su Tăm Trơn Không Viền Mỏng Nhẹ 892 – Co Giãn 4 Chiều, Thoáng Mát, Không Lộ Viền (Size L/XL/XXL)</t>
+          <t>Đầm xoè linen cao cấp,độ bền cao,mát mịn,thấm hút mồ hôi,may viền tỉ mỉ,sản xuất độc quyền tại Kiều Oanh Designer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nu-su-tam-tron-khong-vien-mong-nhe-892-co-gian-4-chieu-thoang-mat-khong-lo-vien-size-l-xl-xxl-p278004504.html?spid=278004508</t>
+          <t>https://tiki.vn/dam-xoe-linen-cao-cap-do-ben-cao-mat-min-tham-hut-mo-hoi-may-vien-ti-mi-san-xuat-doc-quyen-tai-kieu-oanh-designer-p279491793.html?spid=279491958</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1743,16 +1743,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>188600</v>
+        <v>860000</v>
       </c>
       <c r="G16" t="n">
-        <v>230000</v>
+        <v>790000</v>
       </c>
       <c r="H16" t="n">
-        <v>41400</v>
+        <v>-70000</v>
       </c>
       <c r="I16" t="n">
-        <v>21.95</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1796,24 +1796,24 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Giá tăng 41,400đ (+22.0%)</t>
+          <t>Giá giảm 70,000đ (8.1%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>74421501</t>
+          <t>113145806</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
+          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
+          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>160000</v>
+        <v>117000</v>
       </c>
       <c r="G17" t="n">
-        <v>129600</v>
+        <v>97110</v>
       </c>
       <c r="H17" t="n">
-        <v>-30400</v>
+        <v>-19890</v>
       </c>
       <c r="I17" t="n">
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="J17" t="n">
-        <v>153</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>153</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1851,26 +1851,26 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1880,29 +1880,29 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá giảm 30,400đ (19.0%)</t>
+          <t>Giá giảm 19,890đ (17.0%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7078807</t>
+          <t>112851354</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
+          <t>Áo ngực học sinh</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858717</t>
+          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138792</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1911,22 +1911,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>385000</v>
+        <v>42000</v>
       </c>
       <c r="G18" t="n">
-        <v>296450</v>
+        <v>35280</v>
       </c>
       <c r="H18" t="n">
-        <v>-88550</v>
+        <v>-6720</v>
       </c>
       <c r="I18" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1935,26 +1935,26 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1964,24 +1964,24 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá giảm 88,550đ (23.0%)</t>
+          <t>Giá giảm 6,720đ (16.0%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>113144956</t>
+          <t>278157402</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>siêu phẩm áo lót nhật trơn đệm nâng ngực nhẹ</t>
+          <t>Áo sơ mi kiểu tay lỡ cổ đức, chất liệu Đũi tơ mềm mát, thấm hút mồ hôi, áo kiểu nữ dễ thương, NeSa Shop AT12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/sieu-pham-ao-lot-tron-dem-nang-nguc-nhe-p113144956.html?spid=142116876</t>
+          <t>https://tiki.vn/ao-so-mi-kieu-tay-lo-co-duc-chat-lieu-dui-to-mem-mat-tham-hut-mo-hoi-ao-kieu-nu-de-thuong-nesa-shop-at12-p278157402.html?spid=278157438</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>123750</v>
+        <v>168000</v>
       </c>
       <c r="G19" t="n">
-        <v>165000</v>
+        <v>168000</v>
       </c>
       <c r="H19" t="n">
-        <v>41250</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,26 +2019,26 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2048,50 +2048,50 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá tăng 41,250đ (+33.3%)</t>
+          <t>Rating 4.0→4.5 (+0.50) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>56041700</t>
+          <t>276827848</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quần bơi nam cao cấp, đồ bơi nam boxer đẹp</t>
+          <t>Quần Jean Ống Rộng Classic Carolina Blue Aaa Jeans</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-boi-nam-cao-cap-do-boi-nam-boxer-dep-p56041700.html?spid=56041702</t>
+          <t>https://tiki.vn/quan-jean-o-ng-rong-classic-carolina-blue-aaa-jeans-p276827848.html?spid=276827850</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>TRIPLE A</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="H20" t="n">
-        <v>-200000</v>
+        <v>650000</v>
       </c>
       <c r="I20" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2103,16 +2103,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2122,118 +2122,118 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>52054230</t>
+          <t>275631855</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>combo 5 quần sịp chéo cotton nam xuất nhật túi zip bạc</t>
+          <t>Thắt lưng nam da bò nguyên chất mặt khóa tự động hợp kim cao cấp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-sip-cheo-cotton-nam-xuat-nhat-tui-zip-bac-p52054230.html?spid=73622918</t>
+          <t>https://tiki.vn/that-lung-nam-da-bo-nguyen-chat-mat-khoa-tu-dong-hop-kim-cao-cap-p275631855.html?spid=275631857</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>ANANSHOP688</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>189000</v>
+        <v>199000</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="H21" t="n">
-        <v>-189000</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
+        <v>36</v>
+      </c>
+      <c r="K21" t="n">
+        <v>36</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>9</v>
+      </c>
+      <c r="R21" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Rating 4.6→4.5 (-0.10) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>173635485</t>
+          <t>152246210</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Giày Lười Nam Tăng Chiều Cao Da Bò Thật BIGGBEN Cao Cấp GM270</t>
+          <t>Giày mọi nam da bò thật BIGGBEN cao cấp GM266</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-luoi-nam-tang-chieu-cao-da-bo-that-biggben-cao-cap-gm269-p173635485.html?spid=278818066</t>
+          <t>https://tiki.vn/giay-moi-nam-da-bo-that-biggben-cao-cap-gm266-p152246210.html?spid=152246220</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2247,22 +2247,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>999000</v>
+        <v>599000</v>
       </c>
       <c r="G22" t="n">
-        <v>1700000</v>
+        <v>800000</v>
       </c>
       <c r="H22" t="n">
-        <v>701000</v>
+        <v>201000</v>
       </c>
       <c r="I22" t="n">
-        <v>70.17</v>
+        <v>33.56</v>
       </c>
       <c r="J22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2271,26 +2271,26 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2300,50 +2300,50 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Giá tăng 701,000đ (+70.2%)</t>
+          <t>Giá tăng 201,000đ (+33.6%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>275042862</t>
+          <t>124273951</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GIÀY CHẠY BỘ VÀ ĐI BỘ ĐỊA HÌNH SLM X-ADVENTURE OLIVE NIGHT - L47386000</t>
+          <t>Bộ Búi Tóc Đa Năng 4 Món Giúp Bạn Có Kiểu Tóc Xinh</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-chay-bo-va-di-bo-dia-hinh-slm-x-adventure-olive-night-l47386000-p275042862.html?spid=275042868</t>
+          <t>https://tiki.vn/bo-bui-toc-da-nang-4-mon-giup-ban-co-kieu-toc-xinh-p124273951.html?spid=124273958</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Salomon</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="G23" t="n">
-        <v>3800000</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3800000</v>
+        <v>-19000</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2355,16 +2355,16 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2374,39 +2374,39 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>113145806</t>
+          <t>278449303</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
+          <t xml:space="preserve">Mấy Xajy Bột Khô Siêu Khỏe 3000W – Bột Mịn Siêu Tốc, Nghiêjn Ngjũ Cốc &amp; Hạt Khô Đa Năng, đèn trang trí   đồng hồ treo tường </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
+          <t>https://tiki.vn/may-xajy-bot-kho-sieu-khoe-3000w-bot-min-sieu-toc-nghiejn-ngju-coc-hat-kho-da-nang-den-trang-tri-dong-ho-treo-tuong-p278449303.html?spid=278449304</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2415,22 +2415,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>88920</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>117000</v>
+        <v>1288000</v>
       </c>
       <c r="H24" t="n">
-        <v>28080</v>
+        <v>1288000</v>
       </c>
       <c r="I24" t="n">
-        <v>31.58</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2439,58 +2439,58 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Giá tăng 28,080đ (+31.6%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>144236336</t>
+          <t>174175573</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COMBO 5 ÁO LÓT VẢI KHÔNG GỌNG KHÔNG MÚT (SIZE 32-42)</t>
+          <t>Combo sỉ 5 quần lót  nam cao cấp</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-ao-lot-vai-khong-gong-khong-mut-size-32-42-p144236336.html?spid=146366320</t>
+          <t>https://tiki.vn/combo-si-5-quan-lot-nam-cao-cap-p174175573.html?spid=174175578</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2499,22 +2499,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>210000</v>
+        <v>150000</v>
       </c>
       <c r="G25" t="n">
-        <v>174300</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-35700</v>
+        <v>-150000</v>
       </c>
       <c r="I25" t="n">
-        <v>-17</v>
+        <v>-100</v>
       </c>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2523,79 +2523,79 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Giá giảm 35,700đ (17.0%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>276086848</t>
+          <t>113144956</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cục bông trang trí nhiều màu sắc chọn lựa (tùy chọn màu sắc) (hàng có sẵn giao nhanh) (Hàng Chính Hãng)</t>
+          <t>siêu phẩm áo lót nhật trơn đệm nâng ngực nhẹ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/cuc-bong-trang-tri-nhieu-mau-sac-chon-lua-tuy-chon-mau-sac-hang-co-san-giao-nhanh-hang-chinh-hang-p276086848.html?spid=276086851</t>
+          <t>https://tiki.vn/sieu-pham-ao-lot-tron-dem-nang-nguc-nhe-p113144956.html?spid=142116876</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bilaha</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="G26" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>70000</v>
+        <v>-165000</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2607,16 +2607,16 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2626,34 +2626,34 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>192642640</t>
+          <t>275738497</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cài tóc bảng nhỏ 1 cm - cài tóc nam nữ - cài tóc đơn giản</t>
+          <t>Mặt Khóa Thắt Lưng Nam Cao Cấp,Mặt Thắt Lưng Nam Khóa Tự Động 203859</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/cai-toc-bang-nho-1-cm-cai-toc-nam-nu-cai-toc-don-gian-p192642640.html?spid=192642674</t>
+          <t>https://tiki.vn/mat-khoa-that-lung-nam-cao-cap-mat-that-lung-nam-khoa-tu-dong-203859-p275738497.html?spid=275738498</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2663,26 +2663,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>TLG Thành Long</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>24000</v>
+        <v>61400</v>
       </c>
       <c r="G27" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-61400</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J27" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2694,50 +2694,50 @@
         <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Review thêm +2</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38160273</t>
+          <t>126091279</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Giày Boot Nam BIGGBEN Da Bò Thật Cao Cấp BT2</t>
+          <t>Giày Mọi, Giày Lười Nam Da Bò SUNPOLO SU5059 Hiện đại (Đen)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-boot-nam-biggben-da-bo-that-cao-cap-bt2-p38160273.html?spid=38160275</t>
+          <t>https://tiki.vn/giay-moi-giay-luoi-nam-da-bo-sunpolo-su5059-hien-dai-den-p126091279.html?spid=126091289</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2747,23 +2747,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>SUNPOLO</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2000000</v>
+        <v>1100000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-2000000</v>
+        <v>-1100000</v>
       </c>
       <c r="I28" t="n">
         <v>-100</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2775,13 +2775,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="Q28" t="n">
         <v>3</v>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2811,52 +2811,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>278957623</t>
+          <t>274586950</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dép quai kẹp Biti's nam (size 38-43)</t>
+          <t>Set 100 Miếng dán chống mồ hôi nách, miếng dán ngăn mồ hôi nách siêu thâm hút cho Nam và Nữ che tên sản phẩm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-kep-biti-s-nam-size-38-43-p278957623.html?spid=278957641</t>
+          <t>https://tiki.vn/set-100-mieng-dan-chong-mo-hoi-nach-mieng-dan-ngan-mo-hoi-nach-sieu-tham-hut-cho-nam-va-nu-che-ten-san-pham-p274586950.html?spid=274586956</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Biti's</t>
+          <t>FTAKY</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>232000</v>
+        <v>199000</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="H29" t="n">
-        <v>-232000</v>
+        <v>-100000</v>
       </c>
       <c r="I29" t="n">
-        <v>-100</v>
+        <v>-50.25</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>-198000</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2878,521 +2878,101 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 100,000đ (50.3%) | Bán thêm -2 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>276827848</t>
+          <t>49733157</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Quần Jean Ống Rộng Classic Carolina Blue Aaa Jeans</t>
+          <t>Quần bơi nam giới dáng vừa, độ dài trên gối, chất thun bơi lạnh dày đẹp, co giãn 4 chiều ôm đùi gọn gàng dễ chịu, thoáng mát nhanh khô | BN005</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-jean-o-ng-rong-classic-carolina-blue-aaa-jeans-p276827848.html?spid=276827850</t>
+          <t>https://tiki.vn/quan-boi-nam-dang-lung-mau-moi-2020-vai-boi-day-dan-dep-co-gian-4-chieu-bn005-p49733157.html?spid=49733161</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TRIPLE A</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>650000</v>
+        <v>115000</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="H30" t="n">
-        <v>-650000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>-920000</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>277744886</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Giày Da Nam Italy - 1720BIA</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/giay-da-nam-italy-1720bia-p277744886.html?spid=277744894</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Gianni Conti</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>278449303</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mấy Xajy Bột Khô Siêu Khỏe 3000W – Bột Mịn Siêu Tốc, Nghiêjn Ngjũ Cốc &amp; Hạt Khô Đa Năng, đèn trang trí   đồng hồ treo tường </t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/may-xajy-bot-kho-sieu-khoe-3000w-bot-min-sieu-toc-nghiejn-ngju-coc-hat-kho-da-nang-den-trang-tri-dong-ho-treo-tuong-p278449303.html?spid=278449304</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1288000</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-1288000</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>68491184</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Kính râm Nam thời trang + Tặng Tuavit Kính Xinh Mini đa năng</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/kinh-ram-nam-thoi-trang-tang-tuavit-kinh-xinh-mini-da-nang-p68491184.html?spid=68491185</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>HOKO</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>169000</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-169000</v>
-      </c>
-      <c r="I33" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>272224450</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Dép quai ngang nam, nữ siêu nhẹ DUWA - Hàng chính hãng - TK9056</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/dep-quai-ngang-nam-nu-sieu-nhe-duwa-hang-chinh-hang-tk9056-p272224450.html?spid=272224458</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>DUWA</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>159000</v>
-      </c>
-      <c r="G34" t="n">
-        <v>159000</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>4</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>-318000</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Bán thêm -2 sản phẩm</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>278000485</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Áo lót nữ 718 – Mút mỏng thông hơi, không gọng, cài sau 3 móc, co giãn thoải mái</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-lot-nu-718-mut-mong-thong-hoi-khong-gong-cai-sau-3-moc-co-gian-thoai-mai-p278000485.html?spid=278000517</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G35" t="n">
-        <v>100000</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>-4</v>
-      </c>
-      <c r="M35" t="n">
-        <v>-400000</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Bán thêm -4 sản phẩm</t>
+          <t>Bán thêm -8 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>132230478</t>
+          <t>7997300</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Lười Nam Da Bò SUNPOLO CS5054 Trẻ trung, thanh lịch (Đen, Nâu)</t>
+          <t>Giày Converse Chuck Taylor All Star 1970s Hi Top - 162050V</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-luoi-nam-da-bo-sunpolo-cs5054-tre-trung-thanh-lich-den-nau-p132230478.html?spid=132230492</t>
+          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-1970s-hi-top-162050v-p7997300.html?spid=13727356</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SUNPOLO</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1100000</v>
+        <v>2000000</v>
       </c>
       <c r="H2" t="n">
-        <v>1100000</v>
+        <v>2000000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>17600000</v>
+        <v>400000000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,37 +627,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>197062475</t>
+          <t>7995370</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Áo khoác măng tô nam cổ đứng dáng ngắn khóa kéo chất vải kaki đẹp NMT34</t>
+          <t>Giày Converse Chuck Taylor All Star Classic Hi Top - 121186</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-mang-to-nam-co-dung-dang-ngan-khoa-keo-chat-vai-kaki-dep-nmt34-p197062475.html?spid=197062507</t>
+          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-classic-hi-top-121186-p7995370.html?spid=20315038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>936000</v>
+        <v>1550000</v>
       </c>
       <c r="H3" t="n">
-        <v>936000</v>
+        <v>1550000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="M3" t="n">
-        <v>6552000</v>
+        <v>142600000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,37 +711,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>270474726</t>
+          <t>96301779</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bộ đồ bơi nam ngắn tay + quần boxer 2 lớp, họa tiết mạnh mẽ, set quần áo đi biển, đi bơi cho nam giới, chất thun bơi dày dặn mịn mát đẹp | BN031</t>
+          <t>Dép Bít Mũi Nam HÀ NAM Da Bò Thật Cao Cấp GSB2068</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-do-boi-nam-ngan-tay-quan-boxer-2-lop-hoa-tiet-manh-me-set-quan-ao-di-bien-di-boi-cho-nam-gioi-chat-thun-boi-day-dan-min-mat-dep-bn031-p270474726.html?spid=275928740</t>
+          <t>https://tiki.vn/dep-bit-mui-nam-sabo-nam-da-bo-that-de-cao-su-gsb2068-p96301779.html?spid=96301783</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>HA NAM</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>420000</v>
+        <v>468000</v>
       </c>
       <c r="H4" t="n">
-        <v>420000</v>
+        <v>468000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,35 +750,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
-        <v>3780000</v>
+        <v>5148000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,37 +795,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>55953905</t>
+          <t>13307720</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày tây tăng chiều cao Trường Hải da bò cao cấp cao 6.5 cm trường Hải GTN0125</t>
+          <t>Combo 10 Quần lót nam, sịp chéo nam xuất Nhật thời trang cao cấp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-tay-nam-tang-chieu-cao-truong-hai-da-bo-cao-cap-cao-6-5-cm-de-cao-su-giay-duoc-gia-cong-tai-xuong-truong-hai-gtn0125-p55953905.html?spid=55953907</t>
+          <t>https://tiki.vn/combo-10-quan-lot-nam-sip-cheo-nam-xuat-nhat-thoi-trang-cao-cap-p13307720.html?spid=278703711</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trường Hải</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>645000</v>
+        <v>336000</v>
       </c>
       <c r="H5" t="n">
-        <v>645000</v>
+        <v>336000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -834,13 +834,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>2580000</v>
+        <v>2688000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -855,14 +855,14 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -879,37 +879,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>48310107</t>
+          <t>193095213</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giày Mọi Nam Da Bò BIGGBEN GM219</t>
+          <t>Kính Râm Kính Mát Nam Nữ TF Mắt To Gọng Nhựa Dẻo TR90 Mắt Màu Vàng, Xanh Dương, Đen Chống Tia UV - BLUE LIGHT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-moi-nam-da-bo-biggben-gm219-p48310107.html?spid=48310111</t>
+          <t>https://tiki.vn/kinh-ram-kinh-mat-nam-nu-tf-mat-to-gong-nhua-deo-tr90-mat-mau-vang-xanh-duong-den-chong-tia-uv-blue-light-p193095213.html?spid=193095217</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>Blue Light</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>800000</v>
+        <v>185000</v>
       </c>
       <c r="H6" t="n">
-        <v>800000</v>
+        <v>185000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -918,35 +918,35 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>2400000</v>
+        <v>2035000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -963,37 +963,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>107491961</t>
+          <t>277877891</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dép Nam Quai Ngang Da Bò BIGGBEN Cao Cấp DN283</t>
+          <t>Móc Nối Tăng Size Áo Ngực 3 Móc 59S – Phụ Kiện Nới Rộng Bra Linh Hoạt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-biggben-cao-cap-dn283-p107491961.html?spid=107491981</t>
+          <t>https://tiki.vn/moc-noi-tang-size-ao-nguc-3-moc-59s-phu-kien-noi-rong-bra-linh-hoat-p277877891.html?spid=277877895</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>395000</v>
+        <v>20000</v>
       </c>
       <c r="H7" t="n">
-        <v>395000</v>
+        <v>20000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1002,35 +1002,35 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>19</v>
+      </c>
+      <c r="L7" t="n">
+        <v>19</v>
+      </c>
+      <c r="M7" t="n">
+        <v>380000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="S7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>395000</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,34 +1047,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>114739740</t>
+          <t>113215403</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cột tóc srunchies mẫu mới màu hồng phấn đẹp</t>
+          <t>Lót giày vải lưới Hương Quế, quế thật, quế thơm, tốt cho sức khỏe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/cot-toc-srunchies-mau-moi-mau-hong-phan-dep-p114739740.html?spid=114739748</t>
+          <t>https://tiki.vn/lot-giay-vai-luoi-huong-que-que-that-que-thom-tot-cho-suc-khoe-p113215403.html?spid=113215415</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Hương quế</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>25000</v>
+        <v>38000</v>
       </c>
       <c r="G8" t="n">
-        <v>25000</v>
+        <v>38000</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1083,38 +1083,38 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="K8" t="n">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>250000</v>
+        <v>190000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1124,125 +1124,125 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +10 sản phẩm</t>
+          <t>Bán thêm +5 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>199607832</t>
+          <t>19843976</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combo 4 Quần Lót Ren Miley Lingerie Màu Trắng Đen - FLS03</t>
+          <t>Combo 10 Đôi Tất Nam Chống Hôi Chân Thời Trang</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-4-quan-lot-ren-miley-lingerie-mau-trang-den-fls03-p199607832.html?spid=199607836</t>
+          <t>https://tiki.vn/combo-10-doi-tat-nam-chong-hoi-chan-thoi-trang-p19843976.html?spid=71526312</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miley Lingerie</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="G9" t="n">
-        <v>216000</v>
+        <v>79000</v>
       </c>
       <c r="H9" t="n">
-        <v>216000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>378</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>216000</v>
+        <v>79000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>67538621</t>
+          <t>212471303</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
+          <t>Sét 8 Kẹp Tóc Size To Phong Cách Hàn Quốc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538623</t>
+          <t>https://tiki.vn/set-8-kep-toc-size-to-phong-cach-han-quoc-p212471303.html?spid=212471304</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>May 10</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>135000</v>
+        <v>59000</v>
       </c>
       <c r="G10" t="n">
-        <v>135000</v>
+        <v>59000</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1251,38 +1251,38 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>16601</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>16602</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>135000</v>
+        <v>59000</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4843</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>4843</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1299,142 +1299,142 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19843976</t>
+          <t>278704460</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Combo 10 Đôi Tất Nam Chống Hôi Chân Thời Trang</t>
+          <t>Áo Thun Basic Tay Ngắn Nam Ninomaxx 2505012</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-doi-tat-nam-chong-hoi-chan-thoi-trang-p19843976.html?spid=71526312</t>
+          <t>https://tiki.vn/ao-thun-basic-tay-ngan-nam-ninomaxx-2505012-p278704460.html?spid=278704476</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ninomaxx</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>79000</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>79000</v>
+        <v>269000</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>269000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>79000</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>187249357</t>
+          <t>16651795</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cặp Cài Tai Giữ Mắt Kính Bằng Silicon Chống Trượt Tiện Dụng</t>
+          <t>️[5 Quần] ComBo 5 Quần Lót Nam THUN LẠNH Lưng Bự Hàng Việt Nam Cao Cấp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/cap-cai-tai-giu-mat-kinh-bang-silicon-chong-truot-tien-dung-p187249357.html?spid=187249358</t>
+          <t>https://tiki.vn/5-quan-combo-5-quan-lot-nam-thun-lanh-lung-bu-hang-viet-nam-cao-cap-p16651795.html?spid=51148102</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OURESS</t>
+          <t>MENLIVE</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10000</v>
+        <v>190000</v>
       </c>
       <c r="G12" t="n">
-        <v>10000</v>
+        <v>159600</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-30400</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J12" t="n">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1460,29 +1460,29 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Bán thêm +3 sản phẩm</t>
+          <t>Giá giảm 30,400đ (16.0%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>83423370</t>
+          <t>16546849</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bộ dụng cụ tua vít đa năng sửa kính, mắt kính</t>
+          <t>Combo 5 Quần Lót Nam Tam Giác Nhật</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-dung-cu-tua-vit-da-nang-sua-kinh-mat-kinh-p83423370.html?spid=113070838</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-tam-giac-nhat-p16546849.html?spid=53006035</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1491,50 +1491,50 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9500</v>
+        <v>210000</v>
       </c>
       <c r="G13" t="n">
-        <v>9500</v>
+        <v>170100</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-39900</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="J13" t="n">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="K13" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,24 +1544,24 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Giá giảm 39,900đ (19.0%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>277996544</t>
+          <t>54569520</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hộp 5 Quần lót nam cotton lụa – Siêu đẹp, mềm mịn, thoáng mát</t>
+          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-5-quan-lot-nam-cotton-lua-muji-sieu-dep-mem-min-thoang-mat-p277996544.html?spid=278006734</t>
+          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1575,22 +1575,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>220000</v>
+        <v>67760</v>
       </c>
       <c r="G14" t="n">
-        <v>169400</v>
+        <v>88000</v>
       </c>
       <c r="H14" t="n">
-        <v>-50600</v>
+        <v>20240</v>
       </c>
       <c r="I14" t="n">
-        <v>-23</v>
+        <v>29.87</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1608,17 +1608,17 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1628,24 +1628,24 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Giá giảm 50,600đ (23.0%)</t>
+          <t>Giá tăng 20,240đ (+29.9%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>278021672</t>
+          <t>127197643</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quần Lót Nam Đùi Boxer Lụa Băng Menpro MP9 - Mỏng nhem Thoáng Khí</t>
+          <t>Bộ Quần Áo Nam Lính Mỹ US ARMY  Kiểu Dáng Túi Hộp, Chất Liệu Kaki Cao Cấp Phong Cách Lính Cực Ngầu (Tặng dây lưng) - HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-dui-boxer-lua-bang-menpro-mp9-mong-nhem-thoang-khi-p278021672.html?spid=278021690</t>
+          <t>https://tiki.vn/bo-quan-ao-nam-linh-my-us-army-kieu-dang-tui-hop-chat-lieu-kaki-cao-cap-phong-cach-linh-cuc-ngau-tang-day-lung-hang-chinh-hang-p127197643.html?spid=182094568</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1655,26 +1655,26 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>79000</v>
+        <v>899000</v>
       </c>
       <c r="G15" t="n">
-        <v>63200</v>
+        <v>899000</v>
       </c>
       <c r="H15" t="n">
-        <v>-15800</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1683,26 +1683,26 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1712,53 +1712,53 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Giá giảm 15,800đ (20.0%)</t>
+          <t>Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>262817701</t>
+          <t>103049077</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Giày Mọi Nam Đế Âm Da Bò Thật TiTi ĐÔ Cao Cấp GDA2021</t>
+          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-moi-nam-de-am-titi-do-da-bo-that-cao-cap-gda2021-p262817701.html?spid=262817709</t>
+          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HA NAM</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>153550</v>
       </c>
       <c r="G16" t="n">
-        <v>760000</v>
+        <v>185000</v>
       </c>
       <c r="H16" t="n">
-        <v>760000</v>
+        <v>31450</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>20.48</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1767,58 +1767,58 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 31,450đ (+20.5%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>59462352</t>
+          <t>16375016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Áo ngực mỏng thêu hoa cài trước có gọng</t>
+          <t>COMBO HỘP 5 Quần Lót ĐÙI Nam Xuất Nhật Cao Cấp (MIX NGẪU NHIÊN)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-mong-theu-hoa-cai-truoc-co-gong-p59462352.html?spid=59462384</t>
+          <t>https://tiki.vn/combo-hop-5-quan-lot-dui-nam-xuat-nhat-cao-cap-mix-ngau-nhien-p16375016.html?spid=277961877</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>90000</v>
+        <v>274000</v>
       </c>
       <c r="G17" t="n">
-        <v>90000</v>
+        <v>210980</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-63020</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="J17" t="n">
-        <v>204</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>204</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1851,26 +1851,26 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1880,53 +1880,53 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Review thêm +5</t>
+          <t>Giá giảm 63,020đ (23.0%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>279104033</t>
+          <t>278850221</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Áo lót nữ form ba lỗ thông hơi trơn big size 1397 – Size XXL–3XL</t>
+          <t>Quần Jean Thời Trang Basic Nam Ống Đứng Ninomaxx 2508004</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-form-ba-lo-thong-hoi-tron-big-size-1397-size-xxl-3xl-p279104033.html?spid=279104035</t>
+          <t>https://tiki.vn/quan-jean-thoi-trang-basic-nam-ong-dung-ninomaxx-2508004-p278850221.html?spid=278850229</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ninomaxx</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>108000</v>
+        <v>769000</v>
       </c>
       <c r="G18" t="n">
-        <v>86400</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-21600</v>
+        <v>-769000</v>
       </c>
       <c r="I18" t="n">
-        <v>-20</v>
+        <v>-100</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1935,82 +1935,82 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá giảm 21,600đ (20.0%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>91973812</t>
+          <t>274795145</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Su Đúc Hình Lá Không Gọng Đệm Dày Nâng Ngực A01 có ảnh thật</t>
+          <t>Dép tổ ong [Size 39-43] KÈM STICKER NGẪU NHIÊN vật liệu EVA cao cấp siêu bền, siêu nhẹ, chống trơn trượt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-su-duc-hinh-la-khong-gong-dem-day-nang-nguc-a01-co-anh-that-p91973812.html?spid=279055013</t>
+          <t>https://tiki.vn/dep-to-ong-size-39-43-kem-sticker-ngau-nhien-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-p274795145.html?spid=274803712</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t xml:space="preserve">VAC </t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>85000</v>
+        <v>83000</v>
       </c>
       <c r="G19" t="n">
-        <v>68000</v>
+        <v>100000</v>
       </c>
       <c r="H19" t="n">
-        <v>-17000</v>
+        <v>17000</v>
       </c>
       <c r="I19" t="n">
-        <v>-20</v>
+        <v>20.48</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,26 +2019,26 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2048,53 +2048,53 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá giảm 17,000đ (20.0%)</t>
+          <t>Giá tăng 17,000đ (+20.5%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>278850221</t>
+          <t>73862702</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quần Jean Thời Trang Basic Nam Ống Đứng Ninomaxx 2508004</t>
+          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-jean-thoi-trang-basic-nam-ong-dung-ninomaxx-2508004-p278850221.html?spid=278850229</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862720</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ninomaxx</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>140130</v>
       </c>
       <c r="G20" t="n">
-        <v>769000</v>
+        <v>173000</v>
       </c>
       <c r="H20" t="n">
-        <v>769000</v>
+        <v>32870</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>23.46</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2103,82 +2103,82 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 32,870đ (+23.5%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>55139307</t>
+          <t>37126497</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Giày Tây Nam Da Bò BIGGBEN Cao Cấp GT179</t>
+          <t>( 10 cái ) quần lót nữ Su đúc không đường may, hàng đẹp loại xịn W19_503</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-tay-nam-da-bo-biggben-cao-cap-gt179-p55139307.html?spid=55139313</t>
+          <t>https://tiki.vn/set-10-quan-lot-su-duc-khong-duong-may-hang-dep-loai-xin-w19_503-p37126497.html?spid=51720423</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BIGGBEN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>280000</v>
       </c>
       <c r="G21" t="n">
-        <v>670000</v>
+        <v>210000</v>
       </c>
       <c r="H21" t="n">
-        <v>670000</v>
+        <v>-70000</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2187,58 +2187,58 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 70,000đ (25.0%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>172474530</t>
+          <t>74421501</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quần short thun nam cao cấp, quần short nam vải cotton LN058</t>
+          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-short-thun-nam-cao-cap-quan-short-nam-vai-cotton-ln058-p172474530.html?spid=276662143</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2247,22 +2247,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>85000</v>
+        <v>129600</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="H22" t="n">
-        <v>-85000</v>
+        <v>30400</v>
       </c>
       <c r="I22" t="n">
-        <v>-100</v>
+        <v>23.46</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>153</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2271,76 +2271,76 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.6</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 30,400đ (+23.5%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>278704460</t>
+          <t>277586478</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Áo Thun Basic Tay Ngắn Nam Ninomaxx 2505012</t>
+          <t>Dép nam quai ngang da thật BHD2512 Dép nam trung niên</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-basic-tay-ngan-nam-ninomaxx-2505012-p278704460.html?spid=278704476</t>
+          <t>https://tiki.vn/dep-nam-quai-ngang-da-that-bhd2512-dep-nam-trung-nien-p277586478.html?spid=277586488</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ninomaxx</t>
+          <t>MARRANT</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>269000</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>299000</v>
       </c>
       <c r="H23" t="n">
-        <v>-269000</v>
+        <v>299000</v>
       </c>
       <c r="I23" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2374,39 +2374,39 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13307720</t>
+          <t>140429170</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Combo 10 Quần lót nam, sịp chéo nam xuất Nhật thời trang cao cấp</t>
+          <t>Bao tay chơi game găng tay 2 ngón cảm ứng điện thoại gamemobile BT01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nam-sip-cheo-nam-xuat-nhat-thoi-trang-cao-cap-p13307720.html?spid=278703711</t>
+          <t>https://tiki.vn/bao-tay-choi-game-gang-tay-2-ngon-cam-ung-dien-thoai-gamemobile-bt01-p140429170.html?spid=198934954</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2415,22 +2415,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>420000</v>
+        <v>9999</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>19999</v>
       </c>
       <c r="H24" t="n">
-        <v>-420000</v>
+        <v>10000</v>
       </c>
       <c r="I24" t="n">
-        <v>-100</v>
+        <v>100.01</v>
       </c>
       <c r="J24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2439,16 +2439,16 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2458,54 +2458,54 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 10,000đ (+100.0%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>279345710</t>
+          <t>87670339</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Áo thun nữ Ruzimay RA2000 lệch vai co giãn mềm mại thanh lịch</t>
+          <t>Áo Khoác Dù 2 Mặt Cao Cấp Chống Thấm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nu-ruzimay-ra2000-lech-vai-co-gian-mem-mai-thanh-lich-p279345710.html?spid=279345726</t>
+          <t>https://tiki.vn/ao-khoac-du-2-mat-cao-cap-chong-tham-p87670339.html?spid=113225543</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ruzimay Style</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>212000</v>
+        <v>317035</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-212000</v>
+        <v>-317035</v>
       </c>
       <c r="I25" t="n">
         <v>-100</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2559,17 +2559,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>272224450</t>
+          <t>7995659</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dép quai ngang nam, nữ siêu nhẹ DUWA - Hàng chính hãng - TK9056</t>
+          <t>Giày Converse Chuck Taylor All Star Classic Low Top - 121176</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-ngang-nam-nu-sieu-nhe-duwa-hang-chinh-hang-tk9056-p272224450.html?spid=272224470</t>
+          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-classic-low-top-121176-p7995659.html?spid=20340964</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2579,23 +2579,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DUWA</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>159000</v>
+        <v>1450000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-159000</v>
+        <v>-1450000</v>
       </c>
       <c r="I26" t="n">
         <v>-100</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2607,16 +2607,16 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.5</v>
+        <v>-4.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2643,43 +2643,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>217139643</t>
+          <t>46773376</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dép quai ngang nam nữ siêu nhẹ DUWA - Hàng chính hãng - TK9048</t>
+          <t>Áo Ngực Tạo 7 Kiểu Mặc Multiway Cực Phong Cách Và Nâng Ngực Siêu Hít AL07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-ngang-nam-nu-sieu-nhe-duwa-hang-chinh-hang-tk9048-p217139643.html?spid=217139655</t>
+          <t>https://tiki.vn/ao-nguc-tao-7-kieu-mac-multiway-cuc-phong-cach-va-nang-nguc-sieu-hit-al07-p46773376.html?spid=52950082</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DUWA</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>159000</v>
+        <v>100000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-159000</v>
+        <v>-100000</v>
       </c>
       <c r="I27" t="n">
         <v>-100</v>
       </c>
       <c r="J27" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2691,16 +2691,16 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.7</v>
+        <v>-5</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2727,17 +2727,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>202048399</t>
+          <t>7997276</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dép quai ngang nam, nữ siêu nhẹ DUWA - Hàng chính hãng - TK9045</t>
+          <t>Giày Sneaker Unisex Converse Chuck Taylor All Star 1970s All Hi 2018 - White (Size</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-ngang-nam-nu-sieu-nhe-duwa-hang-chinh-hang-tk9045-p202048399.html?spid=202048466</t>
+          <t>https://tiki.vn/giay-sneaker-unisex-converse-chuck-taylor-all-star-1970s-all-white-hi-2018-p7997276.html?spid=26499478</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2747,23 +2747,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DUWA</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>159000</v>
+        <v>2000000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-159000</v>
+        <v>-2000000</v>
       </c>
       <c r="I28" t="n">
         <v>-100</v>
       </c>
       <c r="J28" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
         <v>-5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2811,17 +2811,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>194131743</t>
+          <t>9810961</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dép đúc quai ngang nam, nữ siêu nhẹ DUWA - Hàng chính hãng - TK193</t>
+          <t>Giày Slip On Unisex Vans - VN000EYEBWW</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-duc-quai-ngang-nam-nu-sieu-nhe-duwa-hang-chinh-hang-tk193-p194131743.html?spid=194131775</t>
+          <t>https://tiki.vn/giay-slip-on-unisex-vans-vn000eyebww-p9810961.html?spid=23839235</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2831,23 +2831,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DUWA</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>179000</v>
+        <v>1450000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-179000</v>
+        <v>-1450000</v>
       </c>
       <c r="I29" t="n">
         <v>-100</v>
       </c>
       <c r="J29" t="n">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2859,16 +2859,16 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-4.8</v>
+        <v>-5</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -2895,43 +2895,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>273466355</t>
+          <t>278994189</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dép xỏ ngón nam, nữ đúc liền khối siêu nhẹ DUWA - Hàng chính hãng - TK288</t>
+          <t>Áo thun tay ngắn nam patch ngực Form Fitted - ROUTINE 10F25TSS003</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-xo-ngon-nam-nu-duc-lien-khoi-sieu-nhe-duwa-hang-chinh-hang-tk288-p273466355.html?spid=273466357</t>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-patch-nguc-form-fitted-routine-10f25tss003-p278994189.html?spid=278994205</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DUWA</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>129000</v>
+        <v>349000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-129000</v>
+        <v>-349000</v>
       </c>
       <c r="I30" t="n">
         <v>-100</v>
       </c>
       <c r="J30" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2943,16 +2943,16 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-4.6</v>
+        <v>-0</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -2979,17 +2979,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>270791815</t>
+          <t>9810794</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dép đúc siêu nhẹ nam, nữ DUWA - Hàng chính hãng - TK2272</t>
+          <t>Giày Slip On Unisex Vans - VN000EYEBLK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-duc-sieu-nhe-nam-nu-duwa-hang-chinh-hang-tk2272-p270791815.html?spid=270791831</t>
+          <t>https://tiki.vn/giay-slip-on-unisex-vans-vn000eyeblk-p9810794.html?spid=20459574</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2999,23 +2999,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DUWA</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>159000</v>
+        <v>1450000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-159000</v>
+        <v>-1450000</v>
       </c>
       <c r="I31" t="n">
         <v>-100</v>
       </c>
       <c r="J31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3057,6 +3057,174 @@
       <c r="V31" t="inlineStr">
         <is>
           <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>72050932</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Khẩu Trang Pitta Nhật Bản Small Chic - Gói 3 cái (mẫu mới 2020)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/khau-trang-pitta-nhat-ban-small-chic-goi-3-cai-mau-moi-2020-p72050932.html?spid=72050933</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PITTA MASK</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-180000</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J32" t="n">
+        <v>49</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>275276395</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dép tổ ong TRẮNG nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/dep-to-ong-trangvat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276395.html?spid=275276411</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VAC </t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>72000</v>
+      </c>
+      <c r="G33" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I33" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="J33" t="n">
+        <v>45</v>
+      </c>
+      <c r="K33" t="n">
+        <v>30</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-15</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-1275000</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Giá tăng 13,000đ (+18.1%) | Bán thêm -15 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7997300</t>
+          <t>6132855</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Converse Chuck Taylor All Star 1970s Hi Top - 162050V</t>
+          <t>Dép Nam BIGGBEN Da Bò Thật DN35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-1970s-hi-top-162050v-p7997300.html?spid=13727356</t>
+          <t>https://tiki.vn/dep-nam-biggben-da-bo-that-dn35-p6132855.html?spid=6132867</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2000000</v>
+        <v>419000</v>
       </c>
       <c r="H2" t="n">
-        <v>2000000</v>
+        <v>419000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="L2" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="M2" t="n">
-        <v>400000000</v>
+        <v>35615000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="P2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="S2" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,37 +627,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7995370</t>
+          <t>273395259</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Giày Converse Chuck Taylor All Star Classic Hi Top - 121186</t>
+          <t>Quần Đùi HUONGTAM  nam cao cấp(QDN). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-classic-hi-top-121186-p7995370.html?spid=20315038</t>
+          <t>https://tiki.vn/quan-dui-huongtam-nam-cao-cap-qdn-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p273395259.html?spid=273395431</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1550000</v>
+        <v>47600</v>
       </c>
       <c r="H3" t="n">
-        <v>1550000</v>
+        <v>47600</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="M3" t="n">
-        <v>142600000</v>
+        <v>1475600</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,101 +711,101 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>96301779</t>
+          <t>186133766</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dép Bít Mũi Nam HÀ NAM Da Bò Thật Cao Cấp GSB2068</t>
+          <t>Quần Short Kaki Nam US ARMY, Quần Túi Hộp Nam Phong Cách Lính Chất Liệu KaKi Cao Cấp, Kiểu Dáng Trẻ Trung Năng Động -HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-bit-mui-nam-sabo-nam-da-bo-that-de-cao-su-gsb2068-p96301779.html?spid=96301783</t>
+          <t>https://tiki.vn/quan-short-kaki-nam-us-army-quan-tui-hop-nam-phong-cach-linh-chat-lieu-kaki-cao-cap-kieu-dang-tre-trung-nang-dong-hang-chinh-hang-p186133766.html?spid=186133780</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HA NAM</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>299000</v>
       </c>
       <c r="G4" t="n">
-        <v>468000</v>
+        <v>299000</v>
       </c>
       <c r="H4" t="n">
-        <v>468000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>269</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>5148000</v>
+        <v>1196000</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>4.7</v>
       </c>
       <c r="P4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +4 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13307720</t>
+          <t>274960088</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Combo 10 Quần lót nam, sịp chéo nam xuất Nhật thời trang cao cấp</t>
+          <t>Quần đùi nam huong tam cao cấp (QDNN6). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nam-sip-cheo-nam-xuat-nhat-thoi-trang-cao-cap-p13307720.html?spid=278703711</t>
+          <t>https://tiki.vn/quan-dui-nam-huong-tam-cao-cap-qdnn6-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p274960088.html?spid=274960112</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>336000</v>
+        <v>47600</v>
       </c>
       <c r="H5" t="n">
-        <v>336000</v>
+        <v>47600</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -834,13 +834,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M5" t="n">
-        <v>2688000</v>
+        <v>1142400</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -855,14 +855,14 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -879,37 +879,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>193095213</t>
+          <t>187336557</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kính Râm Kính Mát Nam Nữ TF Mắt To Gọng Nhựa Dẻo TR90 Mắt Màu Vàng, Xanh Dương, Đen Chống Tia UV - BLUE LIGHT</t>
+          <t>Giày Sandal Nam Bít Mũi Da Bò Thật BIGGBEN SD124</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/kinh-ram-kinh-mat-nam-nu-tf-mat-to-gong-nhua-deo-tr90-mat-mau-vang-xanh-duong-den-chong-tia-uv-blue-light-p193095213.html?spid=193095217</t>
+          <t>https://tiki.vn/giay-sandal-nam-bit-mui-da-bo-that-biggben-sd124-p187336557.html?spid=187336571</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blue Light</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>185000</v>
+        <v>499000</v>
       </c>
       <c r="H6" t="n">
-        <v>185000</v>
+        <v>499000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -918,35 +918,35 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>2035000</v>
+        <v>998000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -963,274 +963,274 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>277877891</t>
+          <t>55747001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Móc Nối Tăng Size Áo Ngực 3 Móc 59S – Phụ Kiện Nới Rộng Bra Linh Hoạt</t>
+          <t>Giày tây nam Trường Hải da bò thật mềm mại không bong tróc không dây mũi tròn màu nâu đế cao su không trơn GT0423</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/moc-noi-tang-size-ao-nguc-3-moc-59s-phu-kien-noi-rong-bra-linh-hoat-p277877891.html?spid=277877895</t>
+          <t>https://tiki.vn/giay-tay-nam-truong-hai-da-bo-that-mem-mai-khong-bong-troc-khong-day-mui-tron-mau-nau-de-cao-su-khong-tron-gt0423-p55747001.html?spid=55747019</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Trường Hải</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>485000</v>
       </c>
       <c r="G7" t="n">
-        <v>20000</v>
+        <v>485000</v>
       </c>
       <c r="H7" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="L7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>380000</v>
+        <v>970000</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +2 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>113215403</t>
+          <t>169468021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lót giày vải lưới Hương Quế, quế thật, quế thơm, tốt cho sức khỏe</t>
+          <t>Q17 Váy ngủ lụa hai dây hở lưng sexy  - Đầm ngủ nữ gợi cảm - đồ ngủ nử mặc nhà</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/lot-giay-vai-luoi-huong-que-que-that-que-thom-tot-cho-suc-khoe-p113215403.html?spid=113215415</t>
+          <t>https://tiki.vn/vay-ngu-lua-hai-day-ho-lung-sexy-bt0033-dam-ngu-nu-goi-cam-do-ngu-nu-mac-nha-p169468021.html?spid=169468029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hương quế</t>
+          <t xml:space="preserve">	OEM</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>38000</v>
+        <v>210000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>184</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>190000</v>
+        <v>840000</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +5 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19843976</t>
+          <t>271158363</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combo 10 Đôi Tất Nam Chống Hôi Chân Thời Trang</t>
+          <t>Bộ Pyjama HUONGTAM Kate  tay ngắn nam cao cấp(PNK02). Chất liệu Kate loại tốt:  mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-doi-tat-nam-chong-hoi-chan-thoi-trang-p19843976.html?spid=71526312</t>
+          <t>https://tiki.vn/bo-pyjama-huongtam-kate-tay-ngan-nam-cao-cap-pnk02-chat-lieu-kate-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p271158363.html?spid=271158431</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>79000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>79000</v>
+        <v>259000</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>259000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>378</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>518000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>79000</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>62</v>
-      </c>
-      <c r="R9" t="n">
-        <v>62</v>
-      </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>212471303</t>
+          <t>173661690</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sét 8 Kẹp Tóc Size To Phong Cách Hàn Quốc</t>
+          <t>Q127 Váy ngủ 2 dây ren xẻ rút dây sexy - Váy ngủ lụa satin sexy gợi cảm - Đồ ngủ nữ - Đầm ngủ mặc nhà</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-8-kep-toc-size-to-phong-cach-han-quoc-p212471303.html?spid=212471304</t>
+          <t>https://tiki.vn/vay-ngu-2-day-ren-xe-rut-day-sexy-bt0065-vay-ngu-lua-satin-sexy-goi-cam-do-ngu-nu-dam-ngu-mac-nha-p173661690.html?spid=173661694</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1239,77 +1239,77 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>59000</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>59000</v>
+        <v>198000</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>396000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>59000</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>278704460</t>
+          <t>172474530</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Áo Thun Basic Tay Ngắn Nam Ninomaxx 2505012</t>
+          <t>Quần short thun nam cao cấp, quần short nam vải cotton LN058</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-basic-tay-ngan-nam-ninomaxx-2505012-p278704460.html?spid=278704476</t>
+          <t>https://tiki.vn/quan-short-thun-nam-cao-cap-quan-short-nam-vai-cotton-ln058-p172474530.html?spid=276917298</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ninomaxx</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>269000</v>
+        <v>95000</v>
       </c>
       <c r="H11" t="n">
-        <v>269000</v>
+        <v>95000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1338,35 +1338,35 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>380000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1383,17 +1383,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16651795</t>
+          <t>276515278</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>️[5 Quần] ComBo 5 Quần Lót Nam THUN LẠNH Lưng Bự Hàng Việt Nam Cao Cấp</t>
+          <t>Quần đùi nam huong tam cao cấp (QDNN10). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/5-quan-combo-5-quan-lot-nam-thun-lanh-lung-bu-hang-viet-nam-cao-cap-p16651795.html?spid=51148102</t>
+          <t>https://tiki.vn/quan-dui-nam-huong-tam-cao-cap-qdnn10-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p276515278.html?spid=276515294</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1403,116 +1403,116 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MENLIVE</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>159600</v>
+        <v>47600</v>
       </c>
       <c r="H12" t="n">
-        <v>-30400</v>
+        <v>47600</v>
       </c>
       <c r="I12" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>333200</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Giá giảm 30,400đ (16.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16546849</t>
+          <t>52758433</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nam Tam Giác Nhật</t>
+          <t>Combo 5 Đôi Tất Nam Vớ Nam Cổ Dài Sợi Cotton Mix Màu</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nam-tam-giac-nhat-p16546849.html?spid=53006035</t>
+          <t>https://tiki.vn/combo-5-doi-tat-nam-vo-nam-co-dai-soi-cotton-mix-mau-p52758433.html?spid=67297062</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>JM Jamano</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>210000</v>
+        <v>175000</v>
       </c>
       <c r="G13" t="n">
-        <v>170100</v>
+        <v>175000</v>
       </c>
       <c r="H13" t="n">
-        <v>-39900</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>34</v>
+        <v>3763</v>
       </c>
       <c r="K13" t="n">
-        <v>34</v>
+        <v>3764</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="N13" t="n">
         <v>4.7</v>
@@ -1524,17 +1524,17 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>1001</v>
       </c>
       <c r="R13" t="n">
-        <v>12</v>
+        <v>1001</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,81 +1544,81 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Giá giảm 39,900đ (19.0%)</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>54569520</t>
+          <t>107802069</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
+          <t>Keo Dán Giày Nhiệt XIMO Trong Suốt Siêu Dính Dùng Không Tổn Thương Da XKDG06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
+          <t>https://tiki.vn/keo-dan-giay-nhiet-ximo-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-xkdg06-p107802069.html?spid=252869410</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>67760</v>
+        <v>42000</v>
       </c>
       <c r="G14" t="n">
-        <v>88000</v>
+        <v>42000</v>
       </c>
       <c r="H14" t="n">
-        <v>20240</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>29.87</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>16</v>
+        <v>1049</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>1051</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1628,24 +1628,24 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Giá tăng 20,240đ (+29.9%)</t>
+          <t>Bán thêm +2 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>127197643</t>
+          <t>276070120</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bộ Quần Áo Nam Lính Mỹ US ARMY  Kiểu Dáng Túi Hộp, Chất Liệu Kaki Cao Cấp Phong Cách Lính Cực Ngầu (Tặng dây lưng) - HÀNG CHÍNH HÃNG</t>
+          <t>Quần short huongtam nam cao cấp(QSNN8). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-quan-ao-nam-linh-my-us-army-kieu-dang-tui-hop-chat-lieu-kaki-cao-cap-phong-cach-linh-cuc-ngau-tang-day-lung-hang-chinh-hang-p127197643.html?spid=182094568</t>
+          <t>https://tiki.vn/quan-short-huongtam-nam-cao-cap-qsnn8-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p276070120.html?spid=276070132</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1655,81 +1655,81 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>899000</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>899000</v>
+        <v>73000</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Review thêm +1</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>103049077</t>
+          <t>277548613</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
+          <t>Bộ Pyjama HUONGTAM Kate tay dài nam cao cấp(PDK01N13). Chất liệu Kate loại tốt:  mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
+          <t>https://tiki.vn/bo-pyjama-huongtam-kate-tay-dai-nam-cao-cap-pdk01n13-chat-lieu-kate-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p277548613.html?spid=277548629</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1739,26 +1739,26 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>153550</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>185000</v>
+        <v>259000</v>
       </c>
       <c r="H16" t="n">
-        <v>31450</v>
+        <v>259000</v>
       </c>
       <c r="I16" t="n">
-        <v>20.48</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1767,53 +1767,53 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Giá tăng 31,450đ (+20.5%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16375016</t>
+          <t>54569520</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COMBO HỘP 5 Quần Lót ĐÙI Nam Xuất Nhật Cao Cấp (MIX NGẪU NHIÊN)</t>
+          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-hop-5-quan-lot-dui-nam-xuat-nhat-cao-cap-mix-ngau-nhien-p16375016.html?spid=277961877</t>
+          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>274000</v>
+        <v>88000</v>
       </c>
       <c r="G17" t="n">
-        <v>210980</v>
+        <v>73920</v>
       </c>
       <c r="H17" t="n">
-        <v>-63020</v>
+        <v>-14080</v>
       </c>
       <c r="I17" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1851,26 +1851,26 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1880,24 +1880,24 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá giảm 63,020đ (23.0%)</t>
+          <t>Giá giảm 14,080đ (16.0%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>278850221</t>
+          <t>278856465</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quần Jean Thời Trang Basic Nam Ống Đứng Ninomaxx 2508004</t>
+          <t>Quần đùi nam huong tam cao cấp (QDNN19). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-jean-thoi-trang-basic-nam-ong-dung-ninomaxx-2508004-p278850221.html?spid=278850229</t>
+          <t>https://tiki.vn/quan-dui-nam-huong-tam-cao-cap-qdnn19-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p278856465.html?spid=278856517</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1907,20 +1907,20 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ninomaxx</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>769000</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>47600</v>
       </c>
       <c r="H18" t="n">
-        <v>-769000</v>
+        <v>47600</v>
       </c>
       <c r="I18" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1938,79 +1938,79 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>274795145</t>
+          <t>278856546</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dép tổ ong [Size 39-43] KÈM STICKER NGẪU NHIÊN vật liệu EVA cao cấp siêu bền, siêu nhẹ, chống trơn trượt</t>
+          <t>Quần đùi nam huong tam cao cấp (QDNN19.1). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-size-39-43-kem-sticker-ngau-nhien-vat-lieu-eva-cao-cap-sieu-ben-sieu-nhe-chong-tron-truot-p274795145.html?spid=274803712</t>
+          <t>https://tiki.vn/quan-dui-nam-huong-tam-cao-cap-qdnn19-1-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p278856546.html?spid=278856560</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>83000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>100000</v>
+        <v>47600</v>
       </c>
       <c r="H19" t="n">
-        <v>17000</v>
+        <v>47600</v>
       </c>
       <c r="I19" t="n">
-        <v>20.48</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,58 +2019,58 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá tăng 17,000đ (+20.5%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>73862702</t>
+          <t>7078807</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
+          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862720</t>
+          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858717</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2079,22 +2079,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>140130</v>
+        <v>420000</v>
       </c>
       <c r="G20" t="n">
-        <v>173000</v>
+        <v>352800</v>
       </c>
       <c r="H20" t="n">
-        <v>32870</v>
+        <v>-67200</v>
       </c>
       <c r="I20" t="n">
-        <v>23.46</v>
+        <v>-16</v>
       </c>
       <c r="J20" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2103,26 +2103,26 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2132,53 +2132,53 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Giá tăng 32,870đ (+23.5%)</t>
+          <t>Giá giảm 67,200đ (16.0%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>37126497</t>
+          <t>273188083</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>( 10 cái ) quần lót nữ Su đúc không đường may, hàng đẹp loại xịn W19_503</t>
+          <t>Quần Short HUONGTAM  nam cao cấp(QSN). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-10-quan-lot-su-duc-khong-duong-may-hang-dep-loai-xin-w19_503-p37126497.html?spid=51720423</t>
+          <t>https://tiki.vn/quan-short-huongtam-nam-cao-cap-qsn-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p273188083.html?spid=273214293</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>280000</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>210000</v>
+        <v>73000</v>
       </c>
       <c r="H21" t="n">
-        <v>-70000</v>
+        <v>73000</v>
       </c>
       <c r="I21" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2187,53 +2187,53 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Giá giảm 70,000đ (25.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>74421501</t>
+          <t>113145806</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
+          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
+          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2247,22 +2247,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>129600</v>
+        <v>97110</v>
       </c>
       <c r="G22" t="n">
-        <v>160000</v>
+        <v>117000</v>
       </c>
       <c r="H22" t="n">
-        <v>30400</v>
+        <v>19890</v>
       </c>
       <c r="I22" t="n">
-        <v>23.46</v>
+        <v>20.48</v>
       </c>
       <c r="J22" t="n">
-        <v>153</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>153</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2271,26 +2271,26 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2300,53 +2300,53 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Giá tăng 30,400đ (+23.5%)</t>
+          <t>Giá tăng 19,890đ (+20.5%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>277586478</t>
+          <t>73862702</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dép nam quai ngang da thật BHD2512 Dép nam trung niên</t>
+          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-da-that-bhd2512-dep-nam-trung-nien-p277586478.html?spid=277586488</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862720</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MARRANT</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>173000</v>
       </c>
       <c r="G23" t="n">
-        <v>299000</v>
+        <v>129750</v>
       </c>
       <c r="H23" t="n">
-        <v>299000</v>
+        <v>-43250</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2355,58 +2355,58 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 43,250đ (25.0%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>140429170</t>
+          <t>74421501</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bao tay chơi game găng tay 2 ngón cảm ứng điện thoại gamemobile BT01</t>
+          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bao-tay-choi-game-gang-tay-2-ngon-cam-ung-dien-thoai-gamemobile-bt01-p140429170.html?spid=198934954</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2415,22 +2415,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9999</v>
+        <v>160000</v>
       </c>
       <c r="G24" t="n">
-        <v>19999</v>
+        <v>120000</v>
       </c>
       <c r="H24" t="n">
-        <v>10000</v>
+        <v>-40000</v>
       </c>
       <c r="I24" t="n">
-        <v>100.01</v>
+        <v>-25</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="K24" t="n">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2439,26 +2439,26 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2468,29 +2468,29 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Giá tăng 10,000đ (+100.0%)</t>
+          <t>Giá giảm 40,000đ (25.0%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>87670339</t>
+          <t>112851354</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Áo Khoác Dù 2 Mặt Cao Cấp Chống Thấm</t>
+          <t>Áo ngực học sinh</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-du-2-mat-cao-cap-chong-tham-p87670339.html?spid=113225543</t>
+          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138792</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2499,22 +2499,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>317035</v>
+        <v>35280</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="H25" t="n">
-        <v>-317035</v>
+        <v>6720</v>
       </c>
       <c r="I25" t="n">
-        <v>-100</v>
+        <v>19.05</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2523,82 +2523,82 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 6,720đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7995659</t>
+          <t>56346167</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Giày Converse Chuck Taylor All Star Classic Low Top - 121176</t>
+          <t>Áo lót nữ ren dày</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-classic-low-top-121176-p7995659.html?spid=20340964</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-day-p56346167.html?spid=61933225</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1450000</v>
+        <v>180000</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="H26" t="n">
-        <v>-1450000</v>
+        <v>-45000</v>
       </c>
       <c r="I26" t="n">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="J26" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2607,53 +2607,53 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.8</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 45,000đ (25.0%)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>46773376</t>
+          <t>59462352</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Áo Ngực Tạo 7 Kiểu Mặc Multiway Cực Phong Cách Và Nâng Ngực Siêu Hít AL07</t>
+          <t>Áo ngực mỏng thêu hoa cài trước có gọng</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-tao-7-kieu-mac-multiway-cuc-phong-cach-va-nang-nguc-sieu-hit-al07-p46773376.html?spid=52950082</t>
+          <t>https://tiki.vn/ao-nguc-mong-theu-hoa-cai-truoc-co-gong-p59462352.html?spid=59462384</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2667,22 +2667,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>100000</v>
+        <v>90000</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>67500</v>
       </c>
       <c r="H27" t="n">
-        <v>-100000</v>
+        <v>-22500</v>
       </c>
       <c r="I27" t="n">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>204</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2691,82 +2691,82 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P27" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 22,500đ (25.0%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7997276</t>
+          <t>270661664</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Giày Sneaker Unisex Converse Chuck Taylor All Star 1970s All Hi 2018 - White (Size</t>
+          <t>ÁO TAY DÀI NỮ THỂ THAO CHẤT THUN LẠNH CAO CẤP, ÁO CHỐNG NẮNG, GIỮ NHIỆT, ĐI BƠI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-sneaker-unisex-converse-chuck-taylor-all-star-1970s-all-white-hi-2018-p7997276.html?spid=26499478</t>
+          <t>https://tiki.vn/ao-tay-dai-nu-the-thao-chat-thun-lanh-cao-cap-ao-chong-nang-giu-nhiet-di-boi-p270661664.html?spid=270661700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2000000</v>
+        <v>99000</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="H28" t="n">
-        <v>-2000000</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2775,79 +2775,79 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P28" t="n">
-        <v>-5</v>
+        <v>0.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Rating 4.0→4.7 (+0.70) | Review thêm +2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9810961</t>
+          <t>278069333</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Giày Slip On Unisex Vans - VN000EYEBWW</t>
+          <t>Quần short huongtam nam cao cấp(QSNN16). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-slip-on-unisex-vans-vn000eyebww-p9810961.html?spid=23839235</t>
+          <t>https://tiki.vn/quan-short-huongtam-nam-cao-cap-qsnn16-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p278069333.html?spid=278069349</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1450000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="H29" t="n">
-        <v>-1450000</v>
+        <v>73000</v>
       </c>
       <c r="I29" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2859,76 +2859,76 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>5</v>
       </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
       <c r="P29" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>278994189</t>
+          <t>276368075</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam patch ngực Form Fitted - ROUTINE 10F25TSS003</t>
+          <t>Giày Sandal Nam Bít Đầu BIGGBEN Da Bò Thật Cao Cấp SD142</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-patch-nguc-form-fitted-routine-10f25tss003-p278994189.html?spid=278994205</t>
+          <t>https://tiki.vn/giay-sandal-nam-bit-dau-biggben-da-bo-that-cao-cap-sd142-p276368075.html?spid=276368093</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>BIGGBEN</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>349000</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>429000</v>
       </c>
       <c r="H30" t="n">
-        <v>-349000</v>
+        <v>429000</v>
       </c>
       <c r="I30" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2962,34 +2962,34 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9810794</t>
+          <t>279100044</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Giày Slip On Unisex Vans - VN000EYEBLK</t>
+          <t>Chai Xịt Khử Mùi Giày Dép 260ML</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-slip-on-unisex-vans-vn000eyeblk-p9810794.html?spid=20459574</t>
+          <t>https://tiki.vn/chai-xit-khu-mui-giay-dep-260ml-p279100044.html?spid=279100045</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2999,26 +2999,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1450000</v>
+        <v>59000</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="H31" t="n">
-        <v>-1450000</v>
+        <v>-5000</v>
       </c>
       <c r="I31" t="n">
-        <v>-100</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3027,16 +3027,16 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3046,63 +3046,63 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 5,000đ (8.5%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>72050932</t>
+          <t>274992671</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Khẩu Trang Pitta Nhật Bản Small Chic - Gói 3 cái (mẫu mới 2020)</t>
+          <t>Giày thể thao nam, giày chạy bộ đế êm nhẹ, thoáng khí đế cao su đúc, chống trơn trượt hạn chế mòn – BEE GEE – GNA2023</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khau-trang-pitta-nhat-ban-small-chic-goi-3-cai-mau-moi-2020-p72050932.html?spid=72050933</t>
+          <t>https://tiki.vn/giay-the-thao-nam-giay-chay-bo-de-em-nhe-thoang-khi-de-cao-su-duc-chong-tron-truot-han-che-mon-bee-gee-gna2023-p274992671.html?spid=274992679</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PITTA MASK</t>
+          <t>Bee Gee</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>180000</v>
+        <v>936000</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="H32" t="n">
-        <v>-180000</v>
+        <v>-336000</v>
       </c>
       <c r="I32" t="n">
-        <v>-100</v>
+        <v>-35.9</v>
       </c>
       <c r="J32" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3111,16 +3111,16 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3130,34 +3130,34 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 336,000đ (35.9%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>275276395</t>
+          <t>276021358</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dép tổ ong TRẮNG nhựa EVA siêu bền, siêu nhẹ, chống trơn trượt, đế dày (FORM LỚN ĐẶT LÙI 1-2 SIZE) Dép Nam Nữ Nhiều Màu Sắc</t>
+          <t>Giày Sục Đạp Gót Mules Vải Sneaker Unisex Nam Nữ DINCOX DC37 Lazy Mule Beige</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-to-ong-trangvat-lieu-eva-sieu-ben-sieu-nhe-chong-tron-truot-form-size-lon-chau-au-p275276395.html?spid=275276411</t>
+          <t>https://tiki.vn/giay-suc-dap-got-mules-vai-sneaker-unisex-nam-nu-dincox-dc37-lazy-mule-beige-p276021358.html?spid=276021364</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3167,64 +3167,2416 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAC </t>
+          <t>DINCOX</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>85000</v>
+        <v>640000</v>
       </c>
       <c r="H33" t="n">
-        <v>13000</v>
+        <v>640000</v>
       </c>
       <c r="I33" t="n">
-        <v>18.06</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1275000</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>198915609</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Giày rọ sabo nam Huy Hoàng màu đen, nâu HJ7515-16-17-18</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-ro-sabo-nam-huy-hoang-mau-den-nau-hj7515-16-17-18-p198915609.html?spid=198915631</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Huy Hoàng</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>629000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>629000</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>275406628</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Giày Sandal Nam BIGGBEN Da Bò Thật Cao Cấp SD137</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-sandal-nam-biggben-da-bo-that-cao-cap-sd137-p275406628.html?spid=275406648</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BIGGBEN</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>449000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>449000</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>279344809</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Dây Nịt Nam - Thắt Lưng Nam Thời Trang Cao Cấp Phong Cách Sang Trọng (DN-138) | Dây Nịch Thắc Lưng</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/video-day-nit-nam-that-lung-nam-thoi-trang-cao-cap-phong-cach-sang-trong-dn-138-day-nich-thac-lung-p279344809.html?spid=279344819</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>29999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>29999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>279344827</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dây Nịt Nam - Thắt Lưng Nam Thời Trang Cao Cấp Phong Cách Sang Trọng (DN-139) | Dây Nịch Thắc Lưng</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/video-day-nit-nam-that-lung-nam-thoi-trang-cao-cap-phong-cach-sang-trong-dn-139-day-nich-thac-lung-p279344827.html?spid=279344861</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>29999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>29999</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>275889202</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Gọng kính cận A5058 hợp kim cước OURESS thời trang nam nữ siêu bền</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/gong-kinh-can-a5058-hop-kim-cuoc-ouress-thoi-trang-nam-nu-sieu-ben-p275889202.html?spid=275889204</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>OURESS</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>224000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>224000</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
         <v>5</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P38" t="n">
         <v>5</v>
       </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>272886599</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Máy làm sạch mắt kính , đồ trang sức dùng sóng siêu âm cỡ nhỏ thiết kế di động sử dụng tại nhà hàng chất lượng cao</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/may-lam-sach-mat-kinh-do-trang-suc-dung-song-sieu-am-co-nho-thiet-ke-di-dong-su-dung-tai-nha-hang-chat-luong-cao-p272886599.html?spid=277469993</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>119000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>119000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Rating 0.0→5.0 (+5.00) | Review thêm +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>278704460</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Áo Thun Basic Tay Ngắn Nam Ninomaxx 2505012</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-basic-tay-ngan-nam-ninomaxx-2505012-p278704460.html?spid=278704476</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ninomaxx</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>269000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-269000</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>270474726</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Bộ đồ bơi nam ngắn tay + quần boxer 2 lớp, họa tiết mạnh mẽ, set quần áo đi biển, đi bơi cho nam giới, chất thun bơi dày dặn mịn mát đẹp | BN031</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-do-boi-nam-ngan-tay-quan-boxer-2-lop-hoa-tiet-manh-me-set-quan-ao-di-bien-di-boi-cho-nam-gioi-chat-thun-boi-day-dan-min-mat-dep-bn031-p270474726.html?spid=275928740</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-420000</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J41" t="n">
+        <v>9</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>263040176</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bộ áo bà nam truyền thống đỏ đô - Có bộ bà ba Bigsize- may sỉ bà ba toàn quốc - May bộ bà ba theo yêu cầu</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-ao-ba-nam-truyen-thong-do-do-p263040176.html?spid=263040188</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CAN THO AO DAI AO BA BA</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>212936093</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Áo khoác gió 1 lớp ALIGRO màu navy AK1G.3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-gio-1-lop-aligro-mau-navy-ak1g-3-p212936093.html?spid=212936099</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aligro</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>620000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-620000</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>197062475</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Áo khoác măng tô nam cổ đứng dáng ngắn khóa kéo chất vải kaki đẹp NMT34</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-mang-to-nam-co-dung-dang-ngan-khoa-keo-chat-vai-kaki-dep-nmt34-p197062475.html?spid=197062507</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>936000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-936000</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q44" t="n">
         <v>3</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>129246479</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Áo khoác măng tô nam trẻ trung thời trang mới NMT74</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-mang-to-nam-tre-trung-thoi-trang-moi-nmt74-p129246479.html?spid=129246507</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1296000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-1296000</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J45" t="n">
+        <v>10</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>102890702</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Quần short nỷ nam Novelty 200043Q</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-short-ny-nam-novelty-200043q-p102890702.html?spid=102890710</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Novelty</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>349000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-349000</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>95053519</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Quần bơi nam lửng màu trơn đơn giản, đồ bơi nam form dài trên gối thiết kế trẻ trung QB022</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-boi-nam-lung-mau-tron-don-gian-do-boi-nam-form-dai-tren-goi-thiet-ke-tre-trung-qb022-p95053519.html?spid=95053523</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>235000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-235000</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J47" t="n">
+        <v>75</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>12</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>84866436</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Quần Lót Nam Lọt Khe Siêu Gợi Cảm Boxers Brave Person B1181</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-lot-nam-lot-khe-goi-cam-brave-person-b1181-thiet-ke-ca-tinh-chat-lieu-cao-cap-mem-mai-co-dan-4-chieu-thoang-khi-khang-khuan-mau-sac-da-dang-phong-phu-cho-ban-thoai-mai-lua-chon-p84866436.html?spid=84866444</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Brave Person</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>139000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-139000</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J48" t="n">
+        <v>40</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>9</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>13307720</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Combo 10 Quần lót nam, sịp chéo nam xuất Nhật thời trang cao cấp</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-10-quan-lot-nam-sip-cheo-nam-xuat-nhat-thoi-trang-cao-cap-p13307720.html?spid=278703711</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>336000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-336000</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>11988957</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Áo Khoác Jean Nam AKB3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-jean-nam-akb3-p11988957.html?spid=113226613</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>499000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-499000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>157808860</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà,đồ bộ mặc nhà đẹp ảnh thật 100%, chất lụa hàn</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-do-bo-mac-nha-dep-anh-that-100-p157808860.html?spid=157808944</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>212500</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-212500</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="Q51" t="n">
         <v>3</v>
       </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Giá tăng 13,000đ (+18.1%) | Bán thêm -15 sản phẩm</t>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>199607832</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Combo 4 Quần Lót Ren Miley Lingerie Màu Trắng Đen - FLS03</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-4-quan-lot-ren-miley-lingerie-mau-trang-den-fls03-p199607832.html?spid=199607836</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Miley Lingerie</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>216000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-216000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>278091584</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Giày MICHILUX Da Bò Thật Chính Hãng Penny Moccasin CIEMS Màu Xanh Navy</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-michilux-da-bo-that-chinh-hang-penny-moccasin-ciems-mau-xanh-navy-p278091584.html?spid=278091596</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Michilux</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>770000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-770000</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>278091365</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Giày MICHILUX Da Bò Thật Chính Hãng Penny Moccasin CIEMS Màu Đen</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-michilux-da-bo-that-chinh-hang-penny-moccasin-ciems-mau-den-p278091365.html?spid=278091531</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Michilux</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>770000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-770000</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>278091845</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Giày MICHILUX Da Bò Thật Chính Hãng Classic Moccasin CSMS0 Màu Nâu Sẫm</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-michilux-da-bo-that-chinh-hang-classic-moccasin-csms0-mau-nau-sam-p278091845.html?spid=278091859</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Michilux</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>750000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-750000</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>278091788</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Giày MICHILUX Da Bò Thật Chính Hãng Horse Bit Moccasin CSHM0 Màu Xanh Navy</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-michilux-da-bo-that-chinh-hang-horse-bit-moccasin-cshm0-mau-xanh-navy-p278091788.html?spid=278091796</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Michilux</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>790000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-790000</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>278091925</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Giày MICHILUX Da Bò Thật Chính Hãng Horse Bit Loafer CIEHL Màu Đen</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-michilux-da-bo-that-chinh-hang-horse-bit-loafer-ciehl-mau-den-p278091925.html?spid=278091937</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Michilux</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>850000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-850000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>278091881</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Giày MICHILUX Da Bò Thật Chính Hãng Classic Moccasin CSMS0 Màu Xanh Navy</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-michilux-da-bo-that-chinh-hang-classic-moccasin-csms0-mau-xanh-navy-p278091881.html?spid=278091893</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Michilux</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>750000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-750000</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>279075646</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gọng kính plastic hiệu Velocity VL92433 - KÍNH NHỰA TRẺ EM HIỆU VELOCITY VL92433 KÍCH THƯỚC 43-17-135</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/gong-kinh-plastic-hieu-velocity-vl92433-kinh-nhua-tre-em-hieu-velocity-vl92433-kich-thuoc-43-17-135-p279075646.html?spid=279075656</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>360000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-360000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>278816464</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Khóa thắt lưng nam khóa tự động khóa thắt lưng hợp kim cao cấp phong cách sang trọng</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/khoa-that-lung-nam-khoa-tu-dong-khoa-that-lung-hop-kim-cao-cap-phong-cach-sang-trong-p278816464.html?spid=278816466</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ANANSHOP688</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>123000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-123000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>160427486</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gọng kính cận nam nữ chống ánh sáng xanh, bức xạ kiểu dáng vuông - Fullbox </t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/gong-kinh-can-nam-nu-chong-anh-sang-xanh-buc-xa-kieu-dang-vuong-fullbox-p160427486.html?spid=160427487</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LiLiLa</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>149000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-149000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V47"/>
+  <dimension ref="A1:V88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,17 +543,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>34702350</t>
+          <t>73330264</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Áo khoác dạ nam dáng vest trẻ trung NAD43</t>
+          <t>Áo Khoác Nam Big Size Áo Khoác Dù Dày Nam Trơn Hai Lớp Chống Lạnh Chống Nắng Chống Gió Cao Cấp QD34 - ShopN6 (Nhiều Màu)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-da-nam-dang-vest-tre-trung-nad43-p34702350.html?spid=34702438</t>
+          <t>https://tiki.vn/ao-khoac-nam-big-size-ao-khoac-du-day-nam-tron-hai-lop-chong-lanh-chong-nang-chong-gio-cao-cap-qd34-shopn6-nhieu-mau-p73330264.html?spid=73330274</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2460000</v>
+        <v>189000</v>
       </c>
       <c r="H2" t="n">
-        <v>2460000</v>
+        <v>189000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,13 +582,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="M2" t="n">
-        <v>4920000</v>
+        <v>31374000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -603,14 +603,14 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,22 +627,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>194096379</t>
+          <t>50405083</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Khẩu trang y tế 5 lớp N95+ KHÁNH AN KAN95+ kháng khuẩn màng lọc ngăn 95% bụi mịn nhỏ hơn 2.5 micromet và 99% tia UV, có đệm xốp không bám hơi kính</t>
+          <t>COMBO 4 QUẦN LÓT BOXER NAM cao cấp chất vải mềm mịn, hút mồ hôi tốt, kiểu dáng quyến rũ L2893</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khau-trang-y-te-5-lop-n95-khanh-an-kan95-khang-khuan-mang-loc-ngan-95-bui-min-nho-hon-2-5-micromet-va-99-tia-uv-co-dem-xop-khong-bam-hoi-kinh-p194096379.html?spid=276797873</t>
+          <t>https://tiki.vn/combo-4-quan-lot-boxer-nam-cao-cap-chat-vai-mem-min-hut-mo-hoi-tot-kieu-dang-quyen-ru-l2893-p50405083.html?spid=95862063</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -654,10 +654,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>48000</v>
+        <v>89999</v>
       </c>
       <c r="H3" t="n">
-        <v>48000</v>
+        <v>89999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="L3" t="n">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="M3" t="n">
-        <v>2976000</v>
+        <v>15479828</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,121 +711,121 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>277808993</t>
+          <t>129246479</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dây thắt lưng 3.5 lớp da bò thân thắt lưng da bò lớp đầu tiên cao cấp</t>
+          <t>Áo khoác măng tô nam trẻ trung thời trang mới NMT74</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/day-that-lung-3-5-lop-da-bo-than-that-lung-da-bo-lop-dau-tien-cao-cap-p277808993.html?spid=278533981</t>
+          <t>https://tiki.vn/ao-khoac-mang-to-nam-tre-trung-thoi-trang-moi-nmt74-p129246479.html?spid=129246507</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ANANSHOP688</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>190000</v>
+        <v>1296000</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1296000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12960000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
-        <v>18</v>
-      </c>
-      <c r="L4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2470000</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="S4" t="n">
         <v>5</v>
       </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Bán thêm +13 sản phẩm | Review thêm +1</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>274999556</t>
+          <t>93233783</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày thể thao nam - nữ cổ cao đế êm nhẹ, thoáng khí đế cao su đúc, chống trơn trượt hạn chế mòn – BEE GEE - G1012</t>
+          <t>Áo Khoác Big Size Nam Nữ Unisex Áo Khoác Dù Nam 2 Lớp Chống Nắng Chống Lạnh Chống Gió Thời Trang Phom Body Phối Màu Hàn Quốc Cao Cấp AD73 - ShopN6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-nam-nu-de-em-nhe-thoang-khi-de-cao-su-duc-chong-tron-truot-han-che-mon-bee-gee-g1012-p274999556.html?spid=274999582</t>
+          <t>https://tiki.vn/ao-khoac-big-size-nam-nu-unisex-ao-khoac-du-nam-2-lop-chong-nang-chong-lanh-chong-gio-thoi-trang-phom-body-phoi-mau-han-quoc-cao-cap-ad73-shopn6-p93233783.html?spid=93233785</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bee Gee</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>450000</v>
+        <v>180000</v>
       </c>
       <c r="H5" t="n">
-        <v>450000</v>
+        <v>180000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -834,35 +834,35 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="M5" t="n">
-        <v>1350000</v>
+        <v>3420000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -879,37 +879,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>113052022</t>
+          <t>90483623</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Áo khoác nữ Áo khoát nữ kaki chống nắng túi hộp đẹp cá tính hàng rất đẹp-A061</t>
+          <t>Combo 3 Áo thun nam ba lỗ cotton FREEMAN ASF205</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-nu-ao-khoat-nu-kaki-chong-nang-tui-hop-dep-ca-tinh-hang-rat-dep-a061-p113052022.html?spid=113052056</t>
+          <t>https://tiki.vn/ao-thun-nam-ba-lo-cotton-freeman-asf205-combo-3-p90483623.html?spid=90483629</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>256450</v>
+        <v>240300</v>
       </c>
       <c r="H6" t="n">
-        <v>256450</v>
+        <v>240300</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -918,35 +918,35 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>769350</v>
+        <v>3364200</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -963,37 +963,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>277388268</t>
+          <t>249723132</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chai xịt tạo bọt vệ sinh giày White Shoes Cleaner 330ml</t>
+          <t>Quần Jean nam cao cấp ống đứng kazata màu xanh trung vải xuất khẩu xướt nhẹ dáng slimfit vải co giãn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-xit-tao-bot-ve-sinh-giay-white-shoes-cleaner-330ml-p277388268.html?spid=277388269</t>
+          <t>https://tiki.vn/quan-jean-nam-cao-cap-ong-dung-le511-mau-xanh-trung-vai-xuat-khau-xuot-nhe-dang-slimfit-vai-co-gian-p249723132.html?spid=249723138</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>malizia</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>85000</v>
+        <v>410000</v>
       </c>
       <c r="H7" t="n">
-        <v>85000</v>
+        <v>410000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1002,35 +1002,35 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3280000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="n">
-        <v>425000</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4</v>
-      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,17 +1047,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>101949588</t>
+          <t>141665125</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quần lót nam 292</t>
+          <t>Áo len nam cổ lọ mẫu mới LNA13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-292-p101949588.html?spid=101949703</t>
+          <t>https://tiki.vn/ao-len-nam-co-lo-mau-moi-lna13-p141665125.html?spid=141665149</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1067,86 +1067,86 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>jones'.</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>27500</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>27500</v>
+        <v>324000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>324000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>357500</v>
+        <v>2268000</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +13 sản phẩm | Review thêm +1</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>174305113</t>
+          <t>249724558</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thùng 300/200 khẩu trang KF94 4D Bảo Long Mask kháng khuẩn chống bụi mịn sản xuất tại Việt Nam theo công nghệ 4D và chuẩn KF94 Hàn Quốc</t>
+          <t>Quần Jean nam cao cấp ống đứng kazata màu xanh rêu vải xuất khẩu xướt nhẹ dáng slimfit vải co giãn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/thung-300-200-khau-trang-kf94-4d-bao-long-mask-khang-khuan-chong-bui-min-san-xuat-tai-viet-nam-theo-cong-nghe-4d-va-chuan-kf94-han-quoc-p174305113.html?spid=174305133</t>
+          <t>https://tiki.vn/quan-jean-nam-cao-cap-ong-dung-le511-mau-xanh-reu-vai-xuat-khau-xuot-nhe-dang-slimfit-vai-co-gian-p249724558.html?spid=249724560</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1158,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>290000</v>
+        <v>410000</v>
       </c>
       <c r="H9" t="n">
-        <v>290000</v>
+        <v>410000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1170,13 +1170,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>290000</v>
+        <v>2050000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1191,14 +1191,14 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1215,17 +1215,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>279229326</t>
+          <t>44012385</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Áo Khoác Chống Nắng Nam Cổ Lọ Gối Áo 2 Lớp Chống UV In Authentic Kiểu Cổ Đơn Sắc Việt Nam</t>
+          <t>Khăn choàng cổ nam nữ siêu nhẹ - UNQ001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-chong-nang-nam-co-lo-goi-ao-2-lop-chong-uv-in-authentic-kieu-co-don-sac-viet-nam-p279229326.html?spid=279229358</t>
+          <t>https://tiki.vn/khan-choang-co-nam-nu-sieu-nhe-unq001-p44012385.html?spid=44012389</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>139000</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>139000</v>
+        <v>259000</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>259000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1254,62 +1254,62 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>278000</v>
+        <v>1036000</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Bán thêm +2 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>276893937</t>
+          <t>253060005</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quần lửng ống rộng nữ Nesa Shop, chất liệu Đũi nhập loại 1, vải mát, mềm mịn, freesize dưới 55kg</t>
+          <t>đồ bộ mặc nhà mẫu lửng vải kate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lung-ong-rong-nu-nesa-shop-chat-lieu-dui-nhap-loai-1-vai-mat-mem-min-freesize-duoi-55kg-p276893937.html?spid=276893943</t>
+          <t>https://tiki.vn/do-bo-mac-nha-mau-lung-vai-kate-p253060005.html?spid=253060019</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>55000</v>
+        <v>160000</v>
       </c>
       <c r="G11" t="n">
-        <v>55000</v>
+        <v>160000</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1338,13 +1338,13 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>220000</v>
+        <v>960000</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1376,128 +1376,128 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Bán thêm +4 sản phẩm</t>
+          <t>Bán thêm +6 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>275295682</t>
+          <t>13299719</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Combo hộp 4 cái Khẩu trang vải 3 lớp thời trang cao cấp</t>
+          <t>Quần lót Nam thời trang mẫu mới - QL004</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-hop-4-cai-khau-trang-vai-3-lop-thoi-trang-cao-cap-p275295682.html?spid=275295686</t>
+          <t>https://tiki.vn/quan-lot-nam-thoi-trang-mau-moi-p13299719.html?spid=13299731</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DONG HO TSTP</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>98000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>98000</v>
+        <v>110000</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>196000</v>
+        <v>880000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Bán thêm +2 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>129916831</t>
+          <t>262054269</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0126903 Bộ 3 kẹp mái BASICARE 3772</t>
+          <t>Quần bơi nam cao cấp, dáng lửng ngang gối, mẫu đa màu lập thể cá tính, thun bơi lạnh dày mát mịn co giãn cực tốt | BN050</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/0126903-bo-3-kep-mai-basicare-3772-p129916831.html?spid=129916838</t>
+          <t>https://tiki.vn/quan-boi-nam-cao-cap-dang-lung-ngang-goi-mau-da-mau-lap-the-ca-tinh-thun-boi-lanh-day-mat-min-co-gian-cuc-tot-bn050-p262054269.html?spid=262054275</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BASICARE</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>39000</v>
+        <v>210000</v>
       </c>
       <c r="H13" t="n">
-        <v>39000</v>
+        <v>210000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1512,29 +1512,29 @@
         <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>117000</v>
+        <v>630000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1551,37 +1551,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>196290975</t>
+          <t>276235321</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Áo thun nam nữ form rộng tay lỡ SPECIAL cá tính freesize 40-70kg, áo phông unisex NeSa shop</t>
+          <t>Combo 5 đôi vớ cổ cao nam công sở mẫu gân chìm, tất đi giày tây chất liệu cotton</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-nu-form-rong-tay-lo-special-ca-tinh-freesize-40-70kg-ao-phong-unisex-nesa-shop-p196290975.html?spid=196290984</t>
+          <t>https://tiki.vn/combo-5-doi-vo-co-cao-nam-cong-so-mau-gan-chim-tat-di-giay-tay-chat-lieu-cotton-p276235321.html?spid=276235322</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>DRU</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>65000</v>
+        <v>75000</v>
       </c>
       <c r="H14" t="n">
-        <v>65000</v>
+        <v>75000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1590,35 +1590,35 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>600000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>65000</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>244297794</t>
+          <t>113052130</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
+          <t>Áo khoác nam Áo khoát nam gió dù 2 lớp chống nắng LOCAL PEOPLE đẹp siêu hot - M100</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
+          <t>https://tiki.vn/p-ao-khoac-nam-ao-khoat-nam-gio-du-2-lop-chong-nang-local-people-dep-sieu-hot-m100-p113052130.html?spid=113052161</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1659,97 +1659,97 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>163400</v>
+        <v>189250</v>
       </c>
       <c r="H15" t="n">
-        <v>-26600</v>
+        <v>189250</v>
       </c>
       <c r="I15" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>567750</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Giá giảm 26,600đ (14.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>170519607</t>
+          <t>146449442</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ÁO DÀI TRUYỀN THỐNG TAY PHỒNG TẶNG CÀI TÓC</t>
+          <t>Combo 6 Quần lót nam thun coton hàng việt nam xuất khẩu dạng cao cấp thoáng mát Từ 40kg đến 75kg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-dai-truyen-thong-tay-phong-tang-cai-toc-p170519607.html?spid=170519615</t>
+          <t>https://tiki.vn/combo-6-quan-lot-nam-thun-coton-hang-viet-nam-xuat-khau-dang-cao-cap-thoang-mat-tu-40kg-den-75kg-p146449442.html?spid=146449450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">	OEM</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>530000</v>
+        <v>180000</v>
       </c>
       <c r="H16" t="n">
-        <v>530000</v>
+        <v>180000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1758,35 +1758,35 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>540000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1803,158 +1803,158 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>91973812</t>
+          <t>276664793</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Su Đúc Hình Lá Không Gọng Đệm Dày Nâng Ngực A01 có ảnh thật</t>
+          <t>Quần gió lót lông QD2 ấm áp thời trang cho nam, Quần nỉ jogger lót lông QD1 sang trọng và dày dặn D Danido</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-su-duc-hinh-la-khong-gong-dem-day-nang-nguc-a01-co-anh-that-p91973812.html?spid=279055013</t>
+          <t>https://tiki.vn/quan-gio-lot-long-qd2-am-ap-thoi-trang-cho-nam-quan-ni-jogger-lot-long-qd1-sang-trong-va-day-dan-d-danido-p276664793.html?spid=276664835</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>D Danido</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>68000</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>85000</v>
+        <v>239000</v>
       </c>
       <c r="H17" t="n">
-        <v>17000</v>
+        <v>239000</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>239000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá tăng 17,000đ (+25.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>279104033</t>
+          <t>52758433</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Áo lót nữ form ba lỗ thông hơi trơn big size 1397 – Size XXL–3XL</t>
+          <t>Combo 5 Đôi Tất Nam Vớ Nam Cổ Dài Sợi Cotton Mix Màu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-form-ba-lo-thong-hoi-tron-big-size-1397-size-xxl-3xl-p279104033.html?spid=279104035</t>
+          <t>https://tiki.vn/combo-5-doi-tat-nam-vo-nam-co-dai-soi-cotton-mix-mau-p52758433.html?spid=67297062</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>JM Jamano</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>86400</v>
+        <v>175000</v>
       </c>
       <c r="G18" t="n">
-        <v>108000</v>
+        <v>175000</v>
       </c>
       <c r="H18" t="n">
-        <v>21600</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>3764</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>3765</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1964,128 +1964,128 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá tăng 21,600đ (+25.0%)</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>104791604</t>
+          <t>276070120</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quần lót nữ thái lan 828 – Chất thun lạnh - giao màu ngẫu nhiên</t>
+          <t>Quần short huongtam nam cao cấp(QSNN8). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nu-thai-lan-828-chat-thun-lanh-giao-mau-ngau-nhien-p104791604.html?spid=270215621</t>
+          <t>https://tiki.vn/quan-short-huongtam-nam-cao-cap-qsnn8-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p276070120.html?spid=276070132</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>HƯƠNG TÂM</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>34760</v>
+        <v>73000</v>
       </c>
       <c r="H19" t="n">
-        <v>-9240</v>
+        <v>73000</v>
       </c>
       <c r="I19" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá giảm 9,240đ (21.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>279345710</t>
+          <t>213706052</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Áo thun nữ Ruzimay RA2000 lệch vai co giãn mềm mại thanh lịch</t>
+          <t>10 - 20 đôi Tất nữ mỏng giấy cổ ngắn Hàn Quốc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nu-ruzimay-ra2000-lech-vai-co-gian-mem-mai-thanh-lich-p279345710.html?spid=279345718</t>
+          <t>https://tiki.vn/tat-nu-mong-giay-co-ngan-han-quoc-p213706052.html?spid=276954507</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ruzimay Style</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>212000</v>
+        <v>70000</v>
       </c>
       <c r="H20" t="n">
-        <v>212000</v>
+        <v>70000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2094,13 +2094,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2139,34 +2139,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>90483829</t>
+          <t>199597031</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Combo 2 Áo lót nam cổ tim tay ngắn FREEMAN TSF311</t>
+          <t>Xi Đánh Giày Sáp Shoe Polish XIMO Đen, Không Màu, Nâu Đủ Màu XI08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nam-co-tim-tay-ngan-freeman-tsf311-combo-2-p90483829.html?spid=90483854</t>
+          <t>https://tiki.vn/xi-danh-giay-sap-shoe-polish-ximo-den-khong-mau-nau-du-mau-chinh-hang-xi08-p199597031.html?spid=252869520</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>245100</v>
+        <v>32000</v>
       </c>
       <c r="G21" t="n">
-        <v>245100</v>
+        <v>32000</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2175,38 +2175,38 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K21" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>32000</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2216,24 +2216,24 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Rating 3.4→3.6 (+0.20) | Review thêm +1</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>278021672</t>
+          <t>16651795</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quần Lót Nam Đùi Boxer Lụa Băng Menpro MP9 - Mỏng nhem Thoáng Khí</t>
+          <t>️[5 Quần] ComBo 5 Quần Lót Nam THUN LẠNH Lưng Bự Hàng Việt Nam Cao Cấp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-dui-boxer-lua-bang-menpro-mp9-mong-nhem-thoang-khi-p278021672.html?spid=278021690</t>
+          <t>https://tiki.vn/5-quan-combo-5-quan-lot-nam-thun-lanh-lung-bu-hang-viet-nam-cao-cap-p16651795.html?spid=51148102</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2243,26 +2243,26 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MENLIVE</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>63200</v>
+        <v>159600</v>
       </c>
       <c r="G22" t="n">
-        <v>79000</v>
+        <v>205000</v>
       </c>
       <c r="H22" t="n">
-        <v>15800</v>
+        <v>45400</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>28.45</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2271,26 +2271,26 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2300,24 +2300,24 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Giá tăng 15,800đ (+25.0%)</t>
+          <t>Giá tăng 45,400đ (+28.4%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>145716807</t>
+          <t>16375016</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Áo phao nam trẻ trung phong cách NAP45</t>
+          <t>COMBO HỘP 5 Quần Lót ĐÙI Nam Xuất Nhật Cao Cấp (MIX NGẪU NHIÊN)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-phao-nam-tre-trung-phong-cach-nap45-p145716807.html?spid=145716819</t>
+          <t>https://tiki.vn/combo-hop-5-quan-lot-dui-nam-xuat-nhat-cao-cap-mix-ngau-nhien-p16375016.html?spid=277961877</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2331,22 +2331,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>210980</v>
       </c>
       <c r="G23" t="n">
-        <v>2016000</v>
+        <v>274000</v>
       </c>
       <c r="H23" t="n">
-        <v>2016000</v>
+        <v>63020</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>29.87</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2374,34 +2374,34 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 63,020đ (+29.9%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>277996544</t>
+          <t>16546849</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hộp 5 Quần lót nam cotton lụa – Siêu đẹp, mềm mịn, thoáng mát</t>
+          <t>Combo 5 Quần Lót Nam Tam Giác Nhật</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-5-quan-lot-nam-cotton-lua-muji-sieu-dep-mem-min-thoang-mat-p277996544.html?spid=278006734</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-tam-giac-nhat-p16546849.html?spid=53006035</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2415,22 +2415,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>169400</v>
+        <v>170100</v>
       </c>
       <c r="G24" t="n">
-        <v>220000</v>
+        <v>210000</v>
       </c>
       <c r="H24" t="n">
-        <v>50600</v>
+        <v>39900</v>
       </c>
       <c r="I24" t="n">
-        <v>29.87</v>
+        <v>23.46</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2439,26 +2439,26 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2468,53 +2468,53 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Giá tăng 50,600đ (+29.9%)</t>
+          <t>Giá tăng 39,900đ (+23.5%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>276817722</t>
+          <t>277437306</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mũ Nồi Thời Trang Nam Nữ, Vừa Giữ Ấm  Tai Vừa Dễ Phối Đồ Mùa Đông</t>
+          <t>Áo polo tay ngắn nam core. Fitted - RT 10F24POL001CR1 | ROUTINE CÀ MAU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mu-noi-co-che-tai-cho-nam-va-nu-vai-ni-day-giu-am-mua-dong-chat-vai-ni-2-lop-cao-cap-phu-hop-voi-nhieu-lua-tuoi-thoi-trang-phong-cach-sang-trong-lich-lam-su-dung-tien-loi-moi-noi-p276817722.html?spid=276817723</t>
+          <t>https://tiki.vn/ao-polo-tay-ngan-nam-core-fitted-rt-10f24pol001cr1-routine-ca-mau-p277437306.html?spid=277437310</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LYNUSAN</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>107000</v>
+        <v>349000</v>
       </c>
       <c r="G25" t="n">
-        <v>115430</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8430</v>
+        <v>-349000</v>
       </c>
       <c r="I25" t="n">
-        <v>7.88</v>
+        <v>-100</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2523,82 +2523,82 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Giá tăng 8,430đ (+7.9%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>273440178</t>
+          <t>276678209</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Giày thể thao nam chất liệu vải mềm mại, phong cách cá tính năng dộng – GNA2017</t>
+          <t>Quần Tam Giác Hiệu Davie Mã DVTL009, Chất Thun Lạnh Cao Cấp</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-nam-chat-lieu-vai-mem-mai-phong-cach-ca-tinh-nang-dong-gna2017-p273440178.html?spid=273440184</t>
+          <t>https://tiki.vn/quan-tam-giac-hieu-davie-ma-dvtl009-chat-thun-lanh-cao-cap-p276678209.html?spid=276678235</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bee Gee</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>300000</v>
+        <v>350000</v>
       </c>
       <c r="G26" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>-350000</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J26" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2607,73 +2607,73 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Rating 4.2→4.3 (+0.10) | Review thêm +1</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>279078887</t>
+          <t>276882727</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Giày thể thao nam đế êm nhẹ, thoáng khí đế cao su đúc, chống trơn trượt hạn chế mòn – BEE GEE - GNA2047</t>
+          <t>Áo vest blazer nam phong cách Hàn Quốc vải Linen thoáng mát, mềm mịn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-nam-de-em-nhe-thoang-khi-de-cao-su-duc-chong-tron-truot-han-che-mon-bee-gee-gna2047-p279078887.html?spid=279078911</t>
+          <t>https://tiki.vn/ao-vest-blazer-nam-phong-cach-han-quoc-vai-linen-thoang-mat-mem-min-p276882727.html?spid=276882729</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bee Gee</t>
+          <t>Haint Boutique</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>750000</v>
+        <v>420000</v>
       </c>
       <c r="H27" t="n">
-        <v>750000</v>
+        <v>420000</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2694,23 +2694,23 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2727,17 +2727,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>249215436</t>
+          <t>274885003</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quần Kaki túi hộp nam trung niên - Quần Jogger kaki vải dày dặn full size</t>
+          <t>Áo thun nam T-Shirt TS063 Leman vải Cotton thấm hút tốt kiểu dáng Slimfit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-kaki-tui-hop-nam-trung-nien-quan-jogger-kaki-vai-day-dan-full-size-p249215436.html?spid=274527238</t>
+          <t>https://tiki.vn/ao-thun-nam-t-shirt-ts063-leman-vai-cotton-tham-hut-tot-kieu-dang-slimfit-p274885003.html?spid=274907292</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2747,26 +2747,26 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Leman</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>179000</v>
+        <v>170000</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="H28" t="n">
-        <v>-179000</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2775,82 +2775,82 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>-4.3</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Rating 3.0→4.0 (+1.00) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>34159085</t>
+          <t>212936093</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Combo 5 Đôi Tất Cổ Trung Cùng Màu Cotton Thương Hiệu MRM Manlywear</t>
+          <t>Áo khoác gió 1 lớp ALIGRO màu navy AK1G.3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-doi-tat-nam-tat-nam-vo-nam-co-dai-cao-cap-mrm-fashion-cung-mau-p34159085.html?spid=34159089</t>
+          <t>https://tiki.vn/ao-khoac-gio-1-lop-aligro-mau-navy-ak1g-3-p212936093.html?spid=212936099</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>Aligro</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>149000</v>
+        <v>620000</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>620000</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>4720</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>4720</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2859,53 +2859,53 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>902</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Review thêm +1</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>67538621</t>
+          <t>244297794</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Combo 5 quần ĐÙI May 10 giao màu ngẫu nhiên</t>
+          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-dui-may-10-p67538621.html?spid=67538623</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2915,26 +2915,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>May 10</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>135000</v>
+        <v>163400</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>205000</v>
       </c>
       <c r="H30" t="n">
-        <v>-135000</v>
+        <v>41600</v>
       </c>
       <c r="I30" t="n">
-        <v>-100</v>
+        <v>25.46</v>
       </c>
       <c r="J30" t="n">
-        <v>16605</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2943,76 +2943,76 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>-4.6</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4843</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 41,600đ (+25.5%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>278956920</t>
+          <t>274051771</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quần Lót Su 897 Không Lộ Viền Lưng Thấp Nâng Mông</t>
+          <t>Áo khoác măng tô nam dáng dài trẻ trung lịch lãm đích thực thời trang nam NMT61</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-su-897-khong-lo-vien-lung-thap-nang-mong-p278956920.html?spid=278956935</t>
+          <t>https://tiki.vn/ao-khoac-mang-to-nam-dang-dai-tre-trung-lich-lam-dich-thuc-thoi-trang-nam-nmt61-p274051771.html?spid=274051803</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sanny House</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3900000</v>
       </c>
       <c r="H31" t="n">
-        <v>-52000</v>
+        <v>3900000</v>
       </c>
       <c r="I31" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3046,34 +3046,34 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>214921236</t>
+          <t>15810955</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Áo thun Victorinox Brand Collection Tinker Graphic Tee - Black - Size</t>
+          <t>Áo thun nam cá sấu</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-victorinox-brand-collection-tinker-graphic-tee-black-p214921236.html?spid=214921238</t>
+          <t>https://tiki.vn/ao-thun-nam-ca-sau-p15810955.html?spid=278513577</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3083,20 +3083,20 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VICTORINOX</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H32" t="n">
-        <v>-1000000</v>
+        <v>100000</v>
       </c>
       <c r="I32" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3130,63 +3130,63 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>276687955</t>
+          <t>262796074</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Áo ngực nữ không gọng đệm mỏng su trơn đứng dáng nâng ngực chuẩn đẹp SAY AL003</t>
+          <t>Chai vệ sinh đồ da làm sạch, dưỡng ẩm chống mốc, kháng khuẩn giày, túi ví, áo, ghế da 150ml</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-nu-khong-gong-dem-mong-su-tron-dung-dang-nang-nguc-chuan-dep-say-al003-p276687955.html?spid=276688003</t>
+          <t>https://tiki.vn/chai-ve-sinh-do-da-lam-sach-duong-am-chong-moc-khang-khuan-giay-tui-vi-ao-ghe-da-150ml-p262796074.html?spid=262796075</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FTAKY</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>45000</v>
+        <v>75000</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="H33" t="n">
-        <v>-45000</v>
+        <v>-5000</v>
       </c>
       <c r="I33" t="n">
-        <v>-100</v>
+        <v>-6.67</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3214,34 +3214,34 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 5,000đ (6.7%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>276316659</t>
+          <t>157808804</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ, Áo Lót Đúc Su Đệm Dày Siêu Nâng Ngực Tạo Khe Quyến Rũ, Áo Ngực Su Bàn Tay Không Gọng</t>
+          <t>đồ bộ mặc nhà đẹp chất lụa hàn</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ao-lot-duc-su-dem-day-sieu-nang-nguc-tao-khe-quyen-ru-ao-nguc-su-ban-tay-khong-gong-p276316659.html?spid=276316691</t>
+          <t>https://tiki.vn/do-bo-mac-nha-dep-chat-lua-han-p157808804.html?spid=157808821</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3251,23 +3251,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FTAKY</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>45000</v>
+        <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="H34" t="n">
-        <v>-45000</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3282,50 +3282,50 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>-0</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Rating 0.0→5.0 (+5.00) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>276147904</t>
+          <t>91973812</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quần lót nữ ren sexy</t>
+          <t>Áo Lót Nữ Su Đúc Hình Lá Không Gọng Đệm Dày Nâng Ngực A01 có ảnh thật</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nu-ren-sexy-p276147904.html?spid=276147905</t>
+          <t>https://tiki.vn/ao-lot-nu-su-duc-hinh-la-khong-gong-dem-day-nang-nguc-a01-co-anh-that-p91973812.html?spid=279055013</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3335,23 +3335,23 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FTAKY</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8000</v>
+        <v>85000</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>64600</v>
       </c>
       <c r="H35" t="n">
-        <v>-8000</v>
+        <v>-20400</v>
       </c>
       <c r="I35" t="n">
-        <v>-100</v>
+        <v>-24</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3382,63 +3382,63 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 20,400đ (24.0%)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>278870360</t>
+          <t>37126497</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dép quai hậu nam, sandal nam, sandal bigsize hàng VN chính hãng Vinasan. Mã VN2224 size 35-45</t>
+          <t>( 10 cái ) quần lót nữ Su đúc không đường may, hàng đẹp loại xịn W19_503</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-hau-nam-sandal-nam-sandal-bigsize-hang-vn-chinh-hang-vinasan-ma-vn2224-size-35-45-p278870360.html?spid=278870528</t>
+          <t>https://tiki.vn/set-10-quan-lot-su-duc-khong-duong-may-hang-dep-loai-xin-w19_503-p37126497.html?spid=51720423</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>VINASAN</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>245000</v>
+        <v>210000</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>280000</v>
       </c>
       <c r="H36" t="n">
-        <v>-245000</v>
+        <v>70000</v>
       </c>
       <c r="I36" t="n">
-        <v>-100</v>
+        <v>33.33</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3447,82 +3447,82 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 70,000đ (+33.3%)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>214504425</t>
+          <t>279104033</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chai Xịt Tạo Bọt Vệ Sinh Giày XIMO Cao Cấp 300ml XVSG02</t>
+          <t>Áo lót nữ form ba lỗ thông hơi trơn big size 1397 – Size XXL–3XL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-xit-tao-bot-ve-sinh-giay-ximo-cao-cap-300ml-xvsg02-p214504425.html?spid=252869350</t>
+          <t>https://tiki.vn/ao-lot-nu-form-ba-lo-thong-hoi-tron-big-size-1397-size-xxl-3xl-p279104033.html?spid=279104035</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>72000</v>
+        <v>108000</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>82080</v>
       </c>
       <c r="H37" t="n">
-        <v>-72000</v>
+        <v>-25920</v>
       </c>
       <c r="I37" t="n">
-        <v>-100</v>
+        <v>-24</v>
       </c>
       <c r="J37" t="n">
-        <v>341</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3531,79 +3531,79 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
-        <v>-4.7</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 25,920đ (24.0%)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>107157675</t>
+          <t>279561449</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dép Nam Sức Khoẻ Spenco Yumi Leather Dark - Dép kẹp quai da ôm vòm chân hỗ trợ giảm mỏi cổ chân, gối</t>
+          <t>Áo Cá Chép (Tùy chọn) - Áo đen Cá Chép vươn lên - XXL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-suc-khoe-spenco-yumi-leather-dark-dep-kep-nam-giam-dau-chan-p107157675.html?spid=107157694</t>
+          <t>https://tiki.vn/ao-ca-chep-tuy-chon-p279561449.html?spid=279561471</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Spenco</t>
+          <t>Cá Chép</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2295000</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="H38" t="n">
-        <v>-2295000</v>
+        <v>190000</v>
       </c>
       <c r="I38" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3634,34 +3634,34 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>214921169</t>
+          <t>276833571</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Áo thun Victorinox Brand Collection Logo Graphic Tee - Red - Size</t>
+          <t>Quần Short Mặt Nhà Thương Hiệu Davie Dvs06 Chất Liệu Kate 100% Cotton Thoáng Mát</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-victorinox-brand-collection-logo-graphic-tee-red-p214921169.html?spid=214921174</t>
+          <t>https://tiki.vn/quan-short-mat-nha-thuong-hieu-davie-dvs06-chat-lieu-kate-100-cotton-thoang-mat-p276833571.html?spid=276833601</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>VICTORINOX</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1000000</v>
+        <v>410000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1000000</v>
+        <v>-410000</v>
       </c>
       <c r="I39" t="n">
         <v>-100</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -3735,17 +3735,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>214921193</t>
+          <t>276832011</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Áo thun Victorinox Brand Collection Tinker Graphic Tee - White - Size</t>
+          <t>Quần Mặc Nhà Nam SKD02 Vải Kate Co Giãn Nhẹ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-victorinox-brand-collection-tinker-graphic-tee-white-p214921193.html?spid=214921195</t>
+          <t>https://tiki.vn/quan-mac-nha-nam-skd02-vai-kate-co-gian-nhe-p276832011.html?spid=276832019</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3755,23 +3755,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>VICTORINOX</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1000000</v>
+        <v>189000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1000000</v>
+        <v>-189000</v>
       </c>
       <c r="I40" t="n">
         <v>-100</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -3819,17 +3819,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>214921162</t>
+          <t>276669234</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Áo thun Victorinox Brand Collection Logo Graphic Tee - White - Size</t>
+          <t>Quần Lót Nam Tam Giác Thương Hiệu Samaki Mã SKCT01 Chất Liệu Co Giãn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-victorinox-brand-collection-logo-graphic-tee-white-p214921162.html?spid=214921166</t>
+          <t>https://tiki.vn/quan-lot-nam-tam-giac-thuong-hieu-samaki-ma-skct01-chat-lieu-co-gian-p276669234.html?spid=276669298</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3839,45 +3839,45 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>VICTORINOX</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1000000</v>
+        <v>215000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1000000</v>
+        <v>-215000</v>
       </c>
       <c r="I41" t="n">
         <v>-100</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -3903,17 +3903,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>214921213</t>
+          <t>277841951</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Áo thun Victorinox Brand Collection Logo Graphic Tee - Blue - Size</t>
+          <t>Quần lót nam tam giác organic cotton phối lưng . Brief - RT 10S25UND002 | ROUTINE CÀ MAU</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-victorinox-brand-collection-logo-graphic-tee-blue-p214921213.html?spid=214921217</t>
+          <t>https://tiki.vn/quan-lot-nam-tam-giac-organic-cotton-phoi-lung-brief-rt-10s25und002-routine-ca-mau-p277841951.html?spid=277841975</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3923,23 +3923,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VICTORINOX</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1000000</v>
+        <v>99000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1000000</v>
+        <v>-99000</v>
       </c>
       <c r="I42" t="n">
         <v>-100</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -3987,17 +3987,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>214921200</t>
+          <t>276667776</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Áo thun Victorinox Brand Collection Mountain Graphic Tee - Grey - Size</t>
+          <t>Quần Short Mặc Nhà Nam Davie Dvs01 Chất Liệu Vải Kate 100% Cotton - Giao Màu Ngẫu Nhiên</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-victorinox-brand-collection-mountain-graphic-tee-grey-p214921200.html?spid=214921202</t>
+          <t>https://tiki.vn/quan-short-mac-nha-nam-davie-dvs01-chat-lieu-vai-kate-100-cotton-giao-mau-ngau-nhien-p276667776.html?spid=276667794</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4007,23 +4007,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>VICTORINOX</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1000000</v>
+        <v>350000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-1000000</v>
+        <v>-350000</v>
       </c>
       <c r="I43" t="n">
         <v>-100</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4071,43 +4071,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>122273813</t>
+          <t>278717007</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kính Chống Dịch, Kính Chống Giọt Bắn, Kinh FACESHIELD, Chống Bụi, Mặt Nạ Kính Bảo Hộ Đa Năng Chống Dịch, Chống Giọt Bắn,</t>
+          <t>Áo khoác raglan dây kéo. Loose - ROUTINE 10F25WJA002</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://tiki.vn/kinh-chong-dich-kinh-chong-giot-ban-kinh-faceshield-chong-bui-mat-na-kinh-bao-ho-da-nang-chong-dich-chong-giot-ban-p122273813.html?spid=122273814</t>
+          <t>https://tiki.vn/ao-khoac-raglan-day-keo-loose-routine-10f25wja002-p278717007.html?spid=278717013</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FTAKY</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>199000</v>
+        <v>549000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-199000</v>
+        <v>-549000</v>
       </c>
       <c r="I44" t="n">
         <v>-100</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -4119,16 +4119,16 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -4155,43 +4155,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>274586950</t>
+          <t>277515096</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Set 100 Miếng dán chống mồ hôi nách, miếng dán ngăn mồ hôi nách siêu thâm hút cho Nam và Nữ che tên sản phẩm</t>
+          <t>Áo sơ mi sọc Nam tay dài N&amp;M 2101087</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-100-mieng-dan-chong-mo-hoi-nach-mieng-dan-ngan-mo-hoi-nach-sieu-tham-hut-cho-nam-va-nu-che-ten-san-pham-p274586950.html?spid=274586956</t>
+          <t>https://tiki.vn/ao-so-mi-soc-nam-tay-dai-n-m-2101087-p277515096.html?spid=277515116</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FTAKY</t>
+          <t>Ninomaxx</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>99000</v>
+        <v>599000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-99000</v>
+        <v>-599000</v>
       </c>
       <c r="I45" t="n">
         <v>-100</v>
       </c>
       <c r="J45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -4239,65 +4239,65 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>213706052</t>
+          <t>278872546</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10 - 20 đôi Tất nữ mỏng giấy cổ ngắn Hàn Quốc</t>
+          <t>Áo thun tay ngắn nam.Fitted - ROUTINE 10F25TSS039</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://tiki.vn/tat-nu-mong-giay-co-ngan-han-quoc-p213706052.html?spid=276954507</t>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-fitted-routine-10f25tss039-p278872546.html?spid=278872562</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>70000</v>
+        <v>349000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-70000</v>
+        <v>-349000</v>
       </c>
       <c r="I46" t="n">
         <v>-100</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -4323,84 +4323,3528 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>275579517</t>
+          <t>279277075</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Giày thể thao nam Asia, đế kếp, bền, rẻ, dùng cho lao động và thể thao (màu trắng)</t>
+          <t>Áo polo len dệt kim tay ngắn nam. Fitted - ROUTINE 10S26KNI019</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-nam-asia-de-kep-ben-re-dung-cho-lao-dong-va-the-thao-mau-trang-p275579517.html?spid=275579520</t>
+          <t>https://tiki.vn/ao-polo-len-det-kim-tay-ngan-nam-fitted-routine-10s26kni019-p279277075.html?spid=279277091</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ASIA</t>
+          <t>Routine</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>225000</v>
+        <v>649000</v>
       </c>
       <c r="G47" t="n">
-        <v>225000</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-649000</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J47" t="n">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>-309</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-69525000</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>111708924</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Combo 6 quần đùi mặc nhà nam cao cấp kate 100% cotton</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-6-quan-dui-mac-nha-nam-cao-cap-kate-100-cotton-p111708924.html?spid=111708928</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DAVIE</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>414000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-414000</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>279380318</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Quần đùi nam cạp chun cao cấp Lucibeaty vải gió phong cách thể thao chính hãng QGH-028</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-dui-nam-cap-chun-cao-cap-lucibeaty-vai-gio-phong-cach-the-thao-chinh-hang-qgh-028-p279380318.html?spid=279380324</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MRM Manlywear</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>270000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-270000</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>279365270</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Quần vải / Quần tây nam màu đen Form Slim - ROUTINE 10F25PFO003</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-vai-quan-tay-nam-mau-den-form-slim-routine-10f25pfo003-p279365270.html?spid=279365278</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>599000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-599000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>279259219</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam hình in . Form Boxy - ROUTINE 10S25TSS032</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-hinh-in-form-boxy-routine-10s25tss032-p279259219.html?spid=279259225</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>349000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-349000</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>278993255</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Áo polo tay ngắn nam viền cổ.Fitted - ROUTINE 10F25POL029</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-polo-tay-ngan-nam-vien-co-fitted-routine-10f25pol029-p278993255.html?spid=278993267</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>499000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-499000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>279256558</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Áo polo nam tay ngắn phối cố Form Fitted - ROUTINE 10F25POL028</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-polo-nam-tay-ngan-phoi-co-form-fitted-routine-10f25pol028-p279256558.html?spid=279256564</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>579000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-579000</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>278935816</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Quần dài kaki nam Form Slim - ROUTINE 10F25PCA014</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-dai-kaki-nam-form-slim-routine-10f25pca014-p278935816.html?spid=278935830</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>599000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-599000</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>278872719</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Áo Polo Nam Tay Ngắn Cotton Hạn Chế Nhăn Form Fitted - ROUTINE 10F25POL005</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-polo-nam-tay-ngan-cotton-han-che-nhan-form-fitted-routine-10f25pol005-p278872719.html?spid=278872733</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>599000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-599000</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>277550023</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Quần vải nam / Quần tây nam dài cotton poly ủi ly trước - RT 10S25PFO004 | ROUTINE CÀ MAU</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-vai-nam-quan-tay-nam-dai-cotton-poly-ui-ly-truoc-rt-10s25pfo004-routine-ca-mau-p277550023.html?spid=277550045</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>479000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-479000</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>278994111</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam nỉ phối vai Form Boxy - ROUTINE 10F25TSS019</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-ni-phoi-vai-form-boxy-routine-10f25tss019-p278994111.html?spid=278994123</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>449000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-449000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>278105237</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam. Form Fitted - RT 10S25TSS004 | ROUTINE CÀ MAU</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-form-fitted-rt-10s25tss004-routine-ca-mau-p278105237.html?spid=278514403</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>449000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-449000</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>279151760</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Áo Thun Nam Tay Ngắn In Chữ Form Boxy - ROUTINE 10F25TSS018</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-tay-ngan-in-chu-form-boxy-routine-10f25tss018-p279151760.html?spid=279151762</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>479000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-479000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>278741557</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Áo Thun Nam Tay Ngắn Cotton Màu Trơn Form Fit - ROUTINE 10S25TSS046</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-tay-ngan-cotton-mau-tron-form-fit-routine-10s25tss046-p278741557.html?spid=278741561</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>299000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-299000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>277826976</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam Scafe thêu Form Boxy - RT 10S25TSS054 | ROUTINE CÀ MAU</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-scafe-theu-form-boxy-rt-10s25tss054-routine-ca-mau-p277826976.html?spid=277826998</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>529000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-529000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>277327114</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam cooling . Fitted - RT 10S25TSS001 | ROUTINE CÀ MAU</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-cooling-fitted-rt-10s25tss001-routine-ca-mau-p277327114.html?spid=277327145</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>379000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>279259355</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Áo Thun Nam Tay Ngắn Cotton Trơn Form Form Fitted - ROUTINE 10F25TSS028</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-tay-ngan-cotton-tron-form-form-fitted-routine-10f25tss028-p279259355.html?spid=279259375</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>329000</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-329000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>278872770</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam in ngực Form Loose - ROUTINE 10F25TSS035</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-in-nguc-form-loose-routine-10f25tss035-p278872770.html?spid=278872778</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>449000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-449000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>277826908</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam S.Café sọc tay Form Loose - RT 10S25TSS007 | ROUTINE CÀ MAU</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-s-cafe-soc-tay-form-loose-rt-10s25tss007-routine-ca-mau-p277826908.html?spid=277826918</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>549000</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-549000</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>279259255</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Áo Thun Nam Tay Ngắn Cotton Nhãn Trang Trí Cổ Tròn - ROUTINE 10F25TSS021</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-tay-ngan-cotton-nhan-trang-tri-co-tron-routine-10f25tss021-p279259255.html?spid=279288440</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>379000</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>279211601</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam vải mỏng hình in Form Boxy - ROUTINE 10F25TSS016</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-vai-mong-hinh-in-form-boxy-routine-10f25tss016-p279211601.html?spid=279211603</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>379000</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>278944658</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam phối rib hình in .Fitted - ROUTINE 10F25TSS046</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-phoi-rib-hinh-in-fitted-routine-10f25tss046-p278944658.html?spid=278944668</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>399000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-399000</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>275233185</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Áo Thun ROUTINE Tay Ngắn Dệt Jacquard Phối Nhãn Form Loose - 10S24TSS014 | LASTORE MENSWEAR</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-routine-tay-ngan-det-jacquard-phoi-nhan-form-loose-10s24tss014-lastore-menswear-p275233185.html?spid=275233197</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>399000</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-399000</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>279438121</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Áo thun nam hình in Form Regular - ROUTINE 10S26TSS031</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-hinh-in-form-regular-routine-10s26tss031-p279438121.html?spid=279438129</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>549000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-549000</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>279289478</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam phối patch trang trí Form Loose -  ROUTINE 10F25TSS023</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-phoi-patch-trang-tri-form-loose-routine-10f25tss023-p279289478.html?spid=279289486</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>449000</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-449000</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>279198805</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam. Fitted - ROUTINE 10F25TSS037</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-fitted-routine-10f25tss037-p279198805.html?spid=279198823</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>349000</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-349000</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>279155321</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Áo Thun Nam Tay Ngắn Cotton Hình In Sau Form Boxy - ROUTINE 10F25TSS017</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-tay-ngan-cotton-hinh-in-sau-form-boxy-routine-10f25tss017-p279155321.html?spid=279155337</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>379000</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>279153927</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam hình thêu Form Regular - ROUTINE 10F25TSS009</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-hinh-theu-form-regular-routine-10f25tss009-p279153927.html?spid=279153947</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>449000</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-449000</v>
+      </c>
+      <c r="I74" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>278105191</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Áo thun nam tay ngắn sọc ngang lớn jacquard Form loose - ROUTINE 10S25TSS050</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-tay-ngan-soc-ngang-lon-jacquard-form-loose-rt-10s25tss050-routine-ca-mau-p278105191.html?spid=279519225</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>689000</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-689000</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>275030945</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Áo Thun Nam ROUTINE Tay Ngắn Cotton Polyester In Hình Form Loose - 10S24TSS002 | LASTORE MENSWEAR</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-routine-tay-ngan-cotton-polyester-in-hinh-form-loose-10s24tss002-lastore-menswear-p275030945.html?spid=275030951</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>449000</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-449000</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>279359972</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam patch trang trí Form Regular - ROUTINE 10S26TSS029</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-patch-trang-tri-form-regular-routine-10s26tss029-p279359972.html?spid=279359980</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>399000</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-399000</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>279347340</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam hình in Form Regular - ROUTINE 10S26TSS032</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-hinh-in-form-regular-routine-10s26tss032-p279347340.html?spid=279347342</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>379000</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>279340303</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam hình in Form Regular - ROUITINE 10S26TSS030</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-hinh-in-form-regular-rouitine-10s26tss030-p279340303.html?spid=279340317</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>399000</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-399000</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>279289499</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Áo Thun Nam Gắn Miếng Patch Form Boxy - ROUTINE 10F25TSS054</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-gan-mieng-patch-form-boxy-routine-10f25tss054-p279289499.html?spid=279289501</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>379000</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>279438146</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Áo thun nam giá tốt basic trơn tay ngắn vải mềm mát Form Fitted - ROUTINE 10F24TSS001C</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-gia-tot-basic-tron-tay-ngan-vai-mem-mat-form-fitted-routine-10f24tss001c-p279438146.html?spid=279438160</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>169000</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-169000</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>277591179</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Găng Tay Chống Nắng UPF 50+ Cho Nữ - Chống Tia UV, Chống Trượt, Dành Cho Lái Xe Máy - HÀNG CHÍNH HÃNG MINIIN</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/gang-tay-chong-nang-upf-50-cho-nu-chong-tia-uv-chong-truot-danh-cho-lai-xe-may-hang-chinh-hang-miniin-p277591179.html?spid=277591187</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>MINIIN</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>69000</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-69000</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>277327053</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn nam. Loose - RT 10S25TSS013 | ROUTINE CÀ MAU</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-nam-loose-rt-10s25tss013-routine-ca-mau-p277327053.html?spid=277327071</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>379000</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-379000</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>276799709</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Áo thun tay ngắn có in form Loose - ROUTINE 10F24TSSU054 | ROUTINE CÀ MAU</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-tay-ngan-co-in-form-loose-routine-10f24tssu054-routine-ca-mau-p276799709.html?spid=277228117</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>349000</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-349000</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>275738233</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TẤT / VỚ LƯỜI / HÀI TRƠN LOGO ROUTINE nhiều màu UNISEX FREESIZE - 10S22SOC003 | LASTORE MENSWEAR</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/tat-vo-luoi-hai-tron-logo-routine-nhieu-mau-unisex-freesize-10s22soc003-lastore-menswear-p275738233.html?spid=275738251</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J85" t="n">
+        <v>7</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>5</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>198918912</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Khăn lau kính Nano chống bám hơi nước, chống mờ sương, sạch bụi bẩn và dấu vân tay, Công nghệ Nhật Bản - Hộp 100 Miếng</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/khan-lau-kinh-nano-chong-bam-hoi-nuoc-chong-mo-suong-sach-bui-ban-va-dau-van-tay-cong-nghe-nhat-ban-hop-100-mieng-p198918912.html?spid=198918913</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-70000</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J86" t="n">
+        <v>468</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
         <v>4.6</v>
       </c>
-      <c r="O47" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>127</v>
-      </c>
-      <c r="R47" t="n">
-        <v>128</v>
-      </c>
-      <c r="S47" t="n">
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>42</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>249724356</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Quần Jean nam cao cấp ống đứng kazata màu xanh đậm vải xuất khẩu xướt nhẹ dáng slimfit vải co giãn</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-jean-nam-cao-cap-ong-dung-le511-mau-xanh-dam-vai-xuat-khau-xuot-nhe-dang-slimfit-vai-co-gian-p249724356.html?spid=249724368</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>410000</v>
+      </c>
+      <c r="G87" t="n">
+        <v>410000</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
+      <c r="K87" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>-410000</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Bán thêm -1 sản phẩm</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>275255891</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Quần Jean nam cao cấp ống đứng kazata màu xanh đen trơn vải co giãn xuất khẩu dáng slimfit</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-jean-nam-cao-cap-ong-dung-le511-mau-xanh-den-tron-vai-co-gian-xuat-khau-dang-slimfit-p275255891.html?spid=275255903</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>410000</v>
+      </c>
+      <c r="G88" t="n">
+        <v>410000</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>8</v>
+      </c>
+      <c r="K88" t="n">
+        <v>7</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>-410000</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5</v>
+      </c>
+      <c r="O88" t="n">
+        <v>5</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
         <v>1</v>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
         <is>
           <t>🔄 Đã cập nhật</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Bán thêm -309 sản phẩm | Review thêm +1</t>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Bán thêm -1 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V88"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>73330264</t>
+          <t>164075726</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Áo Khoác Nam Big Size Áo Khoác Dù Dày Nam Trơn Hai Lớp Chống Lạnh Chống Nắng Chống Gió Cao Cấp QD34 - ShopN6 (Nhiều Màu)</t>
+          <t>Kính Lão, Kính Viễn 2 Tròng Gọng Khoan Sang Trọng Vừa Dùng Đi Đường Vừa Dùng Đọc Sách, Chống tia Uv400, Chống Lóa - BLUE LIGHT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-nam-big-size-ao-khoac-du-day-nam-tron-hai-lop-chong-lanh-chong-nang-chong-gio-cao-cap-qd34-shopn6-nhieu-mau-p73330264.html?spid=73330274</t>
+          <t>https://tiki.vn/kinh-lao-kinh-vien-2-trong-gong-khoan-sang-trong-vua-dung-di-duong-vua-dung-doc-sach-chong-tia-uv400-chong-loa-blue-light-p164075726.html?spid=164075734</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N6</t>
+          <t>Blue Light</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>189000</v>
+        <v>185000</v>
       </c>
       <c r="H2" t="n">
-        <v>189000</v>
+        <v>185000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="L2" t="n">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="M2" t="n">
-        <v>31374000</v>
+        <v>26640000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="S2" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,22 +627,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>50405083</t>
+          <t>74743103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COMBO 4 QUẦN LÓT BOXER NAM cao cấp chất vải mềm mịn, hút mồ hôi tốt, kiểu dáng quyến rũ L2893</t>
+          <t xml:space="preserve"> Kẹp Tóc Càng Cua Hàn Quốc Dễ Thương Với Thiết Kế Tinh Tế KT18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-4-quan-lot-boxer-nam-cao-cap-chat-vai-mem-min-hut-mo-hoi-tot-kieu-dang-quyen-ru-l2893-p50405083.html?spid=95862063</t>
+          <t>https://tiki.vn/kep-toc-cang-cua-han-quoc-de-thuong-voi-thiet-ke-tinh-te-kt18-p74743103.html?spid=105736848</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -654,10 +654,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>89999</v>
+        <v>24000</v>
       </c>
       <c r="H3" t="n">
-        <v>89999</v>
+        <v>24000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>172</v>
+        <v>763</v>
       </c>
       <c r="L3" t="n">
-        <v>172</v>
+        <v>763</v>
       </c>
       <c r="M3" t="n">
-        <v>15479828</v>
+        <v>18312000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,17 +711,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>129246479</t>
+          <t>95053519</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Áo khoác măng tô nam trẻ trung thời trang mới NMT74</t>
+          <t>Quần bơi nam lửng màu trơn đơn giản, đồ bơi nam form dài trên gối thiết kế trẻ trung QB022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-mang-to-nam-tre-trung-thoi-trang-moi-nmt74-p129246479.html?spid=129246507</t>
+          <t>https://tiki.vn/quan-boi-nam-lung-mau-tron-don-gian-do-boi-nam-form-dai-tren-goi-thiet-ke-tre-trung-qb022-p95053519.html?spid=95053523</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -738,10 +738,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1296000</v>
+        <v>235000</v>
       </c>
       <c r="H4" t="n">
-        <v>1296000</v>
+        <v>235000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,35 +750,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="M4" t="n">
-        <v>12960000</v>
+        <v>17625000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,121 +795,121 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>93233783</t>
+          <t>1752845</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Áo Khoác Big Size Nam Nữ Unisex Áo Khoác Dù Nam 2 Lớp Chống Nắng Chống Lạnh Chống Gió Thời Trang Phom Body Phối Màu Hàn Quốc Cao Cấp AD73 - ShopN6</t>
+          <t>Bộ 10 Quần Lót Nữ Modal Miley Lingerie - Giao Màu Ngẫu Nhiên - Size</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-big-size-nam-nu-unisex-ao-khoac-du-nam-2-lop-chong-nang-chong-lanh-chong-gio-thoi-trang-phom-body-phoi-mau-han-quoc-cao-cap-ad73-shopn6-p93233783.html?spid=93233785</t>
+          <t>https://tiki.vn/bo-10-quan-lot-nu-modal-miley-lingerie-giao-mau-ngau-nhien-p1752845.html?spid=4720785</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N6</t>
+          <t>Miley Lingerie</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="G5" t="n">
-        <v>180000</v>
+        <v>550000</v>
       </c>
       <c r="H5" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1984</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="L5" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M5" t="n">
-        <v>3420000</v>
+        <v>16500000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>454</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +30 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>90483623</t>
+          <t>74360894</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Combo 3 Áo thun nam ba lỗ cotton FREEMAN ASF205</t>
+          <t>Quần Lót Nữ Modal Trơn Comfort Miley Lingerie BCS-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-ba-lo-cotton-freeman-asf205-combo-3-p90483623.html?spid=90483629</t>
+          <t>https://tiki.vn/quan-lot-nu-modal-tron-comfort-miley-lingerie-bcs-04-p74360894.html?spid=74360914</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>Miley Lingerie</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>240300</v>
+        <v>65000</v>
       </c>
       <c r="H6" t="n">
-        <v>240300</v>
+        <v>65000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -918,35 +918,35 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>208</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>208</v>
       </c>
       <c r="M6" t="n">
-        <v>3364200</v>
+        <v>13520000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -963,22 +963,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>249723132</t>
+          <t>14815778</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quần Jean nam cao cấp ống đứng kazata màu xanh trung vải xuất khẩu xướt nhẹ dáng slimfit vải co giãn</t>
+          <t>Chân Váy Taka</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-jean-nam-cao-cap-ong-dung-le511-mau-xanh-trung-vai-xuat-khau-xuot-nhe-dang-slimfit-vai-co-gian-p249723132.html?spid=249723138</t>
+          <t>https://tiki.vn/chan-vay-taka-p14815778.html?spid=14815786</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -990,10 +990,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>410000</v>
+        <v>135000</v>
       </c>
       <c r="H7" t="n">
-        <v>410000</v>
+        <v>135000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1002,35 +1002,35 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="M7" t="n">
-        <v>3280000</v>
+        <v>7560000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,22 +1047,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>141665125</t>
+          <t>165984354</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Áo len nam cổ lọ mẫu mới LNA13</t>
+          <t>đồ bộ mặc nhà chất lụa hàn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-len-nam-co-lo-mau-moi-lna13-p141665125.html?spid=141665149</t>
+          <t>https://tiki.vn/do-bo-mac-nha-chat-lua-han-p165984354.html?spid=165984405</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1074,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>324000</v>
+        <v>225000</v>
       </c>
       <c r="H8" t="n">
-        <v>324000</v>
+        <v>225000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1086,35 +1086,35 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>2268000</v>
+        <v>2025000</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1131,22 +1131,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>249724558</t>
+          <t>40885424</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quần Jean nam cao cấp ống đứng kazata màu xanh rêu vải xuất khẩu xướt nhẹ dáng slimfit vải co giãn</t>
+          <t>ÁO SƠ MI CỔ SEN 3 NÚT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-jean-nam-cao-cap-ong-dung-le511-mau-xanh-reu-vai-xuat-khau-xuot-nhe-dang-slimfit-vai-co-gian-p249724558.html?spid=249724560</t>
+          <t>https://tiki.vn/ao-so-mi-co-sen-3-nut-p40885424.html?spid=40885440</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1158,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>410000</v>
+        <v>124000</v>
       </c>
       <c r="H9" t="n">
-        <v>410000</v>
+        <v>124000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1170,13 +1170,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>2050000</v>
+        <v>1736000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1191,14 +1191,14 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1215,101 +1215,101 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>44012385</t>
+          <t>276366333</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Khăn choàng cổ nam nữ siêu nhẹ - UNQ001</t>
+          <t>Aó khoác gió nam US ARMY đặc biệt Chống Gió, Chống nắng form chuẩn hàng đẹp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khan-choang-co-nam-nu-sieu-nhe-unq001-p44012385.html?spid=44012389</t>
+          <t>https://tiki.vn/ao-khoac-gio-nam-us-army-dac-biet-chong-gio-chong-nang-form-chuan-hang-dep-p276366333.html?spid=276366828</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>429000</v>
       </c>
       <c r="G10" t="n">
-        <v>259000</v>
+        <v>429000</v>
       </c>
       <c r="H10" t="n">
-        <v>259000</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
+        <v>12</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>858000</v>
+      </c>
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" t="n">
+      <c r="O10" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
-        <v>1036000</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +2 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>253060005</t>
+          <t>171209012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>đồ bộ mặc nhà mẫu lửng vải kate</t>
+          <t>Quần baggy nữ Hiền Trần BOUTIQUE đồ công sở lưng cạp cao đi học form dáng đẹp thanh lịch màu đen ghi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/do-bo-mac-nha-mau-lung-vai-kate-p253060005.html?spid=253060019</t>
+          <t>https://tiki.vn/quan-baggy-nu-hien-tran-boutique-do-cong-so-lung-cap-cao-di-hoc-form-dang-dep-thanh-lich-mau-den-ghi-p171209012.html?spid=171209014</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1319,81 +1319,81 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Hiền Trần BOUTIQUE</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>160000</v>
+        <v>350000</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>960000</v>
+        <v>700000</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Bán thêm +6 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13299719</t>
+          <t>102890702</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quần lót Nam thời trang mẫu mới - QL004</t>
+          <t>Quần short nỷ nam Novelty 200043Q</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-thoi-trang-mau-moi-p13299719.html?spid=13299731</t>
+          <t>https://tiki.vn/quan-short-ny-nam-novelty-200043q-p102890702.html?spid=102890710</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Novelty</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>110000</v>
+        <v>349000</v>
       </c>
       <c r="H12" t="n">
-        <v>110000</v>
+        <v>349000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1422,35 +1422,35 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>880000</v>
+        <v>698000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1467,121 +1467,121 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>262054269</t>
+          <t>41535995</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quần bơi nam cao cấp, dáng lửng ngang gối, mẫu đa màu lập thể cá tính, thun bơi lạnh dày mát mịn co giãn cực tốt | BN050</t>
+          <t>Combo 10 đôi tất nam vớ nam Cao Cấp Cổ Ngắn MRM FASHION</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-boi-nam-cao-cap-dang-lung-ngang-goi-mau-da-mau-lap-the-ca-tinh-thun-boi-lanh-day-mat-min-co-gian-cuc-tot-bn050-p262054269.html?spid=262054275</t>
+          <t>https://tiki.vn/combo-10-doi-tat-nam-vo-nam-cao-cap-co-ngan-mrm-fashion-p41535995.html?spid=41536001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MRM Manlywear</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>275000</v>
       </c>
       <c r="G13" t="n">
-        <v>210000</v>
+        <v>275000</v>
       </c>
       <c r="H13" t="n">
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>630000</v>
+        <v>550000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +2 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>276235321</t>
+          <t>278129481</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Combo 5 đôi vớ cổ cao nam công sở mẫu gân chìm, tất đi giày tây chất liệu cotton</t>
+          <t>Áo Lót Dán Nâng Ngực Silicon MÀU ĐEN - Áo Bra Dán Ngực Silicon Cài Trước Không Gọng</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-doi-vo-co-cao-nam-cong-so-mau-gan-chim-tat-di-giay-tay-chat-lieu-cotton-p276235321.html?spid=276235322</t>
+          <t>https://tiki.vn/a-o-lot-da-n-nang-ngu-c-silicon-mau-den-a-o-bra-dan-nguc-silicon-cai-truoc-khong-gong-p278129481.html?spid=278050406</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DRU</t>
+          <t>LuckyJQR</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="H14" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1590,35 +1590,35 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>600000</v>
+        <v>450000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1635,37 +1635,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>113052130</t>
+          <t>216205243</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Áo khoác nam Áo khoát nam gió dù 2 lớp chống nắng LOCAL PEOPLE đẹp siêu hot - M100</t>
+          <t>Bộ Áo Cúp Ngang và Quần Lót Nữ Thun Lạnh Miley Lingerie BRM11202_FMM1105</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/p-ao-khoac-nam-ao-khoat-nam-gio-du-2-lop-chong-nang-local-people-dep-sieu-hot-m100-p113052130.html?spid=113052161</t>
+          <t>https://tiki.vn/bo-ao-cup-ngang-va-quan-lot-nu-thun-lanh-miley-lingerie-brm11202_fmm1105-p216205243.html?spid=216205251</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Miley Lingerie</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>189250</v>
+        <v>199000</v>
       </c>
       <c r="H15" t="n">
-        <v>189250</v>
+        <v>199000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1674,13 +1674,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>567750</v>
+        <v>398000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1719,37 +1719,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>146449442</t>
+          <t>188412428</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Combo 6 Quần lót nam thun coton hàng việt nam xuất khẩu dạng cao cấp thoáng mát Từ 40kg đến 75kg</t>
+          <t>Dây Giày Loại Tròn Cao Cấp DGD2024a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-6-quan-lot-nam-thun-coton-hang-viet-nam-xuat-khau-dang-cao-cap-thoang-mat-tu-40kg-den-75kg-p146449442.html?spid=146449450</t>
+          <t>https://tiki.vn/day-giay-loai-tron-cao-cap-dgd2024a-p188412428.html?spid=188412432</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>HA NAM</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>180000</v>
+        <v>16000</v>
       </c>
       <c r="H16" t="n">
-        <v>180000</v>
+        <v>16000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1758,13 +1758,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="M16" t="n">
-        <v>540000</v>
+        <v>288000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1779,14 +1779,14 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1803,37 +1803,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>276664793</t>
+          <t>199607832</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quần gió lót lông QD2 ấm áp thời trang cho nam, Quần nỉ jogger lót lông QD1 sang trọng và dày dặn D Danido</t>
+          <t>Combo 4 Quần Lót Ren Miley Lingerie Màu Trắng Đen - FLS03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-gio-lot-long-qd2-am-ap-thoi-trang-cho-nam-quan-ni-jogger-lot-long-qd1-sang-trong-va-day-dan-d-danido-p276664793.html?spid=276664835</t>
+          <t>https://tiki.vn/combo-4-quan-lot-ren-miley-lingerie-mau-trang-den-fls03-p199607832.html?spid=199607836</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>D Danido</t>
+          <t>Miley Lingerie</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>239000</v>
+        <v>216000</v>
       </c>
       <c r="H17" t="n">
-        <v>239000</v>
+        <v>216000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1848,29 +1848,29 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>239000</v>
+        <v>216000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1887,121 +1887,121 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>52758433</t>
+          <t>263040176</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Combo 5 Đôi Tất Nam Vớ Nam Cổ Dài Sợi Cotton Mix Màu</t>
+          <t>Bộ áo bà nam truyền thống đỏ đô - Có bộ bà ba Bigsize- may sỉ bà ba toàn quốc - May bộ bà ba theo yêu cầu</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-doi-tat-nam-vo-nam-co-dai-soi-cotton-mix-mau-p52758433.html?spid=67297062</t>
+          <t>https://tiki.vn/bo-ao-ba-nam-truyen-thong-do-do-p263040176.html?spid=263040188</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JM Jamano</t>
+          <t>CAN THO AO DAI AO BA BA</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>175000</v>
+        <v>199000</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3764</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>3765</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>175000</v>
+        <v>199000</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>276070120</t>
+          <t>277591240</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quần short huongtam nam cao cấp(QSNN8). Chất liệu vải loại tốt: mềm mại, thoáng mát, không phai màu</t>
+          <t>Kẹp Tóc Nơ Bong Bóng Nhiều Lớp Hoa Cho Nữ - Phụ Kiện Tóc Dễ Thương</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-short-huongtam-nam-cao-cap-qsnn8-chat-lieu-vai-loai-tot-mem-mai-thoang-mat-khong-phai-mau-p276070120.html?spid=276070132</t>
+          <t>https://tiki.vn/kep-toc-no-bong-bong-nhieu-lop-hoa-cho-nu-phu-kien-toc-de-thuong-p277591240.html?spid=277591246</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HƯƠNG TÂM</t>
+          <t>MINIIN</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>73000</v>
+        <v>24000</v>
       </c>
       <c r="H19" t="n">
-        <v>73000</v>
+        <v>24000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2010,35 +2010,35 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>73000</v>
+        <v>192000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2055,17 +2055,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>213706052</t>
+          <t>274586950</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10 - 20 đôi Tất nữ mỏng giấy cổ ngắn Hàn Quốc</t>
+          <t>Set 100 Miếng dán chống mồ hôi nách, miếng dán ngăn mồ hôi nách siêu thâm hút cho Nam và Nữ che tên sản phẩm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/tat-nu-mong-giay-co-ngan-han-quoc-p213706052.html?spid=276954507</t>
+          <t>https://tiki.vn/set-100-mieng-dan-chong-mo-hoi-nach-mieng-dan-ngan-mo-hoi-nach-sieu-tham-hut-cho-nam-va-nu-che-ten-san-pham-p274586950.html?spid=274586954</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2075,17 +2075,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>FTAKY</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>70000</v>
+        <v>25000</v>
       </c>
       <c r="H20" t="n">
-        <v>70000</v>
+        <v>25000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2094,13 +2094,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>70000</v>
+        <v>175000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2139,17 +2139,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>199597031</t>
+          <t>276634531</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Xi Đánh Giày Sáp Shoe Polish XIMO Đen, Không Màu, Nâu Đủ Màu XI08</t>
+          <t>Keo Dán Giày Thể Thao Sêu Dính Dùng Nhiệt Trong Suốt Không Tổn Thương Da, Keo Dính Giày Đa Năng Siêu Bền Chống Nước Tốt Xanh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/xi-danh-giay-sap-shoe-polish-ximo-den-khong-mau-nau-du-mau-chinh-hang-xi08-p199597031.html?spid=252869520</t>
+          <t>https://tiki.vn/keo-dan-giay-the-thao-seu-dinh-dung-nhiet-trong-suot-khong-ton-thuong-da-keo-dinh-giay-da-nang-sieu-ben-chong-nuoc-tot-p276634531.html?spid=276634532</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2159,14 +2159,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>LuckyJQR</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>32000</v>
+        <v>160000</v>
       </c>
       <c r="G21" t="n">
-        <v>32000</v>
+        <v>160000</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2175,38 +2175,38 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="K21" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>32000</v>
+        <v>160000</v>
       </c>
       <c r="N21" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2223,52 +2223,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16651795</t>
+          <t>273406567</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>️[5 Quần] ComBo 5 Quần Lót Nam THUN LẠNH Lưng Bự Hàng Việt Nam Cao Cấp</t>
+          <t>Kẹp tóc sau đính pha lê sang trọng - kẹp tóc sang trọng - kẹp tóc 5 răng cao cấp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/5-quan-combo-5-quan-lot-nam-thun-lanh-lung-bu-hang-viet-nam-cao-cap-p16651795.html?spid=51148102</t>
+          <t>https://tiki.vn/kep-toc-cang-cua-dinh-hoa-pha-le-charm-p273406567.html?spid=273406571</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MENLIVE</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>159600</v>
+        <v>45000</v>
       </c>
       <c r="G22" t="n">
-        <v>205000</v>
+        <v>45000</v>
       </c>
       <c r="H22" t="n">
-        <v>45400</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>28.45</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="N22" t="n">
         <v>5</v>
@@ -2280,17 +2280,17 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2300,59 +2300,59 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Giá tăng 45,400đ (+28.4%)</t>
+          <t>Bán thêm +3 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16375016</t>
+          <t>276316659</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COMBO HỘP 5 Quần Lót ĐÙI Nam Xuất Nhật Cao Cấp (MIX NGẪU NHIÊN)</t>
+          <t>Áo Lót Nữ, Áo Lót Đúc Su Đệm Dày Siêu Nâng Ngực Tạo Khe Quyến Rũ, Áo Ngực Su Bàn Tay Không Gọng</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-hop-5-quan-lot-dui-nam-xuat-nhat-cao-cap-mix-ngau-nhien-p16375016.html?spid=277961877</t>
+          <t>https://tiki.vn/ao-lot-nu-ao-lot-duc-su-dem-day-sieu-nang-nguc-tao-khe-quyen-ru-ao-nguc-su-ban-tay-khong-gong-p276316659.html?spid=276316691</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>FTAKY</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>210980</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>274000</v>
+        <v>45000</v>
       </c>
       <c r="H23" t="n">
-        <v>63020</v>
+        <v>45000</v>
       </c>
       <c r="I23" t="n">
-        <v>29.87</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2374,237 +2374,237 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Giá tăng 63,020đ (+29.9%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16546849</t>
+          <t>276744158</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nam Tam Giác Nhật</t>
+          <t xml:space="preserve">Quần lót nữ nơ ren sexy gợi cảm cao cấp Quần chip ren nữ nơ mềm mại xuyên thấu gợi cảm </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nam-tam-giac-nhat-p16546849.html?spid=53006035</t>
+          <t>https://tiki.vn/quan-lot-nu-no-ren-sexy-goi-cam-cao-cap-quan-chip-ren-nu-no-mem-mai-xuyen-thau-goi-cam-p276744158.html?spid=276744159</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>FTAKY</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>170100</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>210000</v>
+        <v>8500</v>
       </c>
       <c r="H24" t="n">
-        <v>39900</v>
+        <v>8500</v>
       </c>
       <c r="I24" t="n">
-        <v>23.46</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>42500</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Giá tăng 39,900đ (+23.5%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>277437306</t>
+          <t>21308472</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Áo polo tay ngắn nam core. Fitted - RT 10F24POL001CR1 | ROUTINE CÀ MAU</t>
+          <t>Set 3 Cột Tóc Dây Chun Buộc Tóc Đính Ngọc Trai Xinh Xắn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-polo-tay-ngan-nam-core-fitted-rt-10f24pol001cr1-routine-ca-mau-p277437306.html?spid=277437310</t>
+          <t>https://tiki.vn/set-3-cot-toc-day-chun-buoc-toc-dinh-ngoc-trai-xinh-xan-p21308472.html?spid=57771841</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>349000</v>
+        <v>24000</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="H25" t="n">
-        <v>-349000</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>276678209</t>
+          <t>276147904</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Quần Tam Giác Hiệu Davie Mã DVTL009, Chất Thun Lạnh Cao Cấp</t>
+          <t>Quần lót nữ ren sexy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-tam-giac-hieu-davie-ma-dvtl009-chat-thun-lanh-cao-cap-p276678209.html?spid=276678235</t>
+          <t>https://tiki.vn/quan-lot-nu-ren-sexy-p276147904.html?spid=276147905</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DAVIE</t>
+          <t>FTAKY</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="H26" t="n">
-        <v>-350000</v>
+        <v>8000</v>
       </c>
       <c r="I26" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2626,34 +2626,34 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>276882727</t>
+          <t>7078807</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Áo vest blazer nam phong cách Hàn Quốc vải Linen thoáng mát, mềm mịn</t>
+          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-vest-blazer-nam-phong-cach-han-quoc-vai-linen-thoang-mat-mem-min-p276882727.html?spid=276882729</t>
+          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2663,26 +2663,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haint Boutique</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>352800</v>
       </c>
       <c r="G27" t="n">
         <v>420000</v>
       </c>
       <c r="H27" t="n">
-        <v>420000</v>
+        <v>67200</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>19.05</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2691,53 +2691,53 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 67,200đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>274885003</t>
+          <t>54569520</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Áo thun nam T-Shirt TS063 Leman vải Cotton thấm hút tốt kiểu dáng Slimfit</t>
+          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-t-shirt-ts063-leman-vai-cotton-tham-hut-tot-kieu-dang-slimfit-p274885003.html?spid=274907292</t>
+          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2747,54 +2747,54 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leman</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>170000</v>
+        <v>73920</v>
       </c>
       <c r="G28" t="n">
-        <v>170000</v>
+        <v>88000</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>14080</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>19.05</v>
       </c>
       <c r="J28" t="n">
+        <v>16</v>
+      </c>
+      <c r="K28" t="n">
+        <v>16</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>5</v>
       </c>
-      <c r="K28" t="n">
+      <c r="O28" t="n">
         <v>5</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" t="n">
-        <v>4</v>
-      </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2804,44 +2804,44 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Rating 3.0→4.0 (+1.00) | Review thêm +1</t>
+          <t>Giá tăng 14,080đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>212936093</t>
+          <t>276687955</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Áo khoác gió 1 lớp ALIGRO màu navy AK1G.3</t>
+          <t>Áo ngực nữ không gọng đệm mỏng su trơn đứng dáng nâng ngực chuẩn đẹp SAY AL003</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-gio-1-lop-aligro-mau-navy-ak1g-3-p212936093.html?spid=212936099</t>
+          <t>https://tiki.vn/ao-nguc-nu-khong-gong-dem-mong-su-tron-dung-dang-nang-nguc-chuan-dep-say-al003-p276687955.html?spid=276688001</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aligro</t>
+          <t>FTAKY</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>620000</v>
+        <v>45000</v>
       </c>
       <c r="H29" t="n">
-        <v>620000</v>
+        <v>45000</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -2895,22 +2895,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>244297794</t>
+          <t>74421501</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
+          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2919,22 +2919,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>163400</v>
+        <v>120000</v>
       </c>
       <c r="G30" t="n">
-        <v>205000</v>
+        <v>160000</v>
       </c>
       <c r="H30" t="n">
-        <v>41600</v>
+        <v>40000</v>
       </c>
       <c r="I30" t="n">
-        <v>25.46</v>
+        <v>33.33</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2943,26 +2943,26 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -2972,29 +2972,29 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Giá tăng 41,600đ (+25.5%)</t>
+          <t>Giá tăng 40,000đ (+33.3%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>274051771</t>
+          <t>59462352</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Áo khoác măng tô nam dáng dài trẻ trung lịch lãm đích thực thời trang nam NMT61</t>
+          <t>Áo ngực mỏng thêu hoa cài trước có gọng</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-mang-to-nam-dang-dai-tre-trung-lich-lam-dich-thuc-thoi-trang-nam-nmt61-p274051771.html?spid=274051803</t>
+          <t>https://tiki.vn/ao-nguc-mong-theu-hoa-cai-truoc-co-gong-p59462352.html?spid=59462384</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3003,22 +3003,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>67500</v>
       </c>
       <c r="G31" t="n">
-        <v>3900000</v>
+        <v>90000</v>
       </c>
       <c r="H31" t="n">
-        <v>3900000</v>
+        <v>22500</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3027,73 +3027,73 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 22,500đ (+33.3%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15810955</t>
+          <t>275663168</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Áo thun nam cá sấu</t>
+          <t>Váy ngủ lụa 302 cổ đổ xẻ tà hai dây đơn giản quyến rũ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-ca-sau-p15810955.html?spid=278513577</t>
+          <t>https://tiki.vn/vay-ngu-lua-302-co-do-xe-ta-hai-day-don-gian-quyen-ru-p275663168.html?spid=275663178</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Sanny House</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>100000</v>
+        <v>312000</v>
       </c>
       <c r="H32" t="n">
-        <v>100000</v>
+        <v>312000</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3147,46 +3147,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>262796074</t>
+          <t>277311177</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chai vệ sinh đồ da làm sạch, dưỡng ẩm chống mốc, kháng khuẩn giày, túi ví, áo, ghế da 150ml</t>
+          <t>Váy 2 dây váy ngủ lụa cổ tim chất lụa satin mềm, mịn thoáng mát VN0003</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chai-ve-sinh-do-da-lam-sach-duong-am-chong-moc-khang-khuan-giay-tui-vi-ao-ghe-da-150ml-p262796074.html?spid=262796075</t>
+          <t>https://tiki.vn/vay-2-day-vay-ngu-lua-co-tim-chat-lua-satin-mem-min-thoang-mat-vn0003-p277311177.html?spid=277311201</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ximo</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>70000</v>
+        <v>199000</v>
       </c>
       <c r="H33" t="n">
-        <v>-5000</v>
+        <v>199000</v>
       </c>
       <c r="I33" t="n">
-        <v>-6.67</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3214,34 +3214,34 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Giá giảm 5,000đ (6.7%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>157808804</t>
+          <t>91324662</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>đồ bộ mặc nhà đẹp chất lụa hàn</t>
+          <t>Áo Dài Đông Phong</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://tiki.vn/do-bo-mac-nha-dep-chat-lua-han-p157808804.html?spid=157808821</t>
+          <t>https://tiki.vn/ao-dai-dong-phong-p91324662.html?spid=91324663</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Baciami</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>200000</v>
+        <v>950000</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>950000</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3282,79 +3282,79 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Rating 0.0→5.0 (+5.00) | Review thêm +1</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>91973812</t>
+          <t>262796074</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Su Đúc Hình Lá Không Gọng Đệm Dày Nâng Ngực A01 có ảnh thật</t>
+          <t>Chai vệ sinh đồ da làm sạch, dưỡng ẩm chống mốc, kháng khuẩn giày, túi ví, áo, ghế da 150ml</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-su-duc-hinh-la-khong-gong-dem-day-nang-nguc-a01-co-anh-that-p91973812.html?spid=279055013</t>
+          <t>https://tiki.vn/chai-ve-sinh-do-da-lam-sach-duong-am-chong-moc-khang-khuan-giay-tui-vi-ao-ghe-da-150ml-p262796074.html?spid=262796075</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Ximo</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>85000</v>
+        <v>70000</v>
       </c>
       <c r="G35" t="n">
-        <v>64600</v>
+        <v>75000</v>
       </c>
       <c r="H35" t="n">
-        <v>-20400</v>
+        <v>5000</v>
       </c>
       <c r="I35" t="n">
-        <v>-24</v>
+        <v>7.14</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -3392,29 +3392,29 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Giá giảm 20,400đ (24.0%)</t>
+          <t>Giá tăng 5,000đ (+7.1%)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>37126497</t>
+          <t>279256467</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>( 10 cái ) quần lót nữ Su đúc không đường may, hàng đẹp loại xịn W19_503</t>
+          <t>Thắt lưng nam</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-10-quan-lot-su-duc-khong-duong-may-hang-dep-loai-xin-w19_503-p37126497.html?spid=51720423</t>
+          <t>https://tiki.vn/that-lung-nam-p279256467.html?spid=279256468</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3423,22 +3423,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>280000</v>
+        <v>9999999</v>
       </c>
       <c r="H36" t="n">
-        <v>70000</v>
+        <v>9999999</v>
       </c>
       <c r="I36" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3447,53 +3447,53 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Giá tăng 70,000đ (+33.3%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>279104033</t>
+          <t>73862702</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Áo lót nữ form ba lỗ thông hơi trơn big size 1397 – Size XXL–3XL</t>
+          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-form-ba-lo-thong-hoi-tron-big-size-1397-size-xxl-3xl-p279104033.html?spid=279104035</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862720</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>108000</v>
+        <v>129750</v>
       </c>
       <c r="G37" t="n">
-        <v>82080</v>
+        <v>173000</v>
       </c>
       <c r="H37" t="n">
-        <v>-25920</v>
+        <v>43250</v>
       </c>
       <c r="I37" t="n">
-        <v>-24</v>
+        <v>33.33</v>
       </c>
       <c r="J37" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="K37" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3540,17 +3540,17 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -3560,53 +3560,53 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Giá giảm 25,920đ (24.0%)</t>
+          <t>Giá tăng 43,250đ (+33.3%)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>279561449</t>
+          <t>56346167</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Áo Cá Chép (Tùy chọn) - Áo đen Cá Chép vươn lên - XXL</t>
+          <t>Áo lót nữ ren dày</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-ca-chep-tuy-chon-p279561449.html?spid=279561471</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-day-p56346167.html?spid=61933225</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cá Chép</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="G38" t="n">
-        <v>190000</v>
+        <v>180000</v>
       </c>
       <c r="H38" t="n">
-        <v>190000</v>
+        <v>45000</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3615,76 +3615,76 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 45,000đ (+33.3%)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>276833571</t>
+          <t>278433685</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Quần Short Mặt Nhà Thương Hiệu Davie Dvs06 Chất Liệu Kate 100% Cotton Thoáng Mát</t>
+          <t>Đồ bộ nữ,đồ ngủ mặc nhà lửng vải lụa mango BL 245 hoạ tiết caro dễ thương size 50-65kg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-short-mat-nha-thuong-hieu-davie-dvs06-chat-lieu-kate-100-cotton-thoang-mat-p276833571.html?spid=276833601</t>
+          <t>https://tiki.vn/do-bo-nu-do-ngu-mac-nha-lung-vai-lua-mango-bl-245-hoa-tiet-caro-de-thuong-size-50-65kg-p278433685.html?spid=278433691</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DAVIE</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>410000</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>155000</v>
       </c>
       <c r="H39" t="n">
-        <v>-410000</v>
+        <v>155000</v>
       </c>
       <c r="I39" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3718,60 +3718,60 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>276832011</t>
+          <t>56930874</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quần Mặc Nhà Nam SKD02 Vải Kate Co Giãn Nhẹ</t>
+          <t>Combo 5 quần lót nữ Modal Miley Lingerie BCS0704 - XL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-mac-nha-nam-skd02-vai-kate-co-gian-nhe-p276832011.html?spid=276832019</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nu-modal-miley-lingerie-bcs0704-p56930874.html?spid=56930882</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>DAVIE</t>
+          <t>Miley Lingerie</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>189000</v>
+        <v>259000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-189000</v>
+        <v>-259000</v>
       </c>
       <c r="I40" t="n">
         <v>-100</v>
       </c>
       <c r="J40" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3783,16 +3783,16 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -3819,37 +3819,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>276669234</t>
+          <t>278013980</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quần Lót Nam Tam Giác Thương Hiệu Samaki Mã SKCT01 Chất Liệu Co Giãn</t>
+          <t>QUẦN ĐÙI CK HOT HIT CÁ TÍNH TỪ 40-70KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-tam-giac-thuong-hieu-samaki-ma-skct01-chat-lieu-co-gian-p276669234.html?spid=276669298</t>
+          <t>https://tiki.vn/quan-dui-ck-hot-hit-ca-tinh-tu-40-70kg-danh-cho-nu-p278013980.html?spid=278021323</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DAVIE</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>215000</v>
+        <v>75000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-215000</v>
+        <v>-75000</v>
       </c>
       <c r="I41" t="n">
         <v>-100</v>
@@ -3867,16 +3867,16 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -3903,46 +3903,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>277841951</t>
+          <t>207818719</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quần lót nam tam giác organic cotton phối lưng . Brief - RT 10S25UND002 | ROUTINE CÀ MAU</t>
+          <t>Kính Râm, Kính Nam Mắt Phi Công Gọng Khoan Full Đen - BLUE LIGHT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-tam-giac-organic-cotton-phoi-lung-brief-rt-10s25und002-routine-ca-mau-p277841951.html?spid=277841975</t>
+          <t>https://tiki.vn/kinh-ram-kinh-nam-mat-phi-cong-gong-khoan-full-den-blue-light-p207818719.html?spid=147980739</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>Blue Light</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>99000</v>
+        <v>185000</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="H42" t="n">
-        <v>-99000</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3951,79 +3951,79 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P42" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>276667776</t>
+          <t>278697497</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Quần Short Mặc Nhà Nam Davie Dvs01 Chất Liệu Vải Kate 100% Cotton - Giao Màu Ngẫu Nhiên</t>
+          <t>Combo Phụ kiện thời trang Đuôi cosplay cáo nhân tạo Cosplay + nơ cổ + kẹp tóc (Halloween / Lễ hội / Trang phục hóa trang)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-short-mac-nha-nam-davie-dvs01-chat-lieu-vai-kate-100-cotton-giao-mau-ngau-nhien-p276667776.html?spid=276667794</t>
+          <t>https://tiki.vn/combo-phu-kien-thoi-trang-duoi-fox-nhan-tao-cosplay-no-co-kep-toc-halloween-le-hoi-trang-phuc-hoa-trang-p278697497.html?spid=278697540</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>DAVIE</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
         <v>350000</v>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
       <c r="H43" t="n">
-        <v>-350000</v>
+        <v>350000</v>
       </c>
       <c r="I43" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -4038,73 +4038,73 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P43" t="n">
-        <v>-0</v>
+        <v>5</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>278717007</t>
+          <t>277459049</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Áo khoác raglan dây kéo. Loose - ROUTINE 10F25WJA002</t>
+          <t>Thắt lưng nam da bò nguyên chất mặt khóa tự động hợp kim cao cấp</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-raglan-day-keo-loose-routine-10f25wja002-p278717007.html?spid=278717013</t>
+          <t>https://tiki.vn/that-lung-nam-da-bo-nguyen-chat-mat-khoa-tu-dong-hop-kim-cao-cap-p277459049.html?spid=277459051</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>ANANSHOP688</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>549000</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>290000</v>
       </c>
       <c r="H44" t="n">
-        <v>-549000</v>
+        <v>290000</v>
       </c>
       <c r="I44" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4119,16 +4119,16 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -4138,34 +4138,34 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>277515096</t>
+          <t>278071763</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Áo sơ mi sọc Nam tay dài N&amp;M 2101087</t>
+          <t>Quần sịp nam thông hơi mát lạnh từ 40-100kg dành cho nam</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-soc-nam-tay-dai-n-m-2101087-p277515096.html?spid=277515116</t>
+          <t>https://tiki.vn/quan-sip-nam-thong-hoi-mat-lanh-tu-50-100kg-danh-cho-nam-p278071763.html?spid=278071767</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4175,17 +4175,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ninomaxx</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>599000</v>
+        <v>94000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-599000</v>
+        <v>-94000</v>
       </c>
       <c r="I45" t="n">
         <v>-100</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -4239,17 +4239,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>278872546</t>
+          <t>278014106</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam.Fitted - ROUTINE 10F25TSS039</t>
+          <t>QUẦN SỊP CHÉO COTTON CAO CẤP MỀM MỊN TỪ 40-85KG DÀNH CHO NAM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-fitted-routine-10f25tss039-p278872546.html?spid=278872562</t>
+          <t>https://tiki.vn/quan-sip-cheo-cotton-cao-cap-mem-min-tu-48-85kg-danh-cho-nam-p278014106.html?spid=279145394</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>349000</v>
+        <v>60000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-349000</v>
+        <v>-60000</v>
       </c>
       <c r="I46" t="n">
         <v>-100</v>
@@ -4287,16 +4287,16 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -4323,17 +4323,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>279277075</t>
+          <t>278015269</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Áo polo len dệt kim tay ngắn nam. Fitted - ROUTINE 10S26KNI019</t>
+          <t>QUẦN SỊP THÔNG HƠI LƯỚI NHỎ TỪ 48-100KG DÀNH CHO NAM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-polo-len-det-kim-tay-ngan-nam-fitted-routine-10s26kni019-p279277075.html?spid=279277091</t>
+          <t>https://tiki.vn/quan-sip-thong-hoi-luoi-nho-tu-48-100kg-danh-cho-nam-p278015269.html?spid=278015277</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4343,23 +4343,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>649000</v>
+        <v>42000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-649000</v>
+        <v>-42000</v>
       </c>
       <c r="I47" t="n">
         <v>-100</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -4407,43 +4407,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>111708924</t>
+          <t>278034486</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Combo 6 quần đùi mặc nhà nam cao cấp kate 100% cotton</t>
+          <t>ÁO NGỰC SU CỰC ĐẸP CỰC XỊN HOTTREND SIZE 34-38 DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-6-quan-dui-mac-nha-nam-cao-cap-kate-100-cotton-p111708924.html?spid=111708928</t>
+          <t>https://tiki.vn/ao-nguc-su-cuc-dep-cuc-xin-hottrend-size-34-38-danh-cho-nu-p278034486.html?spid=278034500</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>DAVIE</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>414000</v>
+        <v>140000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-414000</v>
+        <v>-140000</v>
       </c>
       <c r="I48" t="n">
         <v>-100</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -4491,37 +4491,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>279380318</t>
+          <t>278026014</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Quần đùi nam cạp chun cao cấp Lucibeaty vải gió phong cách thể thao chính hãng QGH-028</t>
+          <t>ÁO NGỰC SU CÚP NGANG ĐẸP SIZE 34-38 DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-dui-nam-cap-chun-cao-cap-lucibeaty-vai-gio-phong-cach-the-thao-chinh-hang-qgh-028-p279380318.html?spid=279380324</t>
+          <t>https://tiki.vn/ao-nguc-su-cup-ngang-dep-size-34-38-danh-cho-nu-p278026014.html?spid=278026026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>270000</v>
+        <v>110000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-270000</v>
+        <v>-110000</v>
       </c>
       <c r="I49" t="n">
         <v>-100</v>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -4575,37 +4575,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>279365270</t>
+          <t>278012255</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Quần vải / Quần tây nam màu đen Form Slim - ROUTINE 10F25PFO003</t>
+          <t>QUẦN LÓT LỤA SIÊU ĐẸP CAO CẤP PHỐI REN TỪ 40-70KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-vai-quan-tay-nam-mau-den-form-slim-routine-10f25pfo003-p279365270.html?spid=279365278</t>
+          <t>https://tiki.vn/quan-lot-lua-sieu-dep-cao-cap-phoi-ren-tu-40-70kg-danh-cho-nu-p278012255.html?spid=278012271</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>599000</v>
+        <v>45000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-599000</v>
+        <v>-45000</v>
       </c>
       <c r="I50" t="n">
         <v>-100</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -4659,37 +4659,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>279259219</t>
+          <t>278012626</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam hình in . Form Boxy - ROUTINE 10S25TSS032</t>
+          <t>QUẦN LÓT SU THÔNG HƠI SIÊU ĐẸP SIÊU MỎNG TỪ 40-60KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-hinh-in-form-boxy-routine-10s25tss032-p279259219.html?spid=279259225</t>
+          <t>https://tiki.vn/quan-lot-su-thong-hoi-sieu-dep-sieu-mong-tu-40-60kg-danh-cho-nu-p278012626.html?spid=278012638</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>349000</v>
+        <v>38000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-349000</v>
+        <v>-38000</v>
       </c>
       <c r="I51" t="n">
         <v>-100</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -4743,37 +4743,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>278993255</t>
+          <t>278016649</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Áo polo tay ngắn nam viền cổ.Fitted - ROUTINE 10F25POL029</t>
+          <t>ÁO LÓT BẦU COTTON SIÊU XINH SIZE 38-42 DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-polo-tay-ngan-nam-vien-co-fitted-routine-10f25pol029-p278993255.html?spid=278993267</t>
+          <t>https://tiki.vn/ao-lot-bau-cotton-sieu-xinh-size-38-42-danh-cho-nu-p278016649.html?spid=278016655</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>499000</v>
+        <v>60000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-499000</v>
+        <v>-60000</v>
       </c>
       <c r="I52" t="n">
         <v>-100</v>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -4827,43 +4827,43 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>279256558</t>
+          <t>278011349</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Áo polo nam tay ngắn phối cố Form Fitted - ROUTINE 10F25POL028</t>
+          <t>QUẦN ĐỘN MÔNG ĐỊNH HÌNH TỪ 40-70KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-polo-nam-tay-ngan-phoi-co-form-fitted-routine-10f25pol028-p279256558.html?spid=279256564</t>
+          <t>https://tiki.vn/quan-don-mong-dinh-hinh-tu-40-70kg-danh-cho-nu-p278011349.html?spid=278011357</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>579000</v>
+        <v>85000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-579000</v>
+        <v>-85000</v>
       </c>
       <c r="I53" t="n">
         <v>-100</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -4911,37 +4911,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>278935816</t>
+          <t>278009461</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Quần dài kaki nam Form Slim - ROUTINE 10F25PCA014</t>
+          <t>ÁO NGỰC BRA ĐẸP QUYẾN RŨ SIZE TỪ 36-40 DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-dai-kaki-nam-form-slim-routine-10f25pca014-p278935816.html?spid=278935830</t>
+          <t>https://tiki.vn/ao-nguc-bra-dep-quyen-ru-size-tu-36-40-danh-cho-nu-p278009461.html?spid=278009483</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>599000</v>
+        <v>110000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-599000</v>
+        <v>-110000</v>
       </c>
       <c r="I54" t="n">
         <v>-100</v>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -4995,43 +4995,43 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>278872719</t>
+          <t>278034638</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Áo Polo Nam Tay Ngắn Cotton Hạn Chế Nhăn Form Fitted - ROUTINE 10F25POL005</t>
+          <t>ÁO LÁ BRA HỌC SINH CHẤT COTTON MÁT KHÔNG MÚT TỪ 8-13 TUỔI DƯỚI 50KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-polo-nam-tay-ngan-cotton-han-che-nhan-form-fitted-routine-10f25pol005-p278872719.html?spid=278872733</t>
+          <t>https://tiki.vn/ao-la-bra-hoc-sinh-chat-cotton-mat-khong-mut-duoi-50kg-danh-cho-nu-p278034638.html?spid=278034640</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>599000</v>
+        <v>62000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-599000</v>
+        <v>-62000</v>
       </c>
       <c r="I55" t="n">
         <v>-100</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -5079,43 +5079,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>277550023</t>
+          <t>277388268</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Quần vải nam / Quần tây nam dài cotton poly ủi ly trước - RT 10S25PFO004 | ROUTINE CÀ MAU</t>
+          <t>Chai xịt tạo bọt vệ sinh giày White Shoes Cleaner 330ml</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-vai-nam-quan-tay-nam-dai-cotton-poly-ui-ly-truoc-rt-10s25pfo004-routine-ca-mau-p277550023.html?spid=277550045</t>
+          <t>https://tiki.vn/chai-xit-tao-bot-ve-sinh-giay-white-shoes-cleaner-330ml-p277388268.html?spid=277388269</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>malizia</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>479000</v>
+        <v>85000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-479000</v>
+        <v>-85000</v>
       </c>
       <c r="I56" t="n">
         <v>-100</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -5127,16 +5127,16 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>-0</v>
+        <v>-4</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -5163,37 +5163,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>278994111</t>
+          <t>279399528</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam nỉ phối vai Form Boxy - ROUTINE 10F25TSS019</t>
+          <t>KHĂN LỤA DÀI KHĂN QUÀNG CỔ KHĂN CHOÀNG LỤA BĂNG ĐÔ TRANG TRÍ NƠ CAO CẤP ĐA NĂNG SANG TRỌNG THANH LỊCH MÃ 18-38</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-ni-phoi-vai-form-boxy-routine-10f25tss019-p278994111.html?spid=278994123</t>
+          <t>https://tiki.vn/khan-lua-dai-khan-quang-co-khan-choang-lua-bang-do-trang-tri-no-cao-cap-da-nang-sang-trong-thanh-lich-ma-18-38-p279399528.html?spid=279399560</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>449000</v>
+        <v>120000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-449000</v>
+        <v>-120000</v>
       </c>
       <c r="I57" t="n">
         <v>-100</v>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -5247,43 +5247,43 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>278105237</t>
+          <t>278008741</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam. Form Fitted - RT 10S25TSS004 | ROUTINE CÀ MAU</t>
+          <t>MIẾNG DÁN NGỰC HÌNH HOA SILICON CỰC CHẮC VÀ XINH DÀNH CHO NỮ - HỘP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-form-fitted-rt-10s25tss004-routine-ca-mau-p278105237.html?spid=278514403</t>
+          <t>https://tiki.vn/mieng-dan-nguc-hinh-hoa-silicon-cuc-chac-va-xinh-danh-cho-nu-p278008741.html?spid=278008743</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>449000</v>
+        <v>57000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-449000</v>
+        <v>-57000</v>
       </c>
       <c r="I58" t="n">
         <v>-100</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -5331,43 +5331,43 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>279151760</t>
+          <t>56183675</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Áo Thun Nam Tay Ngắn In Chữ Form Boxy - ROUTINE 10F25TSS018</t>
+          <t>Quần lót nữ hộp quà tặng Modal New Color modern Miley Lingerie BCS_04</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-tay-ngan-in-chu-form-boxy-routine-10f25tss018-p279151760.html?spid=279151762</t>
+          <t>https://tiki.vn/quan-lot-nu-hop-qua-tang-modal-new-color-modern-miley-lingerie-bcs_04-p56183675.html?spid=56183681</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>Miley Lingerie</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>479000</v>
+        <v>252000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-479000</v>
+        <v>-252000</v>
       </c>
       <c r="I59" t="n">
         <v>-100</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -5379,16 +5379,16 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -5415,37 +5415,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>278741557</t>
+          <t>279004066</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Áo Thun Nam Tay Ngắn Cotton Màu Trơn Form Fit - ROUTINE 10S25TSS046</t>
+          <t>QUẦN ĐỘN MÔNG ĐỊNH HÌNH SIÊU ĐẸP TỪ 40-75KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-tay-ngan-cotton-mau-tron-form-fit-routine-10s25tss046-p278741557.html?spid=278741561</t>
+          <t>https://tiki.vn/quan-don-mong-dinh-hinh-sieu-dep-tu-40-75kg-danh-cho-nu-p279004066.html?spid=279004070</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>299000</v>
+        <v>115000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-299000</v>
+        <v>-115000</v>
       </c>
       <c r="I60" t="n">
         <v>-100</v>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -5499,37 +5499,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>277826976</t>
+          <t>276900256</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam Scafe thêu Form Boxy - RT 10S25TSS054 | ROUTINE CÀ MAU</t>
+          <t>Quần Lót Nữ Ren Ôm Nửa Mông Nhiều Mẫu Sanny House</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-scafe-theu-form-boxy-rt-10s25tss054-routine-ca-mau-p277826976.html?spid=277826998</t>
+          <t>https://tiki.vn/quan-lot-nu-ren-om-nua-mong-nhieu-mau-sanny-house-p276900256.html?spid=276900425</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>Sanny House</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>529000</v>
+        <v>52500</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-529000</v>
+        <v>-52500</v>
       </c>
       <c r="I61" t="n">
         <v>-100</v>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -5583,37 +5583,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>277327114</t>
+          <t>278026067</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam cooling . Fitted - RT 10S25TSS001 | ROUTINE CÀ MAU</t>
+          <t>ÁO CHỐNG NẮNG MỀM MÁT TỪ 40-60KG DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-cooling-fitted-rt-10s25tss001-routine-ca-mau-p277327114.html?spid=277327145</t>
+          <t>https://tiki.vn/ao-chong-nang-mem-mat-tu-40-60kg-danh-cho-nu-p278026067.html?spid=278026069</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>379000</v>
+        <v>110000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-379000</v>
+        <v>-110000</v>
       </c>
       <c r="I62" t="n">
         <v>-100</v>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -5667,43 +5667,43 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>279259355</t>
+          <t>109570000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Áo Thun Nam Tay Ngắn Cotton Trơn Form Form Fitted - ROUTINE 10F25TSS028</t>
+          <t>Combo 3 Quần Lót Cotton Lụa Plus Size Miley Lingerie Nature Wind FCP_11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-tay-ngan-cotton-tron-form-form-fitted-routine-10f25tss028-p279259355.html?spid=279259375</t>
+          <t>https://tiki.vn/combo-3-quan-lot-cotton-lua-phoi-ren-plus-size-miley-lingerie-nature-wind-fcp_11-p109570000.html?spid=109570010</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>Miley Lingerie</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>329000</v>
+        <v>135000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-329000</v>
+        <v>-135000</v>
       </c>
       <c r="I63" t="n">
         <v>-100</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -5715,16 +5715,16 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>-0</v>
+        <v>-4.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -5751,43 +5751,43 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>278872770</t>
+          <t>140429170</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam in ngực Form Loose - ROUTINE 10F25TSS035</t>
+          <t>Bao tay chơi game găng tay 2 ngón cảm ứng điện thoại gamemobile BT01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-in-nguc-form-loose-routine-10f25tss035-p278872770.html?spid=278872778</t>
+          <t>https://tiki.vn/bao-tay-choi-game-gang-tay-2-ngon-cam-ung-dien-thoai-gamemobile-bt01-p140429170.html?spid=198934954</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>449000</v>
+        <v>19999</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-449000</v>
+        <v>-19999</v>
       </c>
       <c r="I64" t="n">
         <v>-100</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -5835,43 +5835,43 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>277826908</t>
+          <t>278366795</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam S.Café sọc tay Form Loose - RT 10S25TSS007 | ROUTINE CÀ MAU</t>
+          <t>Khung nắn chỉnh cột sống hỗ trợ điều trị đau lưng mỏi lưng</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-s-cafe-soc-tay-form-loose-rt-10s25tss007-routine-ca-mau-p277826908.html?spid=277826918</t>
+          <t>https://tiki.vn/kinh-p278366795.html?spid=278786317</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>549000</v>
+        <v>91000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-549000</v>
+        <v>-91000</v>
       </c>
       <c r="I65" t="n">
         <v>-100</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -5919,37 +5919,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>279259255</t>
+          <t>278064718</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Áo Thun Nam Tay Ngắn Cotton Nhãn Trang Trí Cổ Tròn - ROUTINE 10F25TSS021</t>
+          <t>KHẨU TRANG COTTON KHÁNG KHUẨN CHÓNG TIA UV DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-tay-ngan-cotton-nhan-trang-tri-co-tron-routine-10f25tss021-p279259255.html?spid=279288440</t>
+          <t>https://tiki.vn/khau-trang-cotton-khang-khuan-chong-tia-uv-danh-cho-nu-p278064718.html?spid=278064724</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>379000</v>
+        <v>34000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-379000</v>
+        <v>-34000</v>
       </c>
       <c r="I66" t="n">
         <v>-100</v>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -6003,43 +6003,43 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>279211601</t>
+          <t>278028606</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam vải mỏng hình in Form Boxy - ROUTINE 10F25TSS016</t>
+          <t>KHẨU TRANG UV LOẠI 1 CHỐNG TIA UV</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-vai-mong-hinh-in-form-boxy-routine-10f25tss016-p279211601.html?spid=279211603</t>
+          <t>https://tiki.vn/khau-trang-uv-loai-1-chong-tia-uv-p278028606.html?spid=278028610</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>379000</v>
+        <v>60000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-379000</v>
+        <v>-60000</v>
       </c>
       <c r="I67" t="n">
         <v>-100</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -6087,43 +6087,43 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>278944658</t>
+          <t>272623225</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam phối rib hình in .Fitted - ROUTINE 10F25TSS046</t>
+          <t>Bộ 5 đôi tất bàn chân nam Co dãn 4 chiều(free size) Hàn Quốc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-phoi-rib-hinh-in-fitted-routine-10f25tss046-p278944658.html?spid=278944668</t>
+          <t>https://tiki.vn/bo-5-doi-tat-ban-chan-nam-co-dan-4-chieu-free-size-han-quoc-p272623225.html?spid=272623249</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>399000</v>
+        <v>42000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-399000</v>
+        <v>-42000</v>
       </c>
       <c r="I68" t="n">
         <v>-100</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -6135,16 +6135,16 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -6171,43 +6171,43 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>275233185</t>
+          <t>278945498</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Áo Thun ROUTINE Tay Ngắn Dệt Jacquard Phối Nhãn Form Loose - 10S24TSS014 | LASTORE MENSWEAR</t>
+          <t>SET 5 ĐÔI TẤT VỚ NỮ CAO CỔ MÃ 17 DÀNH CHO NỮ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-routine-tay-ngan-det-jacquard-phoi-nhan-form-loose-10s24tss014-lastore-menswear-p275233185.html?spid=275233197</t>
+          <t>https://tiki.vn/set-5-doi-tat-vo-nu-cao-co-ma-17-danh-cho-nu-p278945498.html?spid=278945500</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>399000</v>
+        <v>100000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-399000</v>
+        <v>-100000</v>
       </c>
       <c r="I69" t="n">
         <v>-100</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -6255,1596 +6255,168 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>279438121</t>
+          <t>277541813</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Áo thun nam hình in Form Regular - ROUTINE 10S26TSS031</t>
+          <t>Găng Tay Chống Nắng Dài Vừa Phải, Chống Trượt Thời Trang Mùa Hè, Đàn Hồi - HÀNG CHÍNH HÃNG MINIIN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-hinh-in-form-regular-routine-10s26tss031-p279438121.html?spid=279438129</t>
+          <t>https://tiki.vn/gang-tay-chong-nang-dai-vua-phai-chong-truot-thoi-trang-mua-he-dan-hoi-hang-chinh-hang-miniin-p277541813.html?spid=277541821</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>MINIIN</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>549000</v>
+        <v>49000</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="H70" t="n">
-        <v>-549000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>-245000</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P70" t="n">
-        <v>-0</v>
+        <v>5</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Bán thêm -5 sản phẩm | Rating 0.0→5.0 (+5.00) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>279289478</t>
+          <t>271307623</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Áo thun tay ngắn nam phối patch trang trí Form Loose -  ROUTINE 10F25TSS023</t>
+          <t>Dép tổ ong asia cao cấp mới, siêu nhẹ, cực bền, chống trơn và rất thời trang (38-44)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-phoi-patch-trang-tri-form-loose-routine-10f25tss023-p279289478.html?spid=279289486</t>
+          <t>https://tiki.vn/dep-to-ong-asia-cao-cap-moi-sieu-nhe-cuc-ben-chong-tron-va-rat-thoi-trang-38-44-p271307623.html?spid=271307629</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Routine</t>
+          <t>ASIA</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>449000</v>
+        <v>80000</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="H71" t="n">
-        <v>-449000</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>-4320000</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P71" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>279198805</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Áo thun tay ngắn nam. Fitted - ROUTINE 10F25TSS037</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-fitted-routine-10f25tss037-p279198805.html?spid=279198823</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>349000</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-349000</v>
-      </c>
-      <c r="I72" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>279155321</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Áo Thun Nam Tay Ngắn Cotton Hình In Sau Form Boxy - ROUTINE 10F25TSS017</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-nam-tay-ngan-cotton-hinh-in-sau-form-boxy-routine-10f25tss017-p279155321.html?spid=279155337</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>379000</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-379000</v>
-      </c>
-      <c r="I73" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>279153927</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Áo thun tay ngắn nam hình thêu Form Regular - ROUTINE 10F25TSS009</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-hinh-theu-form-regular-routine-10f25tss009-p279153927.html?spid=279153947</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>449000</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-449000</v>
-      </c>
-      <c r="I74" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>278105191</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Áo thun nam tay ngắn sọc ngang lớn jacquard Form loose - ROUTINE 10S25TSS050</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-nam-tay-ngan-soc-ngang-lon-jacquard-form-loose-rt-10s25tss050-routine-ca-mau-p278105191.html?spid=279519225</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>689000</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-689000</v>
-      </c>
-      <c r="I75" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>275030945</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Áo Thun Nam ROUTINE Tay Ngắn Cotton Polyester In Hình Form Loose - 10S24TSS002 | LASTORE MENSWEAR</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-nam-routine-tay-ngan-cotton-polyester-in-hinh-form-loose-10s24tss002-lastore-menswear-p275030945.html?spid=275030951</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>449000</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-449000</v>
-      </c>
-      <c r="I76" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>279359972</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Áo thun tay ngắn nam patch trang trí Form Regular - ROUTINE 10S26TSS029</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-patch-trang-tri-form-regular-routine-10s26tss029-p279359972.html?spid=279359980</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>399000</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-399000</v>
-      </c>
-      <c r="I77" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>279347340</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Áo thun tay ngắn nam hình in Form Regular - ROUTINE 10S26TSS032</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-hinh-in-form-regular-routine-10s26tss032-p279347340.html?spid=279347342</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>379000</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-379000</v>
-      </c>
-      <c r="I78" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>279340303</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Áo thun tay ngắn nam hình in Form Regular - ROUITINE 10S26TSS030</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-hinh-in-form-regular-rouitine-10s26tss030-p279340303.html?spid=279340317</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>399000</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-399000</v>
-      </c>
-      <c r="I79" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>279289499</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Áo Thun Nam Gắn Miếng Patch Form Boxy - ROUTINE 10F25TSS054</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-nam-gan-mieng-patch-form-boxy-routine-10f25tss054-p279289499.html?spid=279289501</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>379000</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-379000</v>
-      </c>
-      <c r="I80" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>279438146</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Áo thun nam giá tốt basic trơn tay ngắn vải mềm mát Form Fitted - ROUTINE 10F24TSS001C</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-nam-gia-tot-basic-tron-tay-ngan-vai-mem-mat-form-fitted-routine-10f24tss001c-p279438146.html?spid=279438160</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>169000</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-169000</v>
-      </c>
-      <c r="I81" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>277591179</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Găng Tay Chống Nắng UPF 50+ Cho Nữ - Chống Tia UV, Chống Trượt, Dành Cho Lái Xe Máy - HÀNG CHÍNH HÃNG MINIIN</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/gang-tay-chong-nang-upf-50-cho-nu-chong-tia-uv-chong-truot-danh-cho-lai-xe-may-hang-chinh-hang-miniin-p277591179.html?spid=277591187</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>MINIIN</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>69000</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-69000</v>
-      </c>
-      <c r="I82" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>4</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>2</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>277327053</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Áo thun tay ngắn nam. Loose - RT 10S25TSS013 | ROUTINE CÀ MAU</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-nam-loose-rt-10s25tss013-routine-ca-mau-p277327053.html?spid=277327071</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>379000</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-379000</v>
-      </c>
-      <c r="I83" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>276799709</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Áo thun tay ngắn có in form Loose - ROUTINE 10F24TSSU054 | ROUTINE CÀ MAU</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-tay-ngan-co-in-form-loose-routine-10f24tssu054-routine-ca-mau-p276799709.html?spid=277228117</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>349000</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-349000</v>
-      </c>
-      <c r="I84" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>275738233</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>TẤT / VỚ LƯỜI / HÀI TRƠN LOGO ROUTINE nhiều màu UNISEX FREESIZE - 10S22SOC003 | LASTORE MENSWEAR</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/tat-vo-luoi-hai-tron-logo-routine-nhieu-mau-unisex-freesize-10s22soc003-lastore-menswear-p275738233.html?spid=275738251</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Routine</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-25000</v>
-      </c>
-      <c r="I85" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J85" t="n">
-        <v>7</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>5</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>5</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>198918912</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Khăn lau kính Nano chống bám hơi nước, chống mờ sương, sạch bụi bẩn và dấu vân tay, Công nghệ Nhật Bản - Hộp 100 Miếng</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/khan-lau-kinh-nano-chong-bam-hoi-nuoc-chong-mo-suong-sach-bui-ban-va-dau-van-tay-cong-nghe-nhat-ban-hop-100-mieng-p198918912.html?spid=198918913</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>70000</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-70000</v>
-      </c>
-      <c r="I86" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J86" t="n">
-        <v>468</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>42</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>249724356</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Quần Jean nam cao cấp ống đứng kazata màu xanh đậm vải xuất khẩu xướt nhẹ dáng slimfit vải co giãn</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/quan-jean-nam-cao-cap-ong-dung-le511-mau-xanh-dam-vai-xuat-khau-xuot-nhe-dang-slimfit-vai-co-gian-p249724356.html?spid=249724368</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>410000</v>
-      </c>
-      <c r="G87" t="n">
-        <v>410000</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>7</v>
-      </c>
-      <c r="K87" t="n">
-        <v>6</v>
-      </c>
-      <c r="L87" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M87" t="n">
-        <v>-410000</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Bán thêm -1 sản phẩm</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>275255891</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Quần Jean nam cao cấp ống đứng kazata màu xanh đen trơn vải co giãn xuất khẩu dáng slimfit</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/quan-jean-nam-cao-cap-ong-dung-le511-mau-xanh-den-tron-vai-co-gian-xuat-khau-dang-slimfit-p275255891.html?spid=275255903</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>410000</v>
-      </c>
-      <c r="G88" t="n">
-        <v>410000</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="n">
-        <v>8</v>
-      </c>
-      <c r="K88" t="n">
-        <v>7</v>
-      </c>
-      <c r="L88" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M88" t="n">
-        <v>-410000</v>
-      </c>
-      <c r="N88" t="n">
-        <v>5</v>
-      </c>
-      <c r="O88" t="n">
-        <v>5</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>1</v>
-      </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Bán thêm -1 sản phẩm</t>
+          <t>Bán thêm -54 sản phẩm | Review thêm +1</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7995643</t>
+          <t>15784024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Giày Converse Chuck Taylor All Star Classic Low Top - 121178</t>
+          <t>Áo Khoác Nam Áo Khoác Dù Dày Nam Trơn  Cao Cấp ShopN6 - AD34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-classic-low-top-121178-p7995643.html?spid=20289798</t>
+          <t>https://tiki.vn/ao-khoac-nam-ao-khoac-du-day-nam-tron-lot-caro-cao-cap-shopn6-ad34-p15784024.html?spid=15784043</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1305000</v>
+        <v>199000</v>
       </c>
       <c r="H2" t="n">
-        <v>1305000</v>
+        <v>199000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,13 +582,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>121</v>
+        <v>2664</v>
       </c>
       <c r="L2" t="n">
-        <v>121</v>
+        <v>2664</v>
       </c>
       <c r="M2" t="n">
-        <v>157905000</v>
+        <v>530136000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -603,14 +603,14 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>26</v>
+        <v>539</v>
       </c>
       <c r="S2" t="n">
-        <v>26</v>
+        <v>539</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,37 +627,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>112357404</t>
+          <t>8068749</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mũ Lưỡi Trai Kaki Nam Nữ US ARMY U833, Kiểu Dáng Nón Beret 2 Lớp Thời Trang Cao Cấp- HÀNG CHÍNH HÃNG</t>
+          <t>Áo Khoác Nữ Xỏ Ngón Comfort Phúc An 4034 Màu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mu-luoi-trai-kaki-nam-nu-us-army-u833-kieu-dang-non-beret-2-lop-thoi-trang-cao-cap-hang-chinh-hang-p112357404.html?spid=176728301</t>
+          <t>https://tiki.vn/ao-khoac-nu-xo-ngon-comfort-phuc-an-4034-p8068749.html?spid=8068761</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>Phúc An Fashion</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>129000</v>
+        <v>180000</v>
       </c>
       <c r="H3" t="n">
-        <v>129000</v>
+        <v>180000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>483</v>
+        <v>328</v>
       </c>
       <c r="L3" t="n">
-        <v>483</v>
+        <v>328</v>
       </c>
       <c r="M3" t="n">
-        <v>62307000</v>
+        <v>59040000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="S3" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,37 +711,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>109776986</t>
+          <t>145289760</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thắt Lưng Vải Nam Phong Cách Lính U669 Mặt Khóa Hợp Kim Thép Không Ghỉ Sáng Bóng-Hàng chính hãng</t>
+          <t>Chân Váy Công Sở New Design Thiết Kế Dáng Váy chữ A, Dài Qua Gối ,Phối Nút, Phom Chuẩn Tôn Dáng Sang Trọng Vải Tốt co Giãn, Màu Đen CV0066</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-vai-nam-phong-cach-linh-u669-mat-khoa-hop-kim-thep-khong-ghi-sang-bong-hang-chinh-hang-p109776986.html?spid=174217854</t>
+          <t>https://tiki.vn/chan-vay-cong-so-dai-chu-a-lung-cao-chan-vay-dai-qua-goi-dang-xoe-midi-mau-den-dep-hang-thiet-ke-cao-cap-vannvannhshop-p145289760.html?spid=145289803</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>95000</v>
+        <v>333000</v>
       </c>
       <c r="H4" t="n">
-        <v>95000</v>
+        <v>333000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,35 +750,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>232</v>
+        <v>91</v>
       </c>
       <c r="L4" t="n">
-        <v>232</v>
+        <v>91</v>
       </c>
       <c r="M4" t="n">
-        <v>22040000</v>
+        <v>30303000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="S4" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,37 +795,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>58614590</t>
+          <t>66803444</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Giày Converse Chuck Taylor All Star 1970S Signature Hi Top 167696C</t>
+          <t>Áo Cardigan Nữ Họa Tiết Xinh Thời Trang Korea ALN037 MayHomes Mẫu Mới Mùa Xuân</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-1970s-signature-hi-top-167696c-p58614590.html?spid=62757883</t>
+          <t>https://tiki.vn/ao-cardigan-nu-hoa-tiet-xinh-thoi-trang-korea-aln037-mayhomes-mau-moi-mua-xuan-p66803444.html?spid=70383594</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>MAYHOMES</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1800000</v>
+        <v>149000</v>
       </c>
       <c r="H5" t="n">
-        <v>1800000</v>
+        <v>149000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -834,35 +834,35 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>172</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>172</v>
       </c>
       <c r="M5" t="n">
-        <v>12600000</v>
+        <v>25628000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -879,17 +879,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>274046223</t>
+          <t>186434946</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Giày thể thao nam / nữ phong cách mới – G1004A</t>
+          <t>Túi than hoạt tính khử mùi giày - 100% từ gáo dừa Bến Tre (Hộp 2 túi) - Hapaku</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-nam-nu-phong-cach-moi-g1004a-p274046223.html?spid=212960112</t>
+          <t>https://tiki.vn/tui-than-hoat-tinh-khu-mui-giay-100-tu-gao-dua-ben-tre-hop-2-tui-hapaku-p186434946.html?spid=29882855</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bee Gee</t>
+          <t>Hapaku</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>420000</v>
+        <v>129000</v>
       </c>
       <c r="H6" t="n">
-        <v>420000</v>
+        <v>129000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -918,35 +918,35 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="M6" t="n">
-        <v>11340000</v>
+        <v>22188000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -963,22 +963,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>197062475</t>
+          <t>14837830</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Áo khoác măng tô nam cổ đứng dáng ngắn khóa kéo chất vải kaki đẹp NMT34</t>
+          <t>Áo Sơ Mi Sọc Janet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-mang-to-nam-co-dung-dang-ngan-khoa-keo-chat-vai-kaki-dep-nmt34-p197062475.html?spid=197062507</t>
+          <t>https://tiki.vn/ao-so-mi-soc-janet-p14837830.html?spid=14837836</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -990,10 +990,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>936000</v>
+        <v>117000</v>
       </c>
       <c r="H7" t="n">
-        <v>936000</v>
+        <v>117000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1002,35 +1002,35 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="M7" t="n">
-        <v>6552000</v>
+        <v>14859000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,106 +1047,106 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>249723132</t>
+          <t>125244664</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quần Jean nam cao cấp ống đứng kazata màu xanh trung vải xuất khẩu xướt nhẹ dáng slimfit vải co giãn</t>
+          <t>Giày Nam, Giày Lười Da Bò Cao Cấp SUNPOLO SUMU05 (Đen, Nâu)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-jean-nam-cao-cap-ong-dung-le511-mau-xanh-trung-vai-xuat-khau-xuot-nhe-dang-slimfit-vai-co-gian-p249723132.html?spid=249723138</t>
+          <t>https://tiki.vn/giay-nam-giay-luoi-da-bo-cao-cap-sunpolo-sumu05-den-nau-p125244664.html?spid=125244674</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>SUNPOLO</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>410000</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>410000</v>
+        <v>1265000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1265000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>5330000</v>
+        <v>12650000</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Bán thêm +13 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13307720</t>
+          <t>34561282</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combo 10 Quần lót nam, sịp chéo nam xuất Nhật thời trang cao cấp</t>
+          <t>Chân Váy Xếp Ly Kèm Belt Nana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nam-sip-cheo-nam-xuat-nhat-thoi-trang-cao-cap-p13307720.html?spid=278703711</t>
+          <t>https://tiki.vn/chan-vay-xep-ly-kem-belt-nana-p34561282.html?spid=34561296</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1158,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>319200</v>
+        <v>138000</v>
       </c>
       <c r="H9" t="n">
-        <v>319200</v>
+        <v>138000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1170,35 +1170,35 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="M9" t="n">
-        <v>2553600</v>
+        <v>8280000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1215,17 +1215,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>174593731</t>
+          <t>173991837</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quần Short NamThể Thao Thanh Lịch US ARMY 8898 Trẻ Trung, Năng Động, Nam Tính -HÀNG CHÍNH HÃNG</t>
+          <t>Quần Jean nam Leman xanh trơn JD02 - Slim Form</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-short-namthe-thao-thanh-lich-us-army-8898-tre-trung-nang-dong-nam-tinh-hang-chinh-hang-p174593731.html?spid=177619669</t>
+          <t>https://tiki.vn/quan-jean-nam-leman-xanh-tron-jd02-slim-form-p173991837.html?spid=173991849</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1235,86 +1235,86 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>Leman</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>150000</v>
+        <v>549000</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>549000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>750000</v>
+        <v>5490000</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>4.8</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Bán thêm +5 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>175413577</t>
+          <t>270474726</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHÂN VÁY CHỮ A SẺ TÀ JENY</t>
+          <t>Bộ đồ bơi nam ngắn tay + quần boxer 2 lớp, họa tiết mạnh mẽ, set quần áo đi biển, đi bơi cho nam giới, chất thun bơi dày dặn mịn mát đẹp | BN031</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/chan-vay-chu-a-se-ta-jeny-p175413577.html?spid=175413579</t>
+          <t>https://tiki.vn/bo-do-boi-nam-ngan-tay-quan-boxer-2-lop-hoa-tiet-manh-me-set-quan-ao-di-bien-di-boi-cho-nam-gioi-chat-thun-boi-day-dan-min-mat-dep-bn031-p270474726.html?spid=275928740</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>139000</v>
+        <v>420000</v>
       </c>
       <c r="H11" t="n">
-        <v>139000</v>
+        <v>420000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1338,35 +1338,35 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3780000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="M11" t="n">
-        <v>695000</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1383,17 +1383,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>275949789</t>
+          <t>16654680</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hộp 10 Miếng Dán Ngực Silicon Siêu Mềm Dùng Được Nhiều Lần - Hàng Loại 1 - Chính Hãng - Túi 10 Miếng</t>
+          <t xml:space="preserve">combo 10 quần lót nữ không đường may </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mieng-dan-nguc-silicon-hinh-hoa-sieu-chac-chan-tien-loi-cho-phai-dep-hang-chinh-hang-p275949789.html?spid=275949791</t>
+          <t>https://tiki.vn/combo-10-quan-lot-nu-khong-duong-may-p16654680.html?spid=16991351</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1403,81 +1403,81 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LuckyJQR</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>100000</v>
+        <v>234000</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>234000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>100000</v>
+        <v>1872000</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>73163978</t>
+          <t>127341900</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hộp miếng dán ngực Silicon màu xanh 5 đôi</t>
+          <t>Áo lót lovely có gọng đệm mỏng thêu hoa nổi xuất nhật</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-mieng-dan-nguc-silicon-mau-xanh-5-doi-p73163978.html?spid=117659470</t>
+          <t>https://tiki.vn/ao-lot-lovely-co-gong-dem-mong-theu-hoa-noi-xuat-nhat-p127341900.html?spid=142061094</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1487,165 +1487,165 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LQ luxury</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41800</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>55000</v>
+        <v>97110</v>
       </c>
       <c r="H13" t="n">
-        <v>13200</v>
+        <v>97110</v>
       </c>
       <c r="I13" t="n">
-        <v>31.58</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1456650</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Giá tăng 13,200đ (+31.6%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>54569520</t>
+          <t>274999556</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
+          <t>Giày thể thao nam - nữ cổ cao đế êm nhẹ, thoáng khí đế cao su đúc, chống trơn trượt hạn chế mòn – BEE GEE - G1012</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
+          <t>https://tiki.vn/giay-the-thao-nam-nu-de-em-nhe-thoang-khi-de-cao-su-duc-chong-tron-truot-han-che-mon-bee-gee-g1012-p274999556.html?spid=274999582</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Bee Gee</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>68640</v>
+        <v>450000</v>
       </c>
       <c r="H14" t="n">
-        <v>-19360</v>
+        <v>450000</v>
       </c>
       <c r="I14" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1350000</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Giá giảm 19,360đ (22.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>56346167</t>
+          <t>83190598</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Áo lót nữ ren dày</t>
+          <t>Áo sơ mi nữ công sở Haint Boutique thiết kế kẻ sọc tay dài SM43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ren-day-p56346167.html?spid=61933225</t>
+          <t>https://tiki.vn/ao-so-mi-nu-cong-so-haint-boutique-thiet-ke-ke-soc-tay-dai-sm43-p83190598.html?spid=83190600</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1655,81 +1655,81 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Haint Boutique</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>151200</v>
+        <v>279000</v>
       </c>
       <c r="H15" t="n">
-        <v>-28800</v>
+        <v>279000</v>
       </c>
       <c r="I15" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1116000</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Giá giảm 28,800đ (16.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>74421501</t>
+          <t>189527267</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
+          <t>Áo sơ mi nữ tay dài form rộng phong cách trẻ trung hàn quốc vải lụa mềm mịn mát -MURD04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
+          <t>https://tiki.vn/ao-so-mi-nu-tay-dai-form-rong-phong-cach-tre-trung-han-quoc-vai-lua-mem-min-mat-murd04-p189527267.html?spid=189527326</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1743,77 +1743,77 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>123200</v>
+        <v>125000</v>
       </c>
       <c r="H16" t="n">
-        <v>-36800</v>
+        <v>125000</v>
       </c>
       <c r="I16" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>875000</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Giá giảm 36,800đ (23.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>59462352</t>
+          <t>43842370</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Áo ngực mỏng thêu hoa cài trước có gọng</t>
+          <t>Áo len tăm nữ cổ tim Haint Boutique al72</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-mong-theu-hoa-cai-truoc-co-gong-p59462352.html?spid=59462384</t>
+          <t>https://tiki.vn/ao-len-tam-nu-co-tim-haint-boutique-al72-p43842370.html?spid=56459190</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1823,86 +1823,86 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Haint Boutique</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>75600</v>
+        <v>199000</v>
       </c>
       <c r="H17" t="n">
-        <v>-14400</v>
+        <v>199000</v>
       </c>
       <c r="I17" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>204</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>796000</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá giảm 14,400đ (16.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7078807</t>
+          <t>102939605</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
+          <t>áo lót ko gọng cúp B dành cho vòng ngực khủng</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858717</t>
+          <t>https://tiki.vn/ao-lot-ko-gong-cup-b-danh-cho-vong-nguc-khung-p102939605.html?spid=201243133</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1911,161 +1911,161 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>420000</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>327600</v>
+        <v>111000</v>
       </c>
       <c r="H18" t="n">
-        <v>-92400</v>
+        <v>111000</v>
       </c>
       <c r="I18" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>777000</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá giảm 92,400đ (22.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7997300</t>
+          <t>108030384</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Giày Converse Chuck Taylor All Star 1970s Hi Top - 162050V</t>
+          <t>Áo sơ mi nữ dáng suông dài mặc giấu quần phong cách Sm165</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-1970s-hi-top-162050v-p7997300.html?spid=13727356</t>
+          <t>https://tiki.vn/ao-so-mi-nu-dang-suong-dai-mac-giau-quan-phong-cach-sm165-p108030384.html?spid=108030411</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Haint Boutique</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1800000</v>
+        <v>238800</v>
       </c>
       <c r="H19" t="n">
-        <v>-200000</v>
+        <v>238800</v>
       </c>
       <c r="I19" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>716400</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá giảm 200,000đ (10.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>73862702</t>
+          <t>275207650</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
+          <t>Áo Thun Nữ Tập Gym - Yoga Mát Rượi Thấm Hút Mồ Hôi Tốt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862720</t>
+          <t>https://tiki.vn/ao-thun-nu-tap-gym-yoga-mat-ruoi-tham-hut-mo-hoi-tot-p275207650.html?spid=275207684</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2079,376 +2079,376 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>173000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>133210</v>
+        <v>109000</v>
       </c>
       <c r="H20" t="n">
-        <v>-39790</v>
+        <v>109000</v>
       </c>
       <c r="I20" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>436000</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Giá giảm 39,790đ (23.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>74820156</t>
+          <t>277388268</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG REN 3 MÓC BIG SIZE 395</t>
+          <t>Chai xịt tạo bọt vệ sinh giày White Shoes Cleaner 330ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-ren-3-moc-big-size-395-p74820156.html?spid=74820178</t>
+          <t>https://tiki.vn/chai-xit-tao-bot-ve-sinh-giay-white-shoes-cleaner-330ml-p277388268.html?spid=277388269</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>malizia</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>99560</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>131000</v>
+        <v>85000</v>
       </c>
       <c r="H21" t="n">
-        <v>31440</v>
+        <v>85000</v>
       </c>
       <c r="I21" t="n">
-        <v>31.58</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>425000</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Giá tăng 31,440đ (+31.6%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>192290689</t>
+          <t>277740239</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Giày Vans Authentic SF Abalone VN0A5HYPAXQ</t>
+          <t>Áo thun Nữ 100% Cotton Sure, Thoáng Mát, Mềm Mại, Thấm Hút Cao, Kháng khuẩn, Sản Phẩm Phù hợp với mùa hè nắng nóng</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-vans-authentic-sf-abalone-vn0a5hypaxq-p192290689.html?spid=192290695</t>
+          <t>https://tiki.vn/ao-thun-nu-100-cotton-sure-thoang-mat-mem-mai-tham-hut-cao-khang-khuan-san-pham-phu-hop-voi-mua-he-nang-nong-p277740239.html?spid=277740251</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t xml:space="preserve">	SURE FASHION S</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1550000</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1395000</v>
+        <v>299000</v>
       </c>
       <c r="H22" t="n">
-        <v>-155000</v>
+        <v>299000</v>
       </c>
       <c r="I22" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>299000</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Giá giảm 155,000đ (10.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7995370</t>
+          <t>276493893</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Giày Converse Chuck Taylor All Star Classic Hi Top - 121186</t>
+          <t>Set Váy Ngủ Dây Nơ V1 Cosplay Bikini 1 Mảnh Sexy Gợi Cảm Độc Lạ Freebra</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-classic-hi-top-121186-p7995370.html?spid=20315038</t>
+          <t>https://tiki.vn/set-vay-ngu-day-no-v1-cosplay-bikini-1-manh-sexy-goi-cam-doc-la-freebra-p276493893.html?spid=276493897</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1550000</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1395000</v>
+        <v>148000</v>
       </c>
       <c r="H23" t="n">
-        <v>-155000</v>
+        <v>148000</v>
       </c>
       <c r="I23" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>296000</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Giá giảm 155,000đ (10.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>160910643</t>
+          <t>168312029</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Áo thun TMAG - BASIC TEE - Hàng Chính Hãng</t>
+          <t>Áo Lót Nâng Ngực Nữ Ren Có Gọng LUPERI LP87M Thiết Kế Đệm Siêu Mỏng Mát Cho Người Ngực To Bản 2 Móc Trẻ Trung</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tmag-basic-tee-hang-chinh-hang-p160910643.html?spid=160910651</t>
+          <t>https://tiki.vn/ao-lot-nang-nguc-nu-ren-co-gong-luperi-lp87-thiet-ke-dem-sieu-mong-mat-cho-nguoi-nguc-to-ban-2-moc-tre-trung-p168312029.html?spid=168312051</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>LUPERI</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>290000</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>235000</v>
       </c>
       <c r="H24" t="n">
-        <v>-290000</v>
+        <v>235000</v>
       </c>
       <c r="I24" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>235000</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2458,118 +2458,118 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>262054269</t>
+          <t>275631855</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quần bơi nam cao cấp, dáng lửng ngang gối, mẫu đa màu lập thể cá tính, thun bơi lạnh dày mát mịn co giãn cực tốt | BN050</t>
+          <t>Thắt lưng nam da bò nguyên chất mặt khóa tự động hợp kim cao cấp</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-boi-nam-cao-cap-dang-lung-ngang-goi-mau-da-mau-lap-the-ca-tinh-thun-boi-lanh-day-mat-min-co-gian-cuc-tot-bn050-p262054269.html?spid=262054275</t>
+          <t>https://tiki.vn/that-lung-nam-da-bo-nguyen-chat-mat-khoa-tu-dong-hop-kim-cao-cap-p275631855.html?spid=275631857</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>ANANSHOP688</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>210000</v>
+        <v>199000</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="H25" t="n">
-        <v>-210000</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P25" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>278150177</t>
+          <t>275875315</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Combo Mix 3 Quần Lót Nữ Cao Cấp Nhiều Mẫu Xinh Xắn Tặng Kèm Nước Hoa Chiết 10ml Chính Hãng</t>
+          <t>QL4343 Quần lót lọt khe ren sexy cao cấp - Quần lót nữ - Quần chip nữ - Quần lọt khe - Đồ lót nữ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-mix-3-quan-lot-nu-cao-cap-nhieu-mau-xinh-xan-tang-kem-nuoc-hoa-chiet-10ml-chinh-hang-p278150177.html?spid=278150237</t>
+          <t>https://tiki.vn/quan-lot-lot-khe-ren-sexy-cao-cap-bt4343-quan-lot-nu-quan-chip-nu-quan-lot-khe-do-lot-nu-p275875315.html?spid=275875319</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2579,32 +2579,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sanny House</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="H26" t="n">
-        <v>-150000</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2626,81 +2626,81 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Bán thêm +4 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7995403</t>
+          <t>175830875</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Giày Converse Chuck Taylor All Star Classic Hi Top - 121184</t>
+          <t>Áo sơ mi lụa nữ lụa tay lỡ trắng cổ viền đen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-converse-chuck-taylor-all-star-classic-hi-top-121184-p7995403.html?spid=20342953</t>
+          <t>https://tiki.vn/ao-so-mi-lua-nu-lua-tay-lo-trang-co-vien-den-p175830875.html?spid=175830883</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1550000</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="H27" t="n">
-        <v>-1550000</v>
+        <v>95000</v>
       </c>
       <c r="I27" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2710,144 +2710,144 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>274999556</t>
+          <t>271010374</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Giày thể thao nam - nữ cổ cao đế êm nhẹ, thoáng khí đế cao su đúc, chống trơn trượt hạn chế mòn – BEE GEE - G1012</t>
+          <t>Mũ Vành Chống Nắng Phong Cách Thời Trang Hàn Quốc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-the-thao-nam-nu-de-em-nhe-thoang-khi-de-cao-su-duc-chong-tron-truot-han-che-mon-bee-gee-g1012-p274999556.html?spid=274999582</t>
+          <t>https://tiki.vn/mu-vanh-chong-nang-phong-cach-thoi-trang-han-quoc-p271010374.html?spid=279253627</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bee Gee</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="H28" t="n">
-        <v>-450000</v>
+        <v>66000</v>
       </c>
       <c r="I28" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>125244664</t>
+          <t>161248930</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Giày Nam, Giày Lười Da Bò Cao Cấp SUNPOLO SUMU05 (Đen, Nâu)</t>
+          <t>Đồ bộ nữ,đồ ngủ mặc nhà lửng 9 tấc vải lụa mango cao cấp BL 67 họa tiết hoa nhí siêu cưng size đại 58-67kg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/giay-nam-giay-luoi-da-bo-cao-cap-sunpolo-sumu05-den-nau-p125244664.html?spid=125244674</t>
+          <t>https://tiki.vn/do-bo-nu-do-ngu-mac-nha-lung-9-tac-vai-lua-mango-cao-cap-bl-67-hoa-tiet-hoa-nhi-sieu-cung-size-dai-58-67kg-p161248930.html?spid=161248981</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SUNPOLO</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1265000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="H29" t="n">
-        <v>-1265000</v>
+        <v>165000</v>
       </c>
       <c r="I29" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2859,16 +2859,16 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2878,39 +2878,39 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>160903645</t>
+          <t>163581431</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Áo thun TMAG - HUNTRESS TEE - Hàng Chính Hãng</t>
+          <t>ĐẦM BẦU VÁY BẦU CÔNG SỞ DÁNG DÀI,(phối tay dài vải mỏng không nóng )</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tmag-huntress-tee-hang-chinh-hang-p160903645.html?spid=160903655</t>
+          <t>https://tiki.vn/dam-bau-vay-bau-cong-so-dang-dai-phoi-tay-dai-vai-mong-khong-nong-p163581431.html?spid=163581441</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2919,19 +2919,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>310000</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="H30" t="n">
-        <v>-310000</v>
+        <v>360000</v>
       </c>
       <c r="I30" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2943,16 +2943,16 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2962,60 +2962,60 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>160910035</t>
+          <t>275830809</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Áo thun TMAG - STARLIGHT TEE - Hàng Chính Hãng</t>
+          <t>Đầm Maxi Linen Tuyền DRE173 thời trang thiết kế Hity</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tmag-starlight-tee-hang-chinh-hang-p160910035.html?spid=160910037</t>
+          <t>https://tiki.vn/dam-maxi-linen-tuyen-dre173-thoi-trang-thiet-ke-hity-p275830809.html?spid=275830836</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Hity</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>320000</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2395000</v>
       </c>
       <c r="H31" t="n">
-        <v>-320000</v>
+        <v>2395000</v>
       </c>
       <c r="I31" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3027,16 +3027,16 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3046,39 +3046,39 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>160910698</t>
+          <t>144236336</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Áo thun TMAG - SPACEGIRL TEE - Hàng Chính Hãng</t>
+          <t>COMBO 5 ÁO LÓT VẢI KHÔNG GỌNG KHÔNG MÚT (SIZE 32-42)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-tmag-spacegirl-tee-hang-chinh-hang-p160910698.html?spid=160910700</t>
+          <t>https://tiki.vn/combo-5-ao-lot-vai-khong-gong-khong-mut-size-32-42-p144236336.html?spid=146366320</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3087,22 +3087,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>320000</v>
+        <v>172200</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="H32" t="n">
-        <v>-320000</v>
+        <v>37800</v>
       </c>
       <c r="I32" t="n">
-        <v>-100</v>
+        <v>21.95</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3114,55 +3114,55 @@
         <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P32" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 37,800đ (+22.0%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>279028429</t>
+          <t>277914930</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thảm Ngải Cứu Gối Ngải Cứu Đông Y Hỗ Trợ Giảm Đau Nhức Xương Khớp Giúp Ngủ Ngon Hỗ Trợ Tuần Hoàn Máu</t>
+          <t>Áo Lót Nữ Ren Siêu Dày Nâng Ngực Boya 029HW – 9 Màu Hot, Size 34-38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://tiki.vn/tham-ngai-cuu-goi-ngai-cuu-dong-y-ho-tro-giam-dau-nhuc-xuong-khop-giup-ngu-ngon-ho-tro-tuan-hoan-mau-p279028429.html?spid=279028430</t>
+          <t>https://tiki.vn/ao-lot-nu-ren-sieu-day-nang-nguc-boya-029hw-9-mau-hot-size-34-38-p277914930.html?spid=277914942</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3171,19 +3171,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>369000</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>193000</v>
       </c>
       <c r="H33" t="n">
-        <v>-369000</v>
+        <v>193000</v>
       </c>
       <c r="I33" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3214,99 +3214,4887 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>277362353</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bộ lụa tơ tằm lững cao cấp 65-70kg, phom dáng chuẩn đẹp</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-lua-to-tam-lung-cao-cap-65-70kg-phom-dang-chuan-dep-p277362353.html?spid=277362355</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>165000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>165000</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>276568370</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>QUẦN BƠI NỮ DÀI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-boi-nu-dai-p276568370.html?spid=277619013</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>185000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>185000</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>112851354</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Áo ngực học sinh</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138792</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>31920</v>
+      </c>
+      <c r="G36" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>10080</v>
+      </c>
+      <c r="I36" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="J36" t="n">
+        <v>68</v>
+      </c>
+      <c r="K36" t="n">
+        <v>68</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Giá tăng 10,080đ (+31.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>74820156</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ÁO LÓT NỮ MỎNG REN 3 MÓC BIG SIZE 395</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-lot-nu-mong-ren-3-moc-big-size-395-p74820156.html?spid=74820178</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>131000</v>
+      </c>
+      <c r="G37" t="n">
+        <v>99560</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-31440</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-24</v>
+      </c>
+      <c r="J37" t="n">
+        <v>30</v>
+      </c>
+      <c r="K37" t="n">
+        <v>30</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>8</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Giá giảm 31,440đ (24.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>214706031</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Áo lót áo ngực Thái lan có gọng mút kép nâng ngực tạo khe, áo lót nữ thông hơi hàng CAO CẤP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-lot-ao-nguc-thai-lan-co-gong-mut-kep-nang-nguc-tao-khe-ao-lot-nu-thong-hoi-hang-cao-cap-p214706031.html?spid=215408041</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>103200</v>
+      </c>
+      <c r="G38" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>16800</v>
+      </c>
+      <c r="I38" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Giá tăng 16,800đ (+16.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>103049077</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>151700</v>
+      </c>
+      <c r="G39" t="n">
+        <v>185000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>33300</v>
+      </c>
+      <c r="I39" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="J39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Giá tăng 33,300đ (+22.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>174585329</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Áo lót nâng ngực boya mút mỏng, Áo ngực boya nâng ngực cài sau 522BT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-lot-nang-nguc-boya-mut-mong-ao-nguc-boya-nang-nguc-cai-sau-522bt-p174585329.html?spid=203717976</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>90300</v>
+      </c>
+      <c r="G40" t="n">
+        <v>105000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>14700</v>
+      </c>
+      <c r="I40" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Giá tăng 14,700đ (+16.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16651795</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>️[5 Quần] ComBo 5 Quần Lót Nam THUN LẠNH Lưng Bự Hàng Việt Nam Cao Cấp</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/5-quan-combo-5-quan-lot-nam-thun-lanh-lung-bu-hang-viet-nam-cao-cap-p16651795.html?spid=51148102</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MENLIVE</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>205000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>170150</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-34850</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-17</v>
+      </c>
+      <c r="J41" t="n">
+        <v>9</v>
+      </c>
+      <c r="K41" t="n">
+        <v>9</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>5</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Giá giảm 34,850đ (17.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>133160820</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Quần Lót Su Đúc Nữ (Hàng Loại 1) Không Đường Mai, Thun Lạnh, SIêu Co Dãn, Được Chọn Màu</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-lot-su-duc-nu-hang-loai-1-khong-duong-mai-thun-lanh-sieu-co-dan-duoc-chon-mau-p133160820.html?spid=198901960</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>22960</v>
+      </c>
+      <c r="G42" t="n">
+        <v>28000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5040</v>
+      </c>
+      <c r="I42" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="J42" t="n">
+        <v>39</v>
+      </c>
+      <c r="K42" t="n">
+        <v>39</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>5</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Giá tăng 5,040đ (+22.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>73163978</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hộp miếng dán ngực Silicon màu xanh 5 đôi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/hop-mieng-dan-nguc-silicon-mau-xanh-5-doi-p73163978.html?spid=117659470</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LQ luxury</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>55000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>45650</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-9350</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-17</v>
+      </c>
+      <c r="J43" t="n">
+        <v>18</v>
+      </c>
+      <c r="K43" t="n">
+        <v>18</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>5</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Giá giảm 9,350đ (17.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>155367068</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Đồ Bộ Mặc Nhà Nữ Quần Đùi Chấm Bi Maxivic, La Mộc - MM112108</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-nu-quan-dui-cham-bi-maxivic-la-moc-mm112108-p155367068.html?spid=155367070</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MAXIVIC</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>299000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>299000</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>276472930</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Giày thể thao nam đế êm nhẹ, thoáng khí đế cao su đúc, chống trơn trượt hạn chế mòn  – BEE GEE - GNA1011A</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-the-thao-nam-de-em-nhe-thoang-khi-de-cao-su-duc-chong-tron-truot-han-che-mon-bee-gee-gna1011a-p276472930.html?spid=276472938</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Bee Gee</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>350000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>350000</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>12</v>
+      </c>
+      <c r="K45" t="n">
+        <v>12</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Rating 5.0→4.8 (-0.20) | Review thêm +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>83685744</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEGING QUẤN NÓNG TAN MỠ  </t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/leging-quan-nong-tan-mo-p83685744.html?spid=83685750</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>136000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>136000</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>101084004</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ÁO CỔ TRÒN PEPLUM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-co-tron-peplum-p101084004.html?spid=101084028</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>124000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>124000</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>279100044</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Chai Xịt Khử Mùi Giày Dép 260ML</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/chai-xit-khu-mui-giay-dep-260ml-p279100044.html?spid=279100045</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>59000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>54000</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Giá giảm 5,000đ (8.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>263276302</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Chuck Taylor Classic Black High | Giày Con Vải Màu Đen Cổ Cao M9160C</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/chuck-taylor-classic-black-high-giay-con-vai-mau-den-co-cao-p263276302.html?spid=263276342</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2142561</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Giày Sneaker Nam Zapas Classcial GZ018 - Đen (Size</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-sneaker-nam-zapas-classcial-gz018-den-p2142561.html?spid=2147943</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Zapas</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>219000</v>
+      </c>
+      <c r="H50" t="n">
+        <v>219000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>100973511</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Găng tay xỏ ngón chống nắng Rhino S101, tất tay nam nữ, chống tia UV, chống bụi, Hàng chính hãng</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/gang-tay-xo-ngon-chong-nang-rhino-s101-tat-tay-nam-nu-chong-tia-uv-chong-bui-hang-chinh-hang-p100973511.html?spid=100973519</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Rhino Store</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>7920</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-80</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>934</v>
+      </c>
+      <c r="K51" t="n">
+        <v>934</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>129</v>
+      </c>
+      <c r="R51" t="n">
+        <v>129</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Giá giảm 80đ (1.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>278697497</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Combo Phụ kiện thời trang Đuôi cosplay cáo nhân tạo Cosplay + nơ cổ + kẹp tóc (Halloween / Lễ hội / Trang phục hóa trang)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>https://tiki.vn/combo-phu-kien-thoi-trang-duoi-fox-nhan-tao-cosplay-no-co-kep-toc-halloween-le-hoi-trang-phuc-hoa-trang-p278697497.html?spid=278697540</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Phụ kiện thời trang</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
         <v>350000</v>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-350000</v>
-      </c>
-      <c r="I34" t="n">
+      <c r="H52" t="n">
+        <v>350000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>5</v>
+      </c>
+      <c r="P52" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>180865595</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tất Chân Dài Thể Thao Nữ - Tất co giãn tốt, thoải mái và êm ái - Không bai, không xù, thoáng khí, không mồ hôi chân</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/tat-chan-dai-the-thao-nu-tat-co-gian-tot-thoai-mai-va-em-ai-khong-bai-khong-xu-thoang-khi-khong-mo-hoi-chan-p180865595.html?spid=180865597</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PGM</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H53" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>277544802</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Áo Chống Nắng Nam ,Chất Vải Thun Lạnh, Chống Tia UV, Thoáng Mát, Thấm Hút Mồ Hôi</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-chong-nang-nam-chat-vai-thun-lanh-chong-tia-uv-thoang-mat-tham-hut-mo-hoi-p277544802.html?spid=277544808</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Kun93</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>185000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-185000</v>
+      </c>
+      <c r="I54" t="n">
         <v>-100</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="J54" t="n">
+        <v>13</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
         <v>5</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
         <v>-5</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>276811753</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Áo khoác nam áo gió vải gió cao cấp 2 lớp chống nắng tia UV và chống nước</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-nam-ao-gio-vai-gio-cao-cap-2-lop-chong-nang-tia-uv-va-chong-nuoc-p276811753.html?spid=276811773</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Uniman</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>129000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-129000</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q55" t="n">
         <v>1</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
         <is>
           <t>❌ Đã xóa</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>271395656</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bao Quần Lót Miễn Giặt Tiện Lợi TRAVEL-MATE Nam, 5 Cái/Bao</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bao-quan-lot-tien-loi-travel-mate-nam-5-cai-bao-p271395656.html?spid=271395660</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Travel-Mate</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J56" t="n">
+        <v>79</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>277610005</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Áo Lót 3281 Không Gọng Mút Mỏng Bản 3 Móc Che Khuyết Điểm Đẹp</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-lot-3281-khong-gong-mut-mong-ban-3-moc-che-khuyet-diem-dep-p277610005.html?spid=277610045</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>96000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-96000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>5</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>275631621</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bộ đồ lót thể thao nữ cotton năng động thấm hút tốt - có quần lẻ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-do-lot-the-thao-nu-cotton-nang-dong-tham-hut-tot-co-quan-le-p275631621.html?spid=275631643</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>75000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-75000</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>271875959</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Quần Mặc Trong Váy - Quần Bảo Hộ Khi Mặc Váy - Quần Jobelli 1258</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-mac-trong-vay-quan-bao-ho-khi-mac-vay-quan-jobelli-1258-p271875959.html?spid=271875963</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>59000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-59000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>277207572</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà cao cấp</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-cao-cap-p277207572.html?spid=277207588</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>190000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-190000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>276064209</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Quần lót nữ Jintana Thái cotton thun lạnh lưng cao mẫu trơn đơn giản</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-lot-nu-jintana-thai-cotton-thun-lanh-lung-cao-mau-tron-don-gian-p276064209.html?spid=276064265</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>136250</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-136250</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>165984326</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà cao cấp chất lụa hàn</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-cao-cap-chat-lua-han-p165984326.html?spid=165984336</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>225000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-225000</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>278247784</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Quần Lọt Khe Đúc Su 009 Viền Mỏng Mẫu Trơn Tàng Hình Tiện Lợi</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-lot-khe-duc-su-009-vien-mong-mau-tron-tang-hinh-tien-loi-p278247784.html?spid=278247802</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>277207589</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà cao cấp</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-cao-cap-p277207589.html?spid=277207603</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>195000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-195000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>276909500</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Quần Lót Nữ Ren Hoa Nhiều Mẫu Xinh Xắn Ôm Nửa Mông Sanny House</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-lot-nu-ren-hoa-nhieu-mau-xinh-xan-om-nua-mong-sanny-house-p276909500.html?spid=276909642</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>118500</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-118500</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>276411815</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Bộ ngủ 123 cotton tay dài quần dài nhiều mẫu dễ thương</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-ngu-123-cotton-tay-dai-quan-dai-nhieu-mau-de-thuong-p276411815.html?spid=276411841</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>306250</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-306250</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>276125714</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>[Tặng 2 Khăn Ướt Cồn/Bao] Bao Quần Lót Dùng 1 Lần Nữ TRAVEL-MATE 5 Cai/Bao | Đã Giặt Sạch, An Toàn, Tiện Lợi</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-quan-lot-tien-loi-travel-mate-nu-5-cai-bao-p276125714.html?spid=276125725</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Travel-Mate</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>210000</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-210000</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J67" t="n">
+        <v>112</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>276118600</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>[Tặng 2 Khăn Ướt Cồn/Bao] Bao Quần Đùi Miễn Giặt Body-Mate Nữ | Đã Giặt Sạch, Đóng Gói Tự Động, An Toàn Tiện Lợi | 3 Cái/Bao</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-quan-dui-mien-giat-body-mate-nu-3-cai-bao-p276118600.html?spid=276118611</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>BODY-MATE</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J68" t="n">
+        <v>6</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>275384173</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Móc nối thun phụ kiện cho áo ngực bản nhỏ 2 móc và bản lớn 3 móc</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/moc-noi-thun-phu-kien-cho-ao-nguc-ban-nho-2-moc-va-ban-lon-3-moc-p275384173.html?spid=277570949</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J69" t="n">
+        <v>10</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>253060005</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà mẫu lửng vải kate</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-mau-lung-vai-kate-p253060005.html?spid=253060019</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-160000</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>276118344</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>[Tặng 2 Khăn Ướt Cồn/Bao] Combo Bao Quần Lót Sau Sinh BODY-MATE Nữ, 5 Cái/Bao | Đã Giặt Sạch, Tiện Lợi, Thoáng Khí</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-quan-lot-mien-giat-sau-sinh-body-mate-nu-5-cai-bao-p276118344.html?spid=276118349</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>BODY-MATE</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>249000</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-249000</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>207240648</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Quần độn mông và hông cho vòng 3 sexy mã 0846</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-don-mong-va-hong-cho-vong-3-sexy-ma-0846-p207240648.html?spid=207240654</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>110000</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-110000</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>201071504</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà xinh chất thô thoáng mát</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-xinh-chat-tho-thoang-mat-p201071504.html?spid=201071554</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>190000</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-190000</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>277812209</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Quần Lót Nữ Lọt Khe 98075 Không Viền Tàng Hình</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-lot-nu-lot-khe-98075-khong-vien-tang-hinh-p277812209.html?spid=277812225</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>36000</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="I74" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>205846207</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Quần lót nữ ren hoa sexy gợi cảm không viền siêu mịn mã 817</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-lot-nu-ren-hoa-sexy-goi-cam-khong-vien-sieu-min-ma-817-p205846207.html?spid=205846217</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>193370304</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà mẫu lửng. chất kate hàn</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-mau-lung-p193370304.html?spid=193370326</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>170000</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-170000</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>278511177</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Đồ bộ nữ,đồ ngủ mặc nhà lửng 9 tấc tay cánh tiên vải lanh BL 52 họa tiết dễ thương size 51-70kg</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-nu-do-ngu-mac-nha-lung-9-tac-tay-canh-tien-vai-lanh-bl-52-hoa-tiet-de-thuong-size-51-70kg-p278511177.html?spid=278511253</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>274544138</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà xinh</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-xinh-p274544138.html?spid=274544160</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>190000</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-190000</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J78" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>170443484</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà chất lụa hàn</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-chat-lua-han-p170443484.html?spid=170443488</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>212500</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-212500</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>157808804</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà đẹp chất lụa hàn</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-dep-chat-lua-han-p157808804.html?spid=157808821</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>275663168</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Váy ngủ lụa 302 cổ đổ xẻ tà hai dây đơn giản quyến rũ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/vay-ngu-lua-302-co-do-xe-ta-hai-day-don-gian-quyen-ru-p275663168.html?spid=275663178</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>312000</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-312000</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>165984354</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>đồ bộ mặc nhà chất lụa hàn</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/do-bo-mac-nha-chat-lua-han-p165984354.html?spid=165984405</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>225000</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-225000</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J82" t="n">
+        <v>9</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>5</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>204057084</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>XỊT KHỬ MÙI HÔI GIÀY ORHE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/xit-khu-mui-hoi-giay-orhe-p204057084.html?spid=204057088</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ORHE</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J83" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>275958007</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Giầy nam da bò,giày da nam phong cách lịch lãm 20941</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-nam-da-bo-giay-da-nam-phong-cach-lich-lam-20941-p275958007.html?spid=275958054</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>TLG Thành Long</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>262730646</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Chai xịt khử mùi giày, chống hôi chân Ligpro, 160ml, công nghệ kháng khuẩn Nano bạc</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/chai-xit-khu-mui-giay-chong-hoi-chan-ligpro-160ml-cong-nghe-khang-khuan-nano-bac-p262730646.html?spid=262730647</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Ligpro</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>79000</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-79000</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>276008302</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tất cổ cao nam/nữ mẫu chữ đơn giản cotton dày dặn - combo 5 tất tặng kèm hộp</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/tat-co-cao-nam-nu-mau-chu-don-gian-cotton-day-dan-combo-5-tat-tang-kem-hop-p276008302.html?spid=276008306</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Sanny House</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>275958178</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Giầy nam da bò cao cấp sang trọng hàng xuất khẩu 20940</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-nam-da-bo-cao-cap-sang-trong-hang-xuat-khau-20940-p275958178.html?spid=275958204</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>TLG Thành Long</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>132286309</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Bộ Dụng Cụ Đánh Giày 7 Món Có Kèm Sẵn 2 Hộp Xi Tiện Dụng- Đánh Bóng Mới - Hàng Loại 1- Chính Hãng MINIIN</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-dung-cu-danh-giay-7-mon-co-kem-san-2-hop-xi-tien-dung-danh-bong-moi-hang-loai-1-chinh-hang-miniin-p132286309.html?spid=132286315</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>MINIIN</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>99000</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-99000</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J88" t="n">
+        <v>53</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>10</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>275738028</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mặt Khóa Thắt Lưng Nam Cao Cấp,Mặt Thắt Lưng Nam Khóa Tự Động 203848</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/mat-khoa-that-lung-nam-cao-cap-mat-that-lung-nam-khoa-tu-dong-203848-p275738028.html?spid=275738029</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>TLG Thành Long</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>60200</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-60200</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>275738156</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mặt Khóa Thắt Lưng Nam Cao Cấp,Mặt Thắt Lưng Nam Khóa Tự Động 203851</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/mat-khoa-that-lung-nam-cao-cap-mat-that-lung-nam-khoa-tu-dong-203851-p275738156.html?spid=275738157</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>TLG Thành Long</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>61250</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-61250</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J90" t="n">
+        <v>9</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2715053</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Thắt lưng nam vải dù, Dây lưng nam lính mỹ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-vai-du-day-lung-nam-linh-my-p2715053.html?spid=84203111</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Good Day</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>107000</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-107000</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J91" t="n">
+        <v>9</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
         <is>
           <t>Không còn xuất hiện trong danh sách</t>
         </is>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>273867988</t>
+          <t>35087712</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dây Đai Nịt Thắt Lưng Giữ Áo Sơ Mi Thẳng Khi Đóng Thùng Loại Quấn Bụng LeGaXi</t>
+          <t>Quần lót nam thun lạnh không đường may, sịp nam tam giác cao cấp chất liệu thoáng mát, mềm mịn QLW606</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/day-dai-nit-that-lung-giu-ao-so-mi-thang-khi-dong-thung-loai-quan-bung-legaxi-p273867988.html?spid=273867991</t>
+          <t>https://tiki.vn/quan-lot-nam-thun-lanh-su-qlw606-p35087712.html?spid=58417679</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Legaxi</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>44000</v>
+        <v>90000</v>
       </c>
       <c r="H2" t="n">
-        <v>44000</v>
+        <v>90000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>48</v>
+        <v>1774</v>
       </c>
       <c r="L2" t="n">
-        <v>48</v>
+        <v>1774</v>
       </c>
       <c r="M2" t="n">
-        <v>2112000</v>
+        <v>159660000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="P2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>278</v>
+        <v>378</v>
       </c>
       <c r="S2" t="n">
-        <v>278</v>
+        <v>378</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,17 +627,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>99968881</t>
+          <t>111708924</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Set 2 quần đùi nam, quần Short Gió nam thể thao Basic trẻ trung năng động, thoáng mát co giãn 4 chiều MRM Manlywear</t>
+          <t>Combo 6 quần đùi mặc nhà nam cao cấp kate 100% cotton</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-2-qua-n-du-i-nam-qua-n-short-gio-nam-the-thao-basic-tre-trung-nang-do-ng-thoa-ng-ma-t-co-gia-n-4-chie-u-mrm-manlywear-p99968881.html?spid=99968992</t>
+          <t>https://tiki.vn/combo-6-quan-dui-mac-nha-nam-cao-cap-kate-100-cotton-p111708924.html?spid=111708928</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -647,185 +647,185 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>249000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>249000</v>
+        <v>414000</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>414000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2517</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2521</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>996000</v>
+        <v>1656000</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>634</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Bán thêm +4 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>275011470</t>
+          <t>276667776</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mũ đi biển nón rộng vành đội 2 mặt vải kaki chống nắng UV gấp gon thời trang Hàn Quốc dona240501</t>
+          <t>Quần Short Mặc Nhà Nam Davie Dvs01 Chất Liệu Vải Kate 100% Cotton - Giao Màu Ngẫu Nhiên</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mu-di-bien-non-rong-vanh-doi-2-mat-vai-kaki-chong-nang-uv-gap-gon-thoi-trang-han-quoc-dona240501-p275011470.html?spid=275011474</t>
+          <t>https://tiki.vn/quan-short-mac-nha-nam-davie-dvs01-chat-lieu-vai-kate-100-cotton-giao-mau-ngau-nhien-p276667776.html?spid=276667794</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>169000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>169000</v>
+        <v>350000</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>507000</v>
+        <v>1400000</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Bán thêm +3 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>276181618</t>
+          <t>277725831</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tất Gấu Cổ Cao Nữ Họa Tiết Hình Gấu,{TP} Vớ Cổ Cao Nữ Hàn Quốc họa tiết</t>
+          <t>[TD] Áo khoác nam Áo khoát nam gió dù 2 lớp chống nắng cao cấp trơn nhiều màu hợp thời trang - A1006 - ĐEN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/tat-gau-co-cao-nu-hoa-tiet-hinh-gau-tp-vo-co-cao-nu-han-quoc-hoa-tiet-p276181618.html?spid=276181620</t>
+          <t>https://tiki.vn/td-ao-khoac-nam-ao-khoat-nam-gio-du-2-lop-chong-nang-cao-cap-tron-nhieu-mau-hop-thoi-trang-a1006-p277725831.html?spid=277725837</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TP Tiến Phát SMART</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>26490</v>
+        <v>249000</v>
       </c>
       <c r="H5" t="n">
-        <v>26490</v>
+        <v>249000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -834,35 +834,35 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>344370</v>
+        <v>1245000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -879,17 +879,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>276098909</t>
+          <t>278873687</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Khăn Lau Kính Nano Hộp 100 Miếng Khăn Giấy Chống Bám Hơi Nước, Chống Mờ Sương, Mồ Hôi, Chống Nhờn - Hàng Loại 1</t>
+          <t>đèn pin tự vệ hợp kim nhôm nguyên khối kéo dài, siêu sáng bền.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khan-lau-kinh-nano-chong-bam-hoi-nuoc-chong-mo-suong-sach-bui-ban-va-dau-van-tay-cong-nghe-nhat-ban-hop-100-mieng-p276098909.html?spid=276098910</t>
+          <t>https://tiki.vn/den-pin-tu-ve-hop-kim-nhom-nguyen-khoi-keo-dai-sieu-sang-ben-p278873687.html?spid=278873688</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -899,165 +899,165 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LuckyJQR</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>100000</v>
+        <v>350000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>200000</v>
+        <v>1050000</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Bán thêm +2 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>278398901</t>
+          <t>193461694</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COMBO 2 Bộ Phụ Kiện Khóa Dây Giày Không Cần Buộc Thắt Giày Thể Thao Bata Ngoài Trời MÀU ĐEN</t>
+          <t>P34 Váy ngủ bodysuit ren kèm khăn sexy gợi cảm - Đầm ngủ bodysuit ren xuyên thấu quyến rũ - Đồ ngủ nữ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/phu-kien-khoa-day-giay-khong-can-buoc-that-giay-the-thao-bata-ngoai-troi-mau-den-p278398901.html?spid=278398902</t>
+          <t>https://tiki.vn/vay-ngu-bodysuit-ren-kem-khan-sexy-goi-cam-p34-dam-ngu-bodysuit-ren-xuyen-thau-quyen-ru-do-ngu-nu-p193461694.html?spid=193461700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LuckyJQR</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>100000</v>
+        <v>298000</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>298000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>100000</v>
+        <v>894000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Bán thêm +1 sản phẩm</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>279104033</t>
+          <t>169468021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Áo lót nữ form ba lỗ thông hơi trơn big size 1397 – Size XXL–3XL</t>
+          <t>Q17 Váy ngủ lụa hai dây hở lưng sexy  - Đầm ngủ nữ gợi cảm - đồ ngủ nử mặc nhà</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-form-ba-lo-thong-hoi-tron-big-size-1397-size-xxl-3xl-p279104033.html?spid=279104035</t>
+          <t>https://tiki.vn/vay-ngu-lua-hai-day-ho-lung-sexy-bt0033-dam-ngu-nu-goi-cam-do-ngu-nu-mac-nha-p169468021.html?spid=169468029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1067,81 +1067,81 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t xml:space="preserve">	OEM</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>108000</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>84240</v>
+        <v>210000</v>
       </c>
       <c r="H8" t="n">
-        <v>-23760</v>
+        <v>210000</v>
       </c>
       <c r="I8" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>840000</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Giá giảm 23,760đ (22.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>74421501</t>
+          <t>275875315</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
+          <t>QL4343 Quần lót lọt khe ren sexy cao cấp - Quần lót nữ - Quần chip nữ - Quần lọt khe - Đồ lót nữ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
+          <t>https://tiki.vn/quan-lot-lot-khe-ren-sexy-cao-cap-bt4343-quan-lot-nu-quan-chip-nu-quan-lot-khe-do-lot-nu-p275875315.html?spid=275875319</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1155,77 +1155,77 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>123200</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>160000</v>
+        <v>35000</v>
       </c>
       <c r="H9" t="n">
-        <v>36800</v>
+        <v>35000</v>
       </c>
       <c r="I9" t="n">
-        <v>29.87</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Giá tăng 36,800đ (+29.9%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>73862702</t>
+          <t>277740239</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
+          <t>Áo thun Nữ 100% Cotton Sure, Thoáng Mát, Mềm Mại, Thấm Hút Cao, Kháng khuẩn, Sản Phẩm Phù hợp với mùa hè nắng nóng</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862720</t>
+          <t>https://tiki.vn/ao-thun-nu-100-cotton-sure-thoang-mat-mem-mai-tham-hut-cao-khang-khuan-san-pham-phu-hop-voi-mua-he-nang-nong-p277740239.html?spid=277740249</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1235,32 +1235,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t xml:space="preserve">	SURE FASHION S</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>133210</v>
+        <v>299000</v>
       </c>
       <c r="G10" t="n">
-        <v>173000</v>
+        <v>199000</v>
       </c>
       <c r="H10" t="n">
-        <v>39790</v>
+        <v>-100000</v>
       </c>
       <c r="I10" t="n">
-        <v>29.87</v>
+        <v>-33.44</v>
       </c>
       <c r="J10" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>597000</v>
       </c>
       <c r="N10" t="n">
         <v>5</v>
@@ -1272,17 +1272,17 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1292,113 +1292,113 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Giá tăng 39,790đ (+29.9%)</t>
+          <t>Giá giảm 100,000đ (33.4%) | Bán thêm +3 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7078807</t>
+          <t>276899017</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
+          <t>Giày nam giá rẻ, giày bảo vệ lao động A014</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858717</t>
+          <t>https://tiki.vn/giay-nam-gia-re-giay-bao-ve-lao-dong-a014-p276899017.html?spid=276899027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Nagaki</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>327600</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>420000</v>
+        <v>230000</v>
       </c>
       <c r="H11" t="n">
-        <v>92400</v>
+        <v>230000</v>
       </c>
       <c r="I11" t="n">
-        <v>28.21</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>460000</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Giá tăng 92,400đ (+28.2%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>54569520</t>
+          <t>173661690</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
+          <t>Q127 Váy ngủ 2 dây ren xẻ rút dây sexy - Váy ngủ lụa satin sexy gợi cảm - Đồ ngủ nữ - Đầm ngủ mặc nhà</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
+          <t>https://tiki.vn/vay-ngu-2-day-ren-xe-rut-day-sexy-bt0065-vay-ngu-lua-satin-sexy-goi-cam-do-ngu-nu-dam-ngu-mac-nha-p173661690.html?spid=173661694</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1407,134 +1407,134 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>68640</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>88000</v>
+        <v>198000</v>
       </c>
       <c r="H12" t="n">
-        <v>19360</v>
+        <v>198000</v>
       </c>
       <c r="I12" t="n">
-        <v>28.21</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>396000</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Giá tăng 19,360đ (+28.2%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16546849</t>
+          <t>197077959</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Combo 5 Quần Lót Nam Tam Giác Nhật</t>
+          <t>Thắt lưng nam da bò nguyên chất mặt khóa tự động hợp kim cao cấp</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-quan-lot-nam-tam-giac-nhat-p16546849.html?spid=53006035</t>
+          <t>https://tiki.vn/that-lung-nam-da-bo-nguyen-chat-mat-khoa-tu-dong-hop-kim-cao-cap-p197077959.html?spid=197077961</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>ANANSHOP688</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>210000</v>
+        <v>266000</v>
       </c>
       <c r="G13" t="n">
-        <v>180600</v>
+        <v>266000</v>
       </c>
       <c r="H13" t="n">
-        <v>-29400</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>266000</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,212 +1544,212 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Giá giảm 29,400đ (14.0%)</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2212215</t>
+          <t>278230191</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Combo 04 quần lót nam Pro Ben bảng nhỏ MS914</t>
+          <t>Set Đồ Ngủ Bodysuit Ren Hầu Gái Xuyên Thấu Phối Bèo Sexy Tôn Dáng Chuẩn Đồ Ngủ Cosplay Maid Girl Thiết Kế Bodysuit Ren Lưới Gợi Cảm Kèm Choker  Set Hầu Gái Sexy Đẳng Cấp Đồ Ngủ Ren Mỏng Xẻ Sâu Tôn Vòng 1 Vòng Bodysuit Lingerie Hầu Gái Phối Ren Bèo C075</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-04-quan-lot-nam-pro-ben-bang-nho-ms914-p2212215.html?spid=53788047</t>
+          <t>https://tiki.vn/set-do-ngu-bodysuit-ren-hau-gai-xuyen-thau-phoi-beo-sexy-ton-dang-chuan-do-ngu-cosplay-maid-girl-thiet-ke-bodysuit-ren-luoi-goi-cam-kem-choker-set-hau-gai-sexy-dang-cap-do-ngu-ren-mong-xe-sau-ton-vong-1-vong-bodysuit-lingerie-hau-gai-phoi-ren-beo-c075-p278230191.html?spid=278230192</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pro Ben</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>192000</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>165120</v>
+        <v>119000</v>
       </c>
       <c r="H14" t="n">
-        <v>-26880</v>
+        <v>119000</v>
       </c>
       <c r="I14" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>238000</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Giá giảm 26,880đ (14.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>59462352</t>
+          <t>276832011</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Áo ngực mỏng thêu hoa cài trước có gọng</t>
+          <t>Quần Mặc Nhà Nam SKD02 Vải Kate Co Giãn Nhẹ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-mong-theu-hoa-cai-truoc-co-gong-p59462352.html?spid=59462384</t>
+          <t>https://tiki.vn/quan-mac-nha-nam-skd02-vai-kate-co-gian-nhe-p276832011.html?spid=276832025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>75600</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90000</v>
+        <v>65000</v>
       </c>
       <c r="H15" t="n">
-        <v>14400</v>
+        <v>65000</v>
       </c>
       <c r="I15" t="n">
-        <v>19.05</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>204</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Giá tăng 14,400đ (+19.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>275972651</t>
+          <t>278230144</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gọng kính cận A5012 Z031 A5114 hợp kim cước OURESS thời trang nam nữ siêu nhẹ siêu bền</t>
+          <t>Bộ Nội Y Ren Mở Ngực Đính Ngọc Trai &amp; Nơ ,Nội Y Lingerie Hở Táo Bạo Ren Đen ,Set Bra Ren Cut-out Mềm Mại Phối Hồng Pastel , Set Lingerie Ren Đen Gợi Cảm C025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/gong-kinh-can-a5012-z031-a5114-hop-kim-cuoc-ouress-thoi-trang-nam-nu-sieu-nhe-sieu-ben-p275972651.html?spid=275972684</t>
+          <t>https://tiki.vn/bo-noi-y-ren-mo-nguc-dinh-ngoc-trai-no-noi-y-lingerie-ho-tao-bao-ren-den-set-bra-ren-cut-out-mem-mai-phoi-hong-pastel-set-lingerie-ren-den-goi-cam-c025-p278230144.html?spid=278230145</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OURESS</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>224000</v>
+        <v>79000</v>
       </c>
       <c r="H16" t="n">
-        <v>224000</v>
+        <v>79000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1758,13 +1758,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>79000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1803,37 +1803,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>278796558</t>
+          <t>276667981</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SÉT BỘ BÀ BA CỔ TRÒN TAY DÀI, ÁO LẺ BÀ BA  CÀI NÚT TAY DÀI CHẤT VẢI GẤM ĐỦ SIZE - 1 ÁO LẺ ĐỎ</t>
+          <t>Quần Lót Nam Thương Hiệu Davie DVBX030 Lưng Bản Nhỏ 1.5 Co Giãn 4 Chiều, Thoải Mái Và Thấm Hút Mồ Hôi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-bo-ba-ba-co-tron-tay-dai-ao-le-ba-ba-cai-nut-tay-dai-chat-vai-gam-du-size-p278796558.html?spid=278796660</t>
+          <t>https://tiki.vn/quan-lot-nam-thuong-hieu-davie-dvbx030-lung-ban-nho-1-5-co-gian-4-chieu-thoai-mai-va-tham-hut-mo-hoi-p276667981.html?spid=276667995</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CAN THO AO DAI AO BA BA</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>199000</v>
+        <v>69000</v>
       </c>
       <c r="H17" t="n">
-        <v>199000</v>
+        <v>69000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1887,46 +1887,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>56346167</t>
+          <t>276669234</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Áo lót nữ ren dày</t>
+          <t>Quần Lót Nam Tam Giác Thương Hiệu Samaki Mã SKCT01 Chất Liệu Co Giãn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ren-day-p56346167.html?spid=61933225</t>
+          <t>https://tiki.vn/quan-lot-nam-tam-giac-thuong-hieu-samaki-ma-skct01-chat-lieu-co-gian-p276669234.html?spid=276669288</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>151200</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>180000</v>
+        <v>215000</v>
       </c>
       <c r="H18" t="n">
-        <v>28800</v>
+        <v>215000</v>
       </c>
       <c r="I18" t="n">
-        <v>19.05</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1935,58 +1935,58 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá tăng 28,800đ (+19.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>91973812</t>
+          <t>11988957</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Su Đúc Hình Lá Không Gọng Đệm Dày Nâng Ngực A01 có ảnh thật</t>
+          <t>Áo Khoác Jean Nam AKB3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-su-duc-hinh-la-khong-gong-dem-day-nang-nguc-a01-co-anh-that-p91973812.html?spid=279055013</t>
+          <t>https://tiki.vn/ao-khoac-jean-nam-akb3-p11988957.html?spid=113226613</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1995,19 +1995,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>85000</v>
+        <v>499000</v>
       </c>
       <c r="G19" t="n">
-        <v>66300</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-18700</v>
+        <v>-499000</v>
       </c>
       <c r="I19" t="n">
-        <v>-22</v>
+        <v>-100</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2038,63 +2038,63 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá giảm 18,700đ (22.0%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>37126497</t>
+          <t>16651795</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>( 10 cái ) quần lót nữ Su đúc không đường may, hàng đẹp loại xịn W19_503</t>
+          <t>️[5 Quần] ComBo 5 Quần Lót Nam THUN LẠNH Lưng Bự Hàng Việt Nam Cao Cấp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-10-quan-lot-su-duc-khong-duong-may-hang-dep-loai-xin-w19_503-p37126497.html?spid=51720423</t>
+          <t>https://tiki.vn/5-quan-combo-5-quan-lot-nam-thun-lanh-lung-bu-hang-viet-nam-cao-cap-p16651795.html?spid=51148102</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>MENLIVE</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>280000</v>
+        <v>170150</v>
       </c>
       <c r="G20" t="n">
-        <v>235200</v>
+        <v>205000</v>
       </c>
       <c r="H20" t="n">
-        <v>-44800</v>
+        <v>34850</v>
       </c>
       <c r="I20" t="n">
-        <v>-16</v>
+        <v>20.48</v>
       </c>
       <c r="J20" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2103,26 +2103,26 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2132,53 +2132,53 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Giá giảm 44,800đ (16.0%)</t>
+          <t>Giá tăng 34,850đ (+20.5%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>276181391</t>
+          <t>7078807</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tất / Vớ Chân Cao Cổ Nữ 29,9K Freesize Tập Yoga Pilates Len Co Giãn Đính Hạt Silicon Chống Trơn Trượt (Cao Cổ Kẻ Sọc)</t>
+          <t>Bộ 10 Quần Lót Nam Chéo Nhật Bản Cao Cấp Thoáng Mát (Giao Màu Ngẫu Nhiên)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/tat-vo-chan-cao-co-nu-freesize-tap-yoga-pilates-len-co-gian-dinh-hat-silicon-chong-tron-truot-cao-co-ke-soc-p276181391.html?spid=276181407</t>
+          <t>https://tiki.vn/bo-10-quan-lot-nam-cheo-nhat-ban-cao-cap-thoang-mat-giao-mau-ngau-nhien-p7078807.html?spid=67858717</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TP Tiến Phát SMART</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>39000</v>
+        <v>420000</v>
       </c>
       <c r="G21" t="n">
-        <v>58000</v>
+        <v>336000</v>
       </c>
       <c r="H21" t="n">
-        <v>19000</v>
+        <v>-84000</v>
       </c>
       <c r="I21" t="n">
-        <v>48.72</v>
+        <v>-20</v>
       </c>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2187,26 +2187,26 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2216,53 +2216,53 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Giá tăng 19,000đ (+48.7%)</t>
+          <t>Giá giảm 84,000đ (20.0%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>277347854</t>
+          <t>276668956</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thắt lưng nữ DA BÒ THẬT - BEE GEE N8051</t>
+          <t>Quần Lót Nam Boxer Thương Hiệu Davie Cao Cấp Mã Dvlx002 Không Đường Viền, Co Giãn Tốt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-nu-da-bo-that-bee-gee-n8051-p277347854.html?spid=277347856</t>
+          <t>https://tiki.vn/quan-lot-nam-boxer-thuong-hieu-davie-cao-cap-ma-dvlx002-khong-duong-vien-co-gian-tot-p276668956.html?spid=276669014</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bee Gee</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>320000</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>160000</v>
+        <v>115000</v>
       </c>
       <c r="H22" t="n">
-        <v>-160000</v>
+        <v>115000</v>
       </c>
       <c r="I22" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2290,63 +2290,63 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Giá giảm 160,000đ (50.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>273467379</t>
+          <t>73163978</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Găng tay nam da cừu nguyên tấm không lót BHYST39 bao tay phượt</t>
+          <t>Hộp miếng dán ngực Silicon màu xanh 5 đôi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/gang-tay-nam-da-cuu-nguyen-tam-khong-lot-bhyst39-bao-tay-phuot-p273467379.html?spid=273467385</t>
+          <t>https://tiki.vn/hop-mieng-dan-nguc-silicon-mau-xanh-5-doi-p73163978.html?spid=117659470</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>YAOYAO</t>
+          <t>LQ luxury</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>45650</v>
       </c>
       <c r="G23" t="n">
-        <v>619000</v>
+        <v>55000</v>
       </c>
       <c r="H23" t="n">
-        <v>619000</v>
+        <v>9350</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>20.48</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2355,82 +2355,82 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 9,350đ (+20.5%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>93164977</t>
+          <t>59462352</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kính Mát Thời Trang Nam Đổi Màu NTD cho nam và nữ hót </t>
+          <t>Áo ngực mỏng thêu hoa cài trước có gọng</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://tiki.vn/kinh-mat-thoi-trang-nam-doi-mau-ntd-cho-nam-va-nu-hot-p93164977.html?spid=93164978</t>
+          <t>https://tiki.vn/ao-nguc-mong-theu-hoa-cai-truoc-co-gong-p59462352.html?spid=59462384</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NTD</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>199000</v>
+        <v>90000</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="H24" t="n">
-        <v>-199000</v>
+        <v>-18000</v>
       </c>
       <c r="I24" t="n">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2439,82 +2439,82 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 18,000đ (20.0%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>91324479</t>
+          <t>35364542</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kính râm Mắt vuông nhỏ đen đẳng cấp cao cấp cho Nam (ĐEN)</t>
+          <t>Hôp 5 quần lót nam boxer thun lạnh cao cấp chuẩn xuất Nhật</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://tiki.vn/kinh-ram-mat-vuong-nho-den-dang-cap-cao-cap-cho-nam-den-p91324479.html?spid=91324480</t>
+          <t>https://tiki.vn/hop-5-quan-lot-nam-boxer-thun-lanh-cao-cap-chuan-xuat-nhat-p35364542.html?spid=54540073</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LALAMIA</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>265000</v>
       </c>
       <c r="G25" t="n">
-        <v>189000</v>
+        <v>206700</v>
       </c>
       <c r="H25" t="n">
-        <v>189000</v>
+        <v>-58300</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2523,79 +2523,79 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 58,300đ (22.0%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>278149853</t>
+          <t>276671080</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1 CẶP Miếng dán ti silicon, miếng dán ngực cao cấp - Hàng chính hãng</t>
+          <t>Quần Lót Nam Tam Giác Davie Mã DVCT033 Chất 100% Cotton, Co Giãn 4 Chiều, Thấm Hút Mồ Hôi Và Khử Mùi Tốt</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://tiki.vn/1-cap-mieng-dan-ti-silicon-mieng-dan-nguc-cao-cap-hang-chinh-hang-p278149853.html?spid=278149854</t>
+          <t>https://tiki.vn/quan-lot-nam-tam-giac-davie-ma-dvct033-chat-100-cotton-co-gian-4-chieu-tham-hut-mo-hoi-va-khu-mui-tot-p276671080.html?spid=276671198</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LuckyJQR</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>310000</v>
       </c>
       <c r="H26" t="n">
-        <v>-70000</v>
+        <v>310000</v>
       </c>
       <c r="I26" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2626,63 +2626,63 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>93151862</t>
+          <t>54569520</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mắt kính mát NTD nam nữ đổi màu dùng cả ngày và đêm ,chống tia uv</t>
+          <t>Quần Lót nam, quần sịp nam lụa Sữa Cao Cấp sp-340</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mat-kinh-mat-ntd-nam-nu-doi-mau-dung-ca-ngay-va-dem-chong-tia-uv-p93151862.html?spid=93151863</t>
+          <t>https://tiki.vn/quan-lot-nam-quan-sip-nam-lua-sua-cao-cap-sp-340-p54569520.html?spid=67859897</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NTD</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>199000</v>
+        <v>88000</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>70400</v>
       </c>
       <c r="H27" t="n">
-        <v>-199000</v>
+        <v>-17600</v>
       </c>
       <c r="I27" t="n">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2694,76 +2694,76 @@
         <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 17,600đ (20.0%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>167932010</t>
+          <t>276678209</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lọ nước lau xịt kính chuyên dụng - Kính mắt Apark</t>
+          <t>Quần Tam Giác Hiệu Davie Mã DVTL009, Chất Thun Lạnh Cao Cấp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://tiki.vn/lo-nuoc-lau-xi-t-kinh-chuyen-dung-kinh-mat-apark-p167932010.html?spid=171515346</t>
+          <t>https://tiki.vn/quan-tam-giac-hieu-davie-ma-dvtl009-chat-thun-lanh-cao-cap-p276678209.html?spid=276678245</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="H28" t="n">
-        <v>-50000</v>
+        <v>75000</v>
       </c>
       <c r="I28" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2775,16 +2775,16 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2794,60 +2794,60 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>117677969</t>
+          <t>276667813</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hộp da đựng mắt kính cao cấp</t>
+          <t>Quần Lót Nam Thương Hiệu Davie Dvtl036 Quần Lưới Thông Hơi Cao Cấp Chất Liệu Thun Lạnh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-da-dung-mat-kinh-cao-cap-p117677969.html?spid=185862789</t>
+          <t>https://tiki.vn/quan-lot-nam-thuong-hieu-davie-dvtl036-quan-luoi-thong-hoi-cao-cap-chat-lieu-thun-lanh-p276667813.html?spid=276667869</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>DAVIE</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="H29" t="n">
-        <v>-50000</v>
+        <v>180000</v>
       </c>
       <c r="I29" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2859,16 +2859,16 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-4.7</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2878,39 +2878,39 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26652440</t>
+          <t>74820156</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1 Hộp Khăn Lau Kính Mắt - Màn Hình Điện Tử</t>
+          <t>ÁO LÓT NỮ MỎNG REN 3 MÓC BIG SIZE 395</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://tiki.vn/1-hop-khan-lau-kinh-mat-man-hinh-dien-tu-p26652440.html?spid=146386798</t>
+          <t>https://tiki.vn/ao-lot-nu-mong-ren-3-moc-big-size-395-p74820156.html?spid=74820178</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2919,22 +2919,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>99000</v>
+        <v>99560</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>131000</v>
       </c>
       <c r="H30" t="n">
-        <v>-99000</v>
+        <v>31440</v>
       </c>
       <c r="I30" t="n">
-        <v>-100</v>
+        <v>31.58</v>
       </c>
       <c r="J30" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2946,117 +2946,3393 @@
         <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 31,440đ (+31.6%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>279330353</t>
+          <t>278892321</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dép quai hậu nam VN2224 size 35-45. Hàng chính hãng VINASAN được sx tại Việt Nam</t>
+          <t>P25 Váy ngủ bodysuit ren xuyên thấu sexy gợi cảm Đầm ngủ bdysuit quyến rũ - Đồ ngủ nữ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-quai-hau-nam-vn2224-size-35-45-hang-chinh-hang-vinasan-duoc-sx-tai-viet-nam-p279330353.html?spid=279330391</t>
+          <t>https://tiki.vn/p25-vay-ngu-bodysuit-ren-xuyen-thau-sexy-goi-cam-dam-ngu-bdysuit-quyen-ru-do-ngu-nu-p278892321.html?spid=278892323</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>198000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>198000</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>56346167</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Áo lót nữ ren dày</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-lot-nu-ren-day-p56346167.html?spid=61933225</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G32" t="n">
+        <v>144000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-36000</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Giá giảm 36,000đ (20.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>275602099</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Quần su mặc lót trong - Quần lót nữ - Quần su nữ mặc trong</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-su-p275602099.html?spid=275602113</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>127341900</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Áo lót lovely có gọng đệm mỏng thêu hoa nổi xuất nhật</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-lot-lovely-co-gong-dem-mong-theu-hoa-noi-xuat-nhat-p127341900.html?spid=142061094</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>97110</v>
+      </c>
+      <c r="G34" t="n">
+        <v>117000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>19890</v>
+      </c>
+      <c r="I34" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="J34" t="n">
+        <v>15</v>
+      </c>
+      <c r="K34" t="n">
+        <v>15</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Giá tăng 19,890đ (+20.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>276181391</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tất / Vớ Chân Cao Cổ Nữ 29,9K Freesize Tập Yoga Pilates Len Co Giãn Đính Hạt Silicon Chống Trơn Trượt (Cao Cổ Kẻ Sọc)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/tat-vo-chan-cao-co-nu-freesize-tap-yoga-pilates-len-co-gian-dinh-hat-silicon-chong-tron-truot-cao-co-ke-soc-p276181391.html?spid=276181407</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>TP Tiến Phát SMART</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>58000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>49000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-15.52</v>
+      </c>
+      <c r="J35" t="n">
+        <v>25</v>
+      </c>
+      <c r="K35" t="n">
+        <v>25</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Giá giảm 9,000đ (15.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>58031901</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Thắt Lưng Da Cá Sấu thật. Da Bông Hông Cá Sấu Rất Đẹp Và Mềm. Kích Thước Chuẩn 3.5*120cm Rất Dễ Sử Dụng</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-da-ca-sau-that-da-bong-hong-ca-sau-rat-dep-va-mem-kich-thuoc-chuan-3-5-120cm-rat-de-su-dung-p58031901.html?spid=58031907</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ovenis</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>751000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>999000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>248000</v>
+      </c>
+      <c r="I36" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="J36" t="n">
+        <v>57</v>
+      </c>
+      <c r="K36" t="n">
+        <v>57</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>27</v>
+      </c>
+      <c r="R36" t="n">
+        <v>27</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Giá tăng 248,000đ (+33.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>276181618</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tất Gấu Cổ Cao Nữ Họa Tiết Hình Gấu,{TP} Vớ Cổ Cao Nữ Hàn Quốc họa tiết</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/tat-gau-co-cao-nu-hoa-tiet-hinh-gau-tp-vo-co-cao-nu-han-quoc-hoa-tiet-p276181618.html?spid=276181620</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TP Tiến Phát SMART</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>26490</v>
+      </c>
+      <c r="G37" t="n">
+        <v>25165</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1325</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>13</v>
+      </c>
+      <c r="K37" t="n">
+        <v>13</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Giá giảm 1,325đ (5.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>276833571</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quần Short Mặt Nhà Thương Hiệu Davie Dvs06 Chất Liệu Kate 100% Cotton Thoáng Mát</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-short-mat-nha-thuong-hieu-davie-dvs06-chat-lieu-kate-100-cotton-thoang-mat-p276833571.html?spid=276833595</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DAVIE</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>410000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>410000</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37975688</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Áo Sơ Mi Nữ Form Dài Che Quần Cá Tính SM013 MayHomes</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-so-mi-nu-form-dai-che-quan-ca-tinh-sm013-mayhomes-p37975688.html?spid=37975696</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MAYHOMES</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>109000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-109000</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J39" t="n">
+        <v>112</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>31</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>279345968</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[Video] Dây Nịt Nam - Thắt Lưng Nam Thời Trang Cao Cấp | Dây Nịch Thắc Lưng (DN-126)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/video-day-nit-nam-that-lung-nam-thoi-trang-cao-cap-day-nich-thac-lung-dn-126-p279345968.html?spid=279345994</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>29999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>29999</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>278697510</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Combo Phụ kiện thời trang Đuôi cosplay cáo Xù Đẹp nhân tạo Cosplay + nơ cổ + kẹp tóc (Halloween / Lễ hội / Trang phục hóa trang)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-phu-kien-thoi-trang-duoi-fox-xu-dep-nhan-tao-cosplay-no-co-kep-toc-halloween-le-hoi-trang-phuc-hoa-trang-p278697510.html?spid=278697549</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>217426754</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Thắt Lưng Nam Da Bò Thật TiTi ĐÔ Bản Lớn Da 1 Lớp Đầu Khóa Kim TLNA2029</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-da-bo-that-ha-nam-co-lon-da-1-lop-tlna2029-p217426754.html?spid=217426760</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>HA NAM</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>380000</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>179206707</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mũ Thể Thao Nam, Nữ - Chất liệu vải Cotton thấm mồ hôi thoáng khí - Thiết kế tinh xảo, đường nét khác biệt, hiện đại, sang trọng - Giúp chống nắng hiệu quả</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/mu-the-thao-nam-nu-chat-lieu-vai-cotton-tham-mo-hoi-thoang-khi-thiet-ke-tinh-xao-duong-net-khac-biet-hien-dai-sang-trong-giup-chong-nang-hieu-qua-p179206707.html?spid=179206715</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PGM</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>68573034</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Quần Bơi Nam Boxer Có Túi CLEACCO DEENYT Chất Liệu Nylon Cao Cấp , Chống Thấm , Nhanh Khô Form Fitness Thời Trang (Tặng kèm nón bơi + bịt tai silicon) - Hàng Chính Hãng</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-boi-nam-boxer-co-tui-cleacco-deenyt-chat-lieu-nylon-cao-cap-chong-tham-nhanh-kho-form-fitness-thoi-trang-tang-kem-non-boi-bit-tai-silicon-hang-chinh-hang-p68573034.html?spid=69171837</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CLEACCO</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>152900</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-152900</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J44" t="n">
+        <v>404</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>93</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>278850221</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Quần Jean Thời Trang Basic Nam Ống Đứng Ninomaxx 2508004</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-jean-thoi-trang-basic-nam-ong-dung-ninomaxx-2508004-p278850221.html?spid=278850229</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ninomaxx</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>769000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-769000</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>276882727</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Áo vest blazer nam phong cách Hàn Quốc vải Linen thoáng mát, mềm mịn</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-vest-blazer-nam-phong-cach-han-quoc-vai-linen-thoang-mat-mem-min-p276882727.html?spid=276882729</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Haint Boutique</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-420000</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>263040176</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Bộ áo bà nam truyền thống đỏ đô - Có bộ bà ba Bigsize- may sỉ bà ba toàn quốc - May bộ bà ba theo yêu cầu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-ao-ba-nam-truyen-thong-do-do-p263040176.html?spid=263040188</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>CAN THO AO DAI AO BA BA</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>212936093</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Áo khoác gió 1 lớp ALIGRO màu navy AK1G.3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-gio-1-lop-aligro-mau-navy-ak1g-3-p212936093.html?spid=212936099</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aligro</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>620000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-620000</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>197062475</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Áo khoác măng tô nam cổ đứng dáng ngắn khóa kéo chất vải kaki đẹp NMT34</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-mang-to-nam-co-dung-dang-ngan-khoa-keo-chat-vai-kaki-dep-nmt34-p197062475.html?spid=197062507</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>936000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-936000</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>129246479</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Áo khoác măng tô nam trẻ trung thời trang mới NMT74</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-mang-to-nam-tre-trung-thoi-trang-moi-nmt74-p129246479.html?spid=129246507</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1296000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-1296000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J50" t="n">
+        <v>10</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>5</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>102890702</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Quần short nỷ nam Novelty 200043Q</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-short-ny-nam-novelty-200043q-p102890702.html?spid=102890710</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Novelty</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>349000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-349000</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>95053519</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Quần bơi nam lửng màu trơn đơn giản, đồ bơi nam form dài trên gối thiết kế trẻ trung QB022</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-boi-nam-lung-mau-tron-don-gian-do-boi-nam-form-dai-tren-goi-thiet-ke-tre-trung-qb022-p95053519.html?spid=95053523</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>235000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-235000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J52" t="n">
+        <v>75</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>12</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>93233783</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Áo Khoác Big Size Nam Nữ Unisex Áo Khoác Dù Nam 2 Lớp Chống Nắng Chống Lạnh Chống Gió Thời Trang Phom Body Phối Màu Hàn Quốc Cao Cấp AD73 - ShopN6</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-big-size-nam-nu-unisex-ao-khoac-du-nam-2-lop-chong-nang-chong-lanh-chong-gio-thoi-trang-phom-body-phoi-mau-han-quoc-cao-cap-ad73-shopn6-p93233783.html?spid=93233785</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-180000</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J53" t="n">
+        <v>19</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>7</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>90483623</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Combo 3 Áo thun nam ba lỗ cotton FREEMAN ASF205</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-ba-lo-cotton-freeman-asf205-combo-3-p90483623.html?spid=90483629</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Freeman</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>240300</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-240300</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J54" t="n">
+        <v>14</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20535045</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Thắt lưng nam da bò AT Leather - P142</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-da-bo-at-leather-p142-p20535045.html?spid=20535047</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ANH THO LEATHER</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>295000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-295000</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J55" t="n">
+        <v>181</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>48</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>253580279</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Áo hai dây nữ cổ đổ mặc trong vest chất vải lụa latin, thoáng mát khi mặc - New Design AO0013</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-hai-day-nu-co-do-mac-trong-vest-chat-vai-lua-latin-thoang-mat-khi-mac-new-design-ao0013-p253580279.html?spid=253580289</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J56" t="n">
+        <v>15</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>163477532</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Quần Đùi Nữ New Design, Quần Short Nữ Cạp Chun, Vải Lụa Mịn, Thoáng Mát ,Mặc Thoải Mái Nhiều Màu ( 40-65 kg) QA0003</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-dui-nu-mac-nha-quan-dui-nu-lua-han-quoc-hang-thiet-ke-cao-cap-45-65kg-vannhshop-qa0003-p163477532.html?spid=163477539</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>69000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-69000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J57" t="n">
+        <v>98</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>12</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>278796558</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SÉT BỘ BÀ BA CỔ TRÒN TAY DÀI, ÁO LẺ BÀ BA  CÀI NÚT TAY DÀI CHẤT VẢI GẤM ĐỦ SIZE - 1 ÁO LẺ ĐỎ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/set-bo-ba-ba-co-tron-tay-dai-ao-le-ba-ba-cai-nut-tay-dai-chat-vai-gam-du-size-p278796558.html?spid=278796660</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CAN THO AO DAI AO BA BA</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>277311177</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Váy 2 dây váy ngủ lụa cổ tim chất lụa satin mềm, mịn thoáng mát VN0003</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/vay-2-day-vay-ngu-lua-co-tim-chat-lua-satin-mem-min-thoang-mat-vn0003-p277311177.html?spid=277311201</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>216205243</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Bộ Áo Cúp Ngang và Quần Lót Nữ Thun Lạnh Miley Lingerie BRM11202_FMM1105</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-ao-cup-ngang-va-quan-lot-nu-thun-lanh-miley-lingerie-brm11202_fmm1105-p216205243.html?spid=216205251</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Miley Lingerie</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>145289760</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chân Váy Công Sở New Design Thiết Kế Dáng Váy chữ A, Dài Qua Gối ,Phối Nút, Phom Chuẩn Tôn Dáng Sang Trọng Vải Tốt co Giãn, Màu Đen CV0066</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/chan-vay-cong-so-dai-chu-a-lung-cao-chan-vay-dai-qua-goi-dang-xoe-midi-mau-den-dep-hang-thiet-ke-cao-cap-vannvannhshop-p145289760.html?spid=145289803</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>333000</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-333000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J61" t="n">
+        <v>91</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>26</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>52137064</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>COMBO 5 QUẦN VÁY THUN CHÂN REN</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-5-quan-vay-thun-chan-ren-p52137064.html?spid=55339015</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>178000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-178000</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>44007367</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5 Quần Tất Vớ Siêu Dai Siêu Mỏng</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/5-quan-tat-vo-sieu-dai-sieu-mong-p44007367.html?spid=44146284</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>189000</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-189000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>186434946</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Túi than hoạt tính khử mùi giày - 100% từ gáo dừa Bến Tre (Hộp 2 túi) - Hapaku</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/tui-than-hoat-tinh-khu-mui-giay-100-tu-gao-dua-ben-tre-hop-2-tui-hapaku-p186434946.html?spid=29882855</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>Giày - Dép nam</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>VINASAN</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>250000</v>
-      </c>
-      <c r="G31" t="n">
-        <v>250000</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Hapaku</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>129000</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-129000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J64" t="n">
+        <v>172</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>15</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>76072069</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Áo thun nam Novelty cổ tròn xám đậm NATMMDNCSR181212N</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-thun-nam-novelty-co-tron-xam-dam-natmmdncsr181212n-p76072069.html?spid=76072071</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Novelty</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>219000</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-219000</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>57300908</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Khăn trùm kín mặt chống nắng, chống tia UV khi đi xe dành cho cả nam và nữ Rimix - Hàng chính hãng</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/khan-trum-kin-mat-chong-nang-chong-tia-uv-khi-di-xe-danh-cho-ca-nam-va-nu-rimix-hang-chinh-hang-p57300908.html?spid=57905453</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>108900</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-108900</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J66" t="n">
+        <v>406</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>81</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2004591</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Thắt Lưng Nam Cao Cấp AT Leather P119 - Đen</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-cao-cap-at-leather-p119-den-p2004591.html?spid=2004593</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ANH THO LEATHER</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>450000</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-450000</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J67" t="n">
+        <v>96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>25</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>73755741</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Thắt lưng nam da bò AT Leather M4K35-06</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-da-bo-at-leather-m4k35-06-p73755741.html?spid=73755743</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ANH THO LEATHER</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>325000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-325000</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J68" t="n">
+        <v>160</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>67</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>214919710</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kẹp Tóc Càng Cua Hoa Trà Hàn Quốc Cao Cấp</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/kep-toc-cang-cua-hoa-tra-han-quoc-cao-cap-p214919710.html?spid=264021788</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>34900</v>
+      </c>
+      <c r="G69" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-9900</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-28.37</v>
+      </c>
+      <c r="J69" t="n">
+        <v>14</v>
+      </c>
+      <c r="K69" t="n">
+        <v>11</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-75000</v>
+      </c>
+      <c r="N69" t="n">
         <v>5</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>-1250000</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="O69" t="n">
         <v>5</v>
       </c>
-      <c r="O31" t="n">
-        <v>5</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="R69" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
         <is>
           <t>🔄 Đã cập nhật</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Bán thêm -5 sản phẩm | Review thêm +1</t>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Giá giảm 9,900đ (28.4%) | Bán thêm -3 sản phẩm</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>87981660</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Combo 2 áo ba lỗ nam, áo 3 lỗ nam, sợi cotton mềm mịn, thấm hút mồ hôi tốt, thoáng mát, mặc thoải mái JAMANO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-2-ao-ba-lo-nam-ao-3-lo-nam-soi-cotton-mem-min-tham-hut-mo-hoi-tot-thoang-mat-mac-thoai-mai-jamano-p87981660.html?spid=87981797</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>JAMANO</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>198000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>198000</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1925</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1921</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-792000</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>332</v>
+      </c>
+      <c r="R70" t="n">
+        <v>332</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Bán thêm -4 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>275276504</t>
+          <t>186434946</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Đồ Bơi Nữ Hai Mảnh Đa Năng Gồm Áo Bơi Nữ Và Váy Bơi Nữ</t>
+          <t>Túi than hoạt tính khử mùi giày - 100% từ gáo dừa Bến Tre (Hộp 2 túi) - Hapaku</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/do-boi-nu-hai-manh-da-nang-gom-ao-boi-nu-va-vay-boi-nu-p275276504.html?spid=275276510</t>
+          <t>https://tiki.vn/tui-than-hoat-tinh-khu-mui-giay-100-tu-gao-dua-ben-tre-hop-2-tui-hapaku-p186434946.html?spid=29882855</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Hapaku</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>219000</v>
+        <v>129000</v>
       </c>
       <c r="H2" t="n">
-        <v>219000</v>
+        <v>129000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="M2" t="n">
-        <v>3066000</v>
+        <v>22188000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,37 +627,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27924842</t>
+          <t>278049759</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cài áo hoa vải</t>
+          <t>Áo sơ mi nam ngắn tay Novelty Casual Hoa văn SMI25001 - 250079N</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/cai-ao-hoa-vai-p27924842.html?spid=27924852</t>
+          <t>https://tiki.vn/ao-so-mi-nam-ngan-tay-novelty-casual-hoa-van-smi25001-p278049759.html?spid=278049917</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Novelty</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>395000</v>
       </c>
       <c r="G3" t="n">
-        <v>35000</v>
+        <v>395000</v>
       </c>
       <c r="H3" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,13 +666,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1470000</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -694,34 +694,34 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Rating 0.0→5.0 (+5.00) | Review thêm +4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>278092142</t>
+          <t>174585329</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quần kiểu nữ ống rộng, chất liệu vải Đũi xước, mềm mịn, mặc mát, Quần Short nữ đẹp Nesa Shop</t>
+          <t>Áo lót nâng ngực boya mút mỏng, Áo ngực boya nâng ngực cài sau 522BT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-kieu-nu-ong-rong-chat-lieu-vai-dui-xuoc-mem-min-mac-mat-quan-short-nu-dep-nesa-shop-p278092142.html?spid=278092148</t>
+          <t>https://tiki.vn/ao-lot-nang-nguc-boya-mut-mong-ao-nguc-boya-nang-nguc-cai-sau-522bt-p174585329.html?spid=203717976</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -735,50 +735,50 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>55000</v>
+        <v>86100</v>
       </c>
       <c r="G4" t="n">
-        <v>55000</v>
+        <v>105000</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>18900</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>21.95</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>660000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -788,137 +788,137 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Bán thêm +12 sản phẩm</t>
+          <t>Giá tăng 18,900đ (+22.0%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>37733512</t>
+          <t>133160820</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sét 2 kẹp tóc nhựa bền Song An Eco KAH118</t>
+          <t>Quần Lót Su Đúc Nữ (Hàng Loại 1) Không Đường Mai, Thun Lạnh, SIêu Co Dãn, Được Chọn Màu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/set-2-kep-toc-nhua-ben-song-an-eco-kah118-p37733512.html?spid=37831891</t>
+          <t>https://tiki.vn/quan-lot-su-duc-nu-hang-loai-1-khong-duong-mai-thun-lanh-sieu-co-dan-duoc-chon-mau-p133160820.html?spid=198901960</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Song An Eco</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="G5" t="n">
-        <v>22000</v>
+        <v>21840</v>
       </c>
       <c r="H5" t="n">
-        <v>22000</v>
+        <v>-6160</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>176000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 6,160đ (22.0%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>276882727</t>
+          <t>158732070</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Áo vest blazer nam phong cách Hàn Quốc vải Linen thoáng mát, mềm mịn</t>
+          <t>❈✣♚Combo 10 quần lót nữ su đúc cao cấp không đường may, chất mát lạnh, mềm mịn, thoáng</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-vest-blazer-nam-phong-cach-han-quoc-vai-linen-thoang-mat-mem-min-p276882727.html?spid=276882729</t>
+          <t>https://tiki.vn/combo-10-quan-lot-nu-su-duc-cao-cap-khong-duong-may-chat-mat-lanh-mem-min-thoang-p158732070.html?spid=242324041</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haint Boutique</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>252800</v>
       </c>
       <c r="G6" t="n">
-        <v>420000</v>
+        <v>320000</v>
       </c>
       <c r="H6" t="n">
-        <v>420000</v>
+        <v>67200</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>26.58</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -927,58 +927,58 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 67,200đ (+26.6%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>133160820</t>
+          <t>103049077</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quần Lót Su Đúc Nữ (Hàng Loại 1) Không Đường Mai, Thun Lạnh, SIêu Co Dãn, Được Chọn Màu</t>
+          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-su-duc-nu-hang-loai-1-khong-duong-mai-thun-lanh-sieu-co-dan-duoc-chon-mau-p133160820.html?spid=198901960</t>
+          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -987,22 +987,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>21280</v>
+        <v>185000</v>
       </c>
       <c r="G7" t="n">
-        <v>28000</v>
+        <v>144300</v>
       </c>
       <c r="H7" t="n">
-        <v>6720</v>
+        <v>-40700</v>
       </c>
       <c r="I7" t="n">
-        <v>31.58</v>
+        <v>-22</v>
       </c>
       <c r="J7" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1011,26 +1011,26 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1040,29 +1040,29 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Giá tăng 6,720đ (+31.6%)</t>
+          <t>Giá giảm 40,700đ (22.0%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>101280655</t>
+          <t>244298352</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bộ 5 Quần Lót Nam Đùi Xuất Nhật Chất Mát từ 40kg đến 90kg (Màu Ngẫu Nghiên)</t>
+          <t>Quần Gen Ôm Bụng Dạng Đùi Có Thanh Chống Cuộn Voronin 8292 – Siêu Gọn, Siêu Định Hình</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bo-5-quan-lot-nam-dui-xuat-nhat-chat-mat-tu-40kg-den-90kg-mau-ngau-nghien-p101280655.html?spid=101280672</t>
+          <t>https://tiki.vn/quan-gen-chong-cuon-dui-8292-p244298352.html?spid=244298362</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>177000</v>
+        <v>102480</v>
       </c>
       <c r="G8" t="n">
-        <v>177000</v>
+        <v>122000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>19520</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>19.05</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1095,26 +1095,26 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1124,53 +1124,53 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Review thêm +1</t>
+          <t>Giá tăng 19,520đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>31638135</t>
+          <t>214706031</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Combo 4 quần lót nam Boxer sợi cạp 1cm sợi tre tự nhiên mềm mịn thấm hút mồ hôi, co giãn 4 chiều MRM Manlywear - Màu ngẫu nhiên</t>
+          <t>Áo lót áo ngực Thái lan có gọng mút kép nâng ngực tạo khe, áo lót nữ thông hơi hàng CAO CẤP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-4-quan-sip-dui-nam-quan-lot-nam-boxer-soi-tre-mem-min-sieu-thoang-mat-co-gian-4-chieu-cao-cap-cap-1cm-mrm-fashion-3-mau-p31638135.html?spid=31638146</t>
+          <t>https://tiki.vn/ao-lot-ao-nguc-thai-lan-co-gong-mut-kep-nang-nguc-tao-khe-ao-lot-nu-thong-hoi-hang-cao-cap-p214706031.html?spid=215408041</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MRM Manlywear</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>340000</v>
+        <v>98400</v>
       </c>
       <c r="G9" t="n">
-        <v>279000</v>
+        <v>120000</v>
       </c>
       <c r="H9" t="n">
-        <v>-61000</v>
+        <v>21600</v>
       </c>
       <c r="I9" t="n">
-        <v>-17.94</v>
+        <v>21.95</v>
       </c>
       <c r="J9" t="n">
-        <v>5871</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>5871</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1179,26 +1179,26 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1372</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1372</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1208,24 +1208,24 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Giá giảm 61,000đ (17.9%)</t>
+          <t>Giá tăng 21,600đ (+22.0%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>73163978</t>
+          <t>112851354</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hộp miếng dán ngực Silicon màu xanh 5 đôi</t>
+          <t>Áo ngực học sinh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/hop-mieng-dan-nguc-silicon-mau-xanh-5-doi-p73163978.html?spid=117659470</t>
+          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138792</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1235,26 +1235,26 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LQ luxury</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>55000</v>
+        <v>42000</v>
       </c>
       <c r="G10" t="n">
-        <v>44550</v>
+        <v>34860</v>
       </c>
       <c r="H10" t="n">
-        <v>-10450</v>
+        <v>-7140</v>
       </c>
       <c r="I10" t="n">
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="J10" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1263,26 +1263,26 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Giá giảm 10,450đ (19.0%)</t>
+          <t>Giá giảm 7,140đ (17.0%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>73862702</t>
+          <t>113145806</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ REN MÚT DÀY 2CM DÂY TRƠN NÂNG NGỰC 024B</t>
+          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-ren-mut-day-2cm-day-tron-nang-nguc-024b-p73862702.html?spid=73862720</t>
+          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>173000</v>
+        <v>124000</v>
       </c>
       <c r="G11" t="n">
-        <v>145320</v>
+        <v>102920</v>
       </c>
       <c r="H11" t="n">
-        <v>-27680</v>
+        <v>-21080</v>
       </c>
       <c r="I11" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="J11" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1347,26 +1347,26 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1376,24 +1376,24 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Giá giảm 27,680đ (16.0%)</t>
+          <t>Giá giảm 21,080đ (17.0%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>113145806</t>
+          <t>144236336</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
+          <t>COMBO 5 ÁO LÓT VẢI KHÔNG GỌNG KHÔNG MÚT (SIZE 32-42)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
+          <t>https://tiki.vn/combo-5-ao-lot-vai-khong-gong-khong-mut-size-32-42-p144236336.html?spid=146366320</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1407,22 +1407,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>95480</v>
+        <v>210000</v>
       </c>
       <c r="G12" t="n">
-        <v>124000</v>
+        <v>163800</v>
       </c>
       <c r="H12" t="n">
-        <v>28520</v>
+        <v>-46200</v>
       </c>
       <c r="I12" t="n">
-        <v>29.87</v>
+        <v>-22</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1431,26 +1431,26 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1460,24 +1460,24 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Giá tăng 28,520đ (+29.9%)</t>
+          <t>Giá giảm 46,200đ (22.0%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>112851354</t>
+          <t>108220832</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Áo ngực học sinh</t>
+          <t>Miếng Dán Ngực Cài Trước Hình Bàn Tay Siêu Nâng Ngực, Siêu Dính P29 Size A-B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138792</t>
+          <t>https://tiki.vn/bra-dan-nguc-ban-tay-p29-kem-day-trong-p108220832.html?spid=242370964</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1491,22 +1491,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>32340</v>
+        <v>63200</v>
       </c>
       <c r="G13" t="n">
-        <v>42000</v>
+        <v>80000</v>
       </c>
       <c r="H13" t="n">
-        <v>9660</v>
+        <v>16800</v>
       </c>
       <c r="I13" t="n">
-        <v>29.87</v>
+        <v>26.58</v>
       </c>
       <c r="J13" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1515,26 +1515,26 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1544,24 +1544,24 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Giá tăng 9,660đ (+29.9%)</t>
+          <t>Giá tăng 16,800đ (+26.6%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>74820156</t>
+          <t>244297862</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG REN 3 MÓC BIG SIZE 395</t>
+          <t>Áo Lót Nữ Bra Ống Su Gân Viền Ren Cài Sau 4003 – Seamless, Co Giãn 4 Chiều</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-ren-3-moc-big-size-395-p74820156.html?spid=74820178</t>
+          <t>https://tiki.vn/ao-bra-ong-su-gan-cai-sau-4003-p244297862.html?spid=244297867</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1575,22 +1575,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>131000</v>
+        <v>38640</v>
       </c>
       <c r="G14" t="n">
-        <v>110040</v>
+        <v>46000</v>
       </c>
       <c r="H14" t="n">
-        <v>-20960</v>
+        <v>7360</v>
       </c>
       <c r="I14" t="n">
-        <v>-16</v>
+        <v>19.05</v>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1599,26 +1599,26 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1628,24 +1628,24 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Giá giảm 20,960đ (16.0%)</t>
+          <t>Giá tăng 7,360đ (+19.0%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>144236336</t>
+          <t>102939605</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COMBO 5 ÁO LÓT VẢI KHÔNG GỌNG KHÔNG MÚT (SIZE 32-42)</t>
+          <t>áo lót ko gọng cúp B dành cho vòng ngực khủng</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-ao-lot-vai-khong-gong-khong-mut-size-32-42-p144236336.html?spid=146366320</t>
+          <t>https://tiki.vn/ao-lot-ko-gong-cup-b-danh-cho-vong-nguc-khung-p102939605.html?spid=201243133</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1659,22 +1659,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>159600</v>
+        <v>111000</v>
       </c>
       <c r="G15" t="n">
-        <v>210000</v>
+        <v>86580</v>
       </c>
       <c r="H15" t="n">
-        <v>50400</v>
+        <v>-24420</v>
       </c>
       <c r="I15" t="n">
-        <v>31.58</v>
+        <v>-22</v>
       </c>
       <c r="J15" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1683,26 +1683,26 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1712,29 +1712,29 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Giá tăng 50,400đ (+31.6%)</t>
+          <t>Giá giảm 24,420đ (22.0%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>74421501</t>
+          <t>276479781</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ÁO LÓT NỮ MỎNG CÓ GỌNG CÀI TRƯỚC VIỀN REN</t>
+          <t>Mũ Nón Chống Nắng Ninja Fullface Kèm Khẩu Trang Lưới Vải Co Giãn Thoáng Khí Có Thể Gấp Gọn Đi Phượt Dã Ngoại Câu Cá Unisex</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nu-mong-co-gong-cai-truoc-vien-ren-p74421501.html?spid=74421553</t>
+          <t>https://tiki.vn/mu-non-chong-nang-ninja-fullface-kem-khau-trang-luoi-vai-co-gian-thoang-khi-co-the-gap-gon-di-phuot-da-ngoai-cau-ca-unisex-p276479781.html?spid=276479783</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>160000</v>
+        <v>74000</v>
       </c>
       <c r="G16" t="n">
-        <v>134400</v>
+        <v>148000</v>
       </c>
       <c r="H16" t="n">
-        <v>-25600</v>
+        <v>74000</v>
       </c>
       <c r="I16" t="n">
-        <v>-16</v>
+        <v>100</v>
       </c>
       <c r="J16" t="n">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1767,26 +1767,26 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1796,53 +1796,53 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Giá giảm 25,600đ (16.0%)</t>
+          <t>Giá tăng 74,000đ (+100.0%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>103049077</t>
+          <t>278993558</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
+          <t>Gọng Kính Cận Giả Cận Nam Nữ Cao Cấp Titanium BLUE LIGHT Mắt Khoan Không Viền Chữ Nhật Bạc Đen Vàng Dày Dặn Cứng Nhẹ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
+          <t>https://tiki.vn/gong-kinh-can-gia-can-nam-nu-cao-cap-titanium-blue-light-mat-khoan-khong-vien-chu-nhat-bac-den-vang-day-dan-cung-nhe-p278993558.html?spid=278993563</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Blue Light</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>140600</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>185000</v>
+        <v>985000</v>
       </c>
       <c r="H17" t="n">
-        <v>44400</v>
+        <v>985000</v>
       </c>
       <c r="I17" t="n">
-        <v>31.58</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1851,82 +1851,82 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Giá tăng 44,400đ (+31.6%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>127341900</t>
+          <t>77625091</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Áo lót lovely có gọng đệm mỏng thêu hoa nổi xuất nhật</t>
+          <t>Gọng Kính cận, Kính giả cận Mắt vuông form nhỏ cao cấp - GCH2276</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-lovely-co-gong-dem-mong-theu-hoa-noi-xuat-nhat-p127341900.html?spid=142061094</t>
+          <t>https://tiki.vn/gong-kinh-can-kinh-gia-can-mat-vuong-form-nho-cao-cap-gch2276-tang-tuavit-kinh-xinh-mini-tien-loi-p77625091.html?spid=77625097</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>LiLiLa</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>94770</v>
+        <v>189000</v>
       </c>
       <c r="H18" t="n">
-        <v>-22230</v>
+        <v>189000</v>
       </c>
       <c r="I18" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1935,82 +1935,82 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Giá giảm 22,230đ (19.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>277880869</t>
+          <t>44666139</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Áo Thun Unisex - Oversize Chất 100% Cotton 2 chiều Dày 250gsm | Nam Nữ Mặc Siêu Đẹp</t>
+          <t>Mũ lưỡi trai nam nữ vải lưới thoáng mát thời trang không logo, không thêu, che nắng tốt, bảo vệ da</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-unisex-form-rong-chat-100-cotton-2-chieu-day-230gsm-mau-hot-gen-z-nam-nu-mac-sieu-dep-p277880869.html?spid=277880880</t>
+          <t>https://tiki.vn/mu-luoi-trai-nam-nu-vai-luoi-thoang-mat-thoi-trang-khong-logo-khong-theu-che-nang-tot-bao-ve-da-p44666139.html?spid=159968964</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">	SURE FASHION S</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>109000</v>
+        <v>35000</v>
       </c>
       <c r="H19" t="n">
-        <v>-59000</v>
+        <v>35000</v>
       </c>
       <c r="I19" t="n">
-        <v>-35.12</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,82 +2019,82 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Giá giảm 59,000đ (35.1%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>102939605</t>
+          <t>188665546</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>áo lót ko gọng cúp B dành cho vòng ngực khủng</t>
+          <t>Lót Giày Nam Chất Liệu Cao Su Non Mềm Êm LGN2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-ko-gong-cup-b-danh-cho-vong-nguc-khung-p102939605.html?spid=201243133</t>
+          <t>https://tiki.vn/lot-giay-nam-chat-lieu-cao-su-non-mem-em-lgn2022-p188665546.html?spid=188665564</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>HA NAM</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>84360</v>
+        <v>22000</v>
       </c>
       <c r="G20" t="n">
-        <v>111000</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>26640</v>
+        <v>-22000</v>
       </c>
       <c r="I20" t="n">
-        <v>31.58</v>
+        <v>-100</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2103,82 +2103,82 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Giá tăng 26,640đ (+31.6%)</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>183725406</t>
+          <t>194096379</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lót giày thể thao, giày tây giày lười cao su non cao 1.5cm TH152</t>
+          <t>Khẩu trang y tế 5 lớp N95+ KHÁNH AN KAN95+ kháng khuẩn màng lọc ngăn 95% bụi mịn nhỏ hơn 2.5 micromet và 99% tia UV, có đệm xốp không bám hơi kính</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/lot-giay-the-thao-giay-tay-giay-luoi-cao-su-non-cao-1-5cm-th152-p183725406.html?spid=183725414</t>
+          <t>https://tiki.vn/khau-trang-y-te-5-lop-n95-khanh-an-kan95-khang-khuan-mang-loc-ngan-95-bui-min-nho-hon-2-5-micromet-va-99-tia-uv-co-dem-xop-khong-bam-hoi-kinh-p194096379.html?spid=276797873</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trường Hải</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>99000</v>
+        <v>48000</v>
       </c>
       <c r="G21" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J21" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="K21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2187,53 +2187,53 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2</v>
+        <v>-5</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Rating 4.5→4.7 (+0.20) | Review thêm +1</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>207936345</t>
+          <t>174305113</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thắt lưng nữ da thật cao cấp nhãn hiệu Macsim ts008</t>
+          <t>Thùng 300/200 khẩu trang KF94 4D Bảo Long Mask kháng khuẩn chống bụi mịn sản xuất tại Việt Nam theo công nghệ 4D và chuẩn KF94 Hàn Quốc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-nu-da-that-cao-cap-nhan-hieu-macsim-ts008-p207936345.html?spid=207936349</t>
+          <t>https://tiki.vn/thung-300-200-khau-trang-kf94-4d-bao-long-mask-khang-khuan-chong-bui-min-san-xuat-tai-viet-nam-theo-cong-nghe-4d-va-chuan-kf94-han-quoc-p174305113.html?spid=174305133</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2243,23 +2243,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Macsim</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>290000</v>
       </c>
       <c r="G22" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>600000</v>
+        <v>-290000</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2271,16 +2271,16 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2290,60 +2290,60 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Không còn xuất hiện trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>276750949</t>
+          <t>249587087</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DÉP NAM QUAI NGANG DA BÒ CAO CẤP VATIS</t>
+          <t>[VỎ ĐỎ MÃ MỚI] Vớ Quần tất Nhật SABRINA Natural da trần tự nhiên mặc hàng ngày chống nắng co giãn thoải mái có size lớn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/dep-nam-quai-ngang-da-bo-cao-cap-vatis-p276750949.html?spid=276750959</t>
+          <t>https://tiki.vn/vo-do-ma-moi-vo-quan-tat-nhat-sabrina-natural-da-tran-tu-nhien-mac-hang-ngay-chong-nang-co-gian-thoai-mai-co-size-lon-p249587087.html?spid=249587139</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vatis</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>149000</v>
+        <v>172000</v>
       </c>
       <c r="G23" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-172000</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2355,876 +2355,36 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5</v>
+        <v>-0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>❌ Đã xóa</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Rating 5.0→4.5 (-0.50) | Review thêm +1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>76369834</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Áo thun nam Novelty cổ tròn 190227 in logo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-nam-novelty-co-tron-190227-in-logo-p76369834.html?spid=76369844</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Novelty</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>299000</v>
-      </c>
-      <c r="G24" t="n">
-        <v>229000</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-70000</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-23.41</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Giá giảm 70,000đ (23.4%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>276811753</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Áo khoác nam áo gió vải gió cao cấp 2 lớp chống nắng tia UV và chống nước</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-khoac-nam-ao-gio-vai-gio-cao-cap-2-lop-chong-nang-tia-uv-va-chong-nuoc-p276811753.html?spid=276811773</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Uniman</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>99000</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-99000</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
           <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>76403471</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Áo thun nam Novelty cổ tim 190236</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-nam-novelty-co-tim-190236-p76403471.html?spid=76403473</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Novelty</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>229000</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-229000</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>90642579</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Sơ mi nữ 2 túi trước,sơ mi đũi nữ, áo form rộng SM28</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/so-mi-nu-2-tui-truoc-so-mi-dui-nu-ao-form-rong-sm28-p90642579.html?spid=90642603</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Thời trang nữ</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Haint Boutique</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>249000</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-249000</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>76309819</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Áo thun nam cổ tròn NOVELTY trơn màu xanh da trời 190154N</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-nam-co-tron-novelty-tron-mau-xanh-da-troi-190154n-p76309819.html?spid=76309825</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Novelty</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>299000</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-299000</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>186192707</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Áo thun Novelty cổ tim Xanh lý NATMMNMCSR190238N</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/ao-thun-novelty-co-tim-xanh-ly-natmmnmcsr190238n-p186192707.html?spid=186192717</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Thời trang nam</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Novelty</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>299000</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-299000</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>277351358</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Nút Nới Rộng Cổ Áo Kim Loại, Mở Rộng Cổ Áo Sơ Mi, Nút Điều Chỉnh Nút Áo Cho Nam Nữ Lò Xo Legaxi</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/nut-noi-rong-co-ao-kim-loai-mo-rong-co-ao-so-mi-nut-dieu-chinh-nut-ao-cho-nam-nu-lo-xo-legaxi-p277351358.html?spid=277351360</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Legaxi</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>52726625</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Combo 5 Đôi Tất Nam Vớ Nam Cổ Ngắn Sợi Cotton Cùng Màu</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/combo-5-doi-tat-nam-vo-nam-co-ngan-soi-cotton-cung-mau-p52726625.html?spid=67278816</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>JM Jamano</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>175000</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-175000</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1592</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>396</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>44012385</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Khăn choàng cổ nam nữ siêu nhẹ - UNQ001</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/khan-choang-co-nam-nu-sieu-nhe-unq001-p44012385.html?spid=44012389</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Phụ kiện thời trang</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>259000</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-259000</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J32" t="n">
-        <v>4</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>❌ Đã xóa</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Không còn xuất hiện trong danh sách</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>278118538</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Keo Dán Giày Nhiệt Trong Suốt Siêu Dính Dùng Không Tổn Thương Da - Giày Da , Giày Thể Thao</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://tiki.vn/keo-dan-giay-nhiet-trong-suot-sieu-dinh-dung-khong-ton-thuong-da-p278118538.html?spid=278118541</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Giày - Dép nam</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LuckyJQR</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>110000</v>
-      </c>
-      <c r="G33" t="n">
-        <v>110000</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>54</v>
-      </c>
-      <c r="K33" t="n">
-        <v>12</v>
-      </c>
-      <c r="L33" t="n">
-        <v>-42</v>
-      </c>
-      <c r="M33" t="n">
-        <v>-4620000</v>
-      </c>
-      <c r="N33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>🔄 Đã cập nhật</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Bán thêm -42 sản phẩm</t>
         </is>
       </c>
     </row>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>186434946</t>
+          <t>112937019</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Túi than hoạt tính khử mùi giày - 100% từ gáo dừa Bến Tre (Hộp 2 túi) - Hapaku</t>
+          <t>Thắt Lưng Co Giãn U863 US ARMY, Mặt Khóa Truyền Thống Chất Liệu Thép Sáng Bóng Không Ghỉ Thiết Kế Thời Trang, Dùng Cho Cả Nam Và Nữ- HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/tui-than-hoat-tinh-khu-mui-giay-100-tu-gao-dua-ben-tre-hop-2-tui-hapaku-p186434946.html?spid=29882855</t>
+          <t>https://tiki.vn/that-lung-co-gian-u863-us-army-mat-khoa-truyen-thong-chat-lieu-thep-sang-bong-khong-ghi-thiet-ke-thoi-trang-dung-cho-ca-nam-va-nu-hang-chinh-hang-p112937019.html?spid=174134839</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hapaku</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>129000</v>
+        <v>170000</v>
       </c>
       <c r="H2" t="n">
-        <v>129000</v>
+        <v>170000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="L2" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="M2" t="n">
-        <v>22188000</v>
+        <v>33830000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,37 +627,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>278049759</t>
+          <t>276125714</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Áo sơ mi nam ngắn tay Novelty Casual Hoa văn SMI25001 - 250079N</t>
+          <t>[Tặng 2 Khăn Ướt Cồn/Bao] Bao Quần Lót Dùng 1 Lần Nữ TRAVEL-MATE 5 Cai/Bao | Đã Giặt Sạch, An Toàn, Tiện Lợi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nam-ngan-tay-novelty-casual-hoa-van-smi25001-p278049759.html?spid=278049917</t>
+          <t>https://tiki.vn/combo-quan-lot-tien-loi-travel-mate-nu-5-cai-bao-p276125714.html?spid=276125729</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Novelty</t>
+          <t>Travel-Mate</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>395000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>395000</v>
+        <v>210000</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,13 +666,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>23730000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -687,293 +687,293 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Rating 0.0→5.0 (+5.00) | Review thêm +4</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>174585329</t>
+          <t>115134722</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Áo lót nâng ngực boya mút mỏng, Áo ngực boya nâng ngực cài sau 522BT</t>
+          <t>Thắt Lưng Nam Vải Dù Mặt Khóa Hợp Kim Thép Đúc Liền Khối A989 US ARMY, Dây lưng lính mỹ -HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nang-nguc-boya-mut-mong-ao-nguc-boya-nang-nguc-cai-sau-522bt-p174585329.html?spid=203717976</t>
+          <t>https://tiki.vn/that-lung-nam-vai-du-mat-khoa-hop-kim-thep-duc-lien-khoi-a989-us-army-day-lung-linh-my-hang-chinh-hang-p115134722.html?spid=174134555</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>86100</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>105000</v>
+        <v>179000</v>
       </c>
       <c r="H4" t="n">
-        <v>18900</v>
+        <v>179000</v>
       </c>
       <c r="I4" t="n">
-        <v>21.95</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>13246000</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Giá tăng 18,900đ (+22.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>133160820</t>
+          <t>183726169</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quần Lót Su Đúc Nữ (Hàng Loại 1) Không Đường Mai, Thun Lạnh, SIêu Co Dãn, Được Chọn Màu</t>
+          <t>Thắt Lưng Nam Vải Dù US ARMY, Dây Nịt Vải Dù Bền Chắc, Khóa Hợp Kim Siêu Bền Cao Cấp- HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-lot-su-duc-nu-hang-loai-1-khong-duong-mai-thun-lanh-sieu-co-dan-duoc-chon-mau-p133160820.html?spid=198901960</t>
+          <t>https://tiki.vn/that-lung-nam-vai-du-us-army-day-nit-vai-du-ben-chac-khoa-hop-kim-sieu-ben-cao-cap-hang-chinh-hang-p183726169.html?spid=183726177</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>21840</v>
+        <v>178000</v>
       </c>
       <c r="H5" t="n">
-        <v>-6160</v>
+        <v>178000</v>
       </c>
       <c r="I5" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>12816000</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Giá giảm 6,160đ (22.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>158732070</t>
+          <t>163716172</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>❈✣♚Combo 10 quần lót nữ su đúc cao cấp không đường may, chất mát lạnh, mềm mịn, thoáng</t>
+          <t>Áo Sơ Mi Nam Xanh Tím Than Ngắn Tay Công Sở Trung Niên Anton Kẻ Caro Thoáng Mát, Thấm Hút Mồ Hôi - NT201</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-10-quan-lot-nu-su-duc-cao-cap-khong-duong-may-chat-mat-lanh-mem-min-thoang-p158732070.html?spid=242324041</t>
+          <t>https://tiki.vn/ao-so-mi-nam-xanh-tim-than-ngan-tay-cong-so-trung-nien-anton-ke-caro-thoang-mat-tham-hut-mo-hoi-nt201-p163716172.html?spid=163716180</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>SOMIANTON</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>252800</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>320000</v>
+        <v>425000</v>
       </c>
       <c r="H6" t="n">
-        <v>67200</v>
+        <v>425000</v>
       </c>
       <c r="I6" t="n">
-        <v>26.58</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5525000</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Giá tăng 67,200đ (+26.6%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>103049077</t>
+          <t>13701589</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (Có size lớn) Hộp 4 quần lót boxer nam William WS60 - Quần sịp đùi lưới thông hơi thoáng mát</t>
+          <t>Áo Khoác Da Nam Nâu Lót Lông Trơn ShopN6 Cao Cấp AKD05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/co-size-lon-hop-4-quan-lot-boxer-nam-william-ws60-quan-sip-dui-luoi-thong-hoi-thoang-mat-p103049077.html?spid=145612013</t>
+          <t>https://tiki.vn/ao-khoac-da-nam-nau-lot-long-tron-shopn6-cao-cap-akd05-p13701589.html?spid=13701597</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -983,333 +983,333 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>185000</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>144300</v>
+        <v>309000</v>
       </c>
       <c r="H7" t="n">
-        <v>-40700</v>
+        <v>309000</v>
       </c>
       <c r="I7" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5253000</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Giá giảm 40,700đ (22.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>244298352</t>
+          <t>90483623</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quần Gen Ôm Bụng Dạng Đùi Có Thanh Chống Cuộn Voronin 8292 – Siêu Gọn, Siêu Định Hình</t>
+          <t>Combo 3 Áo thun nam ba lỗ cotton FREEMAN ASF205</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-gen-chong-cuon-dui-8292-p244298352.html?spid=244298362</t>
+          <t>https://tiki.vn/ao-thun-nam-ba-lo-cotton-freeman-asf205-combo-3-p90483623.html?spid=90483629</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>102480</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>122000</v>
+        <v>240300</v>
       </c>
       <c r="H8" t="n">
-        <v>19520</v>
+        <v>240300</v>
       </c>
       <c r="I8" t="n">
-        <v>19.05</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3364200</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Giá tăng 19,520đ (+19.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>214706031</t>
+          <t>248928122</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Áo lót áo ngực Thái lan có gọng mút kép nâng ngực tạo khe, áo lót nữ thông hơi hàng CAO CẤP</t>
+          <t>Quần Âu Nam Công Sở Trung Niên Thương Hiệu Anton Dáng Suông Rộng Màu Đen Xếp Ly Mã QA404</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-ao-nguc-thai-lan-co-gong-mut-kep-nang-nguc-tao-khe-ao-lot-nu-thong-hoi-hang-cao-cap-p214706031.html?spid=215408041</t>
+          <t>https://tiki.vn/quan-au-nam-cong-so-trung-nien-thuong-hieu-anton-dang-suong-rong-mau-den-xep-ly-ma-qa404-p248928122.html?spid=248928126</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>SOMIANTON</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>98400</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>120000</v>
+        <v>328000</v>
       </c>
       <c r="H9" t="n">
-        <v>21600</v>
+        <v>328000</v>
       </c>
       <c r="I9" t="n">
-        <v>21.95</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3280000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Giá tăng 21,600đ (+22.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>112851354</t>
+          <t>271395656</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Áo ngực học sinh</t>
+          <t>Bao Quần Lót Miễn Giặt Tiện Lợi TRAVEL-MATE Nam, 5 Cái/Bao</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-nguc-hoc-sinh-p112851354.html?spid=142138792</t>
+          <t>https://tiki.vn/bao-quan-lot-tien-loi-travel-mate-nam-5-cai-bao-p271395656.html?spid=271395660</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Travel-Mate</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>34860</v>
+        <v>30000</v>
       </c>
       <c r="H10" t="n">
-        <v>-7140</v>
+        <v>30000</v>
       </c>
       <c r="I10" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2370000</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Giá giảm 7,140đ (17.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>113145806</t>
+          <t>276118600</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Áo lót nâng ngực nhẹ quả trơn mẫu siêu bền</t>
+          <t>[Tặng 2 Khăn Ướt Cồn/Bao] Bao Quần Đùi Miễn Giặt Body-Mate Nữ | Đã Giặt Sạch, Đóng Gói Tự Động, An Toàn Tiện Lợi | 3 Cái/Bao</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-nang-nguc-nhe-qua-tron-mau-sieu-ben-p113145806.html?spid=142118731</t>
+          <t>https://tiki.vn/combo-quan-dui-mien-giat-body-mate-nu-3-cai-bao-p276118600.html?spid=276118611</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1319,138 +1319,138 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>BODY-MATE</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>124000</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>102920</v>
+        <v>300000</v>
       </c>
       <c r="H11" t="n">
-        <v>-21080</v>
+        <v>300000</v>
       </c>
       <c r="I11" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Giá giảm 21,080đ (17.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>144236336</t>
+          <t>87981660</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COMBO 5 ÁO LÓT VẢI KHÔNG GỌNG KHÔNG MÚT (SIZE 32-42)</t>
+          <t>Combo 2 áo ba lỗ nam, áo 3 lỗ nam, sợi cotton mềm mịn, thấm hút mồ hôi tốt, thoáng mát, mặc thoải mái JAMANO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-5-ao-lot-vai-khong-gong-khong-mut-size-32-42-p144236336.html?spid=146366320</t>
+          <t>https://tiki.vn/combo-2-ao-ba-lo-nam-ao-3-lo-nam-soi-cotton-mem-min-tham-hut-mo-hoi-tot-thoang-mat-mac-thoai-mai-jamano-p87981660.html?spid=87981797</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>JAMANO</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>210000</v>
+        <v>198000</v>
       </c>
       <c r="G12" t="n">
-        <v>163800</v>
+        <v>198000</v>
       </c>
       <c r="H12" t="n">
-        <v>-46200</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>30</v>
+        <v>1921</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>1929</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1584000</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>332</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>332</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1460,143 +1460,143 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Giá giảm 46,200đ (22.0%)</t>
+          <t>Bán thêm +8 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>108220832</t>
+          <t>248632967</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Miếng Dán Ngực Cài Trước Hình Bàn Tay Siêu Nâng Ngực, Siêu Dính P29 Size A-B</t>
+          <t>Áo Sơ Mi Nam Trung Niên Công Sở Anton Somianton Dài Tay Vải Sợi Tre Kẻ Caro - AC26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bra-dan-nguc-ban-tay-p29-kem-day-trong-p108220832.html?spid=242370964</t>
+          <t>https://tiki.vn/ao-so-mi-nam-trung-nien-cong-so-anton-somianton-dai-tay-vai-soi-tre-ke-caro-ac26-p248632967.html?spid=248632971</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>63200</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>80000</v>
+        <v>325000</v>
       </c>
       <c r="H13" t="n">
-        <v>16800</v>
+        <v>325000</v>
       </c>
       <c r="I13" t="n">
-        <v>26.58</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1300000</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Giá tăng 16,800đ (+26.6%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>244297862</t>
+          <t>67548437</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Áo Lót Nữ Bra Ống Su Gân Viền Ren Cài Sau 4003 – Seamless, Co Giãn 4 Chiều</t>
+          <t>Áo Khoác Nam Áo Khoác Dù Nam Hai Lớp Cổ Cao Chống Nắng Tia Cực Tím Chống Lạnh Giá Tốt AD60 - ShopN6 (Nhiều Màu)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-bra-ong-su-gan-cai-sau-4003-p244297862.html?spid=244297867</t>
+          <t>https://tiki.vn/ao-khoac-nam-ao-khoac-du-nam-hai-lop-co-cao-chong-nang-tia-cuc-tim-chong-lanh-gia-tot-ad60-shopn6-nhieu-mau-p67548437.html?spid=67548445</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>38640</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>46000</v>
+        <v>199000</v>
       </c>
       <c r="H14" t="n">
-        <v>7360</v>
+        <v>199000</v>
       </c>
       <c r="I14" t="n">
-        <v>19.05</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1194000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1618,39 +1618,39 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>🔄 Đã cập nhật</t>
+          <t>🆕 Sản phẩm mới</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Giá tăng 7,360đ (+19.0%)</t>
+          <t>Xuất hiện lần đầu trong danh sách</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>102939605</t>
+          <t>276479781</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>áo lót ko gọng cúp B dành cho vòng ngực khủng</t>
+          <t>Mũ Nón Chống Nắng Ninja Fullface Kèm Khẩu Trang Lưới Vải Co Giãn Thoáng Khí Có Thể Gấp Gọn Đi Phượt Dã Ngoại Câu Cá Unisex</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-lot-ko-gong-cup-b-danh-cho-vong-nguc-khung-p102939605.html?spid=201243133</t>
+          <t>https://tiki.vn/mu-non-chong-nang-ninja-fullface-kem-khau-trang-luoi-vai-co-gian-thoang-khi-co-the-gap-gon-di-phuot-da-ngoai-cau-ca-unisex-p276479781.html?spid=276479783</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1659,50 +1659,50 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>111000</v>
+        <v>148000</v>
       </c>
       <c r="G15" t="n">
-        <v>86580</v>
+        <v>148000</v>
       </c>
       <c r="H15" t="n">
-        <v>-24420</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>296000</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1712,24 +1712,24 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Giá giảm 24,420đ (22.0%)</t>
+          <t>Bán thêm +2 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>276479781</t>
+          <t>16621985</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mũ Nón Chống Nắng Ninja Fullface Kèm Khẩu Trang Lưới Vải Co Giãn Thoáng Khí Có Thể Gấp Gọn Đi Phượt Dã Ngoại Câu Cá Unisex</t>
+          <t>Bộ găng tay chống nắng xỏ ngón</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mu-non-chong-nang-ninja-fullface-kem-khau-trang-luoi-vai-co-gian-thoang-khi-co-the-gap-gon-di-phuot-da-ngoai-cau-ca-unisex-p276479781.html?spid=276479783</t>
+          <t>https://tiki.vn/bo-gang-tay-chong-nang-xo-ngon-p16621985.html?spid=17014647</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1743,50 +1743,50 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>74000</v>
+        <v>28000</v>
       </c>
       <c r="G16" t="n">
-        <v>148000</v>
+        <v>28000</v>
       </c>
       <c r="H16" t="n">
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>9</v>
+        <v>658</v>
       </c>
       <c r="K16" t="n">
-        <v>9</v>
+        <v>659</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1796,24 +1796,24 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Giá tăng 74,000đ (+100.0%)</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>278993558</t>
+          <t>275737280</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gọng Kính Cận Giả Cận Nam Nữ Cao Cấp Titanium BLUE LIGHT Mắt Khoan Không Viền Chữ Nhật Bạc Đen Vàng Dày Dặn Cứng Nhẹ</t>
+          <t>Dụng cụ che mắt ngủ - Đen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://tiki.vn/gong-kinh-can-gia-can-nam-nu-cao-cap-titanium-blue-light-mat-khoan-khong-vien-chu-nhat-bac-den-vang-day-dan-cung-nhe-p278993558.html?spid=278993563</t>
+          <t>https://tiki.vn/dung-cu-che-mat-ngu-p275737280.html?spid=20283217</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1823,110 +1823,110 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Blue Light</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="G17" t="n">
-        <v>985000</v>
+        <v>28000</v>
       </c>
       <c r="H17" t="n">
-        <v>985000</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>77625091</t>
+          <t>108772138</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gọng Kính cận, Kính giả cận Mắt vuông form nhỏ cao cấp - GCH2276</t>
+          <t>Áo Thun Nam Ngắn Tay Không Cổ US ARMY U229, Chất Liệu Cotton Thoáng Mát, Mềm Mịn, Mát, Bền Màu-HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://tiki.vn/gong-kinh-can-kinh-gia-can-mat-vuong-form-nho-cao-cap-gch2276-tang-tuavit-kinh-xinh-mini-tien-loi-p77625091.html?spid=77625097</t>
+          <t>https://tiki.vn/ao-thun-nam-ngan-tay-kieu-linh-khong-co-us-army-u229-chat-lieu-cotton-thoang-mat-mem-min-mat-ben-mau-hang-chinh-hang-p108772138.html?spid=178779987</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LiLiLa</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>199000</v>
       </c>
       <c r="G18" t="n">
-        <v>189000</v>
+        <v>398000</v>
       </c>
       <c r="H18" t="n">
-        <v>189000</v>
+        <v>199000</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1935,82 +1935,82 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 199,000đ (+100.0%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>44666139</t>
+          <t>276366333</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mũ lưỡi trai nam nữ vải lưới thoáng mát thời trang không logo, không thêu, che nắng tốt, bảo vệ da</t>
+          <t>Aó khoác gió nam US ARMY đặc biệt Chống Gió, Chống nắng form chuẩn hàng đẹp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://tiki.vn/mu-luoi-trai-nam-nu-vai-luoi-thoang-mat-thoi-trang-khong-logo-khong-theu-che-nang-tot-bao-ve-da-p44666139.html?spid=159968964</t>
+          <t>https://tiki.vn/ao-khoac-gio-nam-us-army-dac-biet-chong-gio-chong-nang-form-chuan-hang-dep-p276366333.html?spid=276366828</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>429000</v>
       </c>
       <c r="G19" t="n">
-        <v>35000</v>
+        <v>858000</v>
       </c>
       <c r="H19" t="n">
-        <v>35000</v>
+        <v>429000</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2019,82 +2019,82 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá tăng 429,000đ (+100.0%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>188665546</t>
+          <t>244297794</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lót Giày Nam Chất Liệu Cao Su Non Mềm Êm LGN2022</t>
+          <t>Combo 5 Quần Lót Nam Thun Lạnh Lưng To Menlive ML1 – Size M–4XL, Co Giãn 4 Chiều</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://tiki.vn/lot-giay-nam-chat-lieu-cao-su-non-mem-em-lgn2022-p188665546.html?spid=188665564</t>
+          <t>https://tiki.vn/combo-5-quan-lot-nam-thun-lanh-menlive-p244297794.html?spid=244297815</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Giày - Dép nam</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HA NAM</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>22000</v>
+        <v>164000</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>205000</v>
       </c>
       <c r="H20" t="n">
-        <v>-22000</v>
+        <v>41000</v>
       </c>
       <c r="I20" t="n">
-        <v>-100</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2103,58 +2103,58 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá tăng 41,000đ (+25.0%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>194096379</t>
+          <t>174585329</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Khẩu trang y tế 5 lớp N95+ KHÁNH AN KAN95+ kháng khuẩn màng lọc ngăn 95% bụi mịn nhỏ hơn 2.5 micromet và 99% tia UV, có đệm xốp không bám hơi kính</t>
+          <t>Áo lót nâng ngực boya mút mỏng, Áo ngực boya nâng ngực cài sau 522BT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://tiki.vn/khau-trang-y-te-5-lop-n95-khanh-an-kan95-khang-khuan-mang-loc-ngan-95-bui-min-nho-hon-2-5-micromet-va-99-tia-uv-co-dem-xop-khong-bam-hoi-kinh-p194096379.html?spid=276797873</t>
+          <t>https://tiki.vn/ao-lot-nang-nguc-boya-mut-mong-ao-nguc-boya-nang-nguc-cai-sau-522bt-p174585329.html?spid=203717976</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2163,22 +2163,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>48000</v>
+        <v>105000</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>90300</v>
       </c>
       <c r="H21" t="n">
-        <v>-48000</v>
+        <v>-14700</v>
       </c>
       <c r="I21" t="n">
-        <v>-100</v>
+        <v>-14</v>
       </c>
       <c r="J21" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2190,55 +2190,55 @@
         <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Giá giảm 14,700đ (14.0%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>174305113</t>
+          <t>278092142</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thùng 300/200 khẩu trang KF94 4D Bảo Long Mask kháng khuẩn chống bụi mịn sản xuất tại Việt Nam theo công nghệ 4D và chuẩn KF94 Hàn Quốc</t>
+          <t>Quần kiểu nữ ống rộng, chất liệu vải Đũi xước, mềm mịn, mặc mát, Quần Short nữ đẹp Nesa Shop</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://tiki.vn/thung-300-200-khau-trang-kf94-4d-bao-long-mask-khang-khuan-chong-bui-min-san-xuat-tai-viet-nam-theo-cong-nghe-4d-va-chuan-kf94-han-quoc-p174305113.html?spid=174305133</t>
+          <t>https://tiki.vn/quan-kieu-nu-ong-rong-chat-lieu-vai-dui-xuoc-mem-min-mac-mat-quan-short-nu-dep-nesa-shop-p278092142.html?spid=278092148</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nữ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2247,142 +2247,3250 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>290000</v>
+        <v>55000</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="H22" t="n">
-        <v>-290000</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>20</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8</v>
+      </c>
+      <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>❌ Đã xóa</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Không còn xuất hiện trong danh sách</t>
+          <t>Rating 4.7→4.6 (-0.10) | Review thêm +1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>249587087</t>
+          <t>174593731</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[VỎ ĐỎ MÃ MỚI] Vớ Quần tất Nhật SABRINA Natural da trần tự nhiên mặc hàng ngày chống nắng co giãn thoải mái có size lớn</t>
+          <t>Quần Short NamThể Thao Thanh Lịch US ARMY 8898 Trẻ Trung, Năng Động, Nam Tính -HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://tiki.vn/vo-do-ma-moi-vo-quan-tat-nhat-sabrina-natural-da-tran-tu-nhien-mac-hang-ngay-chong-nang-co-gian-thoai-mai-co-size-lon-p249587087.html?spid=249587139</t>
+          <t>https://tiki.vn/quan-short-namthe-thao-thanh-lich-us-army-8898-tre-trung-nang-dong-nam-tinh-hang-chinh-hang-p174593731.html?spid=177619669</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>73</v>
+      </c>
+      <c r="K23" t="n">
+        <v>73</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>29</v>
+      </c>
+      <c r="R23" t="n">
+        <v>29</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Giá tăng 150,000đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>52184516</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Combo 3 quần lót nam Boxer sợi Organic mềm mịn thoáng mát co giãn 4 chiều MRM Manlywear ( TẶNG Đôi Tất Nam Cao Cấp Giao Ngẫu Nhiên)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-3-qua-n-lo-t-nam-boxer-so-i-cotton-organic-me-m-mi-n-thoa-ng-ma-t-co-gia-n-4-chie-u-mrm-manlywear-tang-doi-tat-nam-cao-cap-giao-ngau-nhien-p52184516.html?spid=270876532</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MRM Manlywear</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>199000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4345</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4345</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1245</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1246</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Review thêm +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>104904605</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quần short nam big size quần sọt nam thể thao quần đùi nam mặc nhà quần thun nam cotton 4 chiều co giãn cao cấp ShopN6 - TSB2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-short-nam-big-size-quan-sot-nam-the-thao-quan-dui-nam-mac-nha-quan-thun-nam-cotton-4-chieu-co-gian-cao-cap-shopn6-tsb2-p104904605.html?spid=104904625</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>69000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>89000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="J25" t="n">
+        <v>714</v>
+      </c>
+      <c r="K25" t="n">
+        <v>714</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>135</v>
+      </c>
+      <c r="R25" t="n">
+        <v>135</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Giá tăng 20,000đ (+29.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>112086654</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Quần Túi Hộp Nam Lính Mỹ US ARMY U768 Cao Cấp, Chất Liệu Vải Kaki,Bền Màu, Ống Rộng Phong Cách, Thiết kế Túi Hộp- HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-tui-hop-nam-linh-my-us-army-u768-cao-cap-chat-lieu-vai-kaki-ben-mau-ong-rong-phong-cach-thiet-ke-tui-hop-hang-chinh-hang-p112086654.html?spid=174219473</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" t="n">
+        <v>92</v>
+      </c>
+      <c r="K26" t="n">
+        <v>92</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>38</v>
+      </c>
+      <c r="R26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Giá tăng 500,000đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>110139205</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Áo Gile Nam Lính Mỹ U869 Phong Cách US ARMY - HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-gile-nam-linh-my-u869-phong-cach-us-army-hang-chinh-hang-p110139205.html?spid=174134971</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>399500</v>
+      </c>
+      <c r="G27" t="n">
+        <v>799000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>399500</v>
+      </c>
+      <c r="I27" t="n">
+        <v>100</v>
+      </c>
+      <c r="J27" t="n">
+        <v>95</v>
+      </c>
+      <c r="K27" t="n">
+        <v>95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>30</v>
+      </c>
+      <c r="R27" t="n">
+        <v>30</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Giá tăng 399,500đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>95052893</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quần short nam big size quần sọt nam thể thao chống nóng quần đùi nam mặc nhà quần thun nam cotton 4 chiều co giãn cao cấp WSB2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-short-nam-big-size-quan-sot-nam-the-thao-chong-nong-quan-dui-nam-mac-nha-quan-thun-nam-cotton-4-chieu-co-gian-cao-cap-wsb2-p95052893.html?spid=95052915</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>69000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>89000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1443</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1443</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>288</v>
+      </c>
+      <c r="R28" t="n">
+        <v>288</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Giá tăng 20,000đ (+29.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>276491587</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Set Váy Ngủ 2 Dây Ren Dài Sexy Dễ Thương Freesize</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/set-vay-ngu-2-day-ren-dai-sexy-de-thuong-freesize-p276491587.html?spid=276491589</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>99000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>198000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>99000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" t="n">
+        <v>13</v>
+      </c>
+      <c r="K29" t="n">
+        <v>13</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Giá tăng 99,000đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>108220832</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Miếng Dán Ngực Cài Trước Hình Bàn Tay Siêu Nâng Ngực, Siêu Dính P29 Size A-B</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bra-dan-nguc-ban-tay-p29-kem-day-trong-p108220832.html?spid=242370964</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>65600</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-14400</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-18</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Giá giảm 14,400đ (18.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>214706031</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Áo lót áo ngực Thái lan có gọng mút kép nâng ngực tạo khe, áo lót nữ thông hơi hàng CAO CẤP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-lot-ao-nguc-thai-lan-co-gong-mut-kep-nang-nguc-tao-khe-ao-lot-nu-thong-hoi-hang-cao-cap-p214706031.html?spid=215408041</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G31" t="n">
+        <v>103200</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-16800</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-14</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Giá giảm 16,800đ (14.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>244298352</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quần Gen Ôm Bụng Dạng Đùi Có Thanh Chống Cuộn Voronin 8292 – Siêu Gọn, Siêu Định Hình</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-gen-chong-cuon-dui-8292-p244298352.html?spid=244298362</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>122000</v>
+      </c>
+      <c r="G32" t="n">
+        <v>97600</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-24400</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Giá giảm 24,400đ (20.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>104791604</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Quần lót nữ thái lan 828 – Chất thun lạnh - giao màu ngẫu nhiên</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/quan-lot-nu-thai-lan-828-chat-thun-lanh-giao-mau-ngau-nhien-p104791604.html?spid=270215621</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>33880</v>
+      </c>
+      <c r="G33" t="n">
+        <v>44000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>10120</v>
+      </c>
+      <c r="I33" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="J33" t="n">
+        <v>24</v>
+      </c>
+      <c r="K33" t="n">
+        <v>24</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Giá tăng 10,120đ (+29.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>158732070</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>❈✣♚Combo 10 quần lót nữ su đúc cao cấp không đường may, chất mát lạnh, mềm mịn, thoáng</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/combo-10-quan-lot-nu-su-duc-cao-cap-khong-duong-may-chat-mat-lanh-mem-min-thoang-p158732070.html?spid=242324041</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>320000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>262400</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-57600</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-18</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>7</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Giá giảm 57,600đ (18.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>244297862</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Áo Lót Nữ Bra Ống Su Gân Viền Ren Cài Sau 4003 – Seamless, Co Giãn 4 Chiều</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-bra-ong-su-gan-cai-sau-4003-p244297862.html?spid=244297867</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>46000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-9200</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Giá giảm 9,200đ (20.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>276838333</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Giày Sandal nam kiểu dáng mới chống trơn, trượt – GSDNA07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/giay-sandal-nam-kieu-dang-moi-chong-tron-truot-gsdna07-p276838333.html?spid=276838339</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Bee Gee</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>880000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>792000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-88000</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Giá giảm 88,000đ (10.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>277808993</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dây thắt lưng 3.5 lớp da bò thân thắt lưng da bò lớp đầu tiên cao cấp</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/day-that-lung-3-5-lop-da-bo-than-that-lung-da-bo-lop-dau-tien-cao-cap-p277808993.html?spid=278533981</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>Phụ kiện thời trang</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ANANSHOP688</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>190000</v>
+      </c>
+      <c r="G37" t="n">
+        <v>190000</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>18</v>
+      </c>
+      <c r="K37" t="n">
+        <v>18</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Review thêm +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>136019521</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Khăn Choàng Lụa Hàng Châu Cao Cấp Sang Trọng 180x90 cm</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/khan-choang-lua-hang-chau-cao-cap-sang-trong-180x90-cm-p136019521.html?spid=278751435</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>172000</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-172000</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="F38" t="n">
+        <v>99000</v>
+      </c>
+      <c r="G38" t="n">
+        <v>198000</v>
+      </c>
+      <c r="H38" t="n">
+        <v>99000</v>
+      </c>
+      <c r="I38" t="n">
+        <v>100</v>
+      </c>
+      <c r="J38" t="n">
+        <v>87</v>
+      </c>
+      <c r="K38" t="n">
+        <v>87</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>21</v>
+      </c>
+      <c r="R38" t="n">
+        <v>21</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Giá tăng 99,000đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>276160187</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DÉP NAM  DA BÒ CAO CẤP VATIS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/dep-nam-da-bo-cao-cap-vatis-p276160187.html?spid=276160193</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Vatis</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>299000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>299000</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>🆕 Sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Xuất hiện lần đầu trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>278883766</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Khăn BANDANA, Khăn Turban Hiphop Nam Nữ Màu Sắc Trẻ Trung Năng Động</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/khan-bandana-khan-turban-hiphop-nam-nu-mau-sac-tre-trung-nang-dong-p278883766.html?spid=278883775</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>24000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I40" t="n">
+        <v>100</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Giá tăng 24,000đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>142538263</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Găng Tay Đi Phượt Hở Ngón 5.11 U890, Găng Tay Phượt, Tập Gym, Thể Thao Đa Năng  - HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/gang-tay-di-phuot-ho-ngon-5-11-u890-gang-tay-phuo-t-tap-gym-the-thao-da-nang-hang-chinh-hang-p142538263.html?spid=174115031</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>49000</v>
+      </c>
+      <c r="G41" t="n">
+        <v>98000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>49000</v>
+      </c>
+      <c r="I41" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" t="n">
+        <v>451</v>
+      </c>
+      <c r="K41" t="n">
+        <v>451</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>104</v>
+      </c>
+      <c r="R41" t="n">
+        <v>104</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Giá tăng 49,000đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>225935219</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Thắt Lưng Nam Vải Dù US ARMY Mặt Khóa Truyền Thống, Phong Cách Cổ Điển Mặt Khóa Hợp Kim Thép Chống Ghỉ Cao Cấp -HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-vai-du-us-army-mat-khoa-truyen-thong-phong-cach-co-dien-mat-khoa-hop-kim-thep-chong-ghi-cao-cap-hang-chinh-hang-p225935219.html?spid=225935221</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>99500</v>
+      </c>
+      <c r="G42" t="n">
+        <v>199000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>99500</v>
+      </c>
+      <c r="I42" t="n">
+        <v>100</v>
+      </c>
+      <c r="J42" t="n">
+        <v>27</v>
+      </c>
+      <c r="K42" t="n">
+        <v>27</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Giá tăng 99,500đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>183685137</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Thắt Lưng Dây Nịt Nam Vải Dù US ARMY, Phong Cách Sang Trọng Cổ Điển Mặt Khóa Hợp Kim Thép Chống Ghỉ Cao Cấp -HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-day-nit-nam-vai-du-us-army-phong-cach-sang-trong-co-dien-mat-khoa-hop-kim-thep-chong-ghi-cao-cap-hang-chinh-hang-p183685137.html?spid=183685139</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>79000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>158000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>79000</v>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="n">
+        <v>222</v>
+      </c>
+      <c r="K43" t="n">
+        <v>222</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>59</v>
+      </c>
+      <c r="R43" t="n">
+        <v>59</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Giá tăng 79,000đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>112814658</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Thắt Lưng Nam Dây Vải Dù Phong Cách Lính U379 US ARMY, Khóa Cài Tự Động Dễ Dàng Điều Chỉnh Theo Vòng Bụng- HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-day-vai-du-phong-cach-linh-u379-us-army-khoa-cai-tu-dong-de-dang-dieu-chinh-theo-vong-bung-hang-chinh-hang-p112814658.html?spid=174134932</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>99000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>198000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>99000</v>
+      </c>
+      <c r="I44" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" t="n">
+        <v>75</v>
+      </c>
+      <c r="K44" t="n">
+        <v>75</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5</v>
+      </c>
+      <c r="O44" t="n">
+        <v>5</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>29</v>
+      </c>
+      <c r="R44" t="n">
+        <v>29</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Giá tăng 99,000đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>52154918</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trâm Cài Áo Nữ Hình Hoa Mẫu Đơn Trang Nhã Sang Trọng </t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/tram-cai-ao-nu-hinh-hoa-mau-don-trang-nha-sang-trong-p52154918.html?spid=52154919</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>74000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>148000</v>
+      </c>
+      <c r="H45" t="n">
+        <v>74000</v>
+      </c>
+      <c r="I45" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" t="n">
+        <v>26</v>
+      </c>
+      <c r="K45" t="n">
+        <v>26</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>5</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>9</v>
+      </c>
+      <c r="R45" t="n">
+        <v>9</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Giá tăng 74,000đ (+100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>276618589</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Găng tay chống gió lạnh Rhino G905 lót lông cừu nam nữ cảm ứng điện thoại</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/gang-tay-chong-gio-lanh-rhino-g905-lot-long-cuu-nam-nu-cam-ung-dien-thoai-p276618589.html?spid=276618595</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Rhino Store</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>165000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>199000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>34000</v>
+      </c>
+      <c r="I46" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Giá tăng 34,000đ (+20.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>114005422</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Thắt Lưng Nam Cao Cấp Vải Dù Bền Bỉ, Mặt Khóa Tự Động U859 US ARMY Phong Cách Lính Mỹ -HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/that-lung-nam-cao-cap-vai-du-ben-bi-mat-khoa-tu-dong-u859-us-army-phong-cach-linh-my-hang-chinh-hang-p114005422.html?spid=174219361</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>89000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>89500</v>
+      </c>
+      <c r="H47" t="n">
+        <v>500</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J47" t="n">
+        <v>79</v>
+      </c>
+      <c r="K47" t="n">
+        <v>79</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5</v>
+      </c>
+      <c r="O47" t="n">
+        <v>5</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>32</v>
+      </c>
+      <c r="R47" t="n">
+        <v>32</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>🔄 Đã cập nhật</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Giá tăng 500đ (+0.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>57786091</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Áo Khoác Kaki Nam 2 Lớp Giả Vest Phối Khóa Ngực Cao Cấp ShopN6 - KK42 (Nhiều Màu)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-kaki-nam-2-lop-gia-vest-phoi-khoa-nguc-cao-cap-shopn6-kk42-nhieu-mau-p57786091.html?spid=57786105</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I48" t="n">
         <v>-100</v>
       </c>
-      <c r="J23" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="J48" t="n">
+        <v>28</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>12</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>111850645</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Bộ Quần Áo KaKi Lính Mỹ US ARMY U569 Kiểu Dáng Túi Hộp Chiến Thuật, Chất Liệu Kaki Cao Cấp Phong Cách Lính Cực Ngầu - HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/bo-quan-ao-kaki-linh-my-us-army-u569-kieu-dang-tui-hop-chien-thuat-chat-lieu-kaki-cao-cap-phong-cach-linh-cuc-ngau-hang-chinh-hang-p111850645.html?spid=174217143</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>899000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-899000</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J49" t="n">
+        <v>18</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>15129168</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Áo Khoác Dù Nam 2 Lớp Chống Nắng Chống Gió Cao Cấp ShopN6 KM08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-du-nam-2-lop-chong-nang-chong-gio-cao-cap-shopn6-km08-p15129168.html?spid=15129182</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>255000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-255000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J50" t="n">
+        <v>158</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>10</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>67595415</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Áo Khoác Dù Nam Nữ Áo Khoác Nam RG Chống Nắng Chống Lạnh Cổ Cao Hai Lớp Cao Cấp AD62 - ShopN6 (Nhiều Màu)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-du-nam-nu-ao-khoac-nam-rg-chong-nang-chong-lanh-co-cao-hai-lop-cao-cap-ad62-shopn6-nhieu-mau-p67595415.html?spid=67595427</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J51" t="n">
+        <v>145</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>61</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51714411</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Áo khoác dù dày nam 2 lớp chống nắng gió lạnh cao cấp ShopN6 - KAD46 (Nhiều Màu)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-du-day-nam-2-lop-chong-nang-gio-lanh-cao-cap-shopn6-kad46-nhieu-mau-p51714411.html?spid=51714417</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J52" t="n">
+        <v>330</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>93</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>73332663</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Áo Khoác Nam Big Size Áo Khoác Dù Nam Dày Hai Lớp Cổ Cao Chống Nắng Tia Uv Chống Gió Chống Lạnh Hàn Quốc Cao Cấp QD28 - ShopN6 (Nhiều Màu)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-nam-big-size-ao-khoac-du-nam-day-hai-lop-co-cao-chong-nang-tia-uv-chong-gio-chong-lanh-han-quoc-cao-cap-qd28-shopn6-nhieu-mau-p73332663.html?spid=73332675</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>189000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-189000</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J53" t="n">
+        <v>229</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>111</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>101463378</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Áo Khoác Big Size Nam Nữ 2 Áo Khoác Dù Bomber Nam Nữ 2 lớp Chống Nắng Chống Nóng Chống Tia Cực Tím UV Chống Lạnh Chống Gió Có Cổ Màu Hàn Quốc Cao Cấp ShopN6 - AD76</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-big-size-nam-nu-2-ao-khoac-du-bomber-nam-nu-2-lop-chong-nang-chong-nong-chong-tia-cuc-tim-uv-chong-lanh-chong-gio-co-co-mau-han-quoc-cao-cap-shopn6-ad76-p101463378.html?spid=101463396</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Thời trang nam</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>199000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-199000</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>70442208</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Áo khoác nữ Áo khoát nữ kaki chống nắng phối lưng cực chất đẹp</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-khoac-nu-ao-khoat-nu-kaki-chong-nang-phoi-lung-cuc-chat-dep-p70442208.html?spid=113228676</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>208150</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-208150</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>67978131</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ÁO SỌC BỤI BỤI FORM RỘNG</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/ao-soc-bui-bui-form-rong-p67978131.html?spid=67978147</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Thời trang nữ</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>119000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-119000</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
         <v>-0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
         <is>
           <t>❌ Đã xóa</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>186677573</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Dép Quai Ngang Nam Đúc Liền Quick Cao Cấp DP15</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/de-p-quai-ngang-nam-du-c-lie-n-quick-cao-ca-p-dp15-p186677573.html?spid=186677583</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Giày - Dép nam</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Laceva</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>278000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-278000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J57" t="n">
+        <v>518</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>111</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>112562057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Dây Lưng Vải Nam U689 US ARMY Phong Cách Lính, Mặt Khóa Hợp Kim Thép Không Ghỉ Sáng Bóng-HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/day-lung-vai-nam-u689-us-army-phong-cach-linh-mat-khoa-hop-kim-thep-khong-ghi-sang-bong-hang-chinh-hang-p112562057.html?spid=174219791</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>89000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-89000</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J58" t="n">
+        <v>174</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>60</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>140843587</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mũ Lưỡi Trai Lính Mỹ US ARMY U890, Nón Lưỡi Trai Rằn Ri Đi Phượt Phong Cách Lính - HÀNG CHÍNH HÃNG</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/mu-luoi-trai-linh-my-us-army-u890-non-luoi-trai-ran-ri-di-phuot-phong-cach-linh-hang-chinh-hang-p140843587.html?spid=174134712</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>US ARMY</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>89000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-89000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J59" t="n">
+        <v>208</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>61</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Không còn xuất hiện trong danh sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>278993558</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Gọng Kính Cận Giả Cận Nam Nữ Cao Cấp Titanium BLUE LIGHT Mắt Khoan Không Viền Chữ Nhật Bạc Đen Vàng Dày Dặn Cứng Nhẹ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://tiki.vn/gong-kinh-can-gia-can-nam-nu-cao-cap-titanium-blue-light-mat-khoan-khong-vien-chu-nhat-bac-den-vang-day-dan-cung-nhe-p278993558.html?spid=278993563</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Phụ kiện thời trang</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Blue Light</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>985000</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-985000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>❌ Đã xóa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
         <is>
           <t>Không còn xuất hiện trong danh sách</t>
         </is>

--- a/tiki_changes_report.xlsx
+++ b/tiki_changes_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>112937019</t>
+          <t>93233783</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thắt Lưng Co Giãn U863 US ARMY, Mặt Khóa Truyền Thống Chất Liệu Thép Sáng Bóng Không Ghỉ Thiết Kế Thời Trang, Dùng Cho Cả Nam Và Nữ- HÀNG CHÍNH HÃNG</t>
+          <t>Áo Khoác Big Size Nam Nữ Unisex Áo Khoác Dù Nam 2 Lớp Chống Nắng Chống Lạnh Chống Gió Thời Trang Phom Body Phối Màu Hàn Quốc Cao Cấp AD73 - ShopN6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-co-gian-u863-us-army-mat-khoa-truyen-thong-chat-lieu-thep-sang-bong-khong-ghi-thiet-ke-thoi-trang-dung-cho-ca-nam-va-nu-hang-chinh-hang-p112937019.html?spid=174134839</t>
+          <t>https://tiki.vn/ao-khoac-big-size-nam-nu-unisex-ao-khoac-du-nam-2-lop-chong-nang-chong-lanh-chong-gio-thoi-trang-phom-body-phoi-mau-han-quoc-cao-cap-ad73-shopn6-p93233783.html?spid=93233785</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Phụ kiện thời trang</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>N6</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="H2" t="n">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,35 +582,35 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>33830000</v>
+        <v>3420000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -627,37 +627,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>276125714</t>
+          <t>274835322</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Tặng 2 Khăn Ướt Cồn/Bao] Bao Quần Lót Dùng 1 Lần Nữ TRAVEL-MATE 5 Cai/Bao | Đã Giặt Sạch, An Toàn, Tiện Lợi</t>
+          <t>Bao da đựng kính, hiệu Khắc Tên - Hàng chính hãng</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-quan-lot-tien-loi-travel-mate-nu-5-cai-bao-p276125714.html?spid=276125729</t>
+          <t>https://tiki.vn/bao-da-dung-kinh-hieu-khacten-com-hang-chinh-hang-p274835322.html?spid=274835328</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Travel-Mate</t>
+          <t>Khacten.com</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>210000</v>
+        <v>500000</v>
       </c>
       <c r="H3" t="n">
-        <v>210000</v>
+        <v>500000</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -666,35 +666,35 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>23730000</v>
+        <v>2000000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -711,17 +711,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>115134722</t>
+          <t>275959689</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thắt Lưng Nam Vải Dù Mặt Khóa Hợp Kim Thép Đúc Liền Khối A989 US ARMY, Dây lưng lính mỹ -HÀNG CHÍNH HÃNG</t>
+          <t>Nước xịt rửa mắt kính chuyên dụng TẶNG KHĂN LAU Màu Ngẫu Nhiên</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-nam-vai-du-mat-khoa-hop-kim-thep-duc-lien-khoi-a989-us-army-day-lung-linh-my-hang-chinh-hang-p115134722.html?spid=174134555</t>
+          <t>https://tiki.vn/day-deo-mat-kinh-giu-gong-kinh-choi-the-thao-chong-roi-kinh-chong-truot-phien-ban-nang-cap-lo-dep-5mm-chat-lieu-silicon-sieu-ben-chuyen-dung-phu-hop-choi-the-thao-du-lich-da-ngoai-golf-sports-lens-thoi-trang-tien-dung-mau-den-p275959689.html?spid=275959690</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>LuckyJQR</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>179000</v>
+        <v>80000</v>
       </c>
       <c r="H4" t="n">
-        <v>179000</v>
+        <v>80000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -750,35 +750,35 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="L4" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="M4" t="n">
-        <v>13246000</v>
+        <v>1600000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -795,17 +795,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>183726169</t>
+          <t>276066691</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thắt Lưng Nam Vải Dù US ARMY, Dây Nịt Vải Dù Bền Chắc, Khóa Hợp Kim Siêu Bền Cao Cấp- HÀNG CHÍNH HÃNG</t>
+          <t>Khăn trùm kín mặt chống nắng, chống tia UV khi đi xe dành cho cả nam và nữ - Hàng chính hãng Khẩu Trang Unisex Văn Phòng Phượt Dã Ngoại Du Lịch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://tiki.vn/that-lung-nam-vai-du-us-army-day-nit-vai-du-ben-chac-khoa-hop-kim-sieu-ben-cao-cap-hang-chinh-hang-p183726169.html?spid=183726177</t>
+          <t>https://tiki.vn/khan-trum-kin-mat-chong-nang-chong-tia-uv-khi-di-xe-danh-cho-ca-nam-va-nu-hang-chinh-hang-p276066691.html?spid=276796565</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>US ARMY</t>
+          <t>LuckyJQR</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>178000</v>
+        <v>130000</v>
       </c>
       <c r="H5" t="n">
-        <v>178000</v>
+        <v>130000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -834,13 +834,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>12816000</v>
+        <v>1040000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -855,14 +855,14 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -879,37 +879,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>163716172</t>
+          <t>275933718</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Áo Sơ Mi Nam Xanh Tím Than Ngắn Tay Công Sở Trung Niên Anton Kẻ Caro Thoáng Mát, Thấm Hút Mồ Hôi - NT201</t>
+          <t>Giày Sneaker Vải Canvas Nam Nữ E18 White Dincox Shoes Sang Trọng</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-so-mi-nam-xanh-tim-than-ngan-tay-cong-so-trung-nien-anton-ke-caro-thoang-mat-tham-hut-mo-hoi-nt201-p163716172.html?spid=163716180</t>
+          <t>https://tiki.vn/giay-sneaker-vai-canvas-nam-nu-e18-white-dincox-shoes-sang-trong-p275933718.html?spid=275933728</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Giày - Dép nam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SOMIANTON</t>
+          <t>DINCOX</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>425000</v>
+        <v>490000</v>
       </c>
       <c r="H6" t="n">
-        <v>425000</v>
+        <v>490000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -918,35 +918,35 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>5525000</v>
+        <v>490000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -963,37 +963,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13701589</t>
+          <t>274528089</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Áo Khoác Da Nam Nâu Lót Lông Trơn ShopN6 Cao Cấp AKD05</t>
+          <t>[Video thật] Mũ nón chống nắng nữ, đa năng vành rộng, kèm khẩu trang, chống tia UV, làm vườn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-khoac-da-nam-nau-lot-long-tron-shopn6-cao-cap-akd05-p13701589.html?spid=13701597</t>
+          <t>https://tiki.vn/video-that-mu-non-chong-nang-nu-da-nang-vanh-rong-kem-khau-trang-chong-tia-uv-lam-vuon-p274528089.html?spid=274528091</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thời trang nam</t>
+          <t>Phụ kiện thời trang</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>N6</t>
+          <t>DRU</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>309000</v>
+        <v>85000</v>
       </c>
       <c r="H7" t="n">
-        <v>309000</v>
+        <v>85000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1002,35 +1002,35 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>5253000</v>
+        <v>340000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1047,17 +1047,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>90483623</t>
+          <t>103076103</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Combo 3 Áo thun nam ba lỗ cotton FREEMAN ASF205</t>
+          <t>áo ba lỗ nam, áo 3 lỗ nam sợi cotton Organic mềm mịn siêu thoáng mát thấm hút mồ hôi JAMANO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://tiki.vn/ao-thun-nam-ba-lo-cotton-freeman-asf205-combo-3-p90483623.html?spid=90483629</t>
+          <t>https://tiki.vn/a-o-ba-lo-nam-a-o-3-lo-nam-so-i-cotton-organic-me-m-mi-n-sieu-thoa-ng-ma-t-tha-m-hu-t-mo-hoi-jamano-p103076103.html?spid=103076105</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1067,81 +1067,81 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>JAMANO</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="G8" t="n">
-        <v>240300</v>
+        <v>99000</v>
       </c>
       <c r="H8" t="n">
-        <v>240300</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1359</v>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>1360</v>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>3364200</v>
+        <v>99000</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>136</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Bán thêm +1 sản phẩm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>248928122</t>
+          <t>174593731</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quần Âu Nam Công Sở Trung Niên Thương Hiệu Anton Dáng Suông Rộng Màu Đen Xếp Ly Mã QA404</t>
+          <t>Quần Short NamThể Thao Thanh Lịch US ARMY 8898 Trẻ Trung, Năng Động, Nam Tính -HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://tiki.vn/quan-au-nam-cong-so-trung-nien-thuong-hieu-anton-dang-suong-rong-mau-den-xep-ly-ma-qa404-p248928122.html?spid=248928126</t>
+          <t>https://tiki.vn/quan-short-namthe-thao-thanh-lich-us-army-8898-tre-trung-nang-dong-nam-tinh-hang-chinh-hang-p174593731.html?spid=177619669</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1151,81 +1151,81 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SOMIANTON</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G9" t="n">
-        <v>328000</v>
+        <v>150000</v>
       </c>
       <c r="H9" t="n">
-        <v>328000</v>
+        <v>-150000</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3280000</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>🆕 Sản phẩm mới</t>
+          <t>🔄 Đã cập nhật</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Xuất hiện lần đầu trong danh sách</t>
+          <t>Giá giảm 150,000đ (50.0%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>271395656</t>
+          <t>278452973</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bao Quần Lót Miễn Giặt Tiện Lợi TRAVEL-MATE Nam, 5 Cái/Bao</t>
+          <t>Áo thun Omada TP-Link - Hàng chính hãng</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://tiki.vn/bao-quan-lot-tien-loi-travel-mate-nam-5-cai-bao-p271395656.html?spid=271395660</t>
+          <t>https://tiki.vn/ao-thun-omada-tp-link-hang-chinh-hang-p278452973.html?spid=279145190</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1235,17 +1235,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Travel-Mate</t>
+          <t>TP-Link</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>30000</v>
+        <v>99000</v>
       </c>
       <c r="H10" t="n">
-        <v>30000</v>
+        <v>99000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2370000</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1299,101 +1299,101 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>276118600</t>
+          <t>110139205</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Tặng 2 Khăn Ướt Cồn/Bao] Bao Quần Đùi Miễn Giặt Body-Mate Nữ | Đã Giặt Sạch, Đóng Gói Tự Động, An Toàn Tiện Lợi | 3 Cái/Bao</t>
+          <t>Áo Gile Nam Lính Mỹ U869 Phong Cách US ARMY - HÀNG CHÍNH HÃNG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://tiki.vn/combo-quan-dui-mien-giat-body-mate-nu-3-cai-bao-p276118600.html?spid=276118611</t>
+          <t>https://tiki.vn/ao-gile-nam-linh-my-u869-phong-cach-us-army-hang-chinh-hang-p110139205.html?spid=174134971</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thời trang nữ</t>
+          <t>Thời trang nam</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BODY-MATE</t>
+          <t>US ARMY</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>799000</v>
       </c>
       <c r="G11" t="n">
-        <v>300000</v>
+        <v>399500</v>
       </c>
       <c r="H11" t="n">
-        <v>300000</v>
+        <v>-399500</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1800000</v>
+        <v>0